--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,135 +473,125 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>cambio_compra_usd</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>var_pct_cambio_compra_usd</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -639,32 +629,30 @@
         <v>5.1216</v>
       </c>
       <c r="K2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="L2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="M2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="N2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="R2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="S2" t="n">
         <v>355671</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -716,78 +702,72 @@
         <v>5.1433</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="L3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="M3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="N3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="R3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="S3" t="n">
-        <v>370395</v>
+        <v>0.631159</v>
       </c>
       <c r="T3" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="W3" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="X3" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.972464</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.003276</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -823,78 +803,72 @@
         <v>5.4394</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="S4" t="n">
-        <v>368886</v>
+        <v>-0.055529</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.055529</v>
+        <v>-2.109407</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.109407</v>
+        <v>5.757004</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="W4" t="n">
-        <v>5.757676</v>
+        <v>2.329166</v>
       </c>
       <c r="X4" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.329166</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -930,78 +904,72 @@
         <v>5.643</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S5" t="n">
-        <v>367927</v>
+        <v>0.53429</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53429</v>
+        <v>-0.58875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.58875</v>
+        <v>3.74306</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="W5" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="X5" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1037,78 +1005,72 @@
         <v>5.6199</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="L6" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="M6" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N6" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S6" t="n">
-        <v>367772</v>
+        <v>1.599501</v>
       </c>
       <c r="T6" t="n">
-        <v>1.599501</v>
+        <v>1.372425</v>
       </c>
       <c r="U6" t="n">
-        <v>1.372425</v>
+        <v>-0.409357</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.409357</v>
+        <v>1.896096</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4094</v>
+        <v>1.160214</v>
       </c>
       <c r="X6" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1144,78 +1106,72 @@
         <v>5.5805</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S7" t="n">
-        <v>362204</v>
+        <v>0.250195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.250195</v>
+        <v>1.49538</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49538</v>
+        <v>-0.70108</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.70108</v>
+        <v>1.856332</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.701155</v>
+        <v>2.135418</v>
       </c>
       <c r="X7" t="n">
-        <v>1.856332</v>
+        <v>1.653884</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1251,78 +1207,72 @@
         <v>5.3574</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S8" t="n">
-        <v>358398</v>
+        <v>-1.889415</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.889415</v>
+        <v>-7.693212</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.693212</v>
+        <v>-3.99785</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99785</v>
+        <v>-0.015397</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.99828</v>
+        <v>-1.385541</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.015397</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1358,78 +1308,72 @@
         <v>5.1394</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S9" t="n">
-        <v>357740</v>
+        <v>0.982105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.982105</v>
+        <v>4.32272</v>
       </c>
       <c r="U9" t="n">
-        <v>4.32272</v>
+        <v>-4.069138</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069138</v>
+        <v>0.975774</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.069594</v>
+        <v>1.257759</v>
       </c>
       <c r="X9" t="n">
-        <v>0.975774</v>
+        <v>0.775073</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1465,78 +1409,72 @@
         <v>4.7378</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S10" t="n">
-        <v>353169</v>
+        <v>1.194746</v>
       </c>
       <c r="T10" t="n">
-        <v>1.194746</v>
+        <v>9.292268999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>9.292268999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.814142</v>
+        <v>1.412174</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.815054</v>
+        <v>1.146068</v>
       </c>
       <c r="X10" t="n">
-        <v>1.412174</v>
+        <v>1.602477</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1572,78 +1510,72 @@
         <v>4.9191</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S11" t="n">
-        <v>345097</v>
+        <v>0.004178</v>
       </c>
       <c r="T11" t="n">
-        <v>0.004178</v>
+        <v>-4.113018</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.113018</v>
+        <v>3.826671</v>
       </c>
       <c r="V11" t="n">
-        <v>3.826671</v>
+        <v>0.816526</v>
       </c>
       <c r="W11" t="n">
-        <v>3.827155</v>
+        <v>0.461006</v>
       </c>
       <c r="X11" t="n">
-        <v>0.816526</v>
+        <v>1.06968</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1679,78 +1611,72 @@
         <v>4.7289</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S12" t="n">
-        <v>346415</v>
+        <v>0.112442</v>
       </c>
       <c r="T12" t="n">
-        <v>0.112442</v>
+        <v>-0.479114</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.479114</v>
+        <v>-3.866561</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.866561</v>
+        <v>1.151595</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.867033</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>1.151595</v>
+        <v>1.598738</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1786,84 +1712,78 @@
         <v>5.238</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S13" t="n">
-        <v>341958</v>
+        <v>-0.156589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.156589</v>
+        <v>-0.436337</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.436337</v>
+        <v>10.765717</v>
       </c>
       <c r="V13" t="n">
-        <v>10.765717</v>
+        <v>1.558597</v>
       </c>
       <c r="W13" t="n">
-        <v>10.767083</v>
+        <v>1.928912</v>
       </c>
       <c r="X13" t="n">
-        <v>1.558597</v>
+        <v>1.299314</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.928912</v>
+        <v>-1.286607</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.299314</v>
+        <v>11.88673</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.286607</v>
+        <v>10.700862</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.700862</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1899,84 +1819,78 @@
         <v>5.1884</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S14" t="n">
-        <v>346403</v>
+        <v>1.9075</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9075</v>
+        <v>4.677002</v>
       </c>
       <c r="U14" t="n">
-        <v>4.677002</v>
+        <v>-0.946926</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.946926</v>
+        <v>0.677481</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.947035</v>
+        <v>-0.269467</v>
       </c>
       <c r="X14" t="n">
-        <v>0.677481</v>
+        <v>1.344714</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.269467</v>
+        <v>1.299867</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.344714</v>
+        <v>10.069235</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.299867</v>
+        <v>10.074751</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.074751</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -2012,84 +1926,78 @@
         <v>5.179</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S15" t="n">
-        <v>339664</v>
+        <v>-0.307887</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.307887</v>
+        <v>0.536686</v>
       </c>
       <c r="U15" t="n">
-        <v>0.536686</v>
+        <v>-0.181173</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181173</v>
+        <v>1.469562</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.181194</v>
+        <v>0.837552</v>
       </c>
       <c r="X15" t="n">
-        <v>1.469562</v>
+        <v>1.907759</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.837552</v>
+        <v>-1.945422</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.907759</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2125,84 +2033,78 @@
         <v>5.4066</v>
       </c>
       <c r="K16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S16" t="n">
-        <v>327580</v>
+        <v>0.051214</v>
       </c>
       <c r="T16" t="n">
-        <v>0.051214</v>
+        <v>-3.18585</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.18585</v>
+        <v>4.394671</v>
       </c>
       <c r="V16" t="n">
-        <v>4.394671</v>
+        <v>1.814888</v>
       </c>
       <c r="W16" t="n">
-        <v>4.39518</v>
+        <v>2.210221</v>
       </c>
       <c r="X16" t="n">
-        <v>1.814888</v>
+        <v>1.543645</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.210221</v>
+        <v>-3.557633</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.543645</v>
+        <v>7.168596</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2238,84 +2140,78 @@
         <v>5.257</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S17" t="n">
-        <v>325546</v>
+        <v>0.283274</v>
       </c>
       <c r="T17" t="n">
-        <v>0.283274</v>
+        <v>-1.093446</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.093446</v>
+        <v>-2.766988</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.766988</v>
+        <v>0.991621</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.767296</v>
+        <v>-0.187221</v>
       </c>
       <c r="X17" t="n">
-        <v>0.991621</v>
+        <v>1.805747</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.187221</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.805747</v>
+        <v>6.470016</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2351,84 +2247,78 @@
         <v>5.2941</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S18" t="n">
-        <v>331505</v>
+        <v>-0.725155</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.725155</v>
+        <v>-0.925949</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.925949</v>
+        <v>0.705726</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705726</v>
+        <v>1.335643</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705806</v>
+        <v>1.161333</v>
       </c>
       <c r="X18" t="n">
-        <v>1.335643</v>
+        <v>1.453667</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.161333</v>
+        <v>1.830463</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.453667</v>
+        <v>5.900488</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2464,84 +2354,78 @@
         <v>5.2177</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S19" t="n">
-        <v>324703</v>
+        <v>-0.249038</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.249038</v>
+        <v>0.821323</v>
       </c>
       <c r="U19" t="n">
-        <v>0.821323</v>
+        <v>-1.443116</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443116</v>
+        <v>1.521325</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.443279</v>
+        <v>2.249624</v>
       </c>
       <c r="X19" t="n">
-        <v>1.521325</v>
+        <v>1.029618</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.249624</v>
+        <v>-2.051854</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.029618</v>
+        <v>5.784842</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2577,84 +2461,78 @@
         <v>5.0993</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S20" t="n">
-        <v>331122</v>
+        <v>-0.342048</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.342048</v>
+        <v>-4.871671</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.871671</v>
+        <v>-2.269199</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.269199</v>
+        <v>0.133468</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.26946</v>
+        <v>-1.232052</v>
       </c>
       <c r="X20" t="n">
-        <v>0.133468</v>
+        <v>1.066493</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.232052</v>
+        <v>1.976883</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.066493</v>
+        <v>5.77432</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2690,84 +2568,78 @@
         <v>5.2078</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S21" t="n">
-        <v>328098</v>
+        <v>2.881581</v>
       </c>
       <c r="T21" t="n">
-        <v>2.881581</v>
+        <v>3.737316</v>
       </c>
       <c r="U21" t="n">
-        <v>3.737316</v>
+        <v>2.127743</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127743</v>
+        <v>-0.042451</v>
       </c>
       <c r="W21" t="n">
-        <v>2.127993</v>
+        <v>-0.710886</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.042451</v>
+        <v>0.403932</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.710886</v>
+        <v>-0.913259</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.403932</v>
+        <v>5.596302</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2803,84 +2675,78 @@
         <v>5.0804</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S22" t="n">
-        <v>341158</v>
+        <v>0.100866</v>
       </c>
       <c r="T22" t="n">
-        <v>0.100866</v>
+        <v>12.127661</v>
       </c>
       <c r="U22" t="n">
-        <v>12.127661</v>
+        <v>-2.446331</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446331</v>
+        <v>1.002821</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.446612</v>
+        <v>0.879872</v>
       </c>
       <c r="X22" t="n">
-        <v>1.002821</v>
+        <v>1.083978</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.879872</v>
+        <v>3.980518</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.083978</v>
+        <v>4.650694</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2916,84 +2782,78 @@
         <v>5.0007</v>
       </c>
       <c r="K23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S23" t="n">
-        <v>345725</v>
+        <v>1.051427</v>
       </c>
       <c r="T23" t="n">
-        <v>1.051427</v>
+        <v>-5.945456</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.945456</v>
+        <v>-1.568774</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568774</v>
+        <v>0.027577</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.568959</v>
+        <v>-0.459418</v>
       </c>
       <c r="X23" t="n">
-        <v>0.027577</v>
+        <v>0.348572</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.459418</v>
+        <v>1.338676</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.348572</v>
+        <v>4.184706</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -3029,84 +2889,78 @@
         <v>5.0959</v>
       </c>
       <c r="K24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S24" t="n">
-        <v>343489</v>
+        <v>-1.655253</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.655253</v>
+        <v>-1.271212</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.271212</v>
+        <v>1.903733</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903733</v>
+        <v>0.504966</v>
       </c>
       <c r="W24" t="n">
-        <v>1.903962</v>
+        <v>0.024709</v>
       </c>
       <c r="X24" t="n">
-        <v>0.504966</v>
+        <v>0.818881</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.024709</v>
+        <v>-0.646757</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.818881</v>
+        <v>3.935832</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3142,84 +2996,78 @@
         <v>4.8192</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="L25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="M25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="N25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="R25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="S25" t="n">
-        <v>343620</v>
+        <v>-0.06297</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.06297</v>
+        <v>-0.424293</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.424293</v>
+        <v>-5.429855</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.429855</v>
+        <v>0.472174</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.430495</v>
+        <v>1.122473</v>
       </c>
       <c r="X25" t="n">
-        <v>0.472174</v>
+        <v>0.050421</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.122473</v>
+        <v>0.038138</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.050421</v>
+        <v>3.161501</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.038138</v>
+        <v>-6.84947</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3255,84 +3103,78 @@
         <v>4.7415</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S26" t="n">
-        <v>345476</v>
+        <v>0.458481</v>
       </c>
       <c r="T26" t="n">
-        <v>0.458481</v>
+        <v>2.993707</v>
       </c>
       <c r="U26" t="n">
-        <v>2.993707</v>
+        <v>-1.612301</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612301</v>
+        <v>0.098769</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.612502</v>
+        <v>-0.740777</v>
       </c>
       <c r="X26" t="n">
-        <v>0.098769</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.740777</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6490939999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="AC26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3368,84 +3210,78 @@
         <v>4.9219</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S27" t="n">
-        <v>344177</v>
+        <v>-0.374379</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.374379</v>
+        <v>0.680131</v>
       </c>
       <c r="U27" t="n">
-        <v>0.680131</v>
+        <v>3.804703</v>
       </c>
       <c r="V27" t="n">
-        <v>3.804703</v>
+        <v>1.352666</v>
       </c>
       <c r="W27" t="n">
-        <v>3.805185</v>
+        <v>0.887701</v>
       </c>
       <c r="X27" t="n">
-        <v>1.352666</v>
+        <v>1.653244</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.887701</v>
+        <v>-0.376003</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.653244</v>
+        <v>4.608216</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3481,84 +3317,78 @@
         <v>5.0076</v>
       </c>
       <c r="K28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S28" t="n">
-        <v>340324</v>
+        <v>0.012734</v>
       </c>
       <c r="T28" t="n">
-        <v>0.012734</v>
+        <v>-4.055314</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.055314</v>
+        <v>1.741198</v>
       </c>
       <c r="V28" t="n">
-        <v>1.741198</v>
+        <v>1.203116</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74141</v>
+        <v>1.956912</v>
       </c>
       <c r="X28" t="n">
-        <v>1.203116</v>
+        <v>0.719465</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.956912</v>
+        <v>-1.119482</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.719465</v>
+        <v>5.185235</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3594,84 +3424,78 @@
         <v>5.0575</v>
       </c>
       <c r="K29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S29" t="n">
-        <v>340247</v>
+        <v>0.313403</v>
       </c>
       <c r="T29" t="n">
-        <v>0.313403</v>
+        <v>0.169608</v>
       </c>
       <c r="U29" t="n">
-        <v>0.169608</v>
+        <v>0.996485</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996485</v>
+        <v>0.495259</v>
       </c>
       <c r="W29" t="n">
-        <v>0.996605</v>
+        <v>-0.467999</v>
       </c>
       <c r="X29" t="n">
-        <v>0.495259</v>
+        <v>1.120891</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.467999</v>
+        <v>-0.022625</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.120891</v>
+        <v>4.819246</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3707,84 +3531,78 @@
         <v>4.9355</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S30" t="n">
-        <v>348406</v>
+        <v>0.739043</v>
       </c>
       <c r="T30" t="n">
-        <v>0.739043</v>
+        <v>-0.243155</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.243155</v>
+        <v>-2.412259</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412259</v>
+        <v>1.013388</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.412545</v>
+        <v>0.723782</v>
       </c>
       <c r="X30" t="n">
-        <v>1.013388</v>
+        <v>1.198521</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.723782</v>
+        <v>2.397964</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.198521</v>
+        <v>4.683537</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3820,84 +3638,78 @@
         <v>4.8413</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S31" t="n">
-        <v>355034</v>
+        <v>1.06955</v>
       </c>
       <c r="T31" t="n">
-        <v>1.06955</v>
+        <v>-0.000138</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000138</v>
+        <v>-1.908621</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908621</v>
+        <v>1.646862</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.908853</v>
+        <v>2.824206</v>
       </c>
       <c r="X31" t="n">
-        <v>1.646862</v>
+        <v>0.897764</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.824206</v>
+        <v>1.902378</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.897764</v>
+        <v>4.621114</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3933,84 +3745,78 @@
         <v>4.9535</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S32" t="n">
-        <v>355066</v>
+        <v>-0.194024</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.194024</v>
+        <v>-2.349549</v>
       </c>
       <c r="U32" t="n">
-        <v>-2.349549</v>
+        <v>2.317559</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317559</v>
+        <v>-0.180012</v>
       </c>
       <c r="W32" t="n">
-        <v>2.317847</v>
+        <v>-2.151229</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.180012</v>
+        <v>1.098143</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.151229</v>
+        <v>0.009013</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.098143</v>
+        <v>4.506637</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="AC32" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -4046,84 +3852,78 @@
         <v>4.9833</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S33" t="n">
-        <v>352705</v>
+        <v>0.14777</v>
       </c>
       <c r="T33" t="n">
-        <v>0.14777</v>
+        <v>2.878185</v>
       </c>
       <c r="U33" t="n">
-        <v>2.878185</v>
+        <v>0.601595</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601595</v>
+        <v>0.366662</v>
       </c>
       <c r="W33" t="n">
-        <v>0.601668</v>
+        <v>0.04207</v>
       </c>
       <c r="X33" t="n">
-        <v>0.366662</v>
+        <v>0.570366</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04207</v>
+        <v>-0.664947</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.570366</v>
+        <v>4.496274</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4159,84 +3959,78 @@
         <v>4.9962</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S34" t="n">
-        <v>355008</v>
+        <v>0.081216</v>
       </c>
       <c r="T34" t="n">
-        <v>0.081216</v>
+        <v>7.260937</v>
       </c>
       <c r="U34" t="n">
-        <v>7.260937</v>
+        <v>0.258865</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258865</v>
+        <v>1.440658</v>
       </c>
       <c r="W34" t="n">
-        <v>0.258896</v>
+        <v>2.257995</v>
       </c>
       <c r="X34" t="n">
-        <v>1.440658</v>
+        <v>0.930417</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.257995</v>
+        <v>0.652954</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.930417</v>
+        <v>3.925596</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4272,84 +4066,78 @@
         <v>5.1718</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S35" t="n">
-        <v>351599</v>
+        <v>0.236126</v>
       </c>
       <c r="T35" t="n">
-        <v>0.236126</v>
+        <v>-0.285629</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.285629</v>
+        <v>3.514671</v>
       </c>
       <c r="V35" t="n">
-        <v>3.514671</v>
+        <v>0.267741</v>
       </c>
       <c r="W35" t="n">
-        <v>3.515093</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="X35" t="n">
-        <v>0.267741</v>
+        <v>0.904602</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>-0.96026</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.904602</v>
+        <v>3.688016</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4385,84 +4173,78 @@
         <v>5.2416</v>
       </c>
       <c r="K36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S36" t="n">
-        <v>355560</v>
+        <v>0.664278</v>
       </c>
       <c r="T36" t="n">
-        <v>0.664278</v>
+        <v>-4.15681</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.15681</v>
+        <v>1.349627</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349627</v>
+        <v>0.64951</v>
       </c>
       <c r="W36" t="n">
-        <v>1.349783</v>
+        <v>0.415624</v>
       </c>
       <c r="X36" t="n">
-        <v>0.64951</v>
+        <v>0.795057</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.415624</v>
+        <v>1.126567</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.795057</v>
+        <v>3.925952</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4498,84 +4280,78 @@
         <v>5.5589</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S37" t="n">
-        <v>357827</v>
+        <v>0.864098</v>
       </c>
       <c r="T37" t="n">
-        <v>0.864098</v>
+        <v>1.103268</v>
       </c>
       <c r="U37" t="n">
-        <v>1.103268</v>
+        <v>6.053495</v>
       </c>
       <c r="V37" t="n">
-        <v>6.053495</v>
+        <v>1.476967</v>
       </c>
       <c r="W37" t="n">
-        <v>6.054188</v>
+        <v>2.569845</v>
       </c>
       <c r="X37" t="n">
-        <v>1.476967</v>
+        <v>0.799559</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.569845</v>
+        <v>0.637586</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.799559</v>
+        <v>4.227578</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4611,84 +4387,78 @@
         <v>5.6621</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S38" t="n">
-        <v>363282</v>
+        <v>0.35244</v>
       </c>
       <c r="T38" t="n">
-        <v>0.35244</v>
+        <v>5.331331</v>
       </c>
       <c r="U38" t="n">
-        <v>5.331331</v>
+        <v>1.856482</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856482</v>
+        <v>0.451961</v>
       </c>
       <c r="W38" t="n">
-        <v>1.856683</v>
+        <v>-0.577528</v>
       </c>
       <c r="X38" t="n">
-        <v>0.451961</v>
+        <v>1.101283</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.577528</v>
+        <v>1.52448</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.101283</v>
+        <v>4.498245</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4724,84 +4494,78 @@
         <v>5.6562</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S39" t="n">
-        <v>369214</v>
+        <v>0.171599</v>
       </c>
       <c r="T39" t="n">
-        <v>0.171599</v>
+        <v>-1.299435</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.299435</v>
+        <v>-0.104202</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104202</v>
+        <v>1.088989</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.104213</v>
+        <v>0.905369</v>
       </c>
       <c r="X39" t="n">
-        <v>1.088989</v>
+        <v>1.202826</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.905369</v>
+        <v>1.632891</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.202826</v>
+        <v>4.237599</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4837,84 +4601,78 @@
         <v>5.4481</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S40" t="n">
-        <v>372016</v>
+        <v>0.80633</v>
       </c>
       <c r="T40" t="n">
-        <v>0.80633</v>
+        <v>-2.710366</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.710366</v>
+        <v>-3.679149</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679149</v>
+        <v>1.323978</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.679539</v>
+        <v>1.72458</v>
       </c>
       <c r="X40" t="n">
-        <v>1.323978</v>
+        <v>1.076262</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72458</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.076262</v>
+        <v>4.42474</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4950,84 +4708,78 @@
         <v>5.7779</v>
       </c>
       <c r="K41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S41" t="n">
-        <v>366096</v>
+        <v>0.192241</v>
       </c>
       <c r="T41" t="n">
-        <v>0.192241</v>
+        <v>1.966032</v>
       </c>
       <c r="U41" t="n">
-        <v>1.966032</v>
+        <v>6.053487</v>
       </c>
       <c r="V41" t="n">
-        <v>6.053487</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>6.054153</v>
+        <v>0.532743</v>
       </c>
       <c r="X41" t="n">
-        <v>0.9424709999999999</v>
+        <v>1.197484</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.532743</v>
+        <v>-1.591329</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.197484</v>
+        <v>4.758099</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5063,84 +4815,78 @@
         <v>6.0535</v>
       </c>
       <c r="K42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S42" t="n">
-        <v>363003</v>
+        <v>-0.221546</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.221546</v>
+        <v>-3.385643</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.385643</v>
+        <v>4.769899</v>
       </c>
       <c r="V42" t="n">
-        <v>4.769899</v>
+        <v>1.443368</v>
       </c>
       <c r="W42" t="n">
-        <v>4.770394</v>
+        <v>1.605359</v>
       </c>
       <c r="X42" t="n">
-        <v>1.443368</v>
+        <v>1.343208</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.605359</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.343208</v>
+        <v>4.873011</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -5176,84 +4922,78 @@
         <v>6.1923</v>
       </c>
       <c r="K43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S43" t="n">
-        <v>329730</v>
+        <v>-0.76507</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.76507</v>
+        <v>-1.261045</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.261045</v>
+        <v>2.292888</v>
       </c>
       <c r="V43" t="n">
-        <v>2.292888</v>
+        <v>1.55383</v>
       </c>
       <c r="W43" t="n">
-        <v>2.293116</v>
+        <v>2.592546</v>
       </c>
       <c r="X43" t="n">
-        <v>1.55383</v>
+        <v>0.909924</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.592546</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.909924</v>
+        <v>4.831296</v>
       </c>
       <c r="AA43" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5289,84 +5029,78 @@
         <v>5.8301</v>
       </c>
       <c r="K44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S44" t="n">
-        <v>328303</v>
+        <v>1.000655</v>
       </c>
       <c r="T44" t="n">
-        <v>1.000655</v>
+        <v>-1.374453</v>
       </c>
       <c r="U44" t="n">
-        <v>-1.374453</v>
+        <v>-5.8492</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.8492</v>
+        <v>0.006404</v>
       </c>
       <c r="W44" t="n">
-        <v>-5.849767</v>
+        <v>-1.889422</v>
       </c>
       <c r="X44" t="n">
-        <v>0.006404</v>
+        <v>1.201233</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.889422</v>
+        <v>-0.432778</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.201233</v>
+        <v>4.559874</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5402,84 +5136,78 @@
         <v>5.8488</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S45" t="n">
-        <v>332508</v>
+        <v>0.491628</v>
       </c>
       <c r="T45" t="n">
-        <v>0.491628</v>
+        <v>4.086263</v>
       </c>
       <c r="U45" t="n">
-        <v>4.086263</v>
+        <v>0.320749</v>
       </c>
       <c r="V45" t="n">
-        <v>0.320749</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>0.320782</v>
+        <v>1.027506</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7181419999999999</v>
+        <v>0.529123</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.027506</v>
+        <v>1.280829</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.529123</v>
+        <v>5.05763</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5515,84 +5243,78 @@
         <v>5.7422</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S46" t="n">
-        <v>336157</v>
+        <v>1.341273</v>
       </c>
       <c r="T46" t="n">
-        <v>1.341273</v>
+        <v>6.727909</v>
       </c>
       <c r="U46" t="n">
-        <v>6.727909</v>
+        <v>-1.822596</v>
       </c>
       <c r="V46" t="n">
-        <v>-1.822596</v>
+        <v>0.99855</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.822783</v>
+        <v>0.852229</v>
       </c>
       <c r="X46" t="n">
-        <v>0.99855</v>
+        <v>1.088394</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.852229</v>
+        <v>1.097417</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.088394</v>
+        <v>5.47719</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5628,84 +5350,78 @@
         <v>5.6608</v>
       </c>
       <c r="K47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S47" t="n">
-        <v>340789</v>
+        <v>-0.131764</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.131764</v>
+        <v>-1.249299</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.249299</v>
+        <v>-1.417575</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.417575</v>
+        <v>0.722029</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.417723</v>
+        <v>0.566954</v>
       </c>
       <c r="X47" t="n">
-        <v>0.722029</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.566954</v>
+        <v>1.377928</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8170269999999999</v>
+        <v>5.529729</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5741,84 +5457,78 @@
         <v>5.7087</v>
       </c>
       <c r="K48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S48" t="n">
-        <v>341459</v>
+        <v>-0.883188</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.883188</v>
+        <v>-3.583696</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.583696</v>
+        <v>0.84617</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84617</v>
+        <v>0.639181</v>
       </c>
       <c r="W48" t="n">
-        <v>0.84626</v>
+        <v>0.807268</v>
       </c>
       <c r="X48" t="n">
-        <v>0.639181</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.807268</v>
+        <v>0.196603</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5364679999999999</v>
+        <v>5.319636</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5854,84 +5564,78 @@
         <v>5.4571</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S49" t="n">
-        <v>344440</v>
+        <v>-0.208448</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.208448</v>
+        <v>-1.100964</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.100964</v>
+        <v>-4.407308</v>
       </c>
       <c r="V49" t="n">
-        <v>-4.407308</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>-4.407771</v>
+        <v>0.591659</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.541686</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.591659</v>
+        <v>0.873018</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.541686</v>
+        <v>5.351165</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5967,84 +5671,78 @@
         <v>5.6021</v>
       </c>
       <c r="K50" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="L50" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="M50" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="N50" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="O50" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="P50" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="R50" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="S50" t="n">
-        <v>345111</v>
+        <v>-0.410362</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.410362</v>
+        <v>5.358126</v>
       </c>
       <c r="U50" t="n">
-        <v>5.358126</v>
+        <v>2.657089</v>
       </c>
       <c r="V50" t="n">
-        <v>2.657089</v>
+        <v>0.440744</v>
       </c>
       <c r="W50" t="n">
-        <v>2.657381</v>
+        <v>-0.129254</v>
       </c>
       <c r="X50" t="n">
-        <v>0.440744</v>
+        <v>0.79014</v>
       </c>
       <c r="Y50" t="n">
-        <v>-0.129254</v>
+        <v>0.194809</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.79014</v>
+        <v>5.225222</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.194809</v>
+        <v>2.961368</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.225222</v>
+        <v>5.127976</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.961368</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -6080,84 +5778,78 @@
         <v>5.4264</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S51" t="n">
-        <v>350767</v>
+        <v>0.393384</v>
       </c>
       <c r="T51" t="n">
-        <v>0.393384</v>
+        <v>-2.419208</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.419208</v>
+        <v>-3.136324</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.136324</v>
+        <v>0.612293</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.13666</v>
+        <v>0.073298</v>
       </c>
       <c r="X51" t="n">
-        <v>0.612293</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.073298</v>
+        <v>1.638893</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.9397180000000001</v>
+        <v>5.130501</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6193,84 +5885,78 @@
         <v>5.3186</v>
       </c>
       <c r="K52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S52" t="n">
-        <v>356582</v>
+        <v>-0.070866</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.070866</v>
+        <v>-0.816658</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.816658</v>
+        <v>-1.986584</v>
       </c>
       <c r="V52" t="n">
-        <v>-1.986584</v>
+        <v>1.155358</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.986804</v>
+        <v>1.710427</v>
       </c>
       <c r="X52" t="n">
-        <v>1.155358</v>
+        <v>0.821088</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.710427</v>
+        <v>1.657796</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.821088</v>
+        <v>5.172369</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6306,84 +5992,78 @@
         <v>5.3843</v>
       </c>
       <c r="K53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S53" t="n">
-        <v>357103</v>
+        <v>0.02339</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02339</v>
+        <v>0.539717</v>
       </c>
       <c r="U53" t="n">
-        <v>0.539717</v>
+        <v>1.235287</v>
       </c>
       <c r="V53" t="n">
-        <v>1.235287</v>
+        <v>1.038729</v>
       </c>
       <c r="W53" t="n">
-        <v>1.235427</v>
+        <v>0.301682</v>
       </c>
       <c r="X53" t="n">
-        <v>1.038729</v>
+        <v>1.486504</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.301682</v>
+        <v>0.146109</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.486504</v>
+        <v>4.680811</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.146109</v>
+        <v>0.924206</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6419,84 +6099,78 @@
         <v>5.3338</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="L54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="M54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="N54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="O54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="P54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="R54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="S54" t="n">
-        <v>360578</v>
+        <v>0.470751</v>
       </c>
       <c r="T54" t="n">
-        <v>0.470751</v>
+        <v>-3.155924</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.155924</v>
+        <v>-0.937912</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.937912</v>
+        <v>1.146567</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.938017</v>
+        <v>0.715383</v>
       </c>
       <c r="X54" t="n">
-        <v>1.146567</v>
+        <v>1.405488</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.715383</v>
+        <v>0.973109</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.405488</v>
+        <v>4.461836</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6532,84 +6206,78 @@
         <v>5.5024</v>
       </c>
       <c r="K55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="L55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="M55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="N55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="P55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="R55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="S55" t="n">
-        <v>358234</v>
+        <v>-0.026441</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.026441</v>
+        <v>0.550798</v>
       </c>
       <c r="U55" t="n">
-        <v>0.550798</v>
+        <v>3.160973</v>
       </c>
       <c r="V55" t="n">
-        <v>3.160973</v>
+        <v>1.90144</v>
       </c>
       <c r="W55" t="n">
-        <v>3.161329</v>
+        <v>3.24641</v>
       </c>
       <c r="X55" t="n">
-        <v>1.90144</v>
+        <v>1.099346</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.24641</v>
+        <v>-0.650067</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.099346</v>
+        <v>4.264385</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6645,84 +6313,78 @@
         <v>5.2301</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="L56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="M56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="N56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="O56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="P56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="S56" t="n">
-        <v>364367</v>
+        <v>0.755789</v>
       </c>
       <c r="T56" t="n">
-        <v>0.755789</v>
+        <v>-3.241421</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.241421</v>
+        <v>-4.94875</v>
       </c>
       <c r="V56" t="n">
-        <v>-4.94875</v>
+        <v>-0.083179</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.949289</v>
+        <v>-1.743482</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.083179</v>
+        <v>0.927966</v>
       </c>
       <c r="Y56" t="n">
-        <v>-1.743482</v>
+        <v>1.712009</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.927966</v>
+        <v>4.441351</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6758,84 +6420,78 @@
         <v>5.1495</v>
       </c>
       <c r="K57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="L57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="M57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="N57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="R57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="S57" t="n">
-        <v>371074</v>
+        <v>0.625412</v>
       </c>
       <c r="T57" t="n">
-        <v>0.625412</v>
+        <v>2.812663</v>
       </c>
       <c r="U57" t="n">
-        <v>2.812663</v>
+        <v>-1.54108</v>
       </c>
       <c r="V57" t="n">
-        <v>-1.54108</v>
+        <v>0.371461</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.541256</v>
+        <v>0.070797</v>
       </c>
       <c r="X57" t="n">
-        <v>0.371461</v>
+        <v>0.549722</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.070797</v>
+        <v>1.840727</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.549722</v>
+        <v>3.812497</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="AB57" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="AC57" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6871,84 +6527,78 @@
         <v>5.2194</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="L58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="M58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="N58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="O58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="P58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="R58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="S58" t="n">
-        <v>362002</v>
+        <v>-0.180258</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.180258</v>
+        <v>10.500625</v>
       </c>
       <c r="U58" t="n">
-        <v>10.500625</v>
+        <v>1.357413</v>
       </c>
       <c r="V58" t="n">
-        <v>1.357413</v>
+        <v>1.12824</v>
       </c>
       <c r="W58" t="n">
-        <v>1.357572</v>
+        <v>1.133877</v>
       </c>
       <c r="X58" t="n">
-        <v>1.12824</v>
+        <v>1.124914</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.133877</v>
+        <v>-2.444795</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.124914</v>
+        <v>4.142847</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="AC58" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6984,84 +6634,78 @@
         <v>4.9886</v>
       </c>
       <c r="K59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="L59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="M59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="N59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="O59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="R59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="S59" t="n">
-        <v>366913</v>
+        <v>0.511964</v>
       </c>
       <c r="T59" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.561276</v>
+        <v>-4.421964</v>
       </c>
       <c r="V59" t="n">
-        <v>-4.421964</v>
+        <v>0.288267</v>
       </c>
       <c r="W59" t="n">
-        <v>-4.422473</v>
+        <v>-0.052977</v>
       </c>
       <c r="X59" t="n">
-        <v>0.288267</v>
+        <v>0.489642</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.052977</v>
+        <v>1.356622</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.489642</v>
+        <v>4.39172</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -7093,80 +6737,74 @@
         <v>5.0569</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="L60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="M60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="N60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="O60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="P60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="R60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="S60" t="n">
         <v>371137</v>
       </c>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>1.369122</v>
+      </c>
       <c r="V60" t="n">
-        <v>1.369122</v>
+        <v>0.565068</v>
       </c>
       <c r="W60" t="n">
-        <v>1.369286</v>
+        <v>0.742264</v>
       </c>
       <c r="X60" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.742264</v>
+        <v>1.151227</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.461065</v>
+        <v>4.724907</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -7193,51 +6831,45 @@
       <c r="J61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="K61" t="n">
-        <v>5.176</v>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>367558</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
+      <c r="U61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="W61" t="n">
-        <v>2.367344</v>
-      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
+      <c r="Y61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>3.177699</v>
-      </c>
-      <c r="AD61" t="inlineStr"/>
+        <v>-0.25</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>-0.000372</v>
+      </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7260,9 +6892,7 @@
       <c r="J62" t="n">
         <v>5.1552</v>
       </c>
-      <c r="K62" t="n">
-        <v>5.1546</v>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7272,33 +6902,29 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
+      <c r="U62" t="n">
         <v>-0.413399</v>
       </c>
-      <c r="W62" t="n">
-        <v>-0.413447</v>
-      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,125 +473,135 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>cambio_compra_usd</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>var_pct_cambio_compra_usd</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -629,30 +639,32 @@
         <v>5.1216</v>
       </c>
       <c r="K2" t="n">
+        <v>5.121</v>
+      </c>
+      <c r="L2" t="n">
         <v>4271865</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1833179</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2438686</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.36</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.58</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2.94</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>20.26</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>355671</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -702,72 +716,78 @@
         <v>5.1433</v>
       </c>
       <c r="K3" t="n">
+        <v>5.1427</v>
+      </c>
+      <c r="L3" t="n">
         <v>4346060</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1851006</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2495054</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.37</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.56</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.96</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>20.92</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>370395</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.631159</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.641498</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
+        <v>0.423745</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -803,72 +823,78 @@
         <v>5.4394</v>
       </c>
       <c r="K4" t="n">
+        <v>5.4388</v>
+      </c>
+      <c r="L4" t="n">
         <v>4441056</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1894119</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2546936</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.34</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.43</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>21.42</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>368886</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>-0.055529</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>-2.109407</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
+        <v>5.757676</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -904,72 +930,78 @@
         <v>5.643</v>
       </c>
       <c r="K5" t="n">
+        <v>5.6424</v>
+      </c>
+      <c r="L5" t="n">
         <v>4511956</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1910940</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2601017</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.33</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.43</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>22.89</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>367927</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.53429</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>-0.58875</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
+        <v>3.743473</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1005,72 +1037,78 @@
         <v>5.6199</v>
       </c>
       <c r="K6" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="L6" t="n">
         <v>4597507</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1933111</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2664395</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.36</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>23.91</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>367772</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1.599501</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.372425</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1106,72 +1144,78 @@
         <v>5.5805</v>
       </c>
       <c r="K7" t="n">
+        <v>5.5799</v>
+      </c>
+      <c r="L7" t="n">
         <v>4682852</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1974391</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2708461</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.35</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>24.21</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>362204</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.250195</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.49538</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
+        <v>-0.701155</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1207,72 +1251,78 @@
         <v>5.3574</v>
       </c>
       <c r="K8" t="n">
+        <v>5.3568</v>
+      </c>
+      <c r="L8" t="n">
         <v>4682131</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1947035</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2735096</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.51</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.46</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>25.23</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>358398</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-1.889415</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>-7.693212</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>-3.99828</v>
+      </c>
+      <c r="X8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1308,72 +1358,78 @@
         <v>5.1394</v>
       </c>
       <c r="K9" t="n">
+        <v>5.1388</v>
+      </c>
+      <c r="L9" t="n">
         <v>4727818</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1971524</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2756295</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.57</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.44</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>25.63</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>357740</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>0.982105</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>4.32272</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
+        <v>-4.069594</v>
+      </c>
+      <c r="X9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1409,72 +1465,78 @@
         <v>4.7378</v>
       </c>
       <c r="K10" t="n">
+        <v>4.7372</v>
+      </c>
+      <c r="L10" t="n">
         <v>4794583</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1994119</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2800464</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.66</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.55</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>26.54</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>353169</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1.194746</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>9.292268999999999</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
+        <v>-7.815054</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1510,72 +1572,78 @@
         <v>4.9191</v>
       </c>
       <c r="K11" t="n">
+        <v>4.9185</v>
+      </c>
+      <c r="L11" t="n">
         <v>4833732</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2003312</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2830420</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.72</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.57</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.46</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>345097</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>0.004178</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-4.113018</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
+        <v>3.827155</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1611,72 +1679,78 @@
         <v>4.7289</v>
       </c>
       <c r="K12" t="n">
+        <v>4.7283</v>
+      </c>
+      <c r="L12" t="n">
         <v>4889397</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2013726</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2875671</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.79</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.57</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>27.42</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346415</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0.112442</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-0.479114</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
+        <v>-3.867033</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1712,78 +1786,84 @@
         <v>5.238</v>
       </c>
       <c r="K13" t="n">
+        <v>5.2374</v>
+      </c>
+      <c r="L13" t="n">
         <v>4965603</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2052569</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2913035</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.73</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.52</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>27.88</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>341958</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.156589</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-0.436337</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>10.767083</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1819,78 +1899,84 @@
         <v>5.1884</v>
       </c>
       <c r="K14" t="n">
+        <v>5.1878</v>
+      </c>
+      <c r="L14" t="n">
         <v>4999244</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2047038</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2952207</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.84</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>29.24</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>346403</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.9075</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>4.677002</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
+        <v>-0.947035</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AJ14" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1926,78 +2012,84 @@
         <v>5.179</v>
       </c>
       <c r="K15" t="n">
+        <v>5.1784</v>
+      </c>
+      <c r="L15" t="n">
         <v>5072711</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2064183</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3008528</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2.9</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>28.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>339664</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-0.307887</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>0.536686</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
+        <v>-0.181194</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2033,78 +2125,84 @@
         <v>5.4066</v>
       </c>
       <c r="K16" t="n">
+        <v>5.406</v>
+      </c>
+      <c r="L16" t="n">
         <v>5164775</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2109806</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3054969</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2.92</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.65</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>28.57</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>327580</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0.051214</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-3.18585</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
+        <v>4.39518</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2140,78 +2238,84 @@
         <v>5.257</v>
       </c>
       <c r="K17" t="n">
+        <v>5.2564</v>
+      </c>
+      <c r="L17" t="n">
         <v>5215990</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2105856</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3110134</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.04</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.77</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.68</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>325546</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0.283274</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-1.093446</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
+        <v>-2.767296</v>
+      </c>
+      <c r="X17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2247,78 +2351,84 @@
         <v>5.2941</v>
       </c>
       <c r="K18" t="n">
+        <v>5.2935</v>
+      </c>
+      <c r="L18" t="n">
         <v>5285657</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2130312</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3155345</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.07</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.81</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.52</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331505</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.725155</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-0.925949</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
+        <v>0.705806</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2354,78 +2464,84 @@
         <v>5.2177</v>
       </c>
       <c r="K19" t="n">
+        <v>5.2171</v>
+      </c>
+      <c r="L19" t="n">
         <v>5366069</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2178236</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3187833</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.07</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1.8</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>29.64</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>324703</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-0.249038</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>0.821323</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
+        <v>-1.443279</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>-0</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>-0</v>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2461,78 +2577,84 @@
         <v>5.0993</v>
       </c>
       <c r="K20" t="n">
+        <v>5.0987</v>
+      </c>
+      <c r="L20" t="n">
         <v>5373231</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2151399</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3221831</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.24</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1.94</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.54</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>331122</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-0.342048</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-4.871671</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
+        <v>-2.26946</v>
+      </c>
+      <c r="X20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2568,78 +2690,84 @@
         <v>5.2078</v>
       </c>
       <c r="K21" t="n">
+        <v>5.2072</v>
+      </c>
+      <c r="L21" t="n">
         <v>5370950</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2136105</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3234845</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.36</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.17</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>30.48</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>328098</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>2.881581</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>3.737316</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
+        <v>2.127993</v>
+      </c>
+      <c r="X21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2675,78 +2803,84 @@
         <v>5.0804</v>
       </c>
       <c r="K22" t="n">
+        <v>5.0798</v>
+      </c>
+      <c r="L22" t="n">
         <v>5424811</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2154900</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3269910</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.35</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>30.99</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>341158</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>0.100866</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>12.127661</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
+        <v>-2.446612</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2782,78 +2916,84 @@
         <v>5.0007</v>
       </c>
       <c r="K23" t="n">
+        <v>5.0001</v>
+      </c>
+      <c r="L23" t="n">
         <v>5426307</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2145000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3281308</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.54</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.45</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>31.62</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>345725</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1.051427</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-5.945456</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
+        <v>-1.568959</v>
+      </c>
+      <c r="X23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2889,78 +3029,84 @@
         <v>5.0959</v>
       </c>
       <c r="K24" t="n">
+        <v>5.0953</v>
+      </c>
+      <c r="L24" t="n">
         <v>5453708</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2145530</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3308178</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.65</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.58</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>31.63</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>343489</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-1.655253</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-1.271212</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
+        <v>1.903962</v>
+      </c>
+      <c r="X24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
         <v>-0</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>-0</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2996,78 +3142,84 @@
         <v>4.8192</v>
       </c>
       <c r="K25" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="L25" t="n">
         <v>5479459</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2169613</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3309846</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.63</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>30.85</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>343620</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.06297</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-0.424293</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="X25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3103,78 +3255,84 @@
         <v>4.7415</v>
       </c>
       <c r="K26" t="n">
+        <v>4.7409</v>
+      </c>
+      <c r="L26" t="n">
         <v>5484871</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2153541</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3331330</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.63</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.73</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>30.43</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>345476</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.458481</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>2.993707</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
+        <v>-1.612502</v>
+      </c>
+      <c r="X26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3210,78 +3368,84 @@
         <v>4.9219</v>
       </c>
       <c r="K27" t="n">
+        <v>4.9213</v>
+      </c>
+      <c r="L27" t="n">
         <v>5559063</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2172658</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3386405</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.61</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.82</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.92</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>344177</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-0.374379</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.680131</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
+        <v>3.805185</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3317,78 +3481,84 @@
         <v>5.0076</v>
       </c>
       <c r="K28" t="n">
+        <v>5.007</v>
+      </c>
+      <c r="L28" t="n">
         <v>5625945</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2215175</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3410769</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.54</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.82</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.66</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>340324</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.012734</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-4.055314</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
+        <v>1.74141</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3424,78 +3594,84 @@
         <v>5.0575</v>
       </c>
       <c r="K29" t="n">
+        <v>5.0569</v>
+      </c>
+      <c r="L29" t="n">
         <v>5653808</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2204808</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3449000</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.56</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.92</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>29.24</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>340247</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>0.313403</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.169608</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
+        <v>0.996605</v>
+      </c>
+      <c r="X29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3531,78 +3707,84 @@
         <v>4.9355</v>
       </c>
       <c r="K30" t="n">
+        <v>4.9349</v>
+      </c>
+      <c r="L30" t="n">
         <v>5711103</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2220766</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3490337</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.53</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.99</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>29.01</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>348406</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>0.739043</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-0.243155</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
+        <v>-2.412545</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3638,78 +3820,84 @@
         <v>4.8413</v>
       </c>
       <c r="K31" t="n">
+        <v>4.8407</v>
+      </c>
+      <c r="L31" t="n">
         <v>5805157</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2283485</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3521672</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.29</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.59</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>28.14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>355034</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1.06955</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>-0.000138</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
+        <v>-1.908853</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AJ31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3745,78 +3933,84 @@
         <v>4.9535</v>
       </c>
       <c r="K32" t="n">
+        <v>4.9529</v>
+      </c>
+      <c r="L32" t="n">
         <v>5794707</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2234362</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3560345</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.38</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.77</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355066</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-0.194024</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-2.349549</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
+        <v>2.317847</v>
+      </c>
+      <c r="X32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AJ32" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3852,78 +4046,84 @@
         <v>4.9833</v>
       </c>
       <c r="K33" t="n">
+        <v>4.9827</v>
+      </c>
+      <c r="L33" t="n">
         <v>5815954</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2235302</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3580652</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.38</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.85</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>352705</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>0.14777</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>2.878185</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
+        <v>0.601668</v>
+      </c>
+      <c r="X33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3959,78 +4159,84 @@
         <v>4.9962</v>
       </c>
       <c r="K34" t="n">
+        <v>4.9956</v>
+      </c>
+      <c r="L34" t="n">
         <v>5899742</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2285775</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3613967</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.33</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.71</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>28.14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355008</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.081216</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>7.260937</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
+        <v>0.258896</v>
+      </c>
+      <c r="X34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4066,78 +4272,84 @@
         <v>5.1718</v>
       </c>
       <c r="K35" t="n">
+        <v>5.1712</v>
+      </c>
+      <c r="L35" t="n">
         <v>5915538</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2268879</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3646659</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.37</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.76</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.86</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>351599</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.236126</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>-0.285629</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
+        <v>3.515093</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4173,78 +4385,84 @@
         <v>5.2416</v>
       </c>
       <c r="K36" t="n">
+        <v>5.241</v>
+      </c>
+      <c r="L36" t="n">
         <v>5953960</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2278309</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3675652</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.43</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.8</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.75</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>355560</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.664278</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>-4.15681</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
+        <v>1.349783</v>
+      </c>
+      <c r="X36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4280,78 +4498,84 @@
         <v>5.5589</v>
       </c>
       <c r="K37" t="n">
+        <v>5.5583</v>
+      </c>
+      <c r="L37" t="n">
         <v>6041898</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2336858</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3705041</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.29</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.64</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.81</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>357827</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.864098</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>1.103268</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
+        <v>6.054188</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4387,78 +4611,84 @@
         <v>5.6621</v>
       </c>
       <c r="K38" t="n">
+        <v>5.6615</v>
+      </c>
+      <c r="L38" t="n">
         <v>6069205</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2323362</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3745844</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.3</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.52</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.74</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>363282</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.35244</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>5.331331</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
+        <v>1.856683</v>
+      </c>
+      <c r="X38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4494,78 +4724,84 @@
         <v>5.6562</v>
       </c>
       <c r="K39" t="n">
+        <v>5.6556</v>
+      </c>
+      <c r="L39" t="n">
         <v>6135298</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2344397</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3790900</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.33</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.55</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.59</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>369214</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.171599</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>-1.299435</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
+        <v>-0.104213</v>
+      </c>
+      <c r="X39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4601,78 +4837,84 @@
         <v>5.4481</v>
       </c>
       <c r="K40" t="n">
+        <v>5.4475</v>
+      </c>
+      <c r="L40" t="n">
         <v>6216528</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2384828</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3831700</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.34</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.56</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>27.49</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>372016</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>0.80633</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-2.710366</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
+        <v>-3.679539</v>
+      </c>
+      <c r="X40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4708,78 +4950,84 @@
         <v>5.7779</v>
       </c>
       <c r="K41" t="n">
+        <v>5.7773</v>
+      </c>
+      <c r="L41" t="n">
         <v>6275117</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2397533</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3877584</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.3</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.52</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>27.94</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>366096</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>0.192241</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>1.966032</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
+        <v>6.054153</v>
+      </c>
+      <c r="X41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4815,78 +5063,84 @@
         <v>6.0535</v>
       </c>
       <c r="K42" t="n">
+        <v>6.0529</v>
+      </c>
+      <c r="L42" t="n">
         <v>6365690</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2436022</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>3929668</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>28.45</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>363003</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>-0.221546</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-3.385643</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
+        <v>4.770394</v>
+      </c>
+      <c r="X42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AJ42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4922,78 +5176,84 @@
         <v>6.1923</v>
       </c>
       <c r="K43" t="n">
+        <v>6.1917</v>
+      </c>
+      <c r="L43" t="n">
         <v>6464602</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2499177</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>3965425</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.08</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.21</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>28.5</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>329730</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>-0.76507</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>-1.261045</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
+        <v>2.293116</v>
+      </c>
+      <c r="X43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Z43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AB43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>1</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AF43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AJ43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5029,78 +5289,84 @@
         <v>5.8301</v>
       </c>
       <c r="K44" t="n">
+        <v>5.8295</v>
+      </c>
+      <c r="L44" t="n">
         <v>6465016</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2451957</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4013059</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.34</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.43</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>29.88</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>328303</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.000655</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>-1.374453</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
+        <v>-5.849767</v>
+      </c>
+      <c r="X44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5136,78 +5402,84 @@
         <v>5.8488</v>
       </c>
       <c r="K45" t="n">
+        <v>5.8482</v>
+      </c>
+      <c r="L45" t="n">
         <v>6511444</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2477151</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4034293</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.41</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.52</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>30.53</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>332508</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>0.491628</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>4.086263</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
+        <v>0.320782</v>
+      </c>
+      <c r="X45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5243,78 +5515,84 @@
         <v>5.7422</v>
       </c>
       <c r="K46" t="n">
+        <v>5.7416</v>
+      </c>
+      <c r="L46" t="n">
         <v>6576464</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2498262</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4078202</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.44</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.49</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.34</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>336157</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>1.341273</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>6.727909</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
+        <v>-1.822783</v>
+      </c>
+      <c r="X46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Z46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AB46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>1</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5350,78 +5628,84 @@
         <v>5.6608</v>
       </c>
       <c r="K47" t="n">
+        <v>5.6602</v>
+      </c>
+      <c r="L47" t="n">
         <v>6623948</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2512426</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4111522</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.67</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.72</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.63</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>340789</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.131764</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.249299</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
+        <v>-1.417723</v>
+      </c>
+      <c r="X47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Z47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AA47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AJ47" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5457,78 +5741,84 @@
         <v>5.7087</v>
       </c>
       <c r="K48" t="n">
+        <v>5.7081</v>
+      </c>
+      <c r="L48" t="n">
         <v>6666287</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2532708</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4133579</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.72</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.67</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.7</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>341459</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.883188</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>-3.583696</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
+        <v>0.84626</v>
+      </c>
+      <c r="X48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Z48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AA48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AB48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AF48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5564,78 +5854,84 @@
         <v>5.4571</v>
       </c>
       <c r="K49" t="n">
+        <v>5.4565</v>
+      </c>
+      <c r="L49" t="n">
         <v>6703663</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2547693</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4155970</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>3.75</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.67</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.85</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>344440</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>-0.208448</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-1.100964</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
+        <v>-4.407771</v>
+      </c>
+      <c r="X49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Y49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Z49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AA49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AB49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AF49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AG49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5671,78 +5967,84 @@
         <v>5.6021</v>
       </c>
       <c r="K50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="L50" t="n">
         <v>6733209</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2544400</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4188808</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>3.96</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.79</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.75</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>345111</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.410362</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>5.358126</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="X50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Z50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AG50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5778,78 +6080,84 @@
         <v>5.4264</v>
       </c>
       <c r="K51" t="n">
+        <v>5.4258</v>
+      </c>
+      <c r="L51" t="n">
         <v>6774436</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2546265</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4228171</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.14</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.85</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>31.87</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>350767</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.393384</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>-2.419208</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
+        <v>-3.13666</v>
+      </c>
+      <c r="X51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AB51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5885,78 +6193,84 @@
         <v>5.3186</v>
       </c>
       <c r="K52" t="n">
+        <v>5.318</v>
+      </c>
+      <c r="L52" t="n">
         <v>6852705</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2589817</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4262888</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.09</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.77</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>31.47</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>356582</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>-0.070866</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-0.816658</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
+        <v>-1.986804</v>
+      </c>
+      <c r="X52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Z52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AB52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AC52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5992,78 +6306,84 @@
         <v>5.3843</v>
       </c>
       <c r="K53" t="n">
+        <v>5.3837</v>
+      </c>
+      <c r="L53" t="n">
         <v>6923886</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2597630</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4326256</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.18</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.82</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>32.04</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>357103</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.02339</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.539717</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
+        <v>1.235427</v>
+      </c>
+      <c r="X53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Z53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AA53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AB53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AJ53" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6099,78 +6419,84 @@
         <v>5.3338</v>
       </c>
       <c r="K54" t="n">
+        <v>5.3332</v>
+      </c>
+      <c r="L54" t="n">
         <v>7003273</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2616213</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4387061</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.23</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.74</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.32</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>360578</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.470751</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-3.155924</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
+        <v>-0.938017</v>
+      </c>
+      <c r="X54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Z54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AA54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AB54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
         <v>-0</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>-0</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AH54" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6206,78 +6532,84 @@
         <v>5.5024</v>
       </c>
       <c r="K55" t="n">
+        <v>5.5018</v>
+      </c>
+      <c r="L55" t="n">
         <v>7136436</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2701146</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4435290</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.2</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>2.68</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>31.99</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>358234</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>-0.026441</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>0.550798</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
+        <v>3.161329</v>
+      </c>
+      <c r="X55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Z55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6313,78 +6645,84 @@
         <v>5.2301</v>
       </c>
       <c r="K56" t="n">
+        <v>5.2295</v>
+      </c>
+      <c r="L56" t="n">
         <v>7130500</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2654052</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4476448</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.45</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>2.87</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.6</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>364367</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>0.755789</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>-3.241421</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
+        <v>-4.949289</v>
+      </c>
+      <c r="X56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Z56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AA56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AB56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AC56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>0.19</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6420,78 +6758,84 @@
         <v>5.1495</v>
       </c>
       <c r="K57" t="n">
+        <v>5.1489</v>
+      </c>
+      <c r="L57" t="n">
         <v>7156987</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2655931</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4501056</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.07</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>32.78</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>371074</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.625412</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>2.812663</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
+        <v>-1.541256</v>
+      </c>
+      <c r="X57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Z57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AA57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AB57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AC57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AJ57" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6527,78 +6871,84 @@
         <v>5.2194</v>
       </c>
       <c r="K58" t="n">
+        <v>5.2188</v>
+      </c>
+      <c r="L58" t="n">
         <v>7237735</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2686046</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4551689</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.52</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.04</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>32.99</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>362002</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>-0.180258</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>10.500625</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
+        <v>1.357572</v>
+      </c>
+      <c r="X58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Y58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Z58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AA58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AB58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AC58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AD58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AE58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AF58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6634,78 +6984,84 @@
         <v>4.9886</v>
       </c>
       <c r="K59" t="n">
+        <v>4.988</v>
+      </c>
+      <c r="L59" t="n">
         <v>7258599</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2684623</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4573976</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.63</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.15</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.51</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>366913</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>0.511964</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>-3.561276</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
+        <v>-4.422473</v>
+      </c>
+      <c r="X59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Y59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Z59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AA59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AB59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AC59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AD59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6737,74 +7093,80 @@
         <v>5.0569</v>
       </c>
       <c r="K60" t="n">
+        <v>5.0563</v>
+      </c>
+      <c r="L60" t="n">
         <v>7299615</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2704550</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4595065</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.74</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.24</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>33.42</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>371137</v>
       </c>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
+        <v>1.369286</v>
+      </c>
+      <c r="X60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Y60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Z60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AA60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AB60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AC60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AD60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -6831,45 +7193,51 @@
       <c r="J61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>5.176</v>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>367558</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="W61" t="n">
+        <v>2.367344</v>
+      </c>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="n">
-        <v>-0.964334</v>
-      </c>
+      <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="n">
-        <v>3.177699</v>
+        <v>-0.964334</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
+        <v>3.177699</v>
+      </c>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6890,9 +7258,11 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1552</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>5.1329</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.1323</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6902,29 +7272,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
-        <v>-0.413399</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
+        <v>-0.844183</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-0.8442809999999999</v>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AG62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7183,11 +7183,15 @@
       <c r="D61" t="n">
         <v>0.053028</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>0.16</v>
+      </c>
       <c r="F61" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>0.14</v>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
@@ -7220,11 +7224,15 @@
       <c r="AA61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>4.641328</v>
+      </c>
       <c r="AC61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AD61" t="inlineStr"/>
+      <c r="AD61" t="n">
+        <v>4.327084</v>
+      </c>
       <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
@@ -7258,10 +7266,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1329</v>
+        <v>5.1088</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1323</v>
+        <v>5.1082</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7274,10 +7282,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-0.844183</v>
+        <v>-1.30974</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.8442809999999999</v>
+        <v>-1.309892</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,160 +448,150 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>igp_m</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>igp_m_acum_12m</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -624,47 +614,45 @@
         <v>0.96</v>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.02</v>
+        <v>96.42256999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>96.42256999999999</v>
+        <v>99.83515</v>
       </c>
       <c r="I2" t="n">
-        <v>99.83515</v>
+        <v>5.1216</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="K2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="L2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="M2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="N2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="R2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="S2" t="n">
         <v>355671</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -701,93 +687,89 @@
         <v>0.87</v>
       </c>
       <c r="F3" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>0.88</v>
+        <v>97.03115</v>
       </c>
       <c r="H3" t="n">
-        <v>97.03115</v>
+        <v>99.19471</v>
       </c>
       <c r="I3" t="n">
-        <v>99.19471</v>
+        <v>5.1433</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="L3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="M3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="N3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="R3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="S3" t="n">
-        <v>370395</v>
+        <v>0.631159</v>
       </c>
       <c r="T3" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="W3" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="X3" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.003276</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -808,93 +790,89 @@
         <v>1.16</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>96.97727</v>
       </c>
       <c r="H4" t="n">
-        <v>96.97727</v>
+        <v>97.10229</v>
       </c>
       <c r="I4" t="n">
-        <v>97.10229</v>
+        <v>5.4394</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="S4" t="n">
-        <v>368886</v>
+        <v>-0.055529</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.055529</v>
+        <v>-2.109407</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.109407</v>
+        <v>5.757004</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="W4" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="X4" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -915,93 +893,89 @@
         <v>1.25</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.16</v>
+        <v>97.49541000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>97.49541000000001</v>
+        <v>96.53060000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>96.53060000000001</v>
+        <v>5.643</v>
       </c>
       <c r="J5" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S5" t="n">
-        <v>367927</v>
+        <v>0.53429</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53429</v>
+        <v>-0.58875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.58875</v>
+        <v>3.74306</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="W5" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="X5" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1022,93 +996,89 @@
         <v>0.95</v>
       </c>
       <c r="F6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99.05485</v>
+      </c>
+      <c r="H6" t="n">
+        <v>97.85541000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.6199</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4597507</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1933111</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2664395</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="R6" t="n">
+        <v>367772</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.599501</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.372425</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.409357</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.896096</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.160214</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.436662</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.042128</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0.02</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H6" t="n">
-        <v>99.05485</v>
-      </c>
-      <c r="I6" t="n">
-        <v>97.85541000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.6199</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.6193</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4597507</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1933111</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2664395</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="S6" t="n">
-        <v>367772</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.599501</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.372425</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.409357</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.042128</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.03</v>
-      </c>
       <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1129,93 +1099,89 @@
         <v>0.73</v>
       </c>
       <c r="F7" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>0.73</v>
+        <v>99.30268</v>
       </c>
       <c r="H7" t="n">
-        <v>99.30268</v>
+        <v>99.31872</v>
       </c>
       <c r="I7" t="n">
-        <v>99.31872</v>
+        <v>5.5805</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S7" t="n">
-        <v>362204</v>
+        <v>0.250195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.250195</v>
+        <v>1.49538</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49538</v>
+        <v>-0.70108</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="X7" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1236,93 +1202,89 @@
         <v>0.54</v>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>0.67</v>
+        <v>97.42644</v>
       </c>
       <c r="H8" t="n">
-        <v>97.42644</v>
+        <v>91.67792</v>
       </c>
       <c r="I8" t="n">
-        <v>91.67792</v>
+        <v>5.3574</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S8" t="n">
-        <v>358398</v>
+        <v>-1.889415</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.889415</v>
+        <v>-7.693212</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.693212</v>
+        <v>-3.99785</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1343,93 +1305,89 @@
         <v>1.01</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>98.38327</v>
       </c>
       <c r="H9" t="n">
-        <v>98.38327</v>
+        <v>95.6409</v>
       </c>
       <c r="I9" t="n">
-        <v>95.6409</v>
+        <v>5.1394</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S9" t="n">
-        <v>357740</v>
+        <v>0.982105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.982105</v>
+        <v>4.32272</v>
       </c>
       <c r="U9" t="n">
-        <v>4.32272</v>
+        <v>-4.069138</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="X9" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1450,93 +1408,89 @@
         <v>1.62</v>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>99.5587</v>
       </c>
       <c r="H10" t="n">
-        <v>99.5587</v>
+        <v>104.52811</v>
       </c>
       <c r="I10" t="n">
-        <v>104.52811</v>
+        <v>4.7378</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S10" t="n">
-        <v>353169</v>
+        <v>1.194746</v>
       </c>
       <c r="T10" t="n">
-        <v>1.194746</v>
+        <v>9.292268999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>9.292268999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="X10" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1557,93 +1511,89 @@
         <v>1.06</v>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.04</v>
+        <v>99.56286</v>
       </c>
       <c r="H11" t="n">
-        <v>99.56286</v>
+        <v>100.22885</v>
       </c>
       <c r="I11" t="n">
-        <v>100.22885</v>
+        <v>4.9191</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S11" t="n">
-        <v>345097</v>
+        <v>0.004178</v>
       </c>
       <c r="T11" t="n">
-        <v>0.004178</v>
+        <v>-4.113018</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.113018</v>
+        <v>3.826671</v>
       </c>
       <c r="V11" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="W11" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="X11" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1664,93 +1614,89 @@
         <v>0.47</v>
       </c>
       <c r="F12" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.45</v>
+        <v>99.67480999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>99.67480999999999</v>
+        <v>99.74863999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>99.74863999999999</v>
+        <v>4.7289</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S12" t="n">
-        <v>346415</v>
+        <v>0.112442</v>
       </c>
       <c r="T12" t="n">
-        <v>0.112442</v>
+        <v>-0.479114</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.479114</v>
+        <v>-3.866561</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="X12" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1771,99 +1717,93 @@
         <v>0.67</v>
       </c>
       <c r="F13" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.62</v>
+        <v>99.51873000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>99.51873000000001</v>
+        <v>99.3134</v>
       </c>
       <c r="I13" t="n">
-        <v>99.3134</v>
+        <v>5.238</v>
       </c>
       <c r="J13" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S13" t="n">
-        <v>341958</v>
+        <v>-0.156589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.156589</v>
+        <v>-0.436337</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.436337</v>
+        <v>10.765717</v>
       </c>
       <c r="V13" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="W13" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="X13" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.299314</v>
+        <v>-1.286607</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.286607</v>
+        <v>11.88673</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.700862</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1884,99 +1824,93 @@
         <v>-0.68</v>
       </c>
       <c r="F14" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6</v>
+        <v>101.41705</v>
       </c>
       <c r="H14" t="n">
-        <v>101.41705</v>
+        <v>103.95829</v>
       </c>
       <c r="I14" t="n">
-        <v>103.95829</v>
+        <v>5.1884</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S14" t="n">
-        <v>346403</v>
+        <v>1.9075</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9075</v>
+        <v>4.677002</v>
       </c>
       <c r="U14" t="n">
-        <v>4.677002</v>
+        <v>-0.946926</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="X14" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.344714</v>
+        <v>1.299867</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.299867</v>
+        <v>10.069235</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.074751</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1997,99 +1931,93 @@
         <v>-0.36</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.31</v>
+        <v>101.1048</v>
       </c>
       <c r="H15" t="n">
-        <v>101.1048</v>
+        <v>104.51622</v>
       </c>
       <c r="I15" t="n">
-        <v>104.51622</v>
+        <v>5.179</v>
       </c>
       <c r="J15" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S15" t="n">
-        <v>339664</v>
+        <v>-0.307887</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.307887</v>
+        <v>0.536686</v>
       </c>
       <c r="U15" t="n">
-        <v>0.536686</v>
+        <v>-0.181173</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="X15" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2110,99 +2038,93 @@
         <v>-0.29</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.32</v>
+        <v>101.15658</v>
       </c>
       <c r="H16" t="n">
-        <v>101.15658</v>
+        <v>101.18649</v>
       </c>
       <c r="I16" t="n">
-        <v>101.18649</v>
+        <v>5.4066</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="K16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S16" t="n">
-        <v>327580</v>
+        <v>0.051214</v>
       </c>
       <c r="T16" t="n">
-        <v>0.051214</v>
+        <v>-3.18585</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.18585</v>
+        <v>4.394671</v>
       </c>
       <c r="V16" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="W16" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="X16" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2223,99 +2145,93 @@
         <v>0.59</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.47</v>
+        <v>101.44313</v>
       </c>
       <c r="H17" t="n">
-        <v>101.44313</v>
+        <v>100.08007</v>
       </c>
       <c r="I17" t="n">
-        <v>100.08007</v>
+        <v>5.257</v>
       </c>
       <c r="J17" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S17" t="n">
-        <v>325546</v>
+        <v>0.283274</v>
       </c>
       <c r="T17" t="n">
-        <v>0.283274</v>
+        <v>-1.093446</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.093446</v>
+        <v>-2.766988</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="X17" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2336,99 +2252,93 @@
         <v>0.41</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.38</v>
+        <v>100.70751</v>
       </c>
       <c r="H18" t="n">
-        <v>100.70751</v>
+        <v>99.15338</v>
       </c>
       <c r="I18" t="n">
-        <v>99.15338</v>
+        <v>5.2941</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S18" t="n">
-        <v>331505</v>
+        <v>-0.725155</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.725155</v>
+        <v>-0.925949</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.925949</v>
+        <v>0.705726</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="X18" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2449,99 +2359,93 @@
         <v>0.62</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.45671</v>
       </c>
       <c r="H19" t="n">
-        <v>100.45671</v>
+        <v>99.96775</v>
       </c>
       <c r="I19" t="n">
-        <v>99.96775</v>
+        <v>5.2177</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S19" t="n">
-        <v>324703</v>
+        <v>-0.249038</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.249038</v>
+        <v>0.821323</v>
       </c>
       <c r="U19" t="n">
-        <v>0.821323</v>
+        <v>-1.443116</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="X19" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2562,99 +2466,93 @@
         <v>0.53</v>
       </c>
       <c r="F20" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.46</v>
+        <v>100.1131</v>
       </c>
       <c r="H20" t="n">
-        <v>100.1131</v>
+        <v>95.09765</v>
       </c>
       <c r="I20" t="n">
-        <v>95.09765</v>
+        <v>5.0993</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S20" t="n">
-        <v>331122</v>
+        <v>-0.342048</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.342048</v>
+        <v>-4.871671</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.871671</v>
+        <v>-2.269199</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="X20" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2675,99 +2573,93 @@
         <v>0.84</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="G21" t="n">
-        <v>0.77</v>
+        <v>102.99794</v>
       </c>
       <c r="H21" t="n">
-        <v>102.99794</v>
+        <v>98.65175000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>98.65175000000001</v>
+        <v>5.2078</v>
       </c>
       <c r="J21" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S21" t="n">
-        <v>328098</v>
+        <v>2.881581</v>
       </c>
       <c r="T21" t="n">
-        <v>2.881581</v>
+        <v>3.737316</v>
       </c>
       <c r="U21" t="n">
-        <v>3.737316</v>
+        <v>2.127743</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="W21" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2788,99 +2680,93 @@
         <v>0.71</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="G22" t="n">
-        <v>0.64</v>
+        <v>103.10183</v>
       </c>
       <c r="H22" t="n">
-        <v>103.10183</v>
+        <v>110.6159</v>
       </c>
       <c r="I22" t="n">
-        <v>110.6159</v>
+        <v>5.0804</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S22" t="n">
-        <v>341158</v>
+        <v>0.100866</v>
       </c>
       <c r="T22" t="n">
-        <v>0.100866</v>
+        <v>12.127661</v>
       </c>
       <c r="U22" t="n">
-        <v>12.127661</v>
+        <v>-2.446331</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="X22" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2901,99 +2787,93 @@
         <v>0.61</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.53</v>
+        <v>104.18587</v>
       </c>
       <c r="H23" t="n">
-        <v>104.18587</v>
+        <v>104.03928</v>
       </c>
       <c r="I23" t="n">
-        <v>104.03928</v>
+        <v>5.0007</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="K23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S23" t="n">
-        <v>345725</v>
+        <v>1.051427</v>
       </c>
       <c r="T23" t="n">
-        <v>1.051427</v>
+        <v>-5.945456</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.945456</v>
+        <v>-1.568774</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="X23" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -3014,99 +2894,93 @@
         <v>0.23</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.36</v>
+        <v>102.46133</v>
       </c>
       <c r="H24" t="n">
-        <v>102.46133</v>
+        <v>102.71672</v>
       </c>
       <c r="I24" t="n">
-        <v>102.71672</v>
+        <v>5.0959</v>
       </c>
       <c r="J24" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="K24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S24" t="n">
-        <v>343489</v>
+        <v>-1.655253</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.655253</v>
+        <v>-1.271212</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.271212</v>
+        <v>1.903733</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="W24" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="X24" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3127,99 +3001,93 @@
         <v>-0.08</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" t="n">
+        <v>102.39681</v>
+      </c>
+      <c r="H25" t="n">
+        <v>102.2809</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.8192</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5479459</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2169613</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3309846</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="R25" t="n">
+        <v>343620</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.06297</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.424293</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-5.429855</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.472174</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.122473</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.050421</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.038138</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.161501</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.998957</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H25" t="n">
-        <v>102.39681</v>
-      </c>
-      <c r="I25" t="n">
-        <v>102.2809</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.8192</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.8186</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5479459</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2169613</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3309846</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="S25" t="n">
-        <v>343620</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-0.06297</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.424293</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-5.429855</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-5.430495</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.472174</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.122473</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.050421</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.038138</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.161501</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>-6.84947</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.998957</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3240,99 +3108,93 @@
         <v>0.12</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.09</v>
+        <v>102.86628</v>
       </c>
       <c r="H26" t="n">
-        <v>102.86628</v>
+        <v>105.34289</v>
       </c>
       <c r="I26" t="n">
-        <v>105.34289</v>
+        <v>4.7415</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S26" t="n">
-        <v>345476</v>
+        <v>0.458481</v>
       </c>
       <c r="T26" t="n">
-        <v>0.458481</v>
+        <v>2.993707</v>
       </c>
       <c r="U26" t="n">
-        <v>2.993707</v>
+        <v>-1.612301</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="X26" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="AC26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3353,99 +3215,93 @@
         <v>0.23</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>102.48117</v>
       </c>
       <c r="H27" t="n">
-        <v>102.48117</v>
+        <v>106.05936</v>
       </c>
       <c r="I27" t="n">
-        <v>106.05936</v>
+        <v>4.9219</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S27" t="n">
-        <v>344177</v>
+        <v>-0.374379</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.374379</v>
+        <v>0.680131</v>
       </c>
       <c r="U27" t="n">
-        <v>0.680131</v>
+        <v>3.804703</v>
       </c>
       <c r="V27" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="W27" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="X27" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3466,99 +3322,93 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11</v>
+        <v>102.49422</v>
       </c>
       <c r="H28" t="n">
-        <v>102.49422</v>
+        <v>101.75832</v>
       </c>
       <c r="I28" t="n">
-        <v>101.75832</v>
+        <v>5.0076</v>
       </c>
       <c r="J28" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="K28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S28" t="n">
-        <v>340324</v>
+        <v>0.012734</v>
       </c>
       <c r="T28" t="n">
-        <v>0.012734</v>
+        <v>-4.055314</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.055314</v>
+        <v>1.741198</v>
       </c>
       <c r="V28" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="X28" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3579,99 +3429,93 @@
         <v>0.24</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.12</v>
+        <v>102.81544</v>
       </c>
       <c r="H29" t="n">
-        <v>102.81544</v>
+        <v>101.93091</v>
       </c>
       <c r="I29" t="n">
-        <v>101.93091</v>
+        <v>5.0575</v>
       </c>
       <c r="J29" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="K29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S29" t="n">
-        <v>340247</v>
+        <v>0.313403</v>
       </c>
       <c r="T29" t="n">
-        <v>0.313403</v>
+        <v>0.169608</v>
       </c>
       <c r="U29" t="n">
-        <v>0.169608</v>
+        <v>0.996485</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="W29" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="X29" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3692,99 +3536,93 @@
         <v>0.28</v>
       </c>
       <c r="F30" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1</v>
+        <v>103.57529</v>
       </c>
       <c r="H30" t="n">
-        <v>103.57529</v>
+        <v>101.68306</v>
       </c>
       <c r="I30" t="n">
-        <v>101.68306</v>
+        <v>4.9355</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S30" t="n">
-        <v>348406</v>
+        <v>0.739043</v>
       </c>
       <c r="T30" t="n">
-        <v>0.739043</v>
+        <v>-0.243155</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.243155</v>
+        <v>-2.412259</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="X30" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3805,99 +3643,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.55</v>
+        <v>104.68308</v>
       </c>
       <c r="H31" t="n">
-        <v>104.68308</v>
+        <v>101.68292</v>
       </c>
       <c r="I31" t="n">
-        <v>101.68292</v>
+        <v>4.8413</v>
       </c>
       <c r="J31" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S31" t="n">
-        <v>355034</v>
+        <v>1.06955</v>
       </c>
       <c r="T31" t="n">
-        <v>1.06955</v>
+        <v>-0.000138</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000138</v>
+        <v>-1.908621</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="X31" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3918,99 +3750,93 @@
         <v>0.42</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="G32" t="n">
-        <v>0.57</v>
+        <v>104.47997</v>
       </c>
       <c r="H32" t="n">
-        <v>104.47997</v>
+        <v>99.29383</v>
       </c>
       <c r="I32" t="n">
-        <v>99.29383</v>
+        <v>4.9535</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S32" t="n">
-        <v>355066</v>
+        <v>-0.194024</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.194024</v>
+        <v>-2.349549</v>
       </c>
       <c r="U32" t="n">
-        <v>-2.349549</v>
+        <v>2.317559</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="W32" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="AC32" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -4031,99 +3857,93 @@
         <v>0.83</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.63436</v>
       </c>
       <c r="H33" t="n">
-        <v>104.63436</v>
+        <v>102.15169</v>
       </c>
       <c r="I33" t="n">
-        <v>102.15169</v>
+        <v>4.9833</v>
       </c>
       <c r="J33" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S33" t="n">
-        <v>352705</v>
+        <v>0.14777</v>
       </c>
       <c r="T33" t="n">
-        <v>0.14777</v>
+        <v>2.878185</v>
       </c>
       <c r="U33" t="n">
-        <v>2.878185</v>
+        <v>0.601595</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="W33" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="X33" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4144,99 +3964,93 @@
         <v>0.16</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="G34" t="n">
-        <v>0.19</v>
+        <v>104.71934</v>
       </c>
       <c r="H34" t="n">
-        <v>104.71934</v>
+        <v>109.56886</v>
       </c>
       <c r="I34" t="n">
-        <v>109.56886</v>
+        <v>4.9962</v>
       </c>
       <c r="J34" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S34" t="n">
-        <v>355008</v>
+        <v>0.081216</v>
       </c>
       <c r="T34" t="n">
-        <v>0.081216</v>
+        <v>7.260937</v>
       </c>
       <c r="U34" t="n">
-        <v>7.260937</v>
+        <v>0.258865</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="W34" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="X34" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4257,99 +4071,93 @@
         <v>0.38</v>
       </c>
       <c r="F35" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="G35" t="n">
-        <v>0.37</v>
+        <v>104.96661</v>
       </c>
       <c r="H35" t="n">
-        <v>104.96661</v>
+        <v>109.2559</v>
       </c>
       <c r="I35" t="n">
-        <v>109.2559</v>
+        <v>5.1718</v>
       </c>
       <c r="J35" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S35" t="n">
-        <v>351599</v>
+        <v>0.236126</v>
       </c>
       <c r="T35" t="n">
-        <v>0.236126</v>
+        <v>-0.285629</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.285629</v>
+        <v>3.514671</v>
       </c>
       <c r="V35" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="W35" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="X35" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4370,99 +4178,93 @@
         <v>0.46</v>
       </c>
       <c r="F36" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="G36" t="n">
-        <v>0.46</v>
+        <v>105.66388</v>
       </c>
       <c r="H36" t="n">
-        <v>105.66388</v>
+        <v>104.71434</v>
       </c>
       <c r="I36" t="n">
-        <v>104.71434</v>
+        <v>5.2416</v>
       </c>
       <c r="J36" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="K36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S36" t="n">
-        <v>355560</v>
+        <v>0.664278</v>
       </c>
       <c r="T36" t="n">
-        <v>0.664278</v>
+        <v>-4.15681</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.15681</v>
+        <v>1.349627</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="W36" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="X36" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4483,99 +4285,93 @@
         <v>0.21</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>0.25</v>
+        <v>106.57692</v>
       </c>
       <c r="H37" t="n">
-        <v>106.57692</v>
+        <v>105.86962</v>
       </c>
       <c r="I37" t="n">
-        <v>105.86962</v>
+        <v>5.5589</v>
       </c>
       <c r="J37" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S37" t="n">
-        <v>357827</v>
+        <v>0.864098</v>
       </c>
       <c r="T37" t="n">
-        <v>0.864098</v>
+        <v>1.103268</v>
       </c>
       <c r="U37" t="n">
-        <v>1.103268</v>
+        <v>6.053495</v>
       </c>
       <c r="V37" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="W37" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="X37" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4596,99 +4392,93 @@
         <v>0.38</v>
       </c>
       <c r="F38" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="G38" t="n">
-        <v>0.26</v>
+        <v>106.95254</v>
       </c>
       <c r="H38" t="n">
-        <v>106.95254</v>
+        <v>111.51388</v>
       </c>
       <c r="I38" t="n">
-        <v>111.51388</v>
+        <v>5.6621</v>
       </c>
       <c r="J38" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S38" t="n">
-        <v>363282</v>
+        <v>0.35244</v>
       </c>
       <c r="T38" t="n">
-        <v>0.35244</v>
+        <v>5.331331</v>
       </c>
       <c r="U38" t="n">
-        <v>5.331331</v>
+        <v>1.856482</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="W38" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="X38" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4709,99 +4499,93 @@
         <v>-0.02</v>
       </c>
       <c r="F39" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.14</v>
+        <v>107.13607</v>
       </c>
       <c r="H39" t="n">
-        <v>107.13607</v>
+        <v>110.06483</v>
       </c>
       <c r="I39" t="n">
-        <v>110.06483</v>
+        <v>5.6562</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S39" t="n">
-        <v>369214</v>
+        <v>0.171599</v>
       </c>
       <c r="T39" t="n">
-        <v>0.171599</v>
+        <v>-1.299435</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.299435</v>
+        <v>-0.104202</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="X39" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4822,99 +4606,93 @@
         <v>0.44</v>
       </c>
       <c r="F40" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="G40" t="n">
-        <v>0.48</v>
+        <v>107.99994</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99994</v>
+        <v>107.08167</v>
       </c>
       <c r="I40" t="n">
-        <v>107.08167</v>
+        <v>5.4481</v>
       </c>
       <c r="J40" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S40" t="n">
-        <v>372016</v>
+        <v>0.80633</v>
       </c>
       <c r="T40" t="n">
-        <v>0.80633</v>
+        <v>-2.710366</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.710366</v>
+        <v>-3.679149</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="X40" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4935,99 +4713,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="G41" t="n">
-        <v>0.61</v>
+        <v>108.20756</v>
       </c>
       <c r="H41" t="n">
-        <v>108.20756</v>
+        <v>109.18693</v>
       </c>
       <c r="I41" t="n">
-        <v>109.18693</v>
+        <v>5.7779</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="K41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S41" t="n">
-        <v>366096</v>
+        <v>0.192241</v>
       </c>
       <c r="T41" t="n">
-        <v>0.192241</v>
+        <v>1.966032</v>
       </c>
       <c r="U41" t="n">
-        <v>1.966032</v>
+        <v>6.053487</v>
       </c>
       <c r="V41" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="W41" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5048,99 +4820,93 @@
         <v>0.39</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="G42" t="n">
-        <v>0.33</v>
+        <v>107.96783</v>
       </c>
       <c r="H42" t="n">
-        <v>107.96783</v>
+        <v>105.49025</v>
       </c>
       <c r="I42" t="n">
-        <v>105.49025</v>
+        <v>6.0535</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="K42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S42" t="n">
-        <v>363003</v>
+        <v>-0.221546</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.221546</v>
+        <v>-3.385643</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.385643</v>
+        <v>4.769899</v>
       </c>
       <c r="V42" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="W42" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="X42" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -5161,99 +4927,93 @@
         <v>0.52</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G43" t="n">
-        <v>0.48</v>
+        <v>107.1418</v>
       </c>
       <c r="H43" t="n">
-        <v>107.1418</v>
+        <v>104.15997</v>
       </c>
       <c r="I43" t="n">
-        <v>104.15997</v>
+        <v>6.1923</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="K43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S43" t="n">
-        <v>329730</v>
+        <v>-0.76507</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.76507</v>
+        <v>-1.261045</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.261045</v>
+        <v>2.292888</v>
       </c>
       <c r="V43" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="W43" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="X43" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="AA43" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5274,99 +5034,93 @@
         <v>0.16</v>
       </c>
       <c r="F44" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>108.21392</v>
       </c>
       <c r="H44" t="n">
-        <v>108.21392</v>
+        <v>102.72834</v>
       </c>
       <c r="I44" t="n">
-        <v>102.72834</v>
+        <v>5.8301</v>
       </c>
       <c r="J44" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="K44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S44" t="n">
-        <v>328303</v>
+        <v>1.000655</v>
       </c>
       <c r="T44" t="n">
-        <v>1.000655</v>
+        <v>-1.374453</v>
       </c>
       <c r="U44" t="n">
-        <v>-1.374453</v>
+        <v>-5.8492</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="W44" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="X44" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5387,99 +5141,93 @@
         <v>1.31</v>
       </c>
       <c r="F45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="G45" t="n">
-        <v>1.48</v>
+        <v>108.74593</v>
       </c>
       <c r="H45" t="n">
-        <v>108.74593</v>
+        <v>106.92609</v>
       </c>
       <c r="I45" t="n">
-        <v>106.92609</v>
+        <v>5.8488</v>
       </c>
       <c r="J45" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S45" t="n">
-        <v>332508</v>
+        <v>0.491628</v>
       </c>
       <c r="T45" t="n">
-        <v>0.491628</v>
+        <v>4.086263</v>
       </c>
       <c r="U45" t="n">
-        <v>4.086263</v>
+        <v>0.320749</v>
       </c>
       <c r="V45" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="W45" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5500,99 +5248,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="G46" t="n">
-        <v>0.51</v>
+        <v>110.20451</v>
       </c>
       <c r="H46" t="n">
-        <v>110.20451</v>
+        <v>114.11998</v>
       </c>
       <c r="I46" t="n">
-        <v>114.11998</v>
+        <v>5.7422</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S46" t="n">
-        <v>336157</v>
+        <v>1.341273</v>
       </c>
       <c r="T46" t="n">
-        <v>1.341273</v>
+        <v>6.727909</v>
       </c>
       <c r="U46" t="n">
-        <v>6.727909</v>
+        <v>-1.822596</v>
       </c>
       <c r="V46" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="X46" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5613,99 +5355,93 @@
         <v>0.43</v>
       </c>
       <c r="F47" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="G47" t="n">
-        <v>0.48</v>
+        <v>110.0593</v>
       </c>
       <c r="H47" t="n">
-        <v>110.0593</v>
+        <v>112.69428</v>
       </c>
       <c r="I47" t="n">
-        <v>112.69428</v>
+        <v>5.6608</v>
       </c>
       <c r="J47" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="K47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S47" t="n">
-        <v>340789</v>
+        <v>-0.131764</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.131764</v>
+        <v>-1.249299</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.249299</v>
+        <v>-1.417575</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="X47" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5726,99 +5462,93 @@
         <v>0.26</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="G48" t="n">
-        <v>0.35</v>
+        <v>109.08727</v>
       </c>
       <c r="H48" t="n">
-        <v>109.08727</v>
+        <v>108.65566</v>
       </c>
       <c r="I48" t="n">
-        <v>108.65566</v>
+        <v>5.7087</v>
       </c>
       <c r="J48" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="K48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S48" t="n">
-        <v>341459</v>
+        <v>-0.883188</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.883188</v>
+        <v>-3.583696</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.583696</v>
+        <v>0.84617</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="W48" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="X48" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5839,99 +5569,93 @@
         <v>0.24</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="G49" t="n">
-        <v>0.23</v>
+        <v>108.85988</v>
       </c>
       <c r="H49" t="n">
-        <v>108.85988</v>
+        <v>107.4594</v>
       </c>
       <c r="I49" t="n">
-        <v>107.4594</v>
+        <v>5.4571</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S49" t="n">
-        <v>344440</v>
+        <v>-0.208448</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.208448</v>
+        <v>-1.100964</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.100964</v>
+        <v>-4.407308</v>
       </c>
       <c r="V49" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="W49" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5952,99 +5676,93 @@
         <v>0.26</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="G50" t="n">
+        <v>108.41316</v>
+      </c>
+      <c r="H50" t="n">
+        <v>113.21721</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="R50" t="n">
+        <v>345111</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-0.410362</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5.358126</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0.21</v>
       </c>
-      <c r="H50" t="n">
-        <v>108.41316</v>
-      </c>
-      <c r="I50" t="n">
-        <v>113.21721</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="L50" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R50" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="S50" t="n">
-        <v>345111</v>
-      </c>
-      <c r="T50" t="n">
-        <v>-0.410362</v>
-      </c>
-      <c r="U50" t="n">
-        <v>5.358126</v>
-      </c>
-      <c r="V50" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>5.225222</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.000562</v>
-      </c>
       <c r="AG50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -6065,99 +5783,93 @@
         <v>-0.11</v>
       </c>
       <c r="F51" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.21</v>
+        <v>108.83964</v>
       </c>
       <c r="H51" t="n">
-        <v>108.83964</v>
+        <v>110.47825</v>
       </c>
       <c r="I51" t="n">
-        <v>110.47825</v>
+        <v>5.4264</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S51" t="n">
-        <v>350767</v>
+        <v>0.393384</v>
       </c>
       <c r="T51" t="n">
-        <v>0.393384</v>
+        <v>-2.419208</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.419208</v>
+        <v>-3.136324</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="X51" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6178,99 +5890,93 @@
         <v>0.48</v>
       </c>
       <c r="F52" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="G52" t="n">
-        <v>0.52</v>
+        <v>108.76251</v>
       </c>
       <c r="H52" t="n">
-        <v>108.76251</v>
+        <v>109.57602</v>
       </c>
       <c r="I52" t="n">
-        <v>109.57602</v>
+        <v>5.3186</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="K52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S52" t="n">
-        <v>356582</v>
+        <v>-0.070866</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.070866</v>
+        <v>-0.816658</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.816658</v>
+        <v>-1.986584</v>
       </c>
       <c r="V52" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="X52" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6291,99 +5997,93 @@
         <v>0.09</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="G53" t="n">
-        <v>0.03</v>
+        <v>108.78795</v>
       </c>
       <c r="H53" t="n">
-        <v>108.78795</v>
+        <v>110.16742</v>
       </c>
       <c r="I53" t="n">
-        <v>110.16742</v>
+        <v>5.3843</v>
       </c>
       <c r="J53" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="K53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S53" t="n">
-        <v>357103</v>
+        <v>0.02339</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02339</v>
+        <v>0.539717</v>
       </c>
       <c r="U53" t="n">
-        <v>0.539717</v>
+        <v>1.235287</v>
       </c>
       <c r="V53" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="W53" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="X53" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6404,99 +6104,93 @@
         <v>0.18</v>
       </c>
       <c r="F54" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="G54" t="n">
-        <v>0.03</v>
+        <v>109.30007</v>
       </c>
       <c r="H54" t="n">
-        <v>109.30007</v>
+        <v>106.69062</v>
       </c>
       <c r="I54" t="n">
-        <v>106.69062</v>
+        <v>5.3338</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="L54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="M54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="N54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="O54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="P54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="R54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="S54" t="n">
-        <v>360578</v>
+        <v>0.470751</v>
       </c>
       <c r="T54" t="n">
-        <v>0.470751</v>
+        <v>-3.155924</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.155924</v>
+        <v>-0.937912</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.938017</v>
+        <v>1.146567</v>
       </c>
       <c r="X54" t="n">
-        <v>1.146567</v>
+        <v>0.715383</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.715383</v>
+        <v>1.405488</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.405488</v>
+        <v>0.973109</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6517,99 +6211,93 @@
         <v>0.33</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="G55" t="n">
-        <v>0.21</v>
+        <v>109.27117</v>
       </c>
       <c r="H55" t="n">
-        <v>109.27117</v>
+        <v>107.27827</v>
       </c>
       <c r="I55" t="n">
-        <v>107.27827</v>
+        <v>5.5024</v>
       </c>
       <c r="J55" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="K55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="L55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="M55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="N55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="P55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="R55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="S55" t="n">
-        <v>358234</v>
+        <v>-0.026441</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.026441</v>
+        <v>0.550798</v>
       </c>
       <c r="U55" t="n">
-        <v>0.550798</v>
+        <v>3.160973</v>
       </c>
       <c r="V55" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="W55" t="n">
-        <v>3.161329</v>
+        <v>1.90144</v>
       </c>
       <c r="X55" t="n">
-        <v>1.90144</v>
+        <v>3.24641</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.24641</v>
+        <v>1.099346</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.099346</v>
+        <v>-0.650067</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6630,99 +6318,93 @@
         <v>0.33</v>
       </c>
       <c r="F56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G56" t="n">
-        <v>0.39</v>
+        <v>110.09703</v>
       </c>
       <c r="H56" t="n">
-        <v>110.09703</v>
+        <v>103.80093</v>
       </c>
       <c r="I56" t="n">
-        <v>103.80093</v>
+        <v>5.2301</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="L56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="M56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="N56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="O56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="P56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="S56" t="n">
-        <v>364367</v>
+        <v>0.755789</v>
       </c>
       <c r="T56" t="n">
-        <v>0.755789</v>
+        <v>-3.241421</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.241421</v>
+        <v>-4.94875</v>
       </c>
       <c r="V56" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.949289</v>
+        <v>-0.083179</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.083179</v>
+        <v>-1.743482</v>
       </c>
       <c r="Y56" t="n">
-        <v>-1.743482</v>
+        <v>0.927966</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.927966</v>
+        <v>1.712009</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6743,99 +6425,93 @@
         <v>0.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.78559</v>
       </c>
       <c r="H57" t="n">
-        <v>110.78559</v>
+        <v>106.7205</v>
       </c>
       <c r="I57" t="n">
-        <v>106.7205</v>
+        <v>5.1495</v>
       </c>
       <c r="J57" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="K57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="L57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="M57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="N57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="R57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="S57" t="n">
-        <v>371074</v>
+        <v>0.625412</v>
       </c>
       <c r="T57" t="n">
-        <v>0.625412</v>
+        <v>2.812663</v>
       </c>
       <c r="U57" t="n">
-        <v>2.812663</v>
+        <v>-1.54108</v>
       </c>
       <c r="V57" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.541256</v>
+        <v>0.371461</v>
       </c>
       <c r="X57" t="n">
-        <v>0.371461</v>
+        <v>0.070797</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.070797</v>
+        <v>0.549722</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.549722</v>
+        <v>1.840727</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="AB57" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="AC57" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6856,99 +6532,93 @@
         <v>0.88</v>
       </c>
       <c r="F58" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="G58" t="n">
-        <v>0.91</v>
+        <v>110.58589</v>
       </c>
       <c r="H58" t="n">
-        <v>110.58589</v>
+        <v>117.92682</v>
       </c>
       <c r="I58" t="n">
-        <v>117.92682</v>
+        <v>5.2194</v>
       </c>
       <c r="J58" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="L58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="M58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="N58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="O58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="P58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="R58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="S58" t="n">
-        <v>362002</v>
+        <v>-0.180258</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.180258</v>
+        <v>10.500625</v>
       </c>
       <c r="U58" t="n">
-        <v>10.500625</v>
+        <v>1.357413</v>
       </c>
       <c r="V58" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="W58" t="n">
-        <v>1.357572</v>
+        <v>1.12824</v>
       </c>
       <c r="X58" t="n">
-        <v>1.12824</v>
+        <v>1.133877</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.133877</v>
+        <v>1.124914</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.124914</v>
+        <v>-2.444795</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="AC58" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6969,99 +6639,93 @@
         <v>0.67</v>
       </c>
       <c r="F59" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8100000000000001</v>
+        <v>111.15205</v>
       </c>
       <c r="H59" t="n">
-        <v>111.15205</v>
+        <v>113.72712</v>
       </c>
       <c r="I59" t="n">
-        <v>113.72712</v>
+        <v>4.9886</v>
       </c>
       <c r="J59" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="K59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="L59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="M59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="N59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="O59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="R59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="S59" t="n">
-        <v>366913</v>
+        <v>0.511964</v>
       </c>
       <c r="T59" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.561276</v>
+        <v>-4.421964</v>
       </c>
       <c r="V59" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="W59" t="n">
-        <v>-4.422473</v>
+        <v>0.288267</v>
       </c>
       <c r="X59" t="n">
-        <v>0.288267</v>
+        <v>-0.052977</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.052977</v>
+        <v>0.489642</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.489642</v>
+        <v>1.356622</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -7082,91 +6746,85 @@
         <v>0.58</v>
       </c>
       <c r="F60" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G60" t="n">
         <v>0.65</v>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>5.0569</v>
+      </c>
       <c r="J60" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="L60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="M60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="N60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="O60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="P60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="R60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="S60" t="n">
         <v>371137</v>
       </c>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>1.369122</v>
+      </c>
       <c r="V60" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="W60" t="n">
-        <v>1.369286</v>
+        <v>0.565068</v>
       </c>
       <c r="X60" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.461065</v>
+        <v>1.151227</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -7187,65 +6845,59 @@
         <v>0.16</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="G61" t="n">
         <v>0.14</v>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>5.1766</v>
+      </c>
       <c r="J61" t="n">
-        <v>5.1766</v>
-      </c>
-      <c r="K61" t="n">
         <v>5.176</v>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>367558</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="V61" t="n">
-        <v>2.367063</v>
-      </c>
-      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="AA61" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="AC61" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7264,13 +6916,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>5.1088</v>
+      </c>
       <c r="J62" t="n">
-        <v>5.1088</v>
-      </c>
-      <c r="K62" t="n">
         <v>5.1082</v>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7280,33 +6932,31 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-1.30974</v>
+      </c>
       <c r="V62" t="n">
-        <v>-1.30974</v>
-      </c>
-      <c r="W62" t="n">
         <v>-1.309892</v>
       </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,150 +448,160 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>igp_m</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>igp_m_acum_12m</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -614,45 +624,47 @@
         <v>0.96</v>
       </c>
       <c r="F2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.02</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>96.42256999999999</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>99.83515</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.121</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4271865</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1833179</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2438686</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.36</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.58</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2.94</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>20.26</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>355671</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -687,89 +701,93 @@
         <v>0.87</v>
       </c>
       <c r="F3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.88</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>97.03115</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>99.19471</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4346060</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1851006</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2495054</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.37</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.56</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.96</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>20.92</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>370395</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.631159</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.641498</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -790,89 +808,93 @@
         <v>1.16</v>
       </c>
       <c r="F4" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.2</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>96.97727</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>97.10229</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4441056</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1894119</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2546936</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.34</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.43</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>21.42</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>368886</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>-0.055529</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>-2.109407</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -893,89 +915,93 @@
         <v>1.25</v>
       </c>
       <c r="F5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.16</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>97.49541000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>96.53060000000001</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5.643</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4511956</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1910940</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2601017</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.33</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.43</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>22.89</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>367927</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.53429</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>-0.58875</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -996,89 +1022,93 @@
         <v>0.95</v>
       </c>
       <c r="F6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.84</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>99.05485</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>97.85541000000001</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4597507</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1933111</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2664395</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.36</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>23.91</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>367772</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1.599501</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.372425</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1099,89 +1129,93 @@
         <v>0.73</v>
       </c>
       <c r="F7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.73</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>99.30268</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>99.31872</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4682852</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1974391</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2708461</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.35</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>24.21</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>362204</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.250195</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.49538</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1202,89 +1236,93 @@
         <v>0.54</v>
       </c>
       <c r="F8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.67</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>97.42644</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>91.67792</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4682131</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1947035</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2735096</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.51</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.46</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>25.23</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>358398</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-1.889415</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>-7.693212</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1305,89 +1343,93 @@
         <v>1.01</v>
       </c>
       <c r="F9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>98.38327</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>95.6409</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4727818</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1971524</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2756295</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.57</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.44</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>25.63</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>357740</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>0.982105</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>4.32272</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1408,89 +1450,93 @@
         <v>1.62</v>
       </c>
       <c r="F10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.71</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>99.5587</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>104.52811</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4794583</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1994119</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2800464</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.66</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.55</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>26.54</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>353169</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1.194746</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>9.292268999999999</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1511,89 +1557,93 @@
         <v>1.06</v>
       </c>
       <c r="F11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.04</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>99.56286</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>100.22885</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4833732</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2003312</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2830420</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.72</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.57</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.46</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>345097</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>0.004178</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-4.113018</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1614,89 +1664,93 @@
         <v>0.47</v>
       </c>
       <c r="F12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.45</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>99.67480999999999</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>99.74863999999999</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4889397</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2013726</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2875671</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.79</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.57</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>27.42</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346415</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0.112442</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-0.479114</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1717,93 +1771,99 @@
         <v>0.67</v>
       </c>
       <c r="F13" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.62</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>99.51873000000001</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>99.3134</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.238</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>4965603</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2052569</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2913035</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.73</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.52</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>27.88</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>341958</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.156589</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-0.436337</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
+        <v>10.700862</v>
+      </c>
+      <c r="AD13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1824,93 +1884,99 @@
         <v>-0.68</v>
       </c>
       <c r="F14" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G14" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>101.41705</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>103.95829</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4999244</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2047038</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2952207</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.84</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>29.24</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>346403</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.9075</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>4.677002</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
+        <v>10.074751</v>
+      </c>
+      <c r="AD14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AJ14" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1931,93 +1997,99 @@
         <v>-0.36</v>
       </c>
       <c r="F15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G15" t="n">
         <v>-0.31</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>101.1048</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>104.51622</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>5.179</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5072711</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2064183</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3008528</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2.9</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>28.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>339664</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-0.307887</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>0.536686</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
+        <v>8.58755</v>
+      </c>
+      <c r="AD15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2038,93 +2110,99 @@
         <v>-0.29</v>
       </c>
       <c r="F16" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="G16" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>101.15658</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>101.18649</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.406</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5164775</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2109806</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3054969</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2.92</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.65</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>28.57</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>327580</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0.051214</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-3.18585</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
+        <v>8.248760000000001</v>
+      </c>
+      <c r="AD16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2145,93 +2223,99 @@
         <v>0.59</v>
       </c>
       <c r="F17" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.47</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>101.44313</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>100.08007</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>5.257</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5215990</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2105856</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3110134</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.04</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.77</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.68</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>325546</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0.283274</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-1.093446</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
+        <v>6.517038</v>
+      </c>
+      <c r="AD17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2252,93 +2336,99 @@
         <v>0.41</v>
       </c>
       <c r="F18" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.38</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>100.70751</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>99.15338</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5285657</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2130312</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3155345</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.07</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.81</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.52</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331505</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.725155</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-0.925949</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
+        <v>5.899363</v>
+      </c>
+      <c r="AD18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2359,93 +2449,99 @@
         <v>0.62</v>
       </c>
       <c r="F19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>100.45671</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>99.96775</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5366069</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2178236</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3187833</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.07</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1.8</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>29.64</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>324703</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-0.249038</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>0.821323</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
+        <v>5.458422</v>
+      </c>
+      <c r="AD19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>-0</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>-0</v>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2466,93 +2562,99 @@
         <v>0.53</v>
       </c>
       <c r="F20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.46</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>100.1131</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>95.09765</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5373231</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2151399</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3221831</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.24</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1.94</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.54</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>331122</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-0.342048</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-4.871671</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
+        <v>3.79089</v>
+      </c>
+      <c r="AD20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2573,93 +2675,99 @@
         <v>0.84</v>
       </c>
       <c r="F21" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.77</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>102.99794</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>98.65175000000001</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5370950</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2136105</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3234845</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.36</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.17</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>30.48</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>328098</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>2.881581</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>3.737316</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
+        <v>1.864495</v>
+      </c>
+      <c r="AD21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2680,93 +2788,99 @@
         <v>0.71</v>
       </c>
       <c r="F22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.64</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>103.10183</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>110.6159</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5424811</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2154900</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3269910</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.35</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>30.99</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>341158</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>0.100866</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>12.127661</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
+        <v>0.172427</v>
+      </c>
+      <c r="AD22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2787,93 +2901,99 @@
         <v>0.61</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="G23" t="n">
         <v>0.53</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>104.18587</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>104.03928</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5426307</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2145000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3281308</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.54</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.45</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>31.62</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>345725</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1.051427</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-5.945456</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
+        <v>-2.158772</v>
+      </c>
+      <c r="AD23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2894,93 +3014,99 @@
         <v>0.23</v>
       </c>
       <c r="F24" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="G24" t="n">
         <v>0.36</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>102.46133</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>102.71672</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5453708</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2145530</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3308178</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.65</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.58</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>31.63</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>343489</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-1.655253</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-1.271212</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
+        <v>-4.45588</v>
+      </c>
+      <c r="AD24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
         <v>-0</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>-0</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3001,93 +3127,99 @@
         <v>-0.08</v>
       </c>
       <c r="F25" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="G25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>102.39681</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>102.2809</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5479459</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2169613</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3309846</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.63</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>30.85</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>343620</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.06297</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-0.424293</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
+        <v>-6.84947</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3108,93 +3240,99 @@
         <v>0.12</v>
       </c>
       <c r="F26" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G26" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>102.86628</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>105.34289</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5484871</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2153541</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3331330</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.63</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.73</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>30.43</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>345476</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.458481</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>2.993707</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
+        <v>-7.713954</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3215,93 +3353,99 @@
         <v>0.23</v>
       </c>
       <c r="F27" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.2</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>102.48117</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>106.05936</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5559063</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2172658</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3386405</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.61</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.82</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.92</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>344177</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-0.374379</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.680131</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
+        <v>-7.193509</v>
+      </c>
+      <c r="AD27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3322,93 +3466,99 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.11</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>102.49422</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>101.75832</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>5.007</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5625945</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2215175</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3410769</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.54</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.82</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.66</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>340324</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.012734</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-4.055314</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
+        <v>-5.956714</v>
+      </c>
+      <c r="AD28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3429,93 +3579,99 @@
         <v>0.24</v>
       </c>
       <c r="F29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.12</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>102.81544</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>101.93091</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5653808</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2204808</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3449000</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.56</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.92</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>29.24</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>340247</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>0.313403</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.169608</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
+        <v>-4.560737</v>
+      </c>
+      <c r="AD29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3536,93 +3692,99 @@
         <v>0.28</v>
       </c>
       <c r="F30" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G30" t="n">
         <v>0.1</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>103.57529</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>101.68306</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5711103</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2220766</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3490337</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.53</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.99</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>29.01</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>348406</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>0.739043</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-0.243155</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
+        <v>-3.457004</v>
+      </c>
+      <c r="AD30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3643,93 +3805,99 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F31" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G31" t="n">
         <v>0.55</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>104.68308</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>101.68292</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5805157</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2283485</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3521672</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.29</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.59</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>28.14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>355034</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1.06955</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>-0.000138</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
+        <v>-3.178284</v>
+      </c>
+      <c r="AD31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AJ31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3750,93 +3918,99 @@
         <v>0.42</v>
       </c>
       <c r="F32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G32" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>104.47997</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>99.29383</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5794707</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2234362</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3560345</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.38</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.77</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355066</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-0.194024</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-2.349549</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
+        <v>-3.31355</v>
+      </c>
+      <c r="AD32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AJ32" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3857,93 +4031,99 @@
         <v>0.83</v>
       </c>
       <c r="F33" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="G33" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>104.63436</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>102.15169</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5815954</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2235302</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3580652</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.38</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.85</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>352705</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>0.14777</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>2.878185</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
+        <v>-3.758575</v>
+      </c>
+      <c r="AD33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3964,93 +4144,99 @@
         <v>0.16</v>
       </c>
       <c r="F34" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.19</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>104.71934</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>109.56886</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5899742</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2285775</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3613967</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.33</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.71</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>28.14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355008</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.081216</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>7.260937</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
+        <v>-4.25878</v>
+      </c>
+      <c r="AD34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4071,93 +4257,99 @@
         <v>0.38</v>
       </c>
       <c r="F35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G35" t="n">
         <v>0.37</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>104.96661</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>109.2559</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>5915538</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2268879</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3646659</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.37</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.76</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.86</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>351599</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.236126</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>-0.285629</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
+        <v>-3.040871</v>
+      </c>
+      <c r="AD35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4178,93 +4370,99 @@
         <v>0.46</v>
       </c>
       <c r="F36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.46</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>105.66388</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>104.71434</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.241</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>5953960</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2278309</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3675652</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.43</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.8</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.75</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>355560</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.664278</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>-4.15681</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Z36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
+        <v>-0.344269</v>
+      </c>
+      <c r="AD36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4285,93 +4483,99 @@
         <v>0.21</v>
       </c>
       <c r="F37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.25</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>106.57692</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>105.86962</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6041898</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2336858</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3705041</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.29</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.64</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.81</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>357827</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.864098</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>1.103268</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Z37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
+        <v>2.440035</v>
+      </c>
+      <c r="AD37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4392,93 +4596,99 @@
         <v>0.38</v>
       </c>
       <c r="F38" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G38" t="n">
         <v>0.26</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>106.95254</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>111.51388</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6069205</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2323362</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3745844</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.3</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.52</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.74</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>363282</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.35244</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>5.331331</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
+        <v>3.812368</v>
+      </c>
+      <c r="AD38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4499,93 +4709,99 @@
         <v>-0.02</v>
       </c>
       <c r="F39" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G39" t="n">
         <v>-0.14</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>107.13607</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>110.06483</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6135298</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2344397</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3790900</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.33</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.55</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.59</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>369214</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.171599</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>-1.299435</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
+        <v>4.259387</v>
+      </c>
+      <c r="AD39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4606,93 +4822,99 @@
         <v>0.44</v>
       </c>
       <c r="F40" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G40" t="n">
         <v>0.48</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>107.99994</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>107.08167</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6216528</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2384828</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3831700</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.34</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.56</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>27.49</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>372016</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>0.80633</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-2.710366</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Z40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AB40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
+        <v>4.519075</v>
+      </c>
+      <c r="AD40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4713,93 +4935,99 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G41" t="n">
         <v>0.61</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>108.20756</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>109.18693</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6275117</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2397533</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3877584</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.3</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.52</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>27.94</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>366096</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>0.192241</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>1.966032</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Y41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
+        <v>5.579866</v>
+      </c>
+      <c r="AD41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4820,93 +5048,99 @@
         <v>0.39</v>
       </c>
       <c r="F42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G42" t="n">
         <v>0.33</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>107.96783</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>105.49025</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6365690</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2436022</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>3929668</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>28.45</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>363003</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>-0.221546</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-3.385643</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Z42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
+        <v>6.325086</v>
+      </c>
+      <c r="AD42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AJ42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4927,93 +5161,99 @@
         <v>0.52</v>
       </c>
       <c r="F43" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G43" t="n">
         <v>0.48</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>107.1418</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>104.15997</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6464602</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2499177</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>3965425</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.08</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.21</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>28.5</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>329730</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>-0.76507</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>-1.261045</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Z43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
+        <v>6.536174</v>
+      </c>
+      <c r="AD43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>1</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AF43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AJ43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5034,93 +5274,99 @@
         <v>0.16</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>108.21392</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>102.72834</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6465016</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2451957</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4013059</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.34</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.43</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>29.88</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>328303</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.000655</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>-1.374453</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Z44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
+        <v>6.749097</v>
+      </c>
+      <c r="AD44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5141,93 +5387,99 @@
         <v>1.31</v>
       </c>
       <c r="F45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G45" t="n">
         <v>1.48</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>108.74593</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>106.92609</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6511444</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2477151</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4034293</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.41</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.52</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>30.53</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>332508</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>0.491628</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>4.086263</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
+        <v>8.444549</v>
+      </c>
+      <c r="AD45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5248,93 +5500,99 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F46" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="G46" t="n">
         <v>0.51</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>110.20451</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>114.11998</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6576464</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2498262</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4078202</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.44</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.49</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.34</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>336157</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>1.341273</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>6.727909</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
+        <v>8.586193</v>
+      </c>
+      <c r="AD46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>1</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5355,93 +5613,99 @@
         <v>0.43</v>
       </c>
       <c r="F47" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.48</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>110.0593</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>112.69428</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6623948</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2512426</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4111522</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.67</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.72</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.63</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>340789</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.131764</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.249299</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Z47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
+        <v>8.510418</v>
+      </c>
+      <c r="AD47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AJ47" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5462,93 +5726,99 @@
         <v>0.26</v>
       </c>
       <c r="F48" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.35</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>109.08727</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>108.65566</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6666287</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2532708</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4133579</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.72</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.67</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.7</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>341459</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.883188</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>-3.583696</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
+        <v>7.026183</v>
+      </c>
+      <c r="AD48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AF48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5569,93 +5839,99 @@
         <v>0.24</v>
       </c>
       <c r="F49" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="G49" t="n">
         <v>0.23</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>108.85988</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>107.4594</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6703663</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2547693</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4155970</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>3.75</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.67</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.85</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>344440</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>-0.208448</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-1.100964</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
+        <v>4.393261</v>
+      </c>
+      <c r="AD49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AF49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AG49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5676,93 +5952,99 @@
         <v>0.26</v>
       </c>
       <c r="F50" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="G50" t="n">
         <v>0.21</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>108.41316</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>113.21721</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6733209</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2544400</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4188808</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>3.96</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.79</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.75</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>345111</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.410362</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>5.358126</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Z50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="AD50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AG50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5783,93 +6065,99 @@
         <v>-0.11</v>
       </c>
       <c r="F51" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G51" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>108.83964</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>110.47825</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6774436</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2546265</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4228171</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.14</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.85</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>31.87</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>350767</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.393384</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>-2.419208</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
+        <v>3.033233</v>
+      </c>
+      <c r="AD51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5890,93 +6178,99 @@
         <v>0.48</v>
       </c>
       <c r="F52" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G52" t="n">
         <v>0.52</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>108.76251</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>109.57602</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.318</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>6852705</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2589817</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4262888</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.09</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.77</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>31.47</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>356582</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>-0.070866</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-0.816658</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
+        <v>2.828436</v>
+      </c>
+      <c r="AD52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5997,93 +6291,99 @@
         <v>0.09</v>
       </c>
       <c r="F53" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="G53" t="n">
         <v>0.03</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>108.78795</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>110.16742</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>6923886</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2597630</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4326256</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.18</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.82</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>32.04</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>357103</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.02339</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.539717</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
+        <v>0.924206</v>
+      </c>
+      <c r="AD53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AJ53" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6104,93 +6404,99 @@
         <v>0.18</v>
       </c>
       <c r="F54" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.03</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>109.30007</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>106.69062</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7003273</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2616213</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4387061</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.23</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.74</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.32</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>360578</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.470751</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-3.155924</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Z54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
+        <v>-0.101973</v>
+      </c>
+      <c r="AD54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
         <v>-0</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>-0</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AH54" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6211,93 +6517,99 @@
         <v>0.33</v>
       </c>
       <c r="F55" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.21</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>109.27117</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>107.27827</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7136436</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2701146</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4435290</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.2</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>2.68</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>31.99</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>358234</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>-0.026441</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>0.550798</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
+        <v>-1.042167</v>
+      </c>
+      <c r="AD55" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6318,93 +6630,99 @@
         <v>0.33</v>
       </c>
       <c r="F56" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.39</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>110.09703</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>103.80093</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7130500</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2654052</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4476448</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.45</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>2.87</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.6</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>364367</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>0.755789</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>-3.241421</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Z56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
+        <v>-0.903999</v>
+      </c>
+      <c r="AD56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>0.19</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6425,93 +6743,99 @@
         <v>0.7</v>
       </c>
       <c r="F57" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>110.78559</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>106.7205</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7156987</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2655931</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4501056</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.07</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>32.78</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>371074</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.625412</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>2.812663</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AC57" t="n">
+        <v>-2.659212</v>
+      </c>
+      <c r="AD57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AJ57" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6532,93 +6856,99 @@
         <v>0.88</v>
       </c>
       <c r="F58" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.91</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>110.58589</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>117.92682</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7237735</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2686046</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4551689</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.52</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.04</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>32.99</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>362002</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>-0.180258</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>10.500625</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AC58" t="n">
+        <v>-1.819225</v>
+      </c>
+      <c r="AD58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AE58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AF58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6639,93 +6969,99 @@
         <v>0.67</v>
       </c>
       <c r="F59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>111.15205</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>113.72712</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>4.988</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7258599</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2684623</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4573976</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.63</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.15</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.51</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>366913</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>0.511964</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>-3.561276</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AB59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AC59" t="n">
+        <v>0.619623</v>
+      </c>
+      <c r="AD59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6746,85 +7082,91 @@
         <v>0.58</v>
       </c>
       <c r="F60" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G60" t="n">
         <v>0.65</v>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7299615</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2704550</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4595065</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.74</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.24</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>33.42</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>371137</v>
       </c>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Z60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AB60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AC60" t="n">
+        <v>1.964454</v>
+      </c>
+      <c r="AD60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -6845,59 +7187,65 @@
         <v>0.16</v>
       </c>
       <c r="F61" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G61" t="n">
         <v>0.14</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.176</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>367558</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="n">
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AB61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AC61" t="n">
+        <v>3.177699</v>
+      </c>
+      <c r="AD61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6916,13 +7264,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>5.1088</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1082</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>5.1183</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.1177</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6932,31 +7280,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
-        <v>-1.30974</v>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.309892</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
+        <v>-1.126222</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-1.126352</v>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AG62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7266,10 +7266,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1183</v>
+        <v>5.0742</v>
       </c>
       <c r="K62" t="n">
-        <v>5.1177</v>
+        <v>5.0736</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7282,10 +7282,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.126222</v>
+        <v>-1.978132</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.126352</v>
+        <v>-1.978362</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,105 +503,95 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -657,14 +647,12 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="R2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="S2" t="n">
         <v>355671</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -734,60 +720,54 @@
         <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="R3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="S3" t="n">
-        <v>370395</v>
+        <v>0.631159</v>
       </c>
       <c r="T3" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="W3" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="X3" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="AF3" t="n">
         <v>0.003276</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -841,60 +821,54 @@
         <v>1.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="S4" t="n">
-        <v>368886</v>
+        <v>-0.055529</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.055529</v>
+        <v>-2.109407</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.109407</v>
+        <v>5.757004</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="W4" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="X4" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="AF4" t="n">
         <v>0.001591</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -948,60 +922,54 @@
         <v>1.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S5" t="n">
-        <v>367927</v>
+        <v>0.53429</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53429</v>
+        <v>-0.58875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.58875</v>
+        <v>3.74306</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="W5" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="X5" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="AF5" t="n">
         <v>0.00324</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1055,60 +1023,54 @@
         <v>1.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S6" t="n">
-        <v>367772</v>
+        <v>1.599501</v>
       </c>
       <c r="T6" t="n">
-        <v>1.599501</v>
+        <v>1.372425</v>
       </c>
       <c r="U6" t="n">
-        <v>1.372425</v>
+        <v>-0.409357</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="X6" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF6" t="n">
         <v>0.005012</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH6" t="n">
         <v>0.03</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1162,60 +1124,54 @@
         <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S7" t="n">
-        <v>362204</v>
+        <v>0.250195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.250195</v>
+        <v>1.49538</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49538</v>
+        <v>-0.70108</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="X7" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF7" t="n">
         <v>0.00406</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1269,60 +1225,54 @@
         <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S8" t="n">
-        <v>358398</v>
+        <v>-1.889415</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.889415</v>
+        <v>-7.693212</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.693212</v>
+        <v>-3.99785</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF8" t="n">
         <v>0.001433</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1376,60 +1326,54 @@
         <v>1.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S9" t="n">
-        <v>357740</v>
+        <v>0.982105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.982105</v>
+        <v>4.32272</v>
       </c>
       <c r="U9" t="n">
-        <v>4.32272</v>
+        <v>-4.069138</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="X9" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF9" t="n">
         <v>0.004849</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1483,60 +1427,54 @@
         <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S10" t="n">
-        <v>353169</v>
+        <v>1.194746</v>
       </c>
       <c r="T10" t="n">
-        <v>1.194746</v>
+        <v>9.292268999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>9.292268999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="X10" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF10" t="n">
         <v>0.002356</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1590,60 +1528,54 @@
         <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S11" t="n">
-        <v>345097</v>
+        <v>0.004178</v>
       </c>
       <c r="T11" t="n">
-        <v>0.004178</v>
+        <v>-4.113018</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.113018</v>
+        <v>3.826671</v>
       </c>
       <c r="V11" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="W11" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="X11" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF11" t="n">
         <v>0.001785</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1697,60 +1629,54 @@
         <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S12" t="n">
-        <v>346415</v>
+        <v>0.112442</v>
       </c>
       <c r="T12" t="n">
-        <v>0.112442</v>
+        <v>-0.479114</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.479114</v>
+        <v>-3.866561</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="X12" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF12" t="n">
         <v>0.003057</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1804,66 +1730,60 @@
         <v>1.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S13" t="n">
-        <v>341958</v>
+        <v>-0.156589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.156589</v>
+        <v>-0.436337</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.436337</v>
+        <v>10.765717</v>
       </c>
       <c r="V13" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="W13" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="X13" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.299314</v>
+        <v>-1.286607</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.286607</v>
+        <v>11.88673</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.919595</v>
+        <v>0.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF13" t="n">
         <v>0.00132</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1917,66 +1837,60 @@
         <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S14" t="n">
-        <v>346403</v>
+        <v>1.9075</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9075</v>
+        <v>4.677002</v>
       </c>
       <c r="U14" t="n">
-        <v>4.677002</v>
+        <v>-0.946926</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="X14" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.344714</v>
+        <v>1.299867</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.299867</v>
+        <v>10.069235</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.124804</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF14" t="n">
         <v>0.0009210000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -2030,66 +1944,60 @@
         <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S15" t="n">
-        <v>339664</v>
+        <v>-0.307887</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.307887</v>
+        <v>0.536686</v>
       </c>
       <c r="U15" t="n">
-        <v>0.536686</v>
+        <v>-0.181173</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="X15" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.825751</v>
+        <v>0.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF15" t="n">
         <v>0.001523</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2143,66 +2051,60 @@
         <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S16" t="n">
-        <v>327580</v>
+        <v>0.051214</v>
       </c>
       <c r="T16" t="n">
-        <v>0.051214</v>
+        <v>-3.18585</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.18585</v>
+        <v>4.394671</v>
       </c>
       <c r="V16" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="W16" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="X16" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF16" t="n">
         <v>0.000228</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2256,46 +2158,46 @@
         <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S17" t="n">
-        <v>325546</v>
+        <v>0.283274</v>
       </c>
       <c r="T17" t="n">
-        <v>0.283274</v>
+        <v>-1.093446</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.093446</v>
+        <v>-2.766988</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="X17" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.470016</v>
+        <v>6.517038</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.517038</v>
+        <v>6.460076</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2304,18 +2206,12 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH17" t="n">
         <v>0.12</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2369,46 +2265,46 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S18" t="n">
-        <v>331505</v>
+        <v>-0.725155</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.725155</v>
+        <v>-0.925949</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.925949</v>
+        <v>0.705726</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="X18" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.900488</v>
+        <v>5.899363</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.899363</v>
+        <v>5.974439</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2417,18 +2313,12 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2482,66 +2372,60 @@
         <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S19" t="n">
-        <v>324703</v>
+        <v>-0.249038</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.249038</v>
+        <v>0.821323</v>
       </c>
       <c r="U19" t="n">
-        <v>0.821323</v>
+        <v>-1.443116</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="X19" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.784842</v>
+        <v>5.458422</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.458422</v>
+        <v>5.932356</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.932356</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF19" t="n">
         <v>-0</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2595,46 +2479,46 @@
         <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S20" t="n">
-        <v>331122</v>
+        <v>-0.342048</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.342048</v>
+        <v>-4.871671</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.871671</v>
+        <v>-2.269199</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="X20" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.77432</v>
+        <v>3.79089</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.79089</v>
+        <v>5.711379</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2643,18 +2527,12 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2708,46 +2586,46 @@
         <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S21" t="n">
-        <v>328098</v>
+        <v>2.881581</v>
       </c>
       <c r="T21" t="n">
-        <v>2.881581</v>
+        <v>3.737316</v>
       </c>
       <c r="U21" t="n">
-        <v>3.737316</v>
+        <v>2.127743</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="W21" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.596302</v>
+        <v>1.864495</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.864495</v>
+        <v>5.47065</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2756,18 +2634,12 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2821,46 +2693,46 @@
         <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S22" t="n">
-        <v>341158</v>
+        <v>0.100866</v>
       </c>
       <c r="T22" t="n">
-        <v>0.100866</v>
+        <v>12.127661</v>
       </c>
       <c r="U22" t="n">
-        <v>12.127661</v>
+        <v>-2.446331</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="X22" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.650694</v>
+        <v>0.172427</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.172427</v>
+        <v>4.361088</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -2869,18 +2741,12 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2934,46 +2800,46 @@
         <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S23" t="n">
-        <v>345725</v>
+        <v>1.051427</v>
       </c>
       <c r="T23" t="n">
-        <v>1.051427</v>
+        <v>-5.945456</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.945456</v>
+        <v>-1.568774</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="X23" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.184706</v>
+        <v>-2.158772</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.158772</v>
+        <v>3.834324</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -2982,18 +2848,12 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -3047,66 +2907,60 @@
         <v>2.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S24" t="n">
-        <v>343489</v>
+        <v>-1.655253</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.655253</v>
+        <v>-1.271212</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.271212</v>
+        <v>1.903733</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="W24" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="X24" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.935832</v>
+        <v>-4.45588</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.45588</v>
+        <v>3.741292</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.741292</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF24" t="n">
         <v>-0</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3160,46 +3014,46 @@
         <v>2.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="R25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="S25" t="n">
-        <v>343620</v>
+        <v>-0.06297</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.06297</v>
+        <v>-0.424293</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.424293</v>
+        <v>-5.429855</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.429855</v>
+        <v>-5.430495</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.430495</v>
+        <v>0.472174</v>
       </c>
       <c r="X25" t="n">
-        <v>0.472174</v>
+        <v>1.122473</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.122473</v>
+        <v>0.050421</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.050421</v>
+        <v>0.038138</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.038138</v>
+        <v>3.161501</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.161501</v>
+        <v>-6.84947</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.84947</v>
+        <v>2.998957</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3208,18 +3062,12 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3273,46 +3121,46 @@
         <v>2.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S26" t="n">
-        <v>345476</v>
+        <v>0.458481</v>
       </c>
       <c r="T26" t="n">
-        <v>0.458481</v>
+        <v>2.993707</v>
       </c>
       <c r="U26" t="n">
-        <v>2.993707</v>
+        <v>-1.612301</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="X26" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.992444</v>
+        <v>-7.713954</v>
       </c>
       <c r="AC26" t="n">
-        <v>-7.713954</v>
+        <v>3.527423</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3321,18 +3169,12 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3386,66 +3228,60 @@
         <v>2.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S27" t="n">
-        <v>344177</v>
+        <v>-0.374379</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.374379</v>
+        <v>0.680131</v>
       </c>
       <c r="U27" t="n">
-        <v>0.680131</v>
+        <v>3.804703</v>
       </c>
       <c r="V27" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="W27" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="X27" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.608216</v>
+        <v>-7.193509</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.193509</v>
+        <v>4.057054</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.057054</v>
+        <v>-0.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF27" t="n">
         <v>-0.001599</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3499,66 +3335,60 @@
         <v>2.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S28" t="n">
-        <v>340324</v>
+        <v>0.012734</v>
       </c>
       <c r="T28" t="n">
-        <v>0.012734</v>
+        <v>-4.055314</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.055314</v>
+        <v>1.741198</v>
       </c>
       <c r="V28" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="X28" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.185235</v>
+        <v>-5.956714</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5.956714</v>
+        <v>4.505936</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.505936</v>
+        <v>-0.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF28" t="n">
         <v>-0.000768</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3612,66 +3442,60 @@
         <v>2.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S29" t="n">
-        <v>340247</v>
+        <v>0.313403</v>
       </c>
       <c r="T29" t="n">
-        <v>0.313403</v>
+        <v>0.169608</v>
       </c>
       <c r="U29" t="n">
-        <v>0.169608</v>
+        <v>0.996485</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="W29" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="X29" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.819246</v>
+        <v>-4.560737</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.560737</v>
+        <v>4.141877</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.141877</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF29" t="n">
         <v>-0.001143</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3725,66 +3549,60 @@
         <v>2.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S30" t="n">
-        <v>348406</v>
+        <v>0.739043</v>
       </c>
       <c r="T30" t="n">
-        <v>0.739043</v>
+        <v>-0.243155</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.243155</v>
+        <v>-2.412259</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="X30" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.683537</v>
+        <v>-3.457004</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.457004</v>
+        <v>3.851383</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.851383</v>
+        <v>-0.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF30" t="n">
         <v>-0.001678</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3838,66 +3656,60 @@
         <v>2.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S31" t="n">
-        <v>355034</v>
+        <v>1.06955</v>
       </c>
       <c r="T31" t="n">
-        <v>1.06955</v>
+        <v>-0.000138</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000138</v>
+        <v>-1.908621</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="X31" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.621114</v>
+        <v>-3.178284</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.178284</v>
+        <v>3.706988</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.706988</v>
+        <v>-0.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF31" t="n">
         <v>-0.001064</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3951,66 +3763,60 @@
         <v>2.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S32" t="n">
-        <v>355066</v>
+        <v>-0.194024</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.194024</v>
+        <v>-2.349549</v>
       </c>
       <c r="U32" t="n">
-        <v>-2.349549</v>
+        <v>2.317559</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="W32" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.506637</v>
+        <v>-3.31355</v>
       </c>
       <c r="AC32" t="n">
-        <v>-3.31355</v>
+        <v>3.820543</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.820543</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF32" t="n">
         <v>-0.000798</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -4064,66 +3870,60 @@
         <v>2.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S33" t="n">
-        <v>352705</v>
+        <v>0.14777</v>
       </c>
       <c r="T33" t="n">
-        <v>0.14777</v>
+        <v>2.878185</v>
       </c>
       <c r="U33" t="n">
-        <v>2.878185</v>
+        <v>0.601595</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="W33" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="X33" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.496274</v>
+        <v>-3.758575</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.758575</v>
+        <v>3.861754</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.861754</v>
+        <v>-0.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF33" t="n">
         <v>-0.001782</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4177,66 +3977,60 @@
         <v>2.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S34" t="n">
-        <v>355008</v>
+        <v>0.081216</v>
       </c>
       <c r="T34" t="n">
-        <v>0.081216</v>
+        <v>7.260937</v>
       </c>
       <c r="U34" t="n">
-        <v>7.260937</v>
+        <v>0.258865</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="W34" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="X34" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925596</v>
+        <v>-4.25878</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4.25878</v>
+        <v>3.397348</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.397348</v>
+        <v>-0.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF34" t="n">
         <v>-0.000537</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4290,66 +4084,60 @@
         <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S35" t="n">
-        <v>351599</v>
+        <v>0.236126</v>
       </c>
       <c r="T35" t="n">
-        <v>0.236126</v>
+        <v>-0.285629</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.285629</v>
+        <v>3.514671</v>
       </c>
       <c r="V35" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="W35" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="X35" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.688016</v>
+        <v>-3.040871</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.040871</v>
+        <v>3.232784</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.232784</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF35" t="n">
         <v>-0.001252</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4403,66 +4191,60 @@
         <v>2.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S36" t="n">
-        <v>355560</v>
+        <v>0.664278</v>
       </c>
       <c r="T36" t="n">
-        <v>0.664278</v>
+        <v>-4.15681</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.15681</v>
+        <v>1.349627</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="W36" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="X36" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.925952</v>
+        <v>-0.344269</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.344269</v>
+        <v>3.335647</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.335647</v>
+        <v>-0.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF36" t="n">
         <v>-0.000684</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4516,66 +4298,60 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S37" t="n">
-        <v>357827</v>
+        <v>0.864098</v>
       </c>
       <c r="T37" t="n">
-        <v>0.864098</v>
+        <v>1.103268</v>
       </c>
       <c r="U37" t="n">
-        <v>1.103268</v>
+        <v>6.053495</v>
       </c>
       <c r="V37" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="W37" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="X37" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.227578</v>
+        <v>2.440035</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.440035</v>
+        <v>3.697684</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.697684</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF37" t="n">
         <v>-0.000214</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4629,46 +4405,46 @@
         <v>2.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S38" t="n">
-        <v>363282</v>
+        <v>0.35244</v>
       </c>
       <c r="T38" t="n">
-        <v>0.35244</v>
+        <v>5.331331</v>
       </c>
       <c r="U38" t="n">
-        <v>5.331331</v>
+        <v>1.856482</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="W38" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="X38" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.498245</v>
+        <v>3.812368</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.812368</v>
+        <v>4.060953</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -4677,18 +4453,12 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4742,46 +4512,46 @@
         <v>2.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S39" t="n">
-        <v>369214</v>
+        <v>0.171599</v>
       </c>
       <c r="T39" t="n">
-        <v>0.171599</v>
+        <v>-1.299435</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.299435</v>
+        <v>-0.104202</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="X39" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.237599</v>
+        <v>4.259387</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.259387</v>
+        <v>3.707852</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -4790,18 +4560,12 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH39" t="n">
         <v>0.03</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4855,66 +4619,60 @@
         <v>2.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S40" t="n">
-        <v>372016</v>
+        <v>0.80633</v>
       </c>
       <c r="T40" t="n">
-        <v>0.80633</v>
+        <v>-2.710366</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.710366</v>
+        <v>-3.679149</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="X40" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.42474</v>
+        <v>4.519075</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.519075</v>
+        <v>4.091149</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.091149</v>
+        <v>0.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF40" t="n">
         <v>0.000342</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4968,66 +4726,60 @@
         <v>2.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S41" t="n">
-        <v>366096</v>
+        <v>0.192241</v>
       </c>
       <c r="T41" t="n">
-        <v>0.192241</v>
+        <v>1.966032</v>
       </c>
       <c r="U41" t="n">
-        <v>1.966032</v>
+        <v>6.053487</v>
       </c>
       <c r="V41" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="W41" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.758099</v>
+        <v>5.579866</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.579866</v>
+        <v>4.600584</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.600584</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF41" t="n">
         <v>0.000556</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5081,66 +4833,60 @@
         <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S42" t="n">
-        <v>363003</v>
+        <v>-0.221546</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.221546</v>
+        <v>-3.385643</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.385643</v>
+        <v>4.769899</v>
       </c>
       <c r="V42" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="W42" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="X42" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.873011</v>
+        <v>6.325086</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.325086</v>
+        <v>4.840925</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.840925</v>
+        <v>0.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF42" t="n">
         <v>0.001412</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -5194,66 +4940,60 @@
         <v>2.21</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S43" t="n">
-        <v>329730</v>
+        <v>-0.76507</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.76507</v>
+        <v>-1.261045</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.261045</v>
+        <v>2.292888</v>
       </c>
       <c r="V43" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="W43" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="X43" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="AA43" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.831296</v>
+        <v>6.536174</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.536174</v>
+        <v>4.767938</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.767938</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF43" t="n">
         <v>0.002578</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5307,66 +5047,60 @@
         <v>2.43</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S44" t="n">
-        <v>328303</v>
+        <v>1.000655</v>
       </c>
       <c r="T44" t="n">
-        <v>1.000655</v>
+        <v>-1.374453</v>
       </c>
       <c r="U44" t="n">
-        <v>-1.374453</v>
+        <v>-5.8492</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="W44" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="X44" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.559874</v>
+        <v>6.749097</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.749097</v>
+        <v>4.174145</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.174145</v>
+        <v>1</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF44" t="n">
         <v>0.001675</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5420,66 +5154,60 @@
         <v>2.52</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S45" t="n">
-        <v>332508</v>
+        <v>0.491628</v>
       </c>
       <c r="T45" t="n">
-        <v>0.491628</v>
+        <v>4.086263</v>
       </c>
       <c r="U45" t="n">
-        <v>4.086263</v>
+        <v>0.320749</v>
       </c>
       <c r="V45" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="W45" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.05763</v>
+        <v>8.444549</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.444549</v>
+        <v>4.866504</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.866504</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF45" t="n">
         <v>0.003204</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5533,66 +5261,60 @@
         <v>2.49</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S46" t="n">
-        <v>336157</v>
+        <v>1.341273</v>
       </c>
       <c r="T46" t="n">
-        <v>1.341273</v>
+        <v>6.727909</v>
       </c>
       <c r="U46" t="n">
-        <v>6.727909</v>
+        <v>-1.822596</v>
       </c>
       <c r="V46" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="X46" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.47719</v>
+        <v>8.586193</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.586193</v>
+        <v>5.201441</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201441</v>
+        <v>1</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF46" t="n">
         <v>0.001471</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5646,66 +5368,60 @@
         <v>2.72</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S47" t="n">
-        <v>340789</v>
+        <v>-0.131764</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.131764</v>
+        <v>-1.249299</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.249299</v>
+        <v>-1.417575</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="X47" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.529729</v>
+        <v>8.510418</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.510418</v>
+        <v>5.316736</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.316736</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF47" t="n">
         <v>0.002023</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH47" t="n">
         <v>0.23</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5759,66 +5475,60 @@
         <v>2.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S48" t="n">
-        <v>341459</v>
+        <v>-0.883188</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.883188</v>
+        <v>-3.583696</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.583696</v>
+        <v>0.84617</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="W48" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="X48" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.319636</v>
+        <v>7.026183</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.026183</v>
+        <v>5.201418</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.201418</v>
+        <v>0.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF48" t="n">
         <v>0.001405</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5872,66 +5582,60 @@
         <v>2.67</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S49" t="n">
-        <v>344440</v>
+        <v>-0.208448</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.208448</v>
+        <v>-1.100964</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.100964</v>
+        <v>-4.407308</v>
       </c>
       <c r="V49" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="W49" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.351165</v>
+        <v>4.393261</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.393261</v>
+        <v>5.18043</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.18043</v>
+        <v>0.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF49" t="n">
         <v>0.000633</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5985,66 +5689,60 @@
         <v>2.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="R50" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="S50" t="n">
-        <v>345111</v>
+        <v>-0.410362</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.410362</v>
+        <v>5.358126</v>
       </c>
       <c r="U50" t="n">
-        <v>5.358126</v>
+        <v>2.657089</v>
       </c>
       <c r="V50" t="n">
-        <v>2.657089</v>
+        <v>2.657381</v>
       </c>
       <c r="W50" t="n">
-        <v>2.657381</v>
+        <v>0.440744</v>
       </c>
       <c r="X50" t="n">
-        <v>0.440744</v>
+        <v>-0.129254</v>
       </c>
       <c r="Y50" t="n">
-        <v>-0.129254</v>
+        <v>0.79014</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.79014</v>
+        <v>0.194809</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.194809</v>
+        <v>5.225222</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.225222</v>
+        <v>2.961368</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.961368</v>
+        <v>5.127976</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.127976</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="AF50" t="n">
         <v>0.000562</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -6098,46 +5796,46 @@
         <v>2.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S51" t="n">
-        <v>350767</v>
+        <v>0.393384</v>
       </c>
       <c r="T51" t="n">
-        <v>0.393384</v>
+        <v>-2.419208</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.419208</v>
+        <v>-3.136324</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="X51" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.130501</v>
+        <v>3.033233</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.033233</v>
+        <v>5.054283</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6146,18 +5844,12 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6211,46 +5903,46 @@
         <v>2.77</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S52" t="n">
-        <v>356582</v>
+        <v>-0.070866</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.070866</v>
+        <v>-0.816658</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.816658</v>
+        <v>-1.986584</v>
       </c>
       <c r="V52" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="X52" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.172369</v>
+        <v>2.828436</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.828436</v>
+        <v>5.096104</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -6259,18 +5951,12 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6324,46 +6010,46 @@
         <v>2.82</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S53" t="n">
-        <v>357103</v>
+        <v>0.02339</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02339</v>
+        <v>0.539717</v>
       </c>
       <c r="U53" t="n">
-        <v>0.539717</v>
+        <v>1.235287</v>
       </c>
       <c r="V53" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="W53" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="X53" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.680811</v>
+        <v>0.924206</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.924206</v>
+        <v>4.490243</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -6372,18 +6058,12 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6437,66 +6117,60 @@
         <v>2.74</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="R54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="S54" t="n">
-        <v>360578</v>
+        <v>0.470751</v>
       </c>
       <c r="T54" t="n">
-        <v>0.470751</v>
+        <v>-3.155924</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.155924</v>
+        <v>-0.937912</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.938017</v>
+        <v>1.146567</v>
       </c>
       <c r="X54" t="n">
-        <v>1.146567</v>
+        <v>0.715383</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.715383</v>
+        <v>1.405488</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.405488</v>
+        <v>0.973109</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.461836</v>
+        <v>-0.101973</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.101973</v>
+        <v>4.177803</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.177803</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF54" t="n">
         <v>-0</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6550,46 +6224,46 @@
         <v>2.68</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="R55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="S55" t="n">
-        <v>358234</v>
+        <v>-0.026441</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.026441</v>
+        <v>0.550798</v>
       </c>
       <c r="U55" t="n">
-        <v>0.550798</v>
+        <v>3.160973</v>
       </c>
       <c r="V55" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="W55" t="n">
-        <v>3.161329</v>
+        <v>1.90144</v>
       </c>
       <c r="X55" t="n">
-        <v>1.90144</v>
+        <v>3.24641</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.24641</v>
+        <v>1.099346</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.099346</v>
+        <v>-0.650067</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.264385</v>
+        <v>-1.042167</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.042167</v>
+        <v>3.897866</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -6598,18 +6272,12 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6663,46 +6331,46 @@
         <v>2.87</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="S56" t="n">
-        <v>364367</v>
+        <v>0.755789</v>
       </c>
       <c r="T56" t="n">
-        <v>0.755789</v>
+        <v>-3.241421</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.241421</v>
+        <v>-4.94875</v>
       </c>
       <c r="V56" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.949289</v>
+        <v>-0.083179</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.083179</v>
+        <v>-1.743482</v>
       </c>
       <c r="Y56" t="n">
-        <v>-1.743482</v>
+        <v>0.927966</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.927966</v>
+        <v>1.712009</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.441351</v>
+        <v>-0.903999</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.903999</v>
+        <v>4.303068</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -6711,18 +6379,12 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6776,46 +6438,46 @@
         <v>3.07</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="R57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="S57" t="n">
-        <v>371074</v>
+        <v>0.625412</v>
       </c>
       <c r="T57" t="n">
-        <v>0.625412</v>
+        <v>2.812663</v>
       </c>
       <c r="U57" t="n">
-        <v>2.812663</v>
+        <v>-1.54108</v>
       </c>
       <c r="V57" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.541256</v>
+        <v>0.371461</v>
       </c>
       <c r="X57" t="n">
-        <v>0.371461</v>
+        <v>0.070797</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.070797</v>
+        <v>0.549722</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.549722</v>
+        <v>1.840727</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="AB57" t="n">
-        <v>3.812497</v>
+        <v>-2.659212</v>
       </c>
       <c r="AC57" t="n">
-        <v>-2.659212</v>
+        <v>3.357475</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -6824,18 +6486,12 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6889,66 +6545,60 @@
         <v>3.04</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="R58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="S58" t="n">
-        <v>362002</v>
+        <v>-0.180258</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.180258</v>
+        <v>10.500625</v>
       </c>
       <c r="U58" t="n">
-        <v>10.500625</v>
+        <v>1.357413</v>
       </c>
       <c r="V58" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="W58" t="n">
-        <v>1.357572</v>
+        <v>1.12824</v>
       </c>
       <c r="X58" t="n">
-        <v>1.12824</v>
+        <v>1.133877</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.133877</v>
+        <v>1.124914</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.124914</v>
+        <v>-2.444795</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.142847</v>
+        <v>-1.819225</v>
       </c>
       <c r="AC58" t="n">
-        <v>-1.819225</v>
+        <v>3.768807</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.768807</v>
+        <v>-0.25</v>
       </c>
       <c r="AE58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF58" t="n">
         <v>-0.000354</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -7002,66 +6652,60 @@
         <v>3.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="R59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="S59" t="n">
-        <v>366913</v>
+        <v>0.511964</v>
       </c>
       <c r="T59" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.561276</v>
+        <v>-4.421964</v>
       </c>
       <c r="V59" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="W59" t="n">
-        <v>-4.422473</v>
+        <v>0.288267</v>
       </c>
       <c r="X59" t="n">
-        <v>0.288267</v>
+        <v>-0.052977</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.052977</v>
+        <v>0.489642</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.489642</v>
+        <v>1.356622</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.39172</v>
+        <v>0.619623</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.619623</v>
+        <v>4.109608</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.109608</v>
+        <v>-0.25</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF59" t="n">
         <v>-0.000554</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -7111,62 +6755,56 @@
         <v>3.24</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="R60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="S60" t="n">
         <v>371137</v>
       </c>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>1.369122</v>
+      </c>
       <c r="V60" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="W60" t="n">
-        <v>1.369286</v>
+        <v>0.565068</v>
       </c>
       <c r="X60" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.461065</v>
+        <v>1.151227</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.724907</v>
+        <v>1.964454</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.964454</v>
+        <v>4.420848</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.420848</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -7206,46 +6844,44 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>367558</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="V61" t="n">
-        <v>2.367063</v>
-      </c>
-      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="AA61" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="AC61" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="AD61" t="n">
-        <v>4.327084</v>
+        <v>-0.25</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7266,10 +6902,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0742</v>
+        <v>5.0727</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0736</v>
+        <v>5.0721</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7280,33 +6916,31 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-2.007109</v>
+      </c>
       <c r="V62" t="n">
-        <v>-1.978132</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-1.978362</v>
-      </c>
+        <v>-2.007342</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,105 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -647,12 +657,14 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R2" t="n">
         <v>20.26</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>355671</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -720,54 +734,60 @@
         <v>1.56</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R3" t="n">
         <v>20.92</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>370395</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.631159</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.641498</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.003276</v>
       </c>
       <c r="AF3" t="n">
         <v>0.003276</v>
       </c>
       <c r="AG3" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -821,54 +841,60 @@
         <v>1.43</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R4" t="n">
         <v>21.42</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>368886</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>-0.055529</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>-2.109407</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.001591</v>
       </c>
       <c r="AF4" t="n">
         <v>0.001591</v>
       </c>
       <c r="AG4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="AH4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -922,54 +948,60 @@
         <v>1.43</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R5" t="n">
         <v>22.89</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>367927</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.53429</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>-0.58875</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.00324</v>
       </c>
       <c r="AF5" t="n">
         <v>0.00324</v>
       </c>
       <c r="AG5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
       <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1023,54 +1055,60 @@
         <v>1.46</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R6" t="n">
         <v>23.91</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>367772</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1.599501</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.372425</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>0.005012</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0.005012</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.03</v>
+        <v>0.005012</v>
       </c>
       <c r="AH6" t="n">
         <v>0.03</v>
       </c>
       <c r="AI6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1124,54 +1162,60 @@
         <v>1.4</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R7" t="n">
         <v>24.21</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>362204</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.250195</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.49538</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="n">
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.00406</v>
       </c>
       <c r="AF7" t="n">
         <v>0.00406</v>
       </c>
       <c r="AG7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="AH7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1225,54 +1269,60 @@
         <v>1.46</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R8" t="n">
         <v>25.23</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>358398</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-1.889415</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>-7.693212</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>0.001433</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0.001433</v>
       </c>
       <c r="AG8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0.16</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>0.06</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1326,54 +1376,60 @@
         <v>1.44</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R9" t="n">
         <v>25.63</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>357740</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>0.982105</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>4.32272</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.004849</v>
       </c>
       <c r="AF9" t="n">
         <v>0.004849</v>
       </c>
       <c r="AG9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1427,54 +1483,60 @@
         <v>1.55</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R10" t="n">
         <v>26.54</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>353169</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1.194746</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>9.292268999999999</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="n">
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.002356</v>
       </c>
       <c r="AF10" t="n">
         <v>0.002356</v>
       </c>
       <c r="AG10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1528,54 +1590,60 @@
         <v>1.57</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R11" t="n">
         <v>27.46</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>345097</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>0.004178</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-4.113018</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>0.001785</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0.001785</v>
       </c>
       <c r="AG11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1629,54 +1697,60 @@
         <v>1.57</v>
       </c>
       <c r="Q12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R12" t="n">
         <v>27.42</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346415</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0.112442</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-0.479114</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
         <v>1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.003057</v>
       </c>
       <c r="AF12" t="n">
         <v>0.003057</v>
       </c>
       <c r="AG12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
       <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1730,60 +1804,66 @@
         <v>1.52</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R13" t="n">
         <v>27.88</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>341958</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.156589</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-0.436337</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.00132</v>
       </c>
       <c r="AF13" t="n">
         <v>0.00132</v>
       </c>
       <c r="AG13" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="AH13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1837,60 +1917,66 @@
         <v>1.6</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R14" t="n">
         <v>29.24</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>346403</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.9075</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>4.677002</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0.0009210000000000001</v>
       </c>
       <c r="AG14" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
         <v>0.08</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1944,60 +2030,66 @@
         <v>1.62</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R15" t="n">
         <v>28.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>339664</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-0.307887</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>0.536686</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.001523</v>
       </c>
       <c r="AF15" t="n">
         <v>0.001523</v>
       </c>
       <c r="AG15" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AI15" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2051,60 +2143,66 @@
         <v>1.65</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R16" t="n">
         <v>28.57</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>327580</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0.051214</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-3.18585</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
-        <v>0.000228</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0.000228</v>
       </c>
       <c r="AG16" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2158,47 +2256,47 @@
         <v>1.77</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="R17" t="n">
         <v>29.68</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>325546</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0.283274</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-1.093446</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
@@ -2206,12 +2304,18 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0.12</v>
       </c>
       <c r="AI17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2265,47 +2369,47 @@
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R18" t="n">
         <v>30.52</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331505</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.725155</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-0.925949</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
@@ -2313,12 +2417,18 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2372,60 +2482,66 @@
         <v>1.8</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="R19" t="n">
         <v>29.64</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>324703</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-0.249038</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>0.821323</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
         <v>-0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2479,47 +2595,47 @@
         <v>1.94</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="R20" t="n">
         <v>30.54</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>331122</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-0.342048</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-4.871671</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
@@ -2527,12 +2643,18 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0.17</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2586,47 +2708,47 @@
         <v>2.17</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R21" t="n">
         <v>30.48</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>328098</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>2.881581</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>3.737316</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
@@ -2634,12 +2756,18 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AI21" t="n">
         <v>0.23</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2693,47 +2821,47 @@
         <v>2.2</v>
       </c>
       <c r="Q22" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="R22" t="n">
         <v>30.99</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>341158</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>0.100866</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>12.127661</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
@@ -2741,12 +2869,18 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2800,47 +2934,47 @@
         <v>2.45</v>
       </c>
       <c r="Q23" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R23" t="n">
         <v>31.62</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>345725</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1.051427</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-5.945456</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
@@ -2848,12 +2982,18 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.19</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2907,60 +3047,66 @@
         <v>2.58</v>
       </c>
       <c r="Q24" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R24" t="n">
         <v>31.63</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>343489</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-1.655253</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-1.271212</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>-0</v>
       </c>
       <c r="AG24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3014,47 +3160,47 @@
         <v>2.63</v>
       </c>
       <c r="Q25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R25" t="n">
         <v>30.85</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>343620</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.06297</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-0.424293</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
@@ -3062,12 +3208,18 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3121,47 +3273,47 @@
         <v>2.73</v>
       </c>
       <c r="Q26" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R26" t="n">
         <v>30.43</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>345476</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.458481</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>2.993707</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
@@ -3169,12 +3321,18 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3228,60 +3386,66 @@
         <v>2.82</v>
       </c>
       <c r="Q27" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="R27" t="n">
         <v>29.92</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>344177</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-0.374379</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.680131</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>-0.001599</v>
       </c>
       <c r="AF27" t="n">
         <v>-0.001599</v>
       </c>
       <c r="AG27" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="AH27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3335,60 +3499,66 @@
         <v>2.82</v>
       </c>
       <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
         <v>29.66</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>340324</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.012734</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-4.055314</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>-0.000768</v>
       </c>
       <c r="AF28" t="n">
         <v>-0.000768</v>
       </c>
       <c r="AG28" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="AH28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
       <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3442,60 +3612,66 @@
         <v>2.92</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="R29" t="n">
         <v>29.24</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>340247</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>0.313403</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.169608</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
       <c r="AE29" t="n">
-        <v>-0.001143</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>-0.001143</v>
       </c>
       <c r="AG29" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3549,60 +3725,66 @@
         <v>2.99</v>
       </c>
       <c r="Q30" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R30" t="n">
         <v>29.01</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>348406</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>0.739043</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-0.243155</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>-0.001678</v>
       </c>
       <c r="AF30" t="n">
         <v>-0.001678</v>
       </c>
       <c r="AG30" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="AH30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3656,60 +3838,66 @@
         <v>2.59</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
         <v>28.14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>355034</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1.06955</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>-0.000138</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>-0.001064</v>
       </c>
       <c r="AF31" t="n">
         <v>-0.001064</v>
       </c>
       <c r="AG31" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="AH31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3763,60 +3951,66 @@
         <v>2.77</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R32" t="n">
         <v>28</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355066</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-0.194024</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-2.349549</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
       <c r="AE32" t="n">
-        <v>-0.000798</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>-0.000798</v>
       </c>
       <c r="AG32" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AI32" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3870,60 +4064,66 @@
         <v>2.76</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R33" t="n">
         <v>27.85</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>352705</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>0.14777</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>2.878185</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>-0.001782</v>
       </c>
       <c r="AF33" t="n">
         <v>-0.001782</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>-0.001782</v>
       </c>
       <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3977,60 +4177,66 @@
         <v>2.71</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R34" t="n">
         <v>28.14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355008</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>0.081216</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>7.260937</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>-0.000537</v>
       </c>
       <c r="AF34" t="n">
         <v>-0.000537</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.05</v>
+        <v>-0.000537</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4084,60 +4290,66 @@
         <v>2.76</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R35" t="n">
         <v>27.86</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>351599</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.236126</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>-0.285629</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
       <c r="AE35" t="n">
-        <v>-0.001252</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>-0.001252</v>
       </c>
       <c r="AG35" t="n">
+        <v>-0.001252</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4191,60 +4403,66 @@
         <v>2.8</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R36" t="n">
         <v>27.75</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>355560</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.664278</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>-4.15681</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Z36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AE36" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>-0.000684</v>
       </c>
       <c r="AF36" t="n">
         <v>-0.000684</v>
       </c>
       <c r="AG36" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AI36" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AJ36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4298,60 +4516,66 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R37" t="n">
         <v>27.81</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>357827</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.864098</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>1.103268</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Z37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
-        <v>-0.000214</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>-0.000214</v>
       </c>
       <c r="AG37" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="AH37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AI37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AJ37" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4405,47 +4629,47 @@
         <v>2.52</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R38" t="n">
         <v>27.74</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>363282</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.35244</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>5.331331</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
@@ -4453,12 +4677,18 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AI38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AJ38" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4512,47 +4742,47 @@
         <v>2.55</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R39" t="n">
         <v>27.59</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>369214</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.171599</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>-1.299435</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
@@ -4560,12 +4790,18 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
         <v>0.03</v>
       </c>
       <c r="AI39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4619,60 +4855,66 @@
         <v>2.56</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R40" t="n">
         <v>27.49</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>372016</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>0.80633</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-2.710366</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Z40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AB40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
         <v>0.25</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.000342</v>
       </c>
       <c r="AF40" t="n">
         <v>0.000342</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.01</v>
+        <v>0.000342</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4726,60 +4968,66 @@
         <v>2.52</v>
       </c>
       <c r="Q41" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="R41" t="n">
         <v>27.94</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>366096</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>0.192241</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>1.966032</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Y41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
       <c r="AE41" t="n">
-        <v>0.000556</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0.000556</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.04</v>
+        <v>0.000556</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4833,60 +5081,66 @@
         <v>2.5</v>
       </c>
       <c r="Q42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R42" t="n">
         <v>28.45</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>363003</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>-0.221546</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-3.385643</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Z42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AE42" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.001412</v>
       </c>
       <c r="AF42" t="n">
         <v>0.001412</v>
       </c>
       <c r="AG42" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="AH42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AI42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AJ42" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4940,60 +5194,66 @@
         <v>2.21</v>
       </c>
       <c r="Q43" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="R43" t="n">
         <v>28.5</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>329730</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>-0.76507</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>-1.261045</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Z43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
         <v>1</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0.002578</v>
       </c>
       <c r="AF43" t="n">
         <v>0.002578</v>
       </c>
       <c r="AG43" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="AH43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AI43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AJ43" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5047,60 +5307,66 @@
         <v>2.43</v>
       </c>
       <c r="Q44" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="R44" t="n">
         <v>29.88</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>328303</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1.000655</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>-1.374453</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Z44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0.001675</v>
       </c>
       <c r="AF44" t="n">
         <v>0.001675</v>
       </c>
       <c r="AG44" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="AH44" t="n">
         <v>0.26</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AI44" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AJ44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5154,60 +5420,66 @@
         <v>2.52</v>
       </c>
       <c r="Q45" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R45" t="n">
         <v>30.53</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>332508</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>0.491628</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>4.086263</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AD45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
       <c r="AE45" t="n">
-        <v>0.003204</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0.003204</v>
       </c>
       <c r="AG45" t="n">
+        <v>0.003204</v>
+      </c>
+      <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AI45" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5261,60 +5533,66 @@
         <v>2.49</v>
       </c>
       <c r="Q46" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R46" t="n">
         <v>31.34</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>336157</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>1.341273</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>6.727909</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AE46" t="n">
         <v>1</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.001471</v>
       </c>
       <c r="AF46" t="n">
         <v>0.001471</v>
       </c>
       <c r="AG46" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AI46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AJ46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5368,60 +5646,66 @@
         <v>2.72</v>
       </c>
       <c r="Q47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R47" t="n">
         <v>31.63</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>340789</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.131764</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.249299</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Z47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AD47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
       <c r="AE47" t="n">
-        <v>0.002023</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
         <v>0.002023</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.23</v>
+        <v>0.002023</v>
       </c>
       <c r="AH47" t="n">
         <v>0.23</v>
       </c>
       <c r="AI47" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5475,60 +5759,66 @@
         <v>2.67</v>
       </c>
       <c r="Q48" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="R48" t="n">
         <v>31.7</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>341459</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.883188</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>-3.583696</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AD48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0.001405</v>
       </c>
       <c r="AF48" t="n">
         <v>0.001405</v>
       </c>
       <c r="AG48" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="AH48" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AI48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AJ48" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5582,60 +5872,66 @@
         <v>2.67</v>
       </c>
       <c r="Q49" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="R49" t="n">
         <v>31.85</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>344440</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>-0.208448</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-1.100964</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AE49" t="n">
         <v>0.25</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0.000633</v>
       </c>
       <c r="AF49" t="n">
         <v>0.000633</v>
       </c>
       <c r="AG49" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
       <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5689,60 +5985,66 @@
         <v>2.79</v>
       </c>
       <c r="Q50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R50" t="n">
         <v>31.75</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>345111</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.410362</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>5.358126</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Z50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
       <c r="AE50" t="n">
-        <v>0.000562</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
         <v>0.000562</v>
       </c>
       <c r="AG50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AI50" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AJ50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5796,47 +6098,47 @@
         <v>2.85</v>
       </c>
       <c r="Q51" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R51" t="n">
         <v>31.87</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>350767</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.393384</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>-2.419208</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
@@ -5844,12 +6146,18 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AI51" t="n">
         <v>0.06</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5903,47 +6211,47 @@
         <v>2.77</v>
       </c>
       <c r="Q52" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R52" t="n">
         <v>31.47</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>356582</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>-0.070866</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-0.816658</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
@@ -5951,12 +6259,18 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AI52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AJ52" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6010,47 +6324,47 @@
         <v>2.82</v>
       </c>
       <c r="Q53" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="R53" t="n">
         <v>32.04</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>357103</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.02339</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.539717</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
@@ -6058,12 +6372,18 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AI53" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6117,60 +6437,66 @@
         <v>2.74</v>
       </c>
       <c r="Q54" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="R54" t="n">
         <v>32.32</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>360578</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.470751</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-3.155924</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Z54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
       <c r="AE54" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
         <v>-0</v>
       </c>
       <c r="AG54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AI54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AJ54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6224,47 +6550,47 @@
         <v>2.68</v>
       </c>
       <c r="Q55" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="R55" t="n">
         <v>31.99</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>358234</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>-0.026441</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>0.550798</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AD55" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
@@ -6272,12 +6598,18 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AI55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6331,47 +6663,47 @@
         <v>2.87</v>
       </c>
       <c r="Q56" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="R56" t="n">
         <v>32.6</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>364367</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>0.755789</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>-3.241421</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Z56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AD56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
@@ -6379,12 +6711,18 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AI56" t="n">
         <v>0.19</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AJ56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6438,47 +6776,47 @@
         <v>3.07</v>
       </c>
       <c r="Q57" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="R57" t="n">
         <v>32.78</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>371074</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.625412</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>2.812663</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AC57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AD57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
@@ -6486,12 +6824,18 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.19</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AI57" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AJ57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6545,60 +6889,66 @@
         <v>3.04</v>
       </c>
       <c r="Q58" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R58" t="n">
         <v>32.99</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>362002</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>-0.180258</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>10.500625</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AC58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AD58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AE58" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>-0.000354</v>
       </c>
       <c r="AF58" t="n">
         <v>-0.000354</v>
       </c>
       <c r="AG58" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="AH58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AJ58" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6652,60 +7002,66 @@
         <v>3.15</v>
       </c>
       <c r="Q59" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="R59" t="n">
         <v>33.51</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>366913</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>0.511964</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>-3.561276</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AB59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AC59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AD59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>-0.000554</v>
       </c>
       <c r="AF59" t="n">
         <v>-0.000554</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.11</v>
+        <v>-0.000554</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6755,56 +7111,62 @@
         <v>3.24</v>
       </c>
       <c r="Q60" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="R60" t="n">
         <v>33.42</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>371137</v>
       </c>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Z60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AB60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AC60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AD60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
       <c r="AE60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
       <c r="AG60" t="n">
+        <v>-0.0008229999999999999</v>
+      </c>
+      <c r="AH60" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AI60" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AJ60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -6844,44 +7206,46 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>367558</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="n">
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AB61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AC61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AD61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>-0.000372</v>
       </c>
       <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="inlineStr"/>
+      <c r="AG61" t="n">
+        <v>-0.000372</v>
+      </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6916,31 +7280,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
         <v>-2.007109</v>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>-2.007342</v>
       </c>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="n">
-        <v>-0.000497</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AG62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7266,10 +7266,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0727</v>
+        <v>5.0975</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0721</v>
+        <v>5.0969</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7282,10 +7282,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-2.007109</v>
+        <v>-1.52803</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.007342</v>
+        <v>-1.528207</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -630,10 +630,10 @@
         <v>1.02</v>
       </c>
       <c r="H2" t="n">
-        <v>96.42256999999999</v>
+        <v>96.31464</v>
       </c>
       <c r="I2" t="n">
-        <v>99.83515</v>
+        <v>99.83978</v>
       </c>
       <c r="J2" t="n">
         <v>5.1216</v>
@@ -707,10 +707,10 @@
         <v>0.88</v>
       </c>
       <c r="H3" t="n">
-        <v>97.03115</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>99.19471</v>
+        <v>99.32829</v>
       </c>
       <c r="J3" t="n">
         <v>5.1433</v>
@@ -743,10 +743,10 @@
         <v>370395</v>
       </c>
       <c r="T3" t="n">
-        <v>0.631159</v>
+        <v>0.79016</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.641498</v>
+        <v>-0.512311</v>
       </c>
       <c r="V3" t="n">
         <v>0.423696</v>
@@ -814,10 +814,10 @@
         <v>1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>96.97727</v>
+        <v>96.95968999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>97.10229</v>
+        <v>97.24746</v>
       </c>
       <c r="J4" t="n">
         <v>5.4394</v>
@@ -850,10 +850,10 @@
         <v>368886</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.055529</v>
+        <v>-0.119484</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.109407</v>
+        <v>-2.094902</v>
       </c>
       <c r="V4" t="n">
         <v>5.757004</v>
@@ -921,10 +921,10 @@
         <v>1.16</v>
       </c>
       <c r="H5" t="n">
-        <v>97.49541000000001</v>
+        <v>97.48142</v>
       </c>
       <c r="I5" t="n">
-        <v>96.53060000000001</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="J5" t="n">
         <v>5.643</v>
@@ -957,10 +957,10 @@
         <v>367927</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53429</v>
+        <v>0.53809</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.58875</v>
+        <v>-0.644377</v>
       </c>
       <c r="V5" t="n">
         <v>3.74306</v>
@@ -1028,10 +1028,10 @@
         <v>0.84</v>
       </c>
       <c r="H6" t="n">
-        <v>99.05485</v>
+        <v>98.97262000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>97.85541000000001</v>
+        <v>98.05768</v>
       </c>
       <c r="J6" t="n">
         <v>5.6199</v>
@@ -1064,10 +1064,10 @@
         <v>367772</v>
       </c>
       <c r="T6" t="n">
-        <v>1.599501</v>
+        <v>1.529727</v>
       </c>
       <c r="U6" t="n">
-        <v>1.372425</v>
+        <v>1.487112</v>
       </c>
       <c r="V6" t="n">
         <v>-0.409357</v>
@@ -1135,10 +1135,10 @@
         <v>0.73</v>
       </c>
       <c r="H7" t="n">
-        <v>99.30268</v>
+        <v>99.35339</v>
       </c>
       <c r="I7" t="n">
-        <v>99.31872</v>
+        <v>99.33126</v>
       </c>
       <c r="J7" t="n">
         <v>5.5805</v>
@@ -1171,10 +1171,10 @@
         <v>362204</v>
       </c>
       <c r="T7" t="n">
-        <v>0.250195</v>
+        <v>0.384723</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49538</v>
+        <v>1.298807</v>
       </c>
       <c r="V7" t="n">
         <v>-0.70108</v>
@@ -1242,10 +1242,10 @@
         <v>0.67</v>
       </c>
       <c r="H8" t="n">
-        <v>97.42644</v>
+        <v>97.34401</v>
       </c>
       <c r="I8" t="n">
-        <v>91.67792</v>
+        <v>90.45032</v>
       </c>
       <c r="J8" t="n">
         <v>5.3574</v>
@@ -1278,10 +1278,10 @@
         <v>358398</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.889415</v>
+        <v>-2.022457</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.693212</v>
+        <v>-8.94073</v>
       </c>
       <c r="V8" t="n">
         <v>-3.99785</v>
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>98.38327</v>
+        <v>98.43725000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>95.6409</v>
+        <v>95.72214</v>
       </c>
       <c r="J9" t="n">
         <v>5.1394</v>
@@ -1385,10 +1385,10 @@
         <v>357740</v>
       </c>
       <c r="T9" t="n">
-        <v>0.982105</v>
+        <v>1.123069</v>
       </c>
       <c r="U9" t="n">
-        <v>4.32272</v>
+        <v>5.828415</v>
       </c>
       <c r="V9" t="n">
         <v>-4.069138</v>
@@ -1456,10 +1456,10 @@
         <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>99.5587</v>
+        <v>99.55981</v>
       </c>
       <c r="I10" t="n">
-        <v>104.52811</v>
+        <v>104.61484</v>
       </c>
       <c r="J10" t="n">
         <v>4.7378</v>
@@ -1492,10 +1492,10 @@
         <v>353169</v>
       </c>
       <c r="T10" t="n">
-        <v>1.194746</v>
+        <v>1.140381</v>
       </c>
       <c r="U10" t="n">
-        <v>9.292268999999999</v>
+        <v>9.290118</v>
       </c>
       <c r="V10" t="n">
         <v>-7.814142</v>
@@ -1563,10 +1563,10 @@
         <v>1.04</v>
       </c>
       <c r="H11" t="n">
-        <v>99.56286</v>
+        <v>99.51646</v>
       </c>
       <c r="I11" t="n">
-        <v>100.22885</v>
+        <v>100.42352</v>
       </c>
       <c r="J11" t="n">
         <v>4.9191</v>
@@ -1599,10 +1599,10 @@
         <v>345097</v>
       </c>
       <c r="T11" t="n">
-        <v>0.004178</v>
+        <v>-0.043542</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.113018</v>
+        <v>-4.00643</v>
       </c>
       <c r="V11" t="n">
         <v>3.826671</v>
@@ -1670,10 +1670,10 @@
         <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>99.67480999999999</v>
+        <v>99.67415</v>
       </c>
       <c r="I12" t="n">
-        <v>99.74863999999999</v>
+        <v>99.79777</v>
       </c>
       <c r="J12" t="n">
         <v>4.7289</v>
@@ -1706,10 +1706,10 @@
         <v>346415</v>
       </c>
       <c r="T12" t="n">
-        <v>0.112442</v>
+        <v>0.158456</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.479114</v>
+        <v>-0.623111</v>
       </c>
       <c r="V12" t="n">
         <v>-3.866561</v>
@@ -1777,10 +1777,10 @@
         <v>0.62</v>
       </c>
       <c r="H13" t="n">
-        <v>99.51873000000001</v>
+        <v>99.6343</v>
       </c>
       <c r="I13" t="n">
-        <v>99.3134</v>
+        <v>99.53784</v>
       </c>
       <c r="J13" t="n">
         <v>5.238</v>
@@ -1813,10 +1813,10 @@
         <v>341958</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.156589</v>
+        <v>-0.03998</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.436337</v>
+        <v>-0.260457</v>
       </c>
       <c r="V13" t="n">
         <v>10.765717</v>
@@ -1890,10 +1890,10 @@
         <v>-0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>101.41705</v>
+        <v>101.27684</v>
       </c>
       <c r="I14" t="n">
-        <v>103.95829</v>
+        <v>103.95861</v>
       </c>
       <c r="J14" t="n">
         <v>5.1884</v>
@@ -1926,10 +1926,10 @@
         <v>346403</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9075</v>
+        <v>1.648569</v>
       </c>
       <c r="U14" t="n">
-        <v>4.677002</v>
+        <v>4.441296</v>
       </c>
       <c r="V14" t="n">
         <v>-0.946926</v>
@@ -2003,10 +2003,10 @@
         <v>-0.31</v>
       </c>
       <c r="H15" t="n">
-        <v>101.1048</v>
+        <v>101.07328</v>
       </c>
       <c r="I15" t="n">
-        <v>104.51622</v>
+        <v>104.56278</v>
       </c>
       <c r="J15" t="n">
         <v>5.179</v>
@@ -2039,10 +2039,10 @@
         <v>339664</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.307887</v>
+        <v>-0.200994</v>
       </c>
       <c r="U15" t="n">
-        <v>0.536686</v>
+        <v>0.581164</v>
       </c>
       <c r="V15" t="n">
         <v>-0.181173</v>
@@ -2116,10 +2116,10 @@
         <v>-0.32</v>
       </c>
       <c r="H16" t="n">
-        <v>101.15658</v>
+        <v>101.17973</v>
       </c>
       <c r="I16" t="n">
-        <v>101.18649</v>
+        <v>101.38087</v>
       </c>
       <c r="J16" t="n">
         <v>5.4066</v>
@@ -2152,10 +2152,10 @@
         <v>327580</v>
       </c>
       <c r="T16" t="n">
-        <v>0.051214</v>
+        <v>0.10532</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.18585</v>
+        <v>-3.043062</v>
       </c>
       <c r="V16" t="n">
         <v>4.394671</v>
@@ -2229,10 +2229,10 @@
         <v>0.47</v>
       </c>
       <c r="H17" t="n">
-        <v>101.44313</v>
+        <v>101.46342</v>
       </c>
       <c r="I17" t="n">
-        <v>100.08007</v>
+        <v>100.20398</v>
       </c>
       <c r="J17" t="n">
         <v>5.257</v>
@@ -2265,10 +2265,10 @@
         <v>325546</v>
       </c>
       <c r="T17" t="n">
-        <v>0.283274</v>
+        <v>0.280382</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.093446</v>
+        <v>-1.16086</v>
       </c>
       <c r="V17" t="n">
         <v>-2.766988</v>
@@ -2342,10 +2342,10 @@
         <v>0.38</v>
       </c>
       <c r="H18" t="n">
-        <v>100.70751</v>
+        <v>100.66227</v>
       </c>
       <c r="I18" t="n">
-        <v>99.15338</v>
+        <v>99.36927</v>
       </c>
       <c r="J18" t="n">
         <v>5.2941</v>
@@ -2378,10 +2378,10 @@
         <v>331505</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.725155</v>
+        <v>-0.789595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.925949</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.705726</v>
@@ -2455,10 +2455,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>100.45671</v>
+        <v>100.58196</v>
       </c>
       <c r="I19" t="n">
-        <v>99.96775</v>
+        <v>99.97806</v>
       </c>
       <c r="J19" t="n">
         <v>5.2177</v>
@@ -2491,10 +2491,10 @@
         <v>324703</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.249038</v>
+        <v>-0.07978200000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.821323</v>
+        <v>0.612654</v>
       </c>
       <c r="V19" t="n">
         <v>-1.443116</v>
@@ -2568,10 +2568,10 @@
         <v>0.46</v>
       </c>
       <c r="H20" t="n">
-        <v>100.1131</v>
+        <v>100.05178</v>
       </c>
       <c r="I20" t="n">
-        <v>95.09765</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="J20" t="n">
         <v>5.0993</v>
@@ -2604,10 +2604,10 @@
         <v>331122</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.342048</v>
+        <v>-0.527112</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.871671</v>
+        <v>-6.187047</v>
       </c>
       <c r="V20" t="n">
         <v>-2.269199</v>
@@ -2681,10 +2681,10 @@
         <v>0.77</v>
       </c>
       <c r="H21" t="n">
-        <v>102.99794</v>
+        <v>103.00964</v>
       </c>
       <c r="I21" t="n">
-        <v>98.65175000000001</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="J21" t="n">
         <v>5.2078</v>
@@ -2717,10 +2717,10 @@
         <v>328098</v>
       </c>
       <c r="T21" t="n">
-        <v>2.881581</v>
+        <v>2.956329</v>
       </c>
       <c r="U21" t="n">
-        <v>3.737316</v>
+        <v>5.286443</v>
       </c>
       <c r="V21" t="n">
         <v>2.127743</v>
@@ -2794,10 +2794,10 @@
         <v>0.64</v>
       </c>
       <c r="H22" t="n">
-        <v>103.10183</v>
+        <v>103.09341</v>
       </c>
       <c r="I22" t="n">
-        <v>110.6159</v>
+        <v>110.62354</v>
       </c>
       <c r="J22" t="n">
         <v>5.0804</v>
@@ -2830,10 +2830,10 @@
         <v>341158</v>
       </c>
       <c r="T22" t="n">
-        <v>0.100866</v>
+        <v>0.08132200000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>12.127661</v>
+        <v>12.023101</v>
       </c>
       <c r="V22" t="n">
         <v>-2.446331</v>
@@ -2907,10 +2907,10 @@
         <v>0.53</v>
       </c>
       <c r="H23" t="n">
-        <v>104.18587</v>
+        <v>104.1626</v>
       </c>
       <c r="I23" t="n">
-        <v>104.03928</v>
+        <v>104.34152</v>
       </c>
       <c r="J23" t="n">
         <v>5.0007</v>
@@ -2943,10 +2943,10 @@
         <v>345725</v>
       </c>
       <c r="T23" t="n">
-        <v>1.051427</v>
+        <v>1.037108</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.945456</v>
+        <v>-5.678737</v>
       </c>
       <c r="V23" t="n">
         <v>-1.568774</v>
@@ -3020,10 +3020,10 @@
         <v>0.36</v>
       </c>
       <c r="H24" t="n">
-        <v>102.46133</v>
+        <v>102.3642</v>
       </c>
       <c r="I24" t="n">
-        <v>102.71672</v>
+        <v>102.66392</v>
       </c>
       <c r="J24" t="n">
         <v>5.0959</v>
@@ -3056,10 +3056,10 @@
         <v>343489</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.655253</v>
+        <v>-1.726531</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.271212</v>
+        <v>-1.607797</v>
       </c>
       <c r="V24" t="n">
         <v>1.903733</v>
@@ -3133,10 +3133,10 @@
         <v>-0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>102.39681</v>
+        <v>102.50431</v>
       </c>
       <c r="I25" t="n">
-        <v>102.2809</v>
+        <v>102.53174</v>
       </c>
       <c r="J25" t="n">
         <v>4.8192</v>
@@ -3169,10 +3169,10 @@
         <v>343620</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.06297</v>
+        <v>0.136874</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.424293</v>
+        <v>-0.12875</v>
       </c>
       <c r="V25" t="n">
         <v>-5.429855</v>
@@ -3246,10 +3246,10 @@
         <v>-0.09</v>
       </c>
       <c r="H26" t="n">
-        <v>102.86628</v>
+        <v>102.83357</v>
       </c>
       <c r="I26" t="n">
-        <v>105.34289</v>
+        <v>105.47522</v>
       </c>
       <c r="J26" t="n">
         <v>4.7415</v>
@@ -3282,10 +3282,10 @@
         <v>345476</v>
       </c>
       <c r="T26" t="n">
-        <v>0.458481</v>
+        <v>0.321216</v>
       </c>
       <c r="U26" t="n">
-        <v>2.993707</v>
+        <v>2.870799</v>
       </c>
       <c r="V26" t="n">
         <v>-1.612301</v>
@@ -3359,10 +3359,10 @@
         <v>0.2</v>
       </c>
       <c r="H27" t="n">
-        <v>102.48117</v>
+        <v>102.45222</v>
       </c>
       <c r="I27" t="n">
-        <v>106.05936</v>
+        <v>106.13139</v>
       </c>
       <c r="J27" t="n">
         <v>4.9219</v>
@@ -3395,10 +3395,10 @@
         <v>344177</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.374379</v>
+        <v>-0.370842</v>
       </c>
       <c r="U27" t="n">
-        <v>0.680131</v>
+        <v>0.622108</v>
       </c>
       <c r="V27" t="n">
         <v>3.804703</v>
@@ -3472,10 +3472,10 @@
         <v>0.11</v>
       </c>
       <c r="H28" t="n">
-        <v>102.49422</v>
+        <v>102.57885</v>
       </c>
       <c r="I28" t="n">
-        <v>101.75832</v>
+        <v>102.00419</v>
       </c>
       <c r="J28" t="n">
         <v>5.0076</v>
@@ -3508,10 +3508,10 @@
         <v>340324</v>
       </c>
       <c r="T28" t="n">
-        <v>0.012734</v>
+        <v>0.123599</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.055314</v>
+        <v>-3.888765</v>
       </c>
       <c r="V28" t="n">
         <v>1.741198</v>
@@ -3585,10 +3585,10 @@
         <v>0.12</v>
       </c>
       <c r="H29" t="n">
-        <v>102.81544</v>
+        <v>102.87707</v>
       </c>
       <c r="I29" t="n">
-        <v>101.93091</v>
+        <v>102.0744</v>
       </c>
       <c r="J29" t="n">
         <v>5.0575</v>
@@ -3621,10 +3621,10 @@
         <v>340247</v>
       </c>
       <c r="T29" t="n">
-        <v>0.313403</v>
+        <v>0.290723</v>
       </c>
       <c r="U29" t="n">
-        <v>0.169608</v>
+        <v>0.068831</v>
       </c>
       <c r="V29" t="n">
         <v>0.996485</v>
@@ -3698,10 +3698,10 @@
         <v>0.1</v>
       </c>
       <c r="H30" t="n">
-        <v>103.57529</v>
+        <v>103.528</v>
       </c>
       <c r="I30" t="n">
-        <v>101.68306</v>
+        <v>101.86494</v>
       </c>
       <c r="J30" t="n">
         <v>4.9355</v>
@@ -3734,10 +3734,10 @@
         <v>348406</v>
       </c>
       <c r="T30" t="n">
-        <v>0.739043</v>
+        <v>0.632726</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.243155</v>
+        <v>-0.205203</v>
       </c>
       <c r="V30" t="n">
         <v>-2.412259</v>
@@ -3811,10 +3811,10 @@
         <v>0.55</v>
       </c>
       <c r="H31" t="n">
-        <v>104.68308</v>
+        <v>104.8991</v>
       </c>
       <c r="I31" t="n">
-        <v>101.68292</v>
+        <v>101.74606</v>
       </c>
       <c r="J31" t="n">
         <v>4.8413</v>
@@ -3847,10 +3847,10 @@
         <v>355034</v>
       </c>
       <c r="T31" t="n">
-        <v>1.06955</v>
+        <v>1.324376</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000138</v>
+        <v>-0.116704</v>
       </c>
       <c r="V31" t="n">
         <v>-1.908621</v>
@@ -3924,10 +3924,10 @@
         <v>0.57</v>
       </c>
       <c r="H32" t="n">
-        <v>104.47997</v>
+        <v>104.53245</v>
       </c>
       <c r="I32" t="n">
-        <v>99.29383</v>
+        <v>98.01879</v>
       </c>
       <c r="J32" t="n">
         <v>4.9535</v>
@@ -3960,10 +3960,10 @@
         <v>355066</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.194024</v>
+        <v>-0.349526</v>
       </c>
       <c r="U32" t="n">
-        <v>-2.349549</v>
+        <v>-3.663306</v>
       </c>
       <c r="V32" t="n">
         <v>2.317559</v>
@@ -4037,10 +4037,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>104.63436</v>
+        <v>104.75961</v>
       </c>
       <c r="I33" t="n">
-        <v>102.15169</v>
+        <v>102.37988</v>
       </c>
       <c r="J33" t="n">
         <v>4.9833</v>
@@ -4073,10 +4073,10 @@
         <v>352705</v>
       </c>
       <c r="T33" t="n">
-        <v>0.14777</v>
+        <v>0.217311</v>
       </c>
       <c r="U33" t="n">
-        <v>2.878185</v>
+        <v>4.449239</v>
       </c>
       <c r="V33" t="n">
         <v>0.601595</v>
@@ -4150,10 +4150,10 @@
         <v>0.19</v>
       </c>
       <c r="H34" t="n">
-        <v>104.71934</v>
+        <v>104.7097</v>
       </c>
       <c r="I34" t="n">
-        <v>109.56886</v>
+        <v>109.58504</v>
       </c>
       <c r="J34" t="n">
         <v>4.9962</v>
@@ -4186,10 +4186,10 @@
         <v>355008</v>
       </c>
       <c r="T34" t="n">
-        <v>0.081216</v>
+        <v>-0.047642</v>
       </c>
       <c r="U34" t="n">
-        <v>7.260937</v>
+        <v>7.037672</v>
       </c>
       <c r="V34" t="n">
         <v>0.258865</v>
@@ -4263,10 +4263,10 @@
         <v>0.37</v>
       </c>
       <c r="H35" t="n">
-        <v>104.96661</v>
+        <v>104.75682</v>
       </c>
       <c r="I35" t="n">
-        <v>109.2559</v>
+        <v>109.36335</v>
       </c>
       <c r="J35" t="n">
         <v>5.1718</v>
@@ -4299,10 +4299,10 @@
         <v>351599</v>
       </c>
       <c r="T35" t="n">
-        <v>0.236126</v>
+        <v>0.045001</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.285629</v>
+        <v>-0.2023</v>
       </c>
       <c r="V35" t="n">
         <v>3.514671</v>
@@ -4376,10 +4376,10 @@
         <v>0.46</v>
       </c>
       <c r="H36" t="n">
-        <v>105.66388</v>
+        <v>105.70704</v>
       </c>
       <c r="I36" t="n">
-        <v>104.71434</v>
+        <v>104.84682</v>
       </c>
       <c r="J36" t="n">
         <v>5.2416</v>
@@ -4412,10 +4412,10 @@
         <v>355560</v>
       </c>
       <c r="T36" t="n">
-        <v>0.664278</v>
+        <v>0.907072</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.15681</v>
+        <v>-4.129839</v>
       </c>
       <c r="V36" t="n">
         <v>1.349627</v>
@@ -4489,10 +4489,10 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>106.57692</v>
+        <v>106.57623</v>
       </c>
       <c r="I37" t="n">
-        <v>105.86962</v>
+        <v>106.03093</v>
       </c>
       <c r="J37" t="n">
         <v>5.5589</v>
@@ -4525,10 +4525,10 @@
         <v>357827</v>
       </c>
       <c r="T37" t="n">
-        <v>0.864098</v>
+        <v>0.822263</v>
       </c>
       <c r="U37" t="n">
-        <v>1.103268</v>
+        <v>1.129371</v>
       </c>
       <c r="V37" t="n">
         <v>6.053495</v>
@@ -4602,10 +4602,10 @@
         <v>0.26</v>
       </c>
       <c r="H38" t="n">
-        <v>106.95254</v>
+        <v>106.88756</v>
       </c>
       <c r="I38" t="n">
-        <v>111.51388</v>
+        <v>111.55002</v>
       </c>
       <c r="J38" t="n">
         <v>5.6621</v>
@@ -4638,10 +4638,10 @@
         <v>363282</v>
       </c>
       <c r="T38" t="n">
-        <v>0.35244</v>
+        <v>0.29212</v>
       </c>
       <c r="U38" t="n">
-        <v>5.331331</v>
+        <v>5.20517</v>
       </c>
       <c r="V38" t="n">
         <v>1.856482</v>
@@ -4715,10 +4715,10 @@
         <v>-0.14</v>
       </c>
       <c r="H39" t="n">
-        <v>107.13607</v>
+        <v>107.14396</v>
       </c>
       <c r="I39" t="n">
-        <v>110.06483</v>
+        <v>110.19363</v>
       </c>
       <c r="J39" t="n">
         <v>5.6562</v>
@@ -4751,10 +4751,10 @@
         <v>369214</v>
       </c>
       <c r="T39" t="n">
-        <v>0.171599</v>
+        <v>0.239878</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.299435</v>
+        <v>-1.215948</v>
       </c>
       <c r="V39" t="n">
         <v>-0.104202</v>
@@ -4828,10 +4828,10 @@
         <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99994</v>
+        <v>107.99916</v>
       </c>
       <c r="I40" t="n">
-        <v>107.08167</v>
+        <v>107.28836</v>
       </c>
       <c r="J40" t="n">
         <v>5.4481</v>
@@ -4864,10 +4864,10 @@
         <v>372016</v>
       </c>
       <c r="T40" t="n">
-        <v>0.80633</v>
+        <v>0.7981780000000001</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.710366</v>
+        <v>-2.636514</v>
       </c>
       <c r="V40" t="n">
         <v>-3.679149</v>
@@ -4941,10 +4941,10 @@
         <v>0.61</v>
       </c>
       <c r="H41" t="n">
-        <v>108.20756</v>
+        <v>108.15356</v>
       </c>
       <c r="I41" t="n">
-        <v>109.18693</v>
+        <v>109.21678</v>
       </c>
       <c r="J41" t="n">
         <v>5.7779</v>
@@ -4977,10 +4977,10 @@
         <v>366096</v>
       </c>
       <c r="T41" t="n">
-        <v>0.192241</v>
+        <v>0.142964</v>
       </c>
       <c r="U41" t="n">
-        <v>1.966032</v>
+        <v>1.797418</v>
       </c>
       <c r="V41" t="n">
         <v>6.053487</v>
@@ -5054,10 +5054,10 @@
         <v>0.33</v>
       </c>
       <c r="H42" t="n">
-        <v>107.96783</v>
+        <v>107.98489</v>
       </c>
       <c r="I42" t="n">
-        <v>105.49025</v>
+        <v>105.74688</v>
       </c>
       <c r="J42" t="n">
         <v>6.0535</v>
@@ -5090,10 +5090,10 @@
         <v>363003</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.221546</v>
+        <v>-0.155954</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.385643</v>
+        <v>-3.177076</v>
       </c>
       <c r="V42" t="n">
         <v>4.769899</v>
@@ -5167,10 +5167,10 @@
         <v>0.48</v>
       </c>
       <c r="H43" t="n">
-        <v>107.1418</v>
+        <v>107.44467</v>
       </c>
       <c r="I43" t="n">
-        <v>104.15997</v>
+        <v>104.2734</v>
       </c>
       <c r="J43" t="n">
         <v>6.1923</v>
@@ -5203,10 +5203,10 @@
         <v>329730</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.76507</v>
+        <v>-0.500274</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.261045</v>
+        <v>-1.393403</v>
       </c>
       <c r="V43" t="n">
         <v>2.292888</v>
@@ -5280,10 +5280,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>108.21392</v>
+        <v>108.06979</v>
       </c>
       <c r="I44" t="n">
-        <v>102.72834</v>
+        <v>101.23438</v>
       </c>
       <c r="J44" t="n">
         <v>5.8301</v>
@@ -5316,10 +5316,10 @@
         <v>328303</v>
       </c>
       <c r="T44" t="n">
-        <v>1.000655</v>
+        <v>0.581806</v>
       </c>
       <c r="U44" t="n">
-        <v>-1.374453</v>
+        <v>-2.914473</v>
       </c>
       <c r="V44" t="n">
         <v>-5.8492</v>
@@ -5393,10 +5393,10 @@
         <v>1.48</v>
       </c>
       <c r="H45" t="n">
-        <v>108.74593</v>
+        <v>108.77346</v>
       </c>
       <c r="I45" t="n">
-        <v>106.92609</v>
+        <v>107.07838</v>
       </c>
       <c r="J45" t="n">
         <v>5.8488</v>
@@ -5429,10 +5429,10 @@
         <v>332508</v>
       </c>
       <c r="T45" t="n">
-        <v>0.491628</v>
+        <v>0.651126</v>
       </c>
       <c r="U45" t="n">
-        <v>4.086263</v>
+        <v>5.772742</v>
       </c>
       <c r="V45" t="n">
         <v>0.320749</v>
@@ -5506,10 +5506,10 @@
         <v>0.51</v>
       </c>
       <c r="H46" t="n">
-        <v>110.20451</v>
+        <v>110.09056</v>
       </c>
       <c r="I46" t="n">
-        <v>114.11998</v>
+        <v>114.05013</v>
       </c>
       <c r="J46" t="n">
         <v>5.7422</v>
@@ -5542,10 +5542,10 @@
         <v>336157</v>
       </c>
       <c r="T46" t="n">
-        <v>1.341273</v>
+        <v>1.210865</v>
       </c>
       <c r="U46" t="n">
-        <v>6.727909</v>
+        <v>6.510885</v>
       </c>
       <c r="V46" t="n">
         <v>-1.822596</v>
@@ -5619,10 +5619,10 @@
         <v>0.48</v>
       </c>
       <c r="H47" t="n">
-        <v>110.0593</v>
+        <v>109.72323</v>
       </c>
       <c r="I47" t="n">
-        <v>112.69428</v>
+        <v>112.73813</v>
       </c>
       <c r="J47" t="n">
         <v>5.6608</v>
@@ -5655,10 +5655,10 @@
         <v>340789</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.131764</v>
+        <v>-0.333662</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.249299</v>
+        <v>-1.150371</v>
       </c>
       <c r="V47" t="n">
         <v>-1.417575</v>
@@ -5732,10 +5732,10 @@
         <v>0.35</v>
       </c>
       <c r="H48" t="n">
-        <v>109.08727</v>
+        <v>109.00057</v>
       </c>
       <c r="I48" t="n">
-        <v>108.65566</v>
+        <v>108.66481</v>
       </c>
       <c r="J48" t="n">
         <v>5.7087</v>
@@ -5768,10 +5768,10 @@
         <v>341459</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.883188</v>
+        <v>-0.658621</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.583696</v>
+        <v>-3.613081</v>
       </c>
       <c r="V48" t="n">
         <v>0.84617</v>
@@ -5845,10 +5845,10 @@
         <v>0.23</v>
       </c>
       <c r="H49" t="n">
-        <v>108.85988</v>
+        <v>108.76683</v>
       </c>
       <c r="I49" t="n">
-        <v>107.4594</v>
+        <v>107.55639</v>
       </c>
       <c r="J49" t="n">
         <v>5.4571</v>
@@ -5881,10 +5881,10 @@
         <v>344440</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.208448</v>
+        <v>-0.214439</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.100964</v>
+        <v>-1.020036</v>
       </c>
       <c r="V49" t="n">
         <v>-4.407308</v>
@@ -5958,10 +5958,10 @@
         <v>0.21</v>
       </c>
       <c r="H50" t="n">
-        <v>108.41316</v>
+        <v>108.27053</v>
       </c>
       <c r="I50" t="n">
-        <v>113.21721</v>
+        <v>113.14433</v>
       </c>
       <c r="J50" t="n">
         <v>5.6021</v>
@@ -5994,10 +5994,10 @@
         <v>345111</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.410362</v>
+        <v>-0.456297</v>
       </c>
       <c r="U50" t="n">
-        <v>5.358126</v>
+        <v>5.195358</v>
       </c>
       <c r="V50" t="n">
         <v>2.657089</v>
@@ -6071,10 +6071,10 @@
         <v>-0.21</v>
       </c>
       <c r="H51" t="n">
-        <v>108.83964</v>
+        <v>108.80021</v>
       </c>
       <c r="I51" t="n">
-        <v>110.47825</v>
+        <v>110.57963</v>
       </c>
       <c r="J51" t="n">
         <v>5.4264</v>
@@ -6107,10 +6107,10 @@
         <v>350767</v>
       </c>
       <c r="T51" t="n">
-        <v>0.393384</v>
+        <v>0.489219</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.419208</v>
+        <v>-2.266751</v>
       </c>
       <c r="V51" t="n">
         <v>-3.136324</v>
@@ -6184,10 +6184,10 @@
         <v>0.52</v>
       </c>
       <c r="H52" t="n">
-        <v>108.76251</v>
+        <v>108.63642</v>
       </c>
       <c r="I52" t="n">
-        <v>109.57602</v>
+        <v>109.59513</v>
       </c>
       <c r="J52" t="n">
         <v>5.3186</v>
@@ -6220,10 +6220,10 @@
         <v>356582</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.070866</v>
+        <v>-0.150542</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.816658</v>
+        <v>-0.890309</v>
       </c>
       <c r="V52" t="n">
         <v>-1.986584</v>
@@ -6297,10 +6297,10 @@
         <v>0.03</v>
       </c>
       <c r="H53" t="n">
-        <v>108.78795</v>
+        <v>108.7159</v>
       </c>
       <c r="I53" t="n">
-        <v>110.16742</v>
+        <v>110.16346</v>
       </c>
       <c r="J53" t="n">
         <v>5.3843</v>
@@ -6333,10 +6333,10 @@
         <v>357103</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02339</v>
+        <v>0.073161</v>
       </c>
       <c r="U53" t="n">
-        <v>0.539717</v>
+        <v>0.518572</v>
       </c>
       <c r="V53" t="n">
         <v>1.235287</v>
@@ -6410,10 +6410,10 @@
         <v>0.03</v>
       </c>
       <c r="H54" t="n">
-        <v>109.30007</v>
+        <v>109.27405</v>
       </c>
       <c r="I54" t="n">
-        <v>106.69062</v>
+        <v>106.90236</v>
       </c>
       <c r="J54" t="n">
         <v>5.3338</v>
@@ -6446,10 +6446,10 @@
         <v>360578</v>
       </c>
       <c r="T54" t="n">
-        <v>0.470751</v>
+        <v>0.513402</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.155924</v>
+        <v>-2.960237</v>
       </c>
       <c r="V54" t="n">
         <v>-0.937912</v>
@@ -6523,10 +6523,10 @@
         <v>0.21</v>
       </c>
       <c r="H55" t="n">
-        <v>109.27117</v>
+        <v>109.41762</v>
       </c>
       <c r="I55" t="n">
-        <v>107.27827</v>
+        <v>107.17649</v>
       </c>
       <c r="J55" t="n">
         <v>5.5024</v>
@@ -6559,10 +6559,10 @@
         <v>358234</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.026441</v>
+        <v>0.131385</v>
       </c>
       <c r="U55" t="n">
-        <v>0.550798</v>
+        <v>0.25643</v>
       </c>
       <c r="V55" t="n">
         <v>3.160973</v>
@@ -6636,10 +6636,10 @@
         <v>0.39</v>
       </c>
       <c r="H56" t="n">
-        <v>110.09703</v>
+        <v>110.05486</v>
       </c>
       <c r="I56" t="n">
-        <v>103.80093</v>
+        <v>102.36456</v>
       </c>
       <c r="J56" t="n">
         <v>5.2301</v>
@@ -6672,10 +6672,10 @@
         <v>364367</v>
       </c>
       <c r="T56" t="n">
-        <v>0.755789</v>
+        <v>0.582392</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.241421</v>
+        <v>-4.489725</v>
       </c>
       <c r="V56" t="n">
         <v>-4.94875</v>
@@ -6749,10 +6749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>110.78559</v>
+        <v>110.65892</v>
       </c>
       <c r="I57" t="n">
-        <v>106.7205</v>
+        <v>106.82125</v>
       </c>
       <c r="J57" t="n">
         <v>5.1495</v>
@@ -6785,10 +6785,10 @@
         <v>371074</v>
       </c>
       <c r="T57" t="n">
-        <v>0.625412</v>
+        <v>0.548872</v>
       </c>
       <c r="U57" t="n">
-        <v>2.812663</v>
+        <v>4.353743</v>
       </c>
       <c r="V57" t="n">
         <v>-1.54108</v>
@@ -6862,10 +6862,10 @@
         <v>0.91</v>
       </c>
       <c r="H58" t="n">
-        <v>110.58589</v>
+        <v>110.51078</v>
       </c>
       <c r="I58" t="n">
-        <v>117.92682</v>
+        <v>117.8089</v>
       </c>
       <c r="J58" t="n">
         <v>5.2194</v>
@@ -6898,10 +6898,10 @@
         <v>362002</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.180258</v>
+        <v>-0.133871</v>
       </c>
       <c r="U58" t="n">
-        <v>10.500625</v>
+        <v>10.286015</v>
       </c>
       <c r="V58" t="n">
         <v>1.357413</v>
@@ -6975,10 +6975,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>111.15205</v>
+        <v>110.95732</v>
       </c>
       <c r="I59" t="n">
-        <v>113.72712</v>
+        <v>113.99365</v>
       </c>
       <c r="J59" t="n">
         <v>4.9886</v>
@@ -7011,10 +7011,10 @@
         <v>366913</v>
       </c>
       <c r="T59" t="n">
-        <v>0.511964</v>
+        <v>0.404069</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.561276</v>
+        <v>-3.238507</v>
       </c>
       <c r="V59" t="n">
         <v>-4.421964</v>
@@ -7087,8 +7087,12 @@
       <c r="G60" t="n">
         <v>0.65</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>111.03587</v>
+      </c>
+      <c r="I60" t="n">
+        <v>109.52993</v>
+      </c>
       <c r="J60" t="n">
         <v>5.0569</v>
       </c>
@@ -7119,8 +7123,12 @@
       <c r="S60" t="n">
         <v>371137</v>
       </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>0.07079299999999999</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-3.915762</v>
+      </c>
       <c r="V60" t="n">
         <v>1.369122</v>
       </c>
@@ -7266,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0975</v>
+        <v>5.1176</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0969</v>
+        <v>5.117</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7282,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.52803</v>
+        <v>-1.139744</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.528207</v>
+        <v>-1.139876</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.1176</v>
+        <v>5.0894</v>
       </c>
       <c r="K62" t="n">
-        <v>5.117</v>
+        <v>5.0888</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.139744</v>
+        <v>-1.684503</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.139876</v>
+        <v>-1.684699</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0894</v>
+        <v>5.078</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0888</v>
+        <v>5.0774</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.684503</v>
+        <v>-1.904725</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.684699</v>
+        <v>-1.904946</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.078</v>
+        <v>5.0638</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0774</v>
+        <v>5.0632</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-1.904725</v>
+        <v>-2.179036</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.904946</v>
+        <v>-2.179289</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -7274,10 +7274,10 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.0638</v>
+        <v>5.0807</v>
       </c>
       <c r="K62" t="n">
-        <v>5.0632</v>
+        <v>5.0801</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-2.179036</v>
+        <v>-1.852567</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.179289</v>
+        <v>-1.852782</v>
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,170 +438,160 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>cdi</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>ipca</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>dif_cdi</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -618,53 +608,51 @@
         <v>0.016137</v>
       </c>
       <c r="D2" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="E2" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.02</v>
+        <v>96.31464</v>
       </c>
       <c r="H2" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="I2" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="K2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="L2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="M2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="N2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="R2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="S2" t="n">
         <v>355671</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -695,99 +681,93 @@
         <v>0.019413</v>
       </c>
       <c r="D3" t="n">
-        <v>0.019413</v>
+        <v>0.87</v>
       </c>
       <c r="E3" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F3" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>0.88</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="I3" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="L3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="M3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="N3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="R3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="S3" t="n">
-        <v>370395</v>
+        <v>0.79016</v>
       </c>
       <c r="T3" t="n">
-        <v>0.79016</v>
+        <v>-0.512311</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.512311</v>
+        <v>0.423696</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="W3" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="X3" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -802,99 +782,93 @@
         <v>0.021003</v>
       </c>
       <c r="D4" t="n">
-        <v>0.021003</v>
+        <v>1.16</v>
       </c>
       <c r="E4" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>96.95968999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>96.95968999999999</v>
+        <v>97.24746</v>
       </c>
       <c r="I4" t="n">
-        <v>97.24746</v>
+        <v>5.4394</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="S4" t="n">
-        <v>368886</v>
+        <v>-0.119484</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.119484</v>
+        <v>-2.094902</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.094902</v>
+        <v>5.757004</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="W4" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="X4" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -909,99 +883,93 @@
         <v>0.024244</v>
       </c>
       <c r="D5" t="n">
-        <v>0.024244</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.16</v>
+        <v>97.48142</v>
       </c>
       <c r="H5" t="n">
-        <v>97.48142</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.643</v>
       </c>
       <c r="J5" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S5" t="n">
-        <v>367927</v>
+        <v>0.53809</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53809</v>
+        <v>-0.644377</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.644377</v>
+        <v>3.74306</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="W5" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="X5" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1016,99 +984,93 @@
         <v>0.029256</v>
       </c>
       <c r="D6" t="n">
-        <v>0.029256</v>
+        <v>0.95</v>
       </c>
       <c r="E6" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="G6" t="n">
-        <v>0.84</v>
+        <v>98.97262000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>98.97262000000001</v>
+        <v>98.05768</v>
       </c>
       <c r="I6" t="n">
-        <v>98.05768</v>
+        <v>5.6199</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="L6" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="M6" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N6" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S6" t="n">
-        <v>367772</v>
+        <v>1.529727</v>
       </c>
       <c r="T6" t="n">
-        <v>1.529727</v>
+        <v>1.487112</v>
       </c>
       <c r="U6" t="n">
-        <v>1.487112</v>
+        <v>-0.409357</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="X6" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1123,99 +1085,93 @@
         <v>0.033316</v>
       </c>
       <c r="D7" t="n">
-        <v>0.033316</v>
+        <v>0.73</v>
       </c>
       <c r="E7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.73</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.87</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.73</v>
+        <v>99.35339</v>
       </c>
       <c r="H7" t="n">
-        <v>99.35339</v>
+        <v>99.33126</v>
       </c>
       <c r="I7" t="n">
-        <v>99.33126</v>
+        <v>5.5805</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S7" t="n">
-        <v>362204</v>
+        <v>0.384723</v>
       </c>
       <c r="T7" t="n">
-        <v>0.384723</v>
+        <v>1.298807</v>
       </c>
       <c r="U7" t="n">
-        <v>1.298807</v>
+        <v>-0.70108</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="X7" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1230,99 +1186,93 @@
         <v>0.034749</v>
       </c>
       <c r="D8" t="n">
-        <v>0.034749</v>
+        <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>0.67</v>
+        <v>97.34401</v>
       </c>
       <c r="H8" t="n">
-        <v>97.34401</v>
+        <v>90.45032</v>
       </c>
       <c r="I8" t="n">
-        <v>90.45032</v>
+        <v>5.3574</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S8" t="n">
-        <v>358398</v>
+        <v>-2.022457</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.022457</v>
+        <v>-8.94073</v>
       </c>
       <c r="U8" t="n">
-        <v>-8.94073</v>
+        <v>-3.99785</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1337,99 +1287,93 @@
         <v>0.039598</v>
       </c>
       <c r="D9" t="n">
-        <v>0.039598</v>
+        <v>1.01</v>
       </c>
       <c r="E9" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>98.43725000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>98.43725000000001</v>
+        <v>95.72214</v>
       </c>
       <c r="I9" t="n">
-        <v>95.72214</v>
+        <v>5.1394</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S9" t="n">
-        <v>357740</v>
+        <v>1.123069</v>
       </c>
       <c r="T9" t="n">
-        <v>1.123069</v>
+        <v>5.828415</v>
       </c>
       <c r="U9" t="n">
-        <v>5.828415</v>
+        <v>-4.069138</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="X9" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1444,99 +1388,93 @@
         <v>0.041954</v>
       </c>
       <c r="D10" t="n">
-        <v>0.041954</v>
+        <v>1.62</v>
       </c>
       <c r="E10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>99.55981</v>
       </c>
       <c r="H10" t="n">
-        <v>99.55981</v>
+        <v>104.61484</v>
       </c>
       <c r="I10" t="n">
-        <v>104.61484</v>
+        <v>4.7378</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S10" t="n">
-        <v>353169</v>
+        <v>1.140381</v>
       </c>
       <c r="T10" t="n">
-        <v>1.140381</v>
+        <v>9.290118</v>
       </c>
       <c r="U10" t="n">
-        <v>9.290118</v>
+        <v>-7.814142</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="X10" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1551,99 +1489,93 @@
         <v>0.043739</v>
       </c>
       <c r="D11" t="n">
-        <v>0.043739</v>
+        <v>1.06</v>
       </c>
       <c r="E11" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.04</v>
+        <v>99.51646</v>
       </c>
       <c r="H11" t="n">
-        <v>99.51646</v>
+        <v>100.42352</v>
       </c>
       <c r="I11" t="n">
-        <v>100.42352</v>
+        <v>4.9191</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S11" t="n">
-        <v>345097</v>
+        <v>-0.043542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.043542</v>
+        <v>-4.00643</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.00643</v>
+        <v>3.826671</v>
       </c>
       <c r="V11" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="W11" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="X11" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1658,99 +1590,93 @@
         <v>0.046796</v>
       </c>
       <c r="D12" t="n">
-        <v>0.046796</v>
+        <v>0.47</v>
       </c>
       <c r="E12" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="F12" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.45</v>
+        <v>99.67415</v>
       </c>
       <c r="H12" t="n">
-        <v>99.67415</v>
+        <v>99.79777</v>
       </c>
       <c r="I12" t="n">
-        <v>99.79777</v>
+        <v>4.7289</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S12" t="n">
-        <v>346415</v>
+        <v>0.158456</v>
       </c>
       <c r="T12" t="n">
-        <v>0.158456</v>
+        <v>-0.623111</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.623111</v>
+        <v>-3.866561</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="X12" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1765,105 +1691,99 @@
         <v>0.048116</v>
       </c>
       <c r="D13" t="n">
-        <v>0.048116</v>
+        <v>0.67</v>
       </c>
       <c r="E13" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="F13" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.62</v>
+        <v>99.6343</v>
       </c>
       <c r="H13" t="n">
-        <v>99.6343</v>
+        <v>99.53784</v>
       </c>
       <c r="I13" t="n">
-        <v>99.53784</v>
+        <v>5.238</v>
       </c>
       <c r="J13" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S13" t="n">
-        <v>341958</v>
+        <v>-0.03998</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.03998</v>
+        <v>-0.260457</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.260457</v>
+        <v>10.765717</v>
       </c>
       <c r="V13" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="W13" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="X13" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.299314</v>
+        <v>-1.286607</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.286607</v>
+        <v>11.88673</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.919595</v>
+        <v>0.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1878,105 +1798,99 @@
         <v>0.049037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.049037</v>
+        <v>-0.68</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="F14" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6</v>
+        <v>101.27684</v>
       </c>
       <c r="H14" t="n">
-        <v>101.27684</v>
+        <v>103.95861</v>
       </c>
       <c r="I14" t="n">
-        <v>103.95861</v>
+        <v>5.1884</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S14" t="n">
-        <v>346403</v>
+        <v>1.648569</v>
       </c>
       <c r="T14" t="n">
-        <v>1.648569</v>
+        <v>4.441296</v>
       </c>
       <c r="U14" t="n">
-        <v>4.441296</v>
+        <v>-0.946926</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="X14" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.344714</v>
+        <v>1.299867</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.299867</v>
+        <v>10.069235</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.124804</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1991,105 +1905,99 @@
         <v>0.05056</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05056</v>
+        <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.31</v>
+        <v>101.07328</v>
       </c>
       <c r="H15" t="n">
-        <v>101.07328</v>
+        <v>104.56278</v>
       </c>
       <c r="I15" t="n">
-        <v>104.56278</v>
+        <v>5.179</v>
       </c>
       <c r="J15" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S15" t="n">
-        <v>339664</v>
+        <v>-0.200994</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.200994</v>
+        <v>0.581164</v>
       </c>
       <c r="U15" t="n">
-        <v>0.581164</v>
+        <v>-0.181173</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="X15" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.825751</v>
+        <v>0.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2104,105 +2012,99 @@
         <v>0.050788</v>
       </c>
       <c r="D16" t="n">
-        <v>0.050788</v>
+        <v>-0.29</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.32</v>
+        <v>101.17973</v>
       </c>
       <c r="H16" t="n">
-        <v>101.17973</v>
+        <v>101.38087</v>
       </c>
       <c r="I16" t="n">
-        <v>101.38087</v>
+        <v>5.4066</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="K16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S16" t="n">
-        <v>327580</v>
+        <v>0.10532</v>
       </c>
       <c r="T16" t="n">
-        <v>0.10532</v>
+        <v>-3.043062</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.043062</v>
+        <v>4.394671</v>
       </c>
       <c r="V16" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="W16" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="X16" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2217,105 +2119,99 @@
         <v>0.050788</v>
       </c>
       <c r="D17" t="n">
-        <v>0.050788</v>
+        <v>0.59</v>
       </c>
       <c r="E17" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.47</v>
+        <v>101.46342</v>
       </c>
       <c r="H17" t="n">
-        <v>101.46342</v>
+        <v>100.20398</v>
       </c>
       <c r="I17" t="n">
-        <v>100.20398</v>
+        <v>5.257</v>
       </c>
       <c r="J17" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S17" t="n">
-        <v>325546</v>
+        <v>0.280382</v>
       </c>
       <c r="T17" t="n">
-        <v>0.280382</v>
+        <v>-1.16086</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.16086</v>
+        <v>-2.766988</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="X17" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.470016</v>
+        <v>6.517038</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.517038</v>
+        <v>6.460076</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2330,105 +2226,99 @@
         <v>0.050788</v>
       </c>
       <c r="D18" t="n">
-        <v>0.050788</v>
+        <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.38</v>
+        <v>100.66227</v>
       </c>
       <c r="H18" t="n">
-        <v>100.66227</v>
+        <v>99.36927</v>
       </c>
       <c r="I18" t="n">
-        <v>99.36927</v>
+        <v>5.2941</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S18" t="n">
-        <v>331505</v>
+        <v>-0.789595</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.789595</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>0.705726</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="X18" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.900488</v>
+        <v>5.899363</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.899363</v>
+        <v>5.974439</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2443,105 +2333,99 @@
         <v>0.050788</v>
       </c>
       <c r="D19" t="n">
-        <v>0.050788</v>
+        <v>0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.58196</v>
       </c>
       <c r="H19" t="n">
-        <v>100.58196</v>
+        <v>99.97806</v>
       </c>
       <c r="I19" t="n">
-        <v>99.97806</v>
+        <v>5.2177</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S19" t="n">
-        <v>324703</v>
+        <v>-0.07978200000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>0.612654</v>
       </c>
       <c r="U19" t="n">
-        <v>0.612654</v>
+        <v>-1.443116</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="X19" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.784842</v>
+        <v>5.458422</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.458422</v>
+        <v>5.932356</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.932356</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AF19" t="n">
-        <v>-0</v>
-      </c>
       <c r="AG19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2556,105 +2440,99 @@
         <v>0.050788</v>
       </c>
       <c r="D20" t="n">
-        <v>0.050788</v>
+        <v>0.53</v>
       </c>
       <c r="E20" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="F20" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.46</v>
+        <v>100.05178</v>
       </c>
       <c r="H20" t="n">
-        <v>100.05178</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0993</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S20" t="n">
-        <v>331122</v>
+        <v>-0.527112</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.527112</v>
+        <v>-6.187047</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.187047</v>
+        <v>-2.269199</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="X20" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.77432</v>
+        <v>3.79089</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.79089</v>
+        <v>5.711379</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2669,105 +2547,99 @@
         <v>0.050788</v>
       </c>
       <c r="D21" t="n">
-        <v>0.050788</v>
+        <v>0.84</v>
       </c>
       <c r="E21" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="G21" t="n">
-        <v>0.77</v>
+        <v>103.00964</v>
       </c>
       <c r="H21" t="n">
-        <v>103.00964</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2078</v>
       </c>
       <c r="J21" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S21" t="n">
-        <v>328098</v>
+        <v>2.956329</v>
       </c>
       <c r="T21" t="n">
-        <v>2.956329</v>
+        <v>5.286443</v>
       </c>
       <c r="U21" t="n">
-        <v>5.286443</v>
+        <v>2.127743</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="W21" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.596302</v>
+        <v>1.864495</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.864495</v>
+        <v>5.47065</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2782,105 +2654,99 @@
         <v>0.050788</v>
       </c>
       <c r="D22" t="n">
-        <v>0.050788</v>
+        <v>0.71</v>
       </c>
       <c r="E22" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="G22" t="n">
-        <v>0.64</v>
+        <v>103.09341</v>
       </c>
       <c r="H22" t="n">
-        <v>103.09341</v>
+        <v>110.62354</v>
       </c>
       <c r="I22" t="n">
-        <v>110.62354</v>
+        <v>5.0804</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S22" t="n">
-        <v>341158</v>
+        <v>0.08132200000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08132200000000001</v>
+        <v>12.023101</v>
       </c>
       <c r="U22" t="n">
-        <v>12.023101</v>
+        <v>-2.446331</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="X22" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.650694</v>
+        <v>0.172427</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.172427</v>
+        <v>4.361088</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2895,105 +2761,99 @@
         <v>0.050788</v>
       </c>
       <c r="D23" t="n">
-        <v>0.050788</v>
+        <v>0.61</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.53</v>
+        <v>104.1626</v>
       </c>
       <c r="H23" t="n">
-        <v>104.1626</v>
+        <v>104.34152</v>
       </c>
       <c r="I23" t="n">
-        <v>104.34152</v>
+        <v>5.0007</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="K23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S23" t="n">
-        <v>345725</v>
+        <v>1.037108</v>
       </c>
       <c r="T23" t="n">
-        <v>1.037108</v>
+        <v>-5.678737</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.678737</v>
+        <v>-1.568774</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="X23" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.184706</v>
+        <v>-2.158772</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.158772</v>
+        <v>3.834324</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -3008,105 +2868,99 @@
         <v>0.050788</v>
       </c>
       <c r="D24" t="n">
-        <v>0.050788</v>
+        <v>0.23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.36</v>
+        <v>102.3642</v>
       </c>
       <c r="H24" t="n">
-        <v>102.3642</v>
+        <v>102.66392</v>
       </c>
       <c r="I24" t="n">
-        <v>102.66392</v>
+        <v>5.0959</v>
       </c>
       <c r="J24" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="K24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S24" t="n">
-        <v>343489</v>
+        <v>-1.726531</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.726531</v>
+        <v>-1.607797</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.607797</v>
+        <v>1.903733</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="W24" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="X24" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.935832</v>
+        <v>-4.45588</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.45588</v>
+        <v>3.741292</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.741292</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3121,105 +2975,99 @@
         <v>0.050788</v>
       </c>
       <c r="D25" t="n">
-        <v>0.050788</v>
+        <v>-0.08</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1</v>
+        <v>102.50431</v>
       </c>
       <c r="H25" t="n">
-        <v>102.50431</v>
+        <v>102.53174</v>
       </c>
       <c r="I25" t="n">
-        <v>102.53174</v>
+        <v>4.8192</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="L25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="M25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="N25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="R25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="S25" t="n">
-        <v>343620</v>
+        <v>0.136874</v>
       </c>
       <c r="T25" t="n">
-        <v>0.136874</v>
+        <v>-0.12875</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.12875</v>
+        <v>-5.429855</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.429855</v>
+        <v>-5.430495</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.430495</v>
+        <v>0.472174</v>
       </c>
       <c r="X25" t="n">
-        <v>0.472174</v>
+        <v>1.122473</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.122473</v>
+        <v>0.050421</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.050421</v>
+        <v>0.038138</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.038138</v>
+        <v>3.161501</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.161501</v>
+        <v>-6.84947</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.84947</v>
+        <v>2.998957</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3234,105 +3082,99 @@
         <v>0.050788</v>
       </c>
       <c r="D26" t="n">
-        <v>0.050788</v>
+        <v>0.12</v>
       </c>
       <c r="E26" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.09</v>
+        <v>102.83357</v>
       </c>
       <c r="H26" t="n">
-        <v>102.83357</v>
+        <v>105.47522</v>
       </c>
       <c r="I26" t="n">
-        <v>105.47522</v>
+        <v>4.7415</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S26" t="n">
-        <v>345476</v>
+        <v>0.321216</v>
       </c>
       <c r="T26" t="n">
-        <v>0.321216</v>
+        <v>2.870799</v>
       </c>
       <c r="U26" t="n">
-        <v>2.870799</v>
+        <v>-1.612301</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="X26" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.992444</v>
+        <v>-7.713954</v>
       </c>
       <c r="AC26" t="n">
-        <v>-7.713954</v>
+        <v>3.527423</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3347,105 +3189,99 @@
         <v>0.049189</v>
       </c>
       <c r="D27" t="n">
-        <v>0.049189</v>
+        <v>0.23</v>
       </c>
       <c r="E27" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>102.45222</v>
       </c>
       <c r="H27" t="n">
-        <v>102.45222</v>
+        <v>106.13139</v>
       </c>
       <c r="I27" t="n">
-        <v>106.13139</v>
+        <v>4.9219</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S27" t="n">
-        <v>344177</v>
+        <v>-0.370842</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.370842</v>
+        <v>0.622108</v>
       </c>
       <c r="U27" t="n">
-        <v>0.622108</v>
+        <v>3.804703</v>
       </c>
       <c r="V27" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="W27" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="X27" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.608216</v>
+        <v>-7.193509</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.193509</v>
+        <v>4.057054</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.057054</v>
+        <v>-0.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3460,105 +3296,99 @@
         <v>0.048422</v>
       </c>
       <c r="D28" t="n">
-        <v>0.048422</v>
+        <v>0.26</v>
       </c>
       <c r="E28" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="F28" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11</v>
+        <v>102.57885</v>
       </c>
       <c r="H28" t="n">
-        <v>102.57885</v>
+        <v>102.00419</v>
       </c>
       <c r="I28" t="n">
-        <v>102.00419</v>
+        <v>5.0076</v>
       </c>
       <c r="J28" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="K28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S28" t="n">
-        <v>340324</v>
+        <v>0.123599</v>
       </c>
       <c r="T28" t="n">
-        <v>0.123599</v>
+        <v>-3.888765</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.888765</v>
+        <v>1.741198</v>
       </c>
       <c r="V28" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="X28" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.185235</v>
+        <v>-5.956714</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5.956714</v>
+        <v>4.505936</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.505936</v>
+        <v>-0.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3573,105 +3403,99 @@
         <v>0.047279</v>
       </c>
       <c r="D29" t="n">
-        <v>0.047279</v>
+        <v>0.24</v>
       </c>
       <c r="E29" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.12</v>
+        <v>102.87707</v>
       </c>
       <c r="H29" t="n">
-        <v>102.87707</v>
+        <v>102.0744</v>
       </c>
       <c r="I29" t="n">
-        <v>102.0744</v>
+        <v>5.0575</v>
       </c>
       <c r="J29" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="K29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S29" t="n">
-        <v>340247</v>
+        <v>0.290723</v>
       </c>
       <c r="T29" t="n">
-        <v>0.290723</v>
+        <v>0.068831</v>
       </c>
       <c r="U29" t="n">
-        <v>0.068831</v>
+        <v>0.996485</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="W29" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="X29" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.819246</v>
+        <v>-4.560737</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.560737</v>
+        <v>4.141877</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.141877</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3686,105 +3510,99 @@
         <v>0.045601</v>
       </c>
       <c r="D30" t="n">
-        <v>0.045601</v>
+        <v>0.28</v>
       </c>
       <c r="E30" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="F30" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1</v>
+        <v>103.528</v>
       </c>
       <c r="H30" t="n">
-        <v>103.528</v>
+        <v>101.86494</v>
       </c>
       <c r="I30" t="n">
-        <v>101.86494</v>
+        <v>4.9355</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S30" t="n">
-        <v>348406</v>
+        <v>0.632726</v>
       </c>
       <c r="T30" t="n">
-        <v>0.632726</v>
+        <v>-0.205203</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.205203</v>
+        <v>-2.412259</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="X30" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.683537</v>
+        <v>-3.457004</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.457004</v>
+        <v>3.851383</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.851383</v>
+        <v>-0.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3799,105 +3617,99 @@
         <v>0.044537</v>
       </c>
       <c r="D31" t="n">
-        <v>0.044537</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="F31" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.55</v>
+        <v>104.8991</v>
       </c>
       <c r="H31" t="n">
-        <v>104.8991</v>
+        <v>101.74606</v>
       </c>
       <c r="I31" t="n">
-        <v>101.74606</v>
+        <v>4.8413</v>
       </c>
       <c r="J31" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S31" t="n">
-        <v>355034</v>
+        <v>1.324376</v>
       </c>
       <c r="T31" t="n">
-        <v>1.324376</v>
+        <v>-0.116704</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.116704</v>
+        <v>-1.908621</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="X31" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.621114</v>
+        <v>-3.178284</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.178284</v>
+        <v>3.706988</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.706988</v>
+        <v>-0.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3912,105 +3724,99 @@
         <v>0.043739</v>
       </c>
       <c r="D32" t="n">
-        <v>0.043739</v>
+        <v>0.42</v>
       </c>
       <c r="E32" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="G32" t="n">
-        <v>0.57</v>
+        <v>104.53245</v>
       </c>
       <c r="H32" t="n">
-        <v>104.53245</v>
+        <v>98.01879</v>
       </c>
       <c r="I32" t="n">
-        <v>98.01879</v>
+        <v>4.9535</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S32" t="n">
-        <v>355066</v>
+        <v>-0.349526</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.349526</v>
+        <v>-3.663306</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.663306</v>
+        <v>2.317559</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="W32" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.506637</v>
+        <v>-3.31355</v>
       </c>
       <c r="AC32" t="n">
-        <v>-3.31355</v>
+        <v>3.820543</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.820543</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -4025,105 +3831,99 @@
         <v>0.041957</v>
       </c>
       <c r="D33" t="n">
-        <v>0.041957</v>
+        <v>0.83</v>
       </c>
       <c r="E33" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.75961</v>
       </c>
       <c r="H33" t="n">
-        <v>104.75961</v>
+        <v>102.37988</v>
       </c>
       <c r="I33" t="n">
-        <v>102.37988</v>
+        <v>4.9833</v>
       </c>
       <c r="J33" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S33" t="n">
-        <v>352705</v>
+        <v>0.217311</v>
       </c>
       <c r="T33" t="n">
-        <v>0.217311</v>
+        <v>4.449239</v>
       </c>
       <c r="U33" t="n">
-        <v>4.449239</v>
+        <v>0.601595</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="W33" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="X33" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.496274</v>
+        <v>-3.758575</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.758575</v>
+        <v>3.861754</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.861754</v>
+        <v>-0.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4138,105 +3938,99 @@
         <v>0.04142</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04142</v>
+        <v>0.16</v>
       </c>
       <c r="E34" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="G34" t="n">
-        <v>0.19</v>
+        <v>104.7097</v>
       </c>
       <c r="H34" t="n">
-        <v>104.7097</v>
+        <v>109.58504</v>
       </c>
       <c r="I34" t="n">
-        <v>109.58504</v>
+        <v>4.9962</v>
       </c>
       <c r="J34" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S34" t="n">
-        <v>355008</v>
+        <v>-0.047642</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.047642</v>
+        <v>7.037672</v>
       </c>
       <c r="U34" t="n">
-        <v>7.037672</v>
+        <v>0.258865</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="W34" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="X34" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925596</v>
+        <v>-4.25878</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4.25878</v>
+        <v>3.397348</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.397348</v>
+        <v>-0.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4251,105 +4045,99 @@
         <v>0.040168</v>
       </c>
       <c r="D35" t="n">
-        <v>0.040168</v>
+        <v>0.38</v>
       </c>
       <c r="E35" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="F35" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="G35" t="n">
-        <v>0.37</v>
+        <v>104.75682</v>
       </c>
       <c r="H35" t="n">
-        <v>104.75682</v>
+        <v>109.36335</v>
       </c>
       <c r="I35" t="n">
-        <v>109.36335</v>
+        <v>5.1718</v>
       </c>
       <c r="J35" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S35" t="n">
-        <v>351599</v>
+        <v>0.045001</v>
       </c>
       <c r="T35" t="n">
-        <v>0.045001</v>
+        <v>-0.2023</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.2023</v>
+        <v>3.514671</v>
       </c>
       <c r="V35" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="W35" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="X35" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.688016</v>
+        <v>-3.040871</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.040871</v>
+        <v>3.232784</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.232784</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4364,105 +4152,99 @@
         <v>0.039484</v>
       </c>
       <c r="D36" t="n">
-        <v>0.039484</v>
+        <v>0.46</v>
       </c>
       <c r="E36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.46</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.89</v>
-      </c>
       <c r="G36" t="n">
-        <v>0.46</v>
+        <v>105.70704</v>
       </c>
       <c r="H36" t="n">
-        <v>105.70704</v>
+        <v>104.84682</v>
       </c>
       <c r="I36" t="n">
-        <v>104.84682</v>
+        <v>5.2416</v>
       </c>
       <c r="J36" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="K36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S36" t="n">
-        <v>355560</v>
+        <v>0.907072</v>
       </c>
       <c r="T36" t="n">
-        <v>0.907072</v>
+        <v>-4.129839</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.129839</v>
+        <v>1.349627</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="W36" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="X36" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.925952</v>
+        <v>-0.344269</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.344269</v>
+        <v>3.335647</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.335647</v>
+        <v>-0.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4477,105 +4259,99 @@
         <v>0.03927</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03927</v>
+        <v>0.21</v>
       </c>
       <c r="E37" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>0.25</v>
+        <v>106.57623</v>
       </c>
       <c r="H37" t="n">
-        <v>106.57623</v>
+        <v>106.03093</v>
       </c>
       <c r="I37" t="n">
-        <v>106.03093</v>
+        <v>5.5589</v>
       </c>
       <c r="J37" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S37" t="n">
-        <v>357827</v>
+        <v>0.822263</v>
       </c>
       <c r="T37" t="n">
-        <v>0.822263</v>
+        <v>1.129371</v>
       </c>
       <c r="U37" t="n">
-        <v>1.129371</v>
+        <v>6.053495</v>
       </c>
       <c r="V37" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="W37" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="X37" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.227578</v>
+        <v>2.440035</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.440035</v>
+        <v>3.697684</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.697684</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4590,105 +4366,99 @@
         <v>0.03927</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03927</v>
+        <v>0.38</v>
       </c>
       <c r="E38" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="F38" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="G38" t="n">
-        <v>0.26</v>
+        <v>106.88756</v>
       </c>
       <c r="H38" t="n">
-        <v>106.88756</v>
+        <v>111.55002</v>
       </c>
       <c r="I38" t="n">
-        <v>111.55002</v>
+        <v>5.6621</v>
       </c>
       <c r="J38" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S38" t="n">
-        <v>363282</v>
+        <v>0.29212</v>
       </c>
       <c r="T38" t="n">
-        <v>0.29212</v>
+        <v>5.20517</v>
       </c>
       <c r="U38" t="n">
-        <v>5.20517</v>
+        <v>1.856482</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="W38" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="X38" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.498245</v>
+        <v>3.812368</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.812368</v>
+        <v>4.060953</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4703,105 +4473,99 @@
         <v>0.03927</v>
       </c>
       <c r="D39" t="n">
-        <v>0.03927</v>
+        <v>-0.02</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="F39" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.14</v>
+        <v>107.14396</v>
       </c>
       <c r="H39" t="n">
-        <v>107.14396</v>
+        <v>110.19363</v>
       </c>
       <c r="I39" t="n">
-        <v>110.19363</v>
+        <v>5.6562</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S39" t="n">
-        <v>369214</v>
+        <v>0.239878</v>
       </c>
       <c r="T39" t="n">
-        <v>0.239878</v>
+        <v>-1.215948</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.215948</v>
+        <v>-0.104202</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="X39" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.237599</v>
+        <v>4.259387</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.259387</v>
+        <v>3.707852</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4816,105 +4580,99 @@
         <v>0.039612</v>
       </c>
       <c r="D40" t="n">
-        <v>0.039612</v>
+        <v>0.44</v>
       </c>
       <c r="E40" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="F40" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="G40" t="n">
-        <v>0.48</v>
+        <v>107.99916</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99916</v>
+        <v>107.28836</v>
       </c>
       <c r="I40" t="n">
-        <v>107.28836</v>
+        <v>5.4481</v>
       </c>
       <c r="J40" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S40" t="n">
-        <v>372016</v>
+        <v>0.7981780000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7981780000000001</v>
+        <v>-2.636514</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.636514</v>
+        <v>-3.679149</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="X40" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.42474</v>
+        <v>4.519075</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.519075</v>
+        <v>4.091149</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.091149</v>
+        <v>0.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4929,105 +4687,99 @@
         <v>0.040168</v>
       </c>
       <c r="D41" t="n">
-        <v>0.040168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="F41" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="G41" t="n">
-        <v>0.61</v>
+        <v>108.15356</v>
       </c>
       <c r="H41" t="n">
-        <v>108.15356</v>
+        <v>109.21678</v>
       </c>
       <c r="I41" t="n">
-        <v>109.21678</v>
+        <v>5.7779</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="K41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S41" t="n">
-        <v>366096</v>
+        <v>0.142964</v>
       </c>
       <c r="T41" t="n">
-        <v>0.142964</v>
+        <v>1.797418</v>
       </c>
       <c r="U41" t="n">
-        <v>1.797418</v>
+        <v>6.053487</v>
       </c>
       <c r="V41" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="W41" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.758099</v>
+        <v>5.579866</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.579866</v>
+        <v>4.600584</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.600584</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5042,105 +4794,99 @@
         <v>0.04158</v>
       </c>
       <c r="D42" t="n">
-        <v>0.04158</v>
+        <v>0.39</v>
       </c>
       <c r="E42" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="G42" t="n">
-        <v>0.33</v>
+        <v>107.98489</v>
       </c>
       <c r="H42" t="n">
-        <v>107.98489</v>
+        <v>105.74688</v>
       </c>
       <c r="I42" t="n">
-        <v>105.74688</v>
+        <v>6.0535</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="K42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S42" t="n">
-        <v>363003</v>
+        <v>-0.155954</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.155954</v>
+        <v>-3.177076</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.177076</v>
+        <v>4.769899</v>
       </c>
       <c r="V42" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="W42" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="X42" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.873011</v>
+        <v>6.325086</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.325086</v>
+        <v>4.840925</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.840925</v>
+        <v>0.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -5155,105 +4901,99 @@
         <v>0.044158</v>
       </c>
       <c r="D43" t="n">
-        <v>0.044158</v>
+        <v>0.52</v>
       </c>
       <c r="E43" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G43" t="n">
-        <v>0.48</v>
+        <v>107.44467</v>
       </c>
       <c r="H43" t="n">
-        <v>107.44467</v>
+        <v>104.2734</v>
       </c>
       <c r="I43" t="n">
-        <v>104.2734</v>
+        <v>6.1923</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="K43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S43" t="n">
-        <v>329730</v>
+        <v>-0.500274</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.500274</v>
+        <v>-1.393403</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.393403</v>
+        <v>2.292888</v>
       </c>
       <c r="V43" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="W43" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="X43" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="AA43" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.831296</v>
+        <v>6.536174</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.536174</v>
+        <v>4.767938</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.767938</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5268,105 +5008,99 @@
         <v>0.045833</v>
       </c>
       <c r="D44" t="n">
-        <v>0.045833</v>
+        <v>0.16</v>
       </c>
       <c r="E44" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="F44" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>108.06979</v>
       </c>
       <c r="H44" t="n">
-        <v>108.06979</v>
+        <v>101.23438</v>
       </c>
       <c r="I44" t="n">
-        <v>101.23438</v>
+        <v>5.8301</v>
       </c>
       <c r="J44" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="K44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S44" t="n">
-        <v>328303</v>
+        <v>0.581806</v>
       </c>
       <c r="T44" t="n">
-        <v>0.581806</v>
+        <v>-2.914473</v>
       </c>
       <c r="U44" t="n">
-        <v>-2.914473</v>
+        <v>-5.8492</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="W44" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="X44" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.559874</v>
+        <v>6.749097</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.749097</v>
+        <v>4.174145</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.174145</v>
+        <v>1</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5381,105 +5115,99 @@
         <v>0.049037</v>
       </c>
       <c r="D45" t="n">
-        <v>0.049037</v>
+        <v>1.31</v>
       </c>
       <c r="E45" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="F45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="G45" t="n">
-        <v>1.48</v>
+        <v>108.77346</v>
       </c>
       <c r="H45" t="n">
-        <v>108.77346</v>
+        <v>107.07838</v>
       </c>
       <c r="I45" t="n">
-        <v>107.07838</v>
+        <v>5.8488</v>
       </c>
       <c r="J45" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S45" t="n">
-        <v>332508</v>
+        <v>0.651126</v>
       </c>
       <c r="T45" t="n">
-        <v>0.651126</v>
+        <v>5.772742</v>
       </c>
       <c r="U45" t="n">
-        <v>5.772742</v>
+        <v>0.320749</v>
       </c>
       <c r="V45" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="W45" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.05763</v>
+        <v>8.444549</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.444549</v>
+        <v>4.866504</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.866504</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5494,105 +5222,99 @@
         <v>0.050508</v>
       </c>
       <c r="D46" t="n">
-        <v>0.050508</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="G46" t="n">
-        <v>0.51</v>
+        <v>110.09056</v>
       </c>
       <c r="H46" t="n">
-        <v>110.09056</v>
+        <v>114.05013</v>
       </c>
       <c r="I46" t="n">
-        <v>114.05013</v>
+        <v>5.7422</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S46" t="n">
-        <v>336157</v>
+        <v>1.210865</v>
       </c>
       <c r="T46" t="n">
-        <v>1.210865</v>
+        <v>6.510885</v>
       </c>
       <c r="U46" t="n">
-        <v>6.510885</v>
+        <v>-1.822596</v>
       </c>
       <c r="V46" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="X46" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.47719</v>
+        <v>8.586193</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.586193</v>
+        <v>5.201441</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201441</v>
+        <v>1</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5607,105 +5329,99 @@
         <v>0.052531</v>
       </c>
       <c r="D47" t="n">
-        <v>0.052531</v>
+        <v>0.43</v>
       </c>
       <c r="E47" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="F47" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="G47" t="n">
-        <v>0.48</v>
+        <v>109.72323</v>
       </c>
       <c r="H47" t="n">
-        <v>109.72323</v>
+        <v>112.73813</v>
       </c>
       <c r="I47" t="n">
-        <v>112.73813</v>
+        <v>5.6608</v>
       </c>
       <c r="J47" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="K47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S47" t="n">
-        <v>340789</v>
+        <v>-0.333662</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.333662</v>
+        <v>-1.150371</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.150371</v>
+        <v>-1.417575</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="X47" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.529729</v>
+        <v>8.510418</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.510418</v>
+        <v>5.316736</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.316736</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5720,105 +5436,99 @@
         <v>0.053936</v>
       </c>
       <c r="D48" t="n">
-        <v>0.053936</v>
+        <v>0.26</v>
       </c>
       <c r="E48" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="G48" t="n">
-        <v>0.35</v>
+        <v>109.00057</v>
       </c>
       <c r="H48" t="n">
-        <v>109.00057</v>
+        <v>108.66481</v>
       </c>
       <c r="I48" t="n">
-        <v>108.66481</v>
+        <v>5.7087</v>
       </c>
       <c r="J48" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="K48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S48" t="n">
-        <v>341459</v>
+        <v>-0.658621</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.658621</v>
+        <v>-3.613081</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.613081</v>
+        <v>0.84617</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="W48" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="X48" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.319636</v>
+        <v>7.026183</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.026183</v>
+        <v>5.201418</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.201418</v>
+        <v>0.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5833,105 +5543,99 @@
         <v>0.054569</v>
       </c>
       <c r="D49" t="n">
-        <v>0.054569</v>
+        <v>0.24</v>
       </c>
       <c r="E49" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="G49" t="n">
-        <v>0.23</v>
+        <v>108.76683</v>
       </c>
       <c r="H49" t="n">
-        <v>108.76683</v>
+        <v>107.55639</v>
       </c>
       <c r="I49" t="n">
-        <v>107.55639</v>
+        <v>5.4571</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S49" t="n">
-        <v>344440</v>
+        <v>-0.214439</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.214439</v>
+        <v>-1.020036</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.020036</v>
+        <v>-4.407308</v>
       </c>
       <c r="V49" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="W49" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.351165</v>
+        <v>4.393261</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.393261</v>
+        <v>5.18043</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.18043</v>
+        <v>0.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5946,105 +5650,99 @@
         <v>0.055131</v>
       </c>
       <c r="D50" t="n">
-        <v>0.055131</v>
+        <v>0.26</v>
       </c>
       <c r="E50" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="G50" t="n">
+        <v>108.27053</v>
+      </c>
+      <c r="H50" t="n">
+        <v>113.14433</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="R50" t="n">
+        <v>345111</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-0.456297</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5.195358</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0.21</v>
       </c>
-      <c r="H50" t="n">
-        <v>108.27053</v>
-      </c>
-      <c r="I50" t="n">
-        <v>113.14433</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="L50" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R50" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="S50" t="n">
-        <v>345111</v>
-      </c>
-      <c r="T50" t="n">
-        <v>-0.456297</v>
-      </c>
-      <c r="U50" t="n">
-        <v>5.195358</v>
-      </c>
-      <c r="V50" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>5.225222</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.000562</v>
-      </c>
       <c r="AG50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -6059,105 +5757,99 @@
         <v>0.055131</v>
       </c>
       <c r="D51" t="n">
-        <v>0.055131</v>
+        <v>-0.11</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="F51" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.21</v>
+        <v>108.80021</v>
       </c>
       <c r="H51" t="n">
-        <v>108.80021</v>
+        <v>110.57963</v>
       </c>
       <c r="I51" t="n">
-        <v>110.57963</v>
+        <v>5.4264</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S51" t="n">
-        <v>350767</v>
+        <v>0.489219</v>
       </c>
       <c r="T51" t="n">
-        <v>0.489219</v>
+        <v>-2.266751</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.266751</v>
+        <v>-3.136324</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="X51" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.130501</v>
+        <v>3.033233</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.033233</v>
+        <v>5.054283</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6172,105 +5864,99 @@
         <v>0.055131</v>
       </c>
       <c r="D52" t="n">
-        <v>0.055131</v>
+        <v>0.48</v>
       </c>
       <c r="E52" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="F52" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="G52" t="n">
-        <v>0.52</v>
+        <v>108.63642</v>
       </c>
       <c r="H52" t="n">
-        <v>108.63642</v>
+        <v>109.59513</v>
       </c>
       <c r="I52" t="n">
-        <v>109.59513</v>
+        <v>5.3186</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="K52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S52" t="n">
-        <v>356582</v>
+        <v>-0.150542</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.150542</v>
+        <v>-0.890309</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.890309</v>
+        <v>-1.986584</v>
       </c>
       <c r="V52" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="X52" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.172369</v>
+        <v>2.828436</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.828436</v>
+        <v>5.096104</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6285,105 +5971,99 @@
         <v>0.055131</v>
       </c>
       <c r="D53" t="n">
-        <v>0.055131</v>
+        <v>0.09</v>
       </c>
       <c r="E53" t="n">
-        <v>0.09</v>
+        <v>-0.36</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="G53" t="n">
-        <v>0.03</v>
+        <v>108.7159</v>
       </c>
       <c r="H53" t="n">
-        <v>108.7159</v>
+        <v>110.16346</v>
       </c>
       <c r="I53" t="n">
-        <v>110.16346</v>
+        <v>5.3843</v>
       </c>
       <c r="J53" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="K53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S53" t="n">
-        <v>357103</v>
+        <v>0.073161</v>
       </c>
       <c r="T53" t="n">
-        <v>0.073161</v>
+        <v>0.518572</v>
       </c>
       <c r="U53" t="n">
-        <v>0.518572</v>
+        <v>1.235287</v>
       </c>
       <c r="V53" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="W53" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="X53" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.680811</v>
+        <v>0.924206</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.924206</v>
+        <v>4.490243</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6398,105 +6078,99 @@
         <v>0.055131</v>
       </c>
       <c r="D54" t="n">
-        <v>0.055131</v>
+        <v>0.18</v>
       </c>
       <c r="E54" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="F54" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="G54" t="n">
-        <v>0.03</v>
+        <v>109.27405</v>
       </c>
       <c r="H54" t="n">
-        <v>109.27405</v>
+        <v>106.90236</v>
       </c>
       <c r="I54" t="n">
-        <v>106.90236</v>
+        <v>5.3338</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="L54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="M54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="N54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="O54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="P54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="R54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="S54" t="n">
-        <v>360578</v>
+        <v>0.513402</v>
       </c>
       <c r="T54" t="n">
-        <v>0.513402</v>
+        <v>-2.960237</v>
       </c>
       <c r="U54" t="n">
-        <v>-2.960237</v>
+        <v>-0.937912</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.938017</v>
+        <v>1.146567</v>
       </c>
       <c r="X54" t="n">
-        <v>1.146567</v>
+        <v>0.715383</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.715383</v>
+        <v>1.405488</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.405488</v>
+        <v>0.973109</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.461836</v>
+        <v>-0.101973</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.101973</v>
+        <v>4.177803</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.177803</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6511,105 +6185,99 @@
         <v>0.055131</v>
       </c>
       <c r="D55" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="E55" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="G55" t="n">
-        <v>0.21</v>
+        <v>109.41762</v>
       </c>
       <c r="H55" t="n">
-        <v>109.41762</v>
+        <v>107.17649</v>
       </c>
       <c r="I55" t="n">
-        <v>107.17649</v>
+        <v>5.5024</v>
       </c>
       <c r="J55" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="K55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="L55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="M55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="N55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="P55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="R55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="S55" t="n">
-        <v>358234</v>
+        <v>0.131385</v>
       </c>
       <c r="T55" t="n">
-        <v>0.131385</v>
+        <v>0.25643</v>
       </c>
       <c r="U55" t="n">
-        <v>0.25643</v>
+        <v>3.160973</v>
       </c>
       <c r="V55" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="W55" t="n">
-        <v>3.161329</v>
+        <v>1.90144</v>
       </c>
       <c r="X55" t="n">
-        <v>1.90144</v>
+        <v>3.24641</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.24641</v>
+        <v>1.099346</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.099346</v>
+        <v>-0.650067</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.264385</v>
+        <v>-1.042167</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.042167</v>
+        <v>3.897866</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0</v>
       </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="AI55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6624,105 +6292,99 @@
         <v>0.055131</v>
       </c>
       <c r="D56" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="E56" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="F56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G56" t="n">
-        <v>0.39</v>
+        <v>110.05486</v>
       </c>
       <c r="H56" t="n">
-        <v>110.05486</v>
+        <v>102.36456</v>
       </c>
       <c r="I56" t="n">
-        <v>102.36456</v>
+        <v>5.2301</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="L56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="M56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="N56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="O56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="P56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="S56" t="n">
-        <v>364367</v>
+        <v>0.582392</v>
       </c>
       <c r="T56" t="n">
-        <v>0.582392</v>
+        <v>-4.489725</v>
       </c>
       <c r="U56" t="n">
-        <v>-4.489725</v>
+        <v>-4.94875</v>
       </c>
       <c r="V56" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.949289</v>
+        <v>-0.083179</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.083179</v>
+        <v>-1.743482</v>
       </c>
       <c r="Y56" t="n">
-        <v>-1.743482</v>
+        <v>0.927966</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.927966</v>
+        <v>1.712009</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.441351</v>
+        <v>-0.903999</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.903999</v>
+        <v>4.303068</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6737,105 +6399,99 @@
         <v>0.055131</v>
       </c>
       <c r="D57" t="n">
-        <v>0.055131</v>
+        <v>0.7</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.65892</v>
       </c>
       <c r="H57" t="n">
-        <v>110.65892</v>
+        <v>106.82125</v>
       </c>
       <c r="I57" t="n">
-        <v>106.82125</v>
+        <v>5.1495</v>
       </c>
       <c r="J57" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="K57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="L57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="M57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="N57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="R57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="S57" t="n">
-        <v>371074</v>
+        <v>0.548872</v>
       </c>
       <c r="T57" t="n">
-        <v>0.548872</v>
+        <v>4.353743</v>
       </c>
       <c r="U57" t="n">
-        <v>4.353743</v>
+        <v>-1.54108</v>
       </c>
       <c r="V57" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.541256</v>
+        <v>0.371461</v>
       </c>
       <c r="X57" t="n">
-        <v>0.371461</v>
+        <v>0.070797</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.070797</v>
+        <v>0.549722</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.549722</v>
+        <v>1.840727</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="AB57" t="n">
-        <v>3.812497</v>
+        <v>-2.659212</v>
       </c>
       <c r="AC57" t="n">
-        <v>-2.659212</v>
+        <v>3.357475</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6850,105 +6506,99 @@
         <v>0.054777</v>
       </c>
       <c r="D58" t="n">
-        <v>0.054777</v>
+        <v>0.88</v>
       </c>
       <c r="E58" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="F58" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="G58" t="n">
-        <v>0.91</v>
+        <v>110.51078</v>
       </c>
       <c r="H58" t="n">
-        <v>110.51078</v>
+        <v>117.8089</v>
       </c>
       <c r="I58" t="n">
-        <v>117.8089</v>
+        <v>5.2194</v>
       </c>
       <c r="J58" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="L58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="M58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="N58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="O58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="P58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="R58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="S58" t="n">
-        <v>362002</v>
+        <v>-0.133871</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.133871</v>
+        <v>10.286015</v>
       </c>
       <c r="U58" t="n">
-        <v>10.286015</v>
+        <v>1.357413</v>
       </c>
       <c r="V58" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="W58" t="n">
-        <v>1.357572</v>
+        <v>1.12824</v>
       </c>
       <c r="X58" t="n">
-        <v>1.12824</v>
+        <v>1.133877</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.133877</v>
+        <v>1.124914</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.124914</v>
+        <v>-2.444795</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.142847</v>
+        <v>-1.819225</v>
       </c>
       <c r="AC58" t="n">
-        <v>-1.819225</v>
+        <v>3.768807</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.768807</v>
+        <v>-0.25</v>
       </c>
       <c r="AE58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6963,105 +6613,99 @@
         <v>0.054223</v>
       </c>
       <c r="D59" t="n">
-        <v>0.054223</v>
+        <v>0.67</v>
       </c>
       <c r="E59" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="F59" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8100000000000001</v>
+        <v>110.95732</v>
       </c>
       <c r="H59" t="n">
-        <v>110.95732</v>
+        <v>113.99365</v>
       </c>
       <c r="I59" t="n">
-        <v>113.99365</v>
+        <v>4.9886</v>
       </c>
       <c r="J59" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="K59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="L59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="M59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="N59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="O59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="R59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="S59" t="n">
-        <v>366913</v>
+        <v>0.404069</v>
       </c>
       <c r="T59" t="n">
-        <v>0.404069</v>
+        <v>-3.238507</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.238507</v>
+        <v>-4.421964</v>
       </c>
       <c r="V59" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="W59" t="n">
-        <v>-4.422473</v>
+        <v>0.288267</v>
       </c>
       <c r="X59" t="n">
-        <v>0.288267</v>
+        <v>-0.052977</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.052977</v>
+        <v>0.489642</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.489642</v>
+        <v>1.356622</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.39172</v>
+        <v>0.619623</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.619623</v>
+        <v>4.109608</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.109608</v>
+        <v>-0.25</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -7076,105 +6720,99 @@
         <v>0.0534</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0534</v>
+        <v>0.58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="F60" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="G60" t="n">
-        <v>0.65</v>
+        <v>111.03587</v>
       </c>
       <c r="H60" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="I60" t="n">
-        <v>109.52993</v>
+        <v>5.0569</v>
       </c>
       <c r="J60" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="L60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="M60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="N60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="O60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="P60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="R60" t="n">
-        <v>33.42</v>
+        <v>371137</v>
       </c>
       <c r="S60" t="n">
-        <v>371137</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="T60" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
       <c r="U60" t="n">
-        <v>-3.915762</v>
+        <v>1.369122</v>
       </c>
       <c r="V60" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="W60" t="n">
-        <v>1.369286</v>
+        <v>0.565068</v>
       </c>
       <c r="X60" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.461065</v>
+        <v>1.151227</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.724907</v>
+        <v>1.964454</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.964454</v>
+        <v>4.420848</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.420848</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -7189,71 +6827,65 @@
         <v>0.053028</v>
       </c>
       <c r="D61" t="n">
-        <v>0.053028</v>
+        <v>0.16</v>
       </c>
       <c r="E61" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="G61" t="n">
         <v>0.14</v>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>5.1766</v>
+      </c>
       <c r="J61" t="n">
-        <v>5.1766</v>
-      </c>
-      <c r="K61" t="n">
         <v>5.176</v>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>367558</v>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="V61" t="n">
-        <v>2.367063</v>
-      </c>
-      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="AA61" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="AC61" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="AD61" t="n">
-        <v>4.327084</v>
+        <v>-0.25</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7265,20 +6897,18 @@
       <c r="C62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="D62" t="n">
-        <v>0.052531</v>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>5.0666</v>
+      </c>
       <c r="J62" t="n">
-        <v>5.0807</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.0801</v>
-      </c>
+        <v>5.066</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7288,33 +6918,29 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-2.124947</v>
+      </c>
       <c r="V62" t="n">
-        <v>-1.852567</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-1.852782</v>
-      </c>
+        <v>-2.125193</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
       <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,160 +438,170 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cdi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>ipca</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ibc_br_sa</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -608,51 +618,53 @@
         <v>0.016137</v>
       </c>
       <c r="D2" t="n">
+        <v>0.016137</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.96</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.78</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1.02</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>96.31464</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>99.83978</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.121</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4271865</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1833179</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2438686</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.36</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.58</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2.94</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>20.26</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>355671</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -681,93 +695,99 @@
         <v>0.019413</v>
       </c>
       <c r="D3" t="n">
+        <v>0.019413</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.66</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.88</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>97.07568000000001</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>99.32829</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4346060</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1851006</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2495054</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.37</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.56</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.96</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>20.92</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>370395</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.79016</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>-0.512311</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -782,93 +802,99 @@
         <v>0.021003</v>
       </c>
       <c r="D4" t="n">
+        <v>0.021003</v>
+      </c>
+      <c r="E4" t="n">
         <v>1.16</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.2</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>96.95968999999999</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>97.24746</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4441056</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1894119</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2546936</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.34</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.43</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>21.42</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>368886</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>-0.119484</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>-2.094902</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="AH4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -883,93 +909,99 @@
         <v>0.024244</v>
       </c>
       <c r="D5" t="n">
+        <v>0.024244</v>
+      </c>
+      <c r="E5" t="n">
         <v>1.25</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.64</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1.16</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>97.48142</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>96.62081999999999</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5.643</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4511956</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1910940</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2601017</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.33</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.43</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>22.89</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>367927</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.53809</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>-0.644377</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -984,93 +1016,99 @@
         <v>0.029256</v>
       </c>
       <c r="D6" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.95</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.02</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.84</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>98.97262000000001</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>98.05768</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4597507</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1933111</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2664395</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.36</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>23.91</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>367772</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1.529727</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.487112</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1085,93 +1123,99 @@
         <v>0.033316</v>
       </c>
       <c r="D7" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.73</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.87</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.73</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>99.35339</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>99.33126</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4682852</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1974391</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2708461</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.35</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>24.21</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>362204</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.384723</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.298807</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="n">
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="AH7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1186,93 +1230,99 @@
         <v>0.034749</v>
       </c>
       <c r="D8" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.82</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.67</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>97.34401</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>90.45032</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4682131</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1947035</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2735096</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.51</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.46</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>25.23</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>358398</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-2.022457</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>-8.94073</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1287,93 +1337,99 @@
         <v>0.039598</v>
       </c>
       <c r="D9" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="E9" t="n">
         <v>1.01</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1.83</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>98.43725000000001</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>95.72214</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4727818</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1971524</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2756295</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.57</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.44</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>25.63</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>357740</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1.123069</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>5.828415</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1388,93 +1444,99 @@
         <v>0.041954</v>
       </c>
       <c r="D10" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="E10" t="n">
         <v>1.62</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1.74</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1.71</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>99.55981</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>104.61484</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4794583</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1994119</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2800464</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.66</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.55</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>26.54</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>353169</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1.140381</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>9.290118</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="n">
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1489,93 +1551,99 @@
         <v>0.043739</v>
       </c>
       <c r="D11" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.06</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1.41</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1.04</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>99.51646</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>100.42352</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4833732</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2003312</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2830420</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.72</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.57</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.46</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>345097</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.043542</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-4.00643</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1590,93 +1658,99 @@
         <v>0.046796</v>
       </c>
       <c r="D12" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.47</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.52</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.45</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>99.67415</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>99.79777</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4889397</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2013726</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2875671</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.79</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.57</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>27.42</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346415</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0.158456</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-0.623111</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1691,99 +1765,105 @@
         <v>0.048116</v>
       </c>
       <c r="D13" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.67</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.59</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.62</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>99.6343</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>99.53784</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.238</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>4965603</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2052569</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2913035</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.73</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.52</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>27.88</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>341958</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.03998</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-0.260457</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="AH13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1798,99 +1878,105 @@
         <v>0.049037</v>
       </c>
       <c r="D14" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="E14" t="n">
         <v>-0.68</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0.21</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>101.27684</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>103.95861</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4999244</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2047038</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2952207</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.84</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>29.24</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>346403</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1.648569</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>4.441296</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AJ14" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1905,99 +1991,105 @@
         <v>0.05056</v>
       </c>
       <c r="D15" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="E15" t="n">
         <v>-0.36</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-0.31</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>101.07328</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>104.56278</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>5.179</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5072711</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2064183</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3008528</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2.9</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>28.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>339664</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-0.200994</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>0.581164</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AF15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AG15" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2012,99 +2104,105 @@
         <v>0.050788</v>
       </c>
       <c r="D16" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E16" t="n">
         <v>-0.29</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>101.17973</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>101.38087</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.406</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5164775</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2109806</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3054969</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2.92</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.65</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>28.57</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>327580</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0.10532</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-3.043062</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AF16" t="n">
-        <v>0.02</v>
-      </c>
       <c r="AG16" t="n">
-        <v>0.03</v>
+        <v>0.000228</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2119,99 +2217,105 @@
         <v>0.050788</v>
       </c>
       <c r="D17" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.59</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-0.97</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.47</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>101.46342</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>100.20398</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>5.257</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5215990</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2105856</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3110134</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.04</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.77</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.68</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>325546</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>0.280382</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-1.16086</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2226,99 +2330,105 @@
         <v>0.050788</v>
       </c>
       <c r="D18" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.41</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.38</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>100.66227</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>99.36927</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5285657</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2130312</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3155345</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.07</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.81</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.52</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331505</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.789595</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-0.8330109999999999</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2333,99 +2443,105 @@
         <v>0.050788</v>
       </c>
       <c r="D19" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.62</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.45</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>100.58196</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>99.97806</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5366069</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2178236</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3187833</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.07</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1.8</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>29.64</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>324703</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-0.07978200000000001</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>0.612654</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>-0</v>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
       <c r="AG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2440,99 +2556,105 @@
         <v>0.050788</v>
       </c>
       <c r="D20" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.53</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.21</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.46</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>100.05178</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>93.79237000000001</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5373231</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2151399</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3221831</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.24</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1.94</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.54</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>331122</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-0.527112</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>-6.187047</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2547,99 +2669,105 @@
         <v>0.050788</v>
       </c>
       <c r="D21" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.84</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.77</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>103.00964</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>98.75064999999999</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5370950</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2136105</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3234845</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.36</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.17</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>30.48</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>328098</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>2.956329</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>5.286443</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2654,99 +2782,105 @@
         <v>0.050788</v>
       </c>
       <c r="D22" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.71</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.05</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.64</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>103.09341</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>110.62354</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5424811</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2154900</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3269910</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.35</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>30.99</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>341158</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>0.08132200000000001</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>12.023101</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2761,99 +2895,105 @@
         <v>0.050788</v>
       </c>
       <c r="D23" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.61</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>0.53</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>104.1626</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>104.34152</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5426307</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2145000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3281308</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.54</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.45</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>31.62</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>345725</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1.037108</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>-5.678737</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2868,99 +3008,105 @@
         <v>0.050788</v>
       </c>
       <c r="D24" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.23</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-1.84</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0.36</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>102.3642</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>102.66392</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5453708</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2145530</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3308178</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.65</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.58</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>31.63</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>343489</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-1.726531</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-1.607797</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
         <v>-0</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2975,99 +3121,105 @@
         <v>0.050788</v>
       </c>
       <c r="D25" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E25" t="n">
         <v>-0.08</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-1.93</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>102.50431</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>102.53174</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5479459</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2169613</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3309846</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.63</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>30.85</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>343620</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>0.136874</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-0.12875</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3082,99 +3234,105 @@
         <v>0.050788</v>
       </c>
       <c r="D26" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.12</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-0.72</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>102.83357</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>105.47522</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5484871</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2153541</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3331330</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.63</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.73</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>30.43</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>345476</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>0.321216</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>2.870799</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3189,99 +3347,105 @@
         <v>0.049189</v>
       </c>
       <c r="D27" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.23</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.2</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>102.45222</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>106.13139</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5559063</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2172658</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3386405</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.61</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.82</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.92</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>344177</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-0.370842</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>0.622108</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AG27" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="AH27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3296,99 +3460,105 @@
         <v>0.048422</v>
       </c>
       <c r="D28" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.26</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.37</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>0.11</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>102.57885</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>102.00419</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>5.007</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5625945</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2215175</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3410769</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.54</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.82</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.66</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>340324</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>0.123599</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-3.888765</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AF28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="AH28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3403,99 +3573,105 @@
         <v>0.047279</v>
       </c>
       <c r="D29" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.24</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.5</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>0.12</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>102.87707</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>102.0744</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5653808</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2204808</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3449000</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.56</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.92</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>29.24</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>340247</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>0.290723</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>0.068831</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
       <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AG29" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3510,99 +3686,105 @@
         <v>0.045601</v>
       </c>
       <c r="D30" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.28</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>0.59</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.1</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>103.528</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>101.86494</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5711103</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2220766</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3490337</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.53</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.99</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>29.01</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>348406</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>0.632726</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-0.205203</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AF30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AG30" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="AH30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3617,99 +3799,105 @@
         <v>0.044537</v>
       </c>
       <c r="D31" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="E31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.74</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.55</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>104.8991</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>101.74606</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5805157</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2283485</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3521672</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.29</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.59</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>28.14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>355034</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1.324376</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>-0.116704</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AG31" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="AH31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AJ31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3724,99 +3912,105 @@
         <v>0.043739</v>
       </c>
       <c r="D32" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.42</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>104.53245</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>98.01879</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5794707</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2234362</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3560345</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.38</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.77</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355066</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-0.349526</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-3.663306</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
       <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AG32" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AJ32" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3831,99 +4025,105 @@
         <v>0.041957</v>
       </c>
       <c r="D33" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="E33" t="n">
         <v>0.83</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>104.75961</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>102.37988</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5815954</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2235302</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3580652</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.38</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.85</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>352705</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>0.217311</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>4.449239</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AF33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
       <c r="AG33" t="n">
+        <v>-0.001782</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3938,99 +4138,105 @@
         <v>0.04142</v>
       </c>
       <c r="D34" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>-0.47</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>0.19</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>104.7097</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>109.58504</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5899742</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2285775</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3613967</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.33</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.71</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>28.14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355008</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>-0.047642</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>7.037672</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AF34" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="AG34" t="n">
-        <v>-0.05</v>
+        <v>-0.000537</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4045,99 +4251,105 @@
         <v>0.040168</v>
       </c>
       <c r="D35" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.38</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>0.31</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.37</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>104.75682</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>109.36335</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>5915538</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2268879</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3646659</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.37</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.76</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.86</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>351599</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>0.045001</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>-0.2023</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
       <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AF35" t="n">
-        <v>0.04</v>
-      </c>
       <c r="AG35" t="n">
-        <v>0.05</v>
+        <v>-0.001252</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4152,99 +4364,105 @@
         <v>0.039484</v>
       </c>
       <c r="D36" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.46</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.89</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>0.46</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>105.70704</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>104.84682</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.241</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>5953960</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2278309</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3675652</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.43</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.8</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.75</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>355560</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>0.907072</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>-4.129839</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Z36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AE36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AF36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AG36" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4259,99 +4477,105 @@
         <v>0.03927</v>
       </c>
       <c r="D37" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.21</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>0.25</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>106.57623</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>106.03093</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6041898</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2336858</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3705041</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.29</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.64</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.81</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>357827</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>0.822263</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>1.129371</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Z37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AG37" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="AH37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4366,99 +4590,105 @@
         <v>0.03927</v>
       </c>
       <c r="D38" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.38</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>0.61</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.26</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>106.88756</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>111.55002</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6069205</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2323362</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3745844</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.3</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.52</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.74</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>363282</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>0.29212</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>5.20517</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4473,99 +4703,105 @@
         <v>0.03927</v>
       </c>
       <c r="D39" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E39" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.29</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>-0.14</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>107.14396</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>110.19363</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6135298</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2344397</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3790900</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.33</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.55</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.59</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>369214</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>0.239878</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>-1.215948</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4580,99 +4816,105 @@
         <v>0.039612</v>
       </c>
       <c r="D40" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="E40" t="n">
         <v>0.44</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>0.62</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.48</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>107.99916</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>107.28836</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6216528</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2384828</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3831700</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.34</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.56</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>27.49</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>372016</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>0.7981780000000001</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>-2.636514</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Y40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Z40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AB40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AF40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AF40" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AG40" t="n">
-        <v>0.01</v>
+        <v>0.000342</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4687,99 +4929,105 @@
         <v>0.040168</v>
       </c>
       <c r="D41" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="E41" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>1.52</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.61</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>108.15356</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>109.21678</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6275117</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2397533</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3877584</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.3</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.52</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>27.94</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>366096</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>0.142964</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>1.797418</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Y41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
       <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AF41" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="AG41" t="n">
-        <v>-0.04</v>
+        <v>0.000556</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4794,99 +5042,105 @@
         <v>0.04158</v>
       </c>
       <c r="D42" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="E42" t="n">
         <v>0.39</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1.3</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>0.33</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>107.98489</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>105.74688</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6365690</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2436022</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>3929668</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>28.45</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>363003</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>-0.155954</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>-3.177076</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Z42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AE42" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AF42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AG42" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="AH42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AJ42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4901,99 +5155,105 @@
         <v>0.044158</v>
       </c>
       <c r="D43" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="E43" t="n">
         <v>0.52</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>0.48</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>107.44467</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>104.2734</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6464602</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2499177</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>3965425</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.08</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.21</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>28.5</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>329730</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>-0.500274</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>-1.393403</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Z43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
         <v>1</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AF43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AG43" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="AH43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AJ43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5008,99 +5268,105 @@
         <v>0.045833</v>
       </c>
       <c r="D44" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="E44" t="n">
         <v>0.16</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>0.27</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>108.06979</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>101.23438</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6465016</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2451957</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4013059</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.34</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.43</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>29.88</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>328303</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>0.581806</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>-2.914473</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Z44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AF44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AF44" t="n">
-        <v>0.26</v>
-      </c>
       <c r="AG44" t="n">
-        <v>0.22</v>
+        <v>0.001675</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5115,99 +5381,105 @@
         <v>0.049037</v>
       </c>
       <c r="D45" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="E45" t="n">
         <v>1.31</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>1.06</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>1.48</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>108.77346</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>107.07838</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6511444</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2477151</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4034293</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.41</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.52</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>30.53</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>332508</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>0.651126</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>5.772742</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AD45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
       <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AF45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="AG45" t="n">
-        <v>0.09</v>
+        <v>0.003204</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5222,99 +5494,105 @@
         <v>0.050508</v>
       </c>
       <c r="D46" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="E46" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>-0.34</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.51</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>110.09056</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>114.05013</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6576464</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2498262</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4078202</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.44</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.49</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.34</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>336157</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>1.210865</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>6.510885</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AE46" t="n">
         <v>1</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AF46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AG46" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5329,99 +5607,105 @@
         <v>0.052531</v>
       </c>
       <c r="D47" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="E47" t="n">
         <v>0.43</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>0.24</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>0.48</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>109.72323</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>112.73813</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6623948</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2512426</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4111522</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.67</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.72</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.63</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>340789</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.333662</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>-1.150371</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Z47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AD47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
       <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="AH47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AJ47" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5436,99 +5720,105 @@
         <v>0.053936</v>
       </c>
       <c r="D48" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="E48" t="n">
         <v>0.26</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>-0.49</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.35</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>109.00057</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>108.66481</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6666287</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2532708</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4133579</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.72</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.67</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.7</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>341459</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.658621</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>-3.613081</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AD48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AF48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AG48" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="AH48" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5543,99 +5833,105 @@
         <v>0.054569</v>
       </c>
       <c r="D49" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="E49" t="n">
         <v>0.24</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>-1.67</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>0.23</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>108.76683</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>107.55639</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6703663</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2547693</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4155970</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>3.75</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.67</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.85</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>344440</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>-0.214439</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>-1.020036</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AE49" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AF49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AG49" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5650,99 +5946,105 @@
         <v>0.055131</v>
       </c>
       <c r="D50" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E50" t="n">
         <v>0.26</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>-0.77</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>0.21</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>108.27053</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>113.14433</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6733209</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2544400</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4188808</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>3.96</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.79</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.75</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>345111</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.456297</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>5.195358</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Z50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
       <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AG50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5757,99 +6059,105 @@
         <v>0.055131</v>
       </c>
       <c r="D51" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E51" t="n">
         <v>-0.11</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>0.36</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>108.80021</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>110.57963</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6774436</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2546265</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4228171</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.14</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.85</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>31.87</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>350767</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>0.489219</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>-2.266751</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5864,99 +6172,105 @@
         <v>0.055131</v>
       </c>
       <c r="D52" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E52" t="n">
         <v>0.48</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>0.42</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.52</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>108.63642</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>109.59513</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.318</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>6852705</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2589817</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4262888</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.09</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.77</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>31.47</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>356582</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>-0.150542</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>-0.890309</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5971,99 +6285,105 @@
         <v>0.055131</v>
       </c>
       <c r="D53" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E53" t="n">
         <v>0.09</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>-0.36</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>0.03</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>108.7159</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>110.16346</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>6923886</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2597630</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4326256</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.18</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.82</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>32.04</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>357103</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>0.073161</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>0.518572</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AJ53" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6078,99 +6398,105 @@
         <v>0.055131</v>
       </c>
       <c r="D54" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E54" t="n">
         <v>0.18</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>0.27</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.03</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>109.27405</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>106.90236</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7003273</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2616213</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4387061</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.23</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.74</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.32</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>360578</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>0.513402</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>-2.960237</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Z54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
       <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
         <v>-0</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AG54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6185,99 +6511,105 @@
         <v>0.055131</v>
       </c>
       <c r="D55" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E55" t="n">
         <v>0.33</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>0.21</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>109.41762</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>107.17649</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7136436</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2701146</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4435290</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.2</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>2.68</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>31.99</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>358234</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>0.131385</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>0.25643</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AD55" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6292,99 +6624,105 @@
         <v>0.055131</v>
       </c>
       <c r="D56" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E56" t="n">
         <v>0.33</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>0.41</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>0.39</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>110.05486</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>102.36456</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7130500</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2654052</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4476448</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.45</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>2.87</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.6</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>364367</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>0.582392</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>-4.489725</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Z56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AD56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>0.19</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6399,99 +6737,105 @@
         <v>0.055131</v>
       </c>
       <c r="D57" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E57" t="n">
         <v>0.7</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>-0.73</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>110.65892</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>106.82125</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7156987</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2655931</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4501056</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.07</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>32.78</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>371074</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.548872</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>4.353743</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AC57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AD57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AJ57" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6506,99 +6850,105 @@
         <v>0.054777</v>
       </c>
       <c r="D58" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="E58" t="n">
         <v>0.88</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>0.52</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.91</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>110.51078</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>117.8089</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7237735</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2686046</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4551689</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.52</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.04</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>32.99</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>362002</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>-0.133871</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>10.286015</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AB58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AC58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AD58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AE58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AF58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AG58" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="AH58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6613,99 +6963,105 @@
         <v>0.054223</v>
       </c>
       <c r="D59" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="E59" t="n">
         <v>0.67</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>2.73</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>110.95732</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>113.99365</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>4.988</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7258599</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2684623</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4573976</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.63</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.15</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.51</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>366913</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>0.404069</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>-3.238507</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AB59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AC59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AD59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AF59" t="n">
-        <v>0.11</v>
-      </c>
       <c r="AG59" t="n">
-        <v>0.11</v>
+        <v>-0.000554</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6720,99 +7076,105 @@
         <v>0.0534</v>
       </c>
       <c r="D60" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="E60" t="n">
         <v>0.58</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>0.84</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>0.65</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>111.03587</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>109.52993</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7299615</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2704550</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4595065</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.74</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.24</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>33.42</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>371137</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>0.07079299999999999</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>-3.915762</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Z60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AB60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AC60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AD60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
       <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AF60" t="n">
-        <v>0.11</v>
-      </c>
       <c r="AG60" t="n">
-        <v>0.09</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -6827,65 +7189,71 @@
         <v>0.053028</v>
       </c>
       <c r="D61" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="E61" t="n">
         <v>0.16</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>0.14</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.176</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>367558</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="n">
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AB61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AC61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AD61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
+      <c r="AG61" t="n">
+        <v>-0.000372</v>
+      </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6897,18 +7265,20 @@
       <c r="C62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>0.052531</v>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
         <v>5.0666</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>5.066</v>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6918,29 +7288,33 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
         <v>-2.124947</v>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>-2.125193</v>
       </c>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AG62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,150 +458,140 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>var_pct_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -630,41 +620,39 @@
         <v>1.02</v>
       </c>
       <c r="H2" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="I2" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="K2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="L2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="M2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="N2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="R2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="S2" t="n">
         <v>355671</v>
       </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -681,8 +669,6 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -707,87 +693,81 @@
         <v>0.88</v>
       </c>
       <c r="H3" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="I3" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="L3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="M3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="N3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="R3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="S3" t="n">
-        <v>370395</v>
+        <v>-0.512311</v>
       </c>
       <c r="T3" t="n">
-        <v>0.79016</v>
+        <v>0.423696</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.512311</v>
+        <v>0.423745</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="W3" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="X3" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.972464</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.003276</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -814,87 +794,81 @@
         <v>1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>96.95968999999999</v>
+        <v>97.24746</v>
       </c>
       <c r="I4" t="n">
-        <v>97.24746</v>
+        <v>5.4394</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="L4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="M4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="N4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="S4" t="n">
-        <v>368886</v>
+        <v>-2.094902</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.119484</v>
+        <v>5.757004</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.094902</v>
+        <v>5.757676</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="W4" t="n">
-        <v>5.757676</v>
+        <v>2.329166</v>
       </c>
       <c r="X4" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.329166</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -921,87 +895,81 @@
         <v>1.16</v>
       </c>
       <c r="H5" t="n">
-        <v>97.48142</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.643</v>
       </c>
       <c r="J5" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="L5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="M5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="N5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="R5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="S5" t="n">
-        <v>367927</v>
+        <v>-0.644377</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53809</v>
+        <v>3.74306</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.644377</v>
+        <v>3.743473</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="W5" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="X5" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1028,87 +996,81 @@
         <v>0.84</v>
       </c>
       <c r="H6" t="n">
-        <v>98.97262000000001</v>
+        <v>98.05768</v>
       </c>
       <c r="I6" t="n">
-        <v>98.05768</v>
+        <v>5.6199</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="L6" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="M6" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="N6" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="R6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="S6" t="n">
-        <v>367772</v>
+        <v>1.487112</v>
       </c>
       <c r="T6" t="n">
-        <v>1.529727</v>
+        <v>-0.409357</v>
       </c>
       <c r="U6" t="n">
-        <v>1.487112</v>
+        <v>-0.4094</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.409357</v>
+        <v>1.896096</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4094</v>
+        <v>1.160214</v>
       </c>
       <c r="X6" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1135,87 +1097,81 @@
         <v>0.73</v>
       </c>
       <c r="H7" t="n">
-        <v>99.35339</v>
+        <v>99.33126</v>
       </c>
       <c r="I7" t="n">
-        <v>99.33126</v>
+        <v>5.5805</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="L7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="M7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="N7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="R7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="S7" t="n">
-        <v>362204</v>
+        <v>1.298807</v>
       </c>
       <c r="T7" t="n">
-        <v>0.384723</v>
+        <v>-0.70108</v>
       </c>
       <c r="U7" t="n">
-        <v>1.298807</v>
+        <v>-0.701155</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.70108</v>
+        <v>1.856332</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.701155</v>
+        <v>2.135418</v>
       </c>
       <c r="X7" t="n">
-        <v>1.856332</v>
+        <v>1.653884</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1242,87 +1198,81 @@
         <v>0.67</v>
       </c>
       <c r="H8" t="n">
-        <v>97.34401</v>
+        <v>90.45032</v>
       </c>
       <c r="I8" t="n">
-        <v>90.45032</v>
+        <v>5.3574</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="L8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="M8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="N8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="R8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="S8" t="n">
-        <v>358398</v>
+        <v>-8.94073</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.022457</v>
+        <v>-3.99785</v>
       </c>
       <c r="U8" t="n">
-        <v>-8.94073</v>
+        <v>-3.99828</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99785</v>
+        <v>-0.015397</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.99828</v>
+        <v>-1.385541</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.015397</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1349,87 +1299,81 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>98.43725000000001</v>
+        <v>95.72214</v>
       </c>
       <c r="I9" t="n">
-        <v>95.72214</v>
+        <v>5.1394</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="L9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="M9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="N9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="R9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="S9" t="n">
-        <v>357740</v>
+        <v>5.828415</v>
       </c>
       <c r="T9" t="n">
-        <v>1.123069</v>
+        <v>-4.069138</v>
       </c>
       <c r="U9" t="n">
-        <v>5.828415</v>
+        <v>-4.069594</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069138</v>
+        <v>0.975774</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.069594</v>
+        <v>1.257759</v>
       </c>
       <c r="X9" t="n">
-        <v>0.975774</v>
+        <v>0.775073</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1456,87 +1400,81 @@
         <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>99.55981</v>
+        <v>104.61484</v>
       </c>
       <c r="I10" t="n">
-        <v>104.61484</v>
+        <v>4.7378</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="L10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="M10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="N10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="R10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="S10" t="n">
-        <v>353169</v>
+        <v>9.290118</v>
       </c>
       <c r="T10" t="n">
-        <v>1.140381</v>
+        <v>-7.814142</v>
       </c>
       <c r="U10" t="n">
-        <v>9.290118</v>
+        <v>-7.815054</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.814142</v>
+        <v>1.412174</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.815054</v>
+        <v>1.146068</v>
       </c>
       <c r="X10" t="n">
-        <v>1.412174</v>
+        <v>1.602477</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1563,87 +1501,81 @@
         <v>1.04</v>
       </c>
       <c r="H11" t="n">
-        <v>99.51646</v>
+        <v>100.42352</v>
       </c>
       <c r="I11" t="n">
-        <v>100.42352</v>
+        <v>4.9191</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="L11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="M11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="N11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="R11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="S11" t="n">
-        <v>345097</v>
+        <v>-4.00643</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.043542</v>
+        <v>3.826671</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.00643</v>
+        <v>3.827155</v>
       </c>
       <c r="V11" t="n">
-        <v>3.826671</v>
+        <v>0.816526</v>
       </c>
       <c r="W11" t="n">
-        <v>3.827155</v>
+        <v>0.461006</v>
       </c>
       <c r="X11" t="n">
-        <v>0.816526</v>
+        <v>1.06968</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1670,87 +1602,81 @@
         <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>99.67415</v>
+        <v>99.79777</v>
       </c>
       <c r="I12" t="n">
-        <v>99.79777</v>
+        <v>4.7289</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="L12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="M12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="N12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="R12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="S12" t="n">
-        <v>346415</v>
+        <v>-0.623111</v>
       </c>
       <c r="T12" t="n">
-        <v>0.158456</v>
+        <v>-3.866561</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.623111</v>
+        <v>-3.867033</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.866561</v>
+        <v>1.151595</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.867033</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>1.151595</v>
+        <v>1.598738</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1777,93 +1703,87 @@
         <v>0.62</v>
       </c>
       <c r="H13" t="n">
-        <v>99.6343</v>
+        <v>99.53784</v>
       </c>
       <c r="I13" t="n">
-        <v>99.53784</v>
+        <v>5.238</v>
       </c>
       <c r="J13" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="L13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="M13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="N13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="R13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="S13" t="n">
-        <v>341958</v>
+        <v>-0.260457</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.03998</v>
+        <v>10.765717</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.260457</v>
+        <v>10.767083</v>
       </c>
       <c r="V13" t="n">
-        <v>10.765717</v>
+        <v>1.558597</v>
       </c>
       <c r="W13" t="n">
-        <v>10.767083</v>
+        <v>1.928912</v>
       </c>
       <c r="X13" t="n">
-        <v>1.558597</v>
+        <v>1.299314</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.928912</v>
+        <v>-1.286607</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.299314</v>
+        <v>11.88673</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.286607</v>
+        <v>10.700862</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.700862</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1890,93 +1810,87 @@
         <v>-0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>101.27684</v>
+        <v>103.95861</v>
       </c>
       <c r="I14" t="n">
-        <v>103.95861</v>
+        <v>5.1884</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="L14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="M14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="N14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="R14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="S14" t="n">
-        <v>346403</v>
+        <v>4.441296</v>
       </c>
       <c r="T14" t="n">
-        <v>1.648569</v>
+        <v>-0.946926</v>
       </c>
       <c r="U14" t="n">
-        <v>4.441296</v>
+        <v>-0.947035</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.946926</v>
+        <v>0.677481</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.947035</v>
+        <v>-0.269467</v>
       </c>
       <c r="X14" t="n">
-        <v>0.677481</v>
+        <v>1.344714</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.269467</v>
+        <v>1.299867</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.344714</v>
+        <v>10.069235</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.299867</v>
+        <v>10.074751</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.074751</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -2003,93 +1917,87 @@
         <v>-0.31</v>
       </c>
       <c r="H15" t="n">
-        <v>101.07328</v>
+        <v>104.56278</v>
       </c>
       <c r="I15" t="n">
-        <v>104.56278</v>
+        <v>5.179</v>
       </c>
       <c r="J15" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="L15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="M15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="N15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="R15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="S15" t="n">
-        <v>339664</v>
+        <v>0.581164</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.200994</v>
+        <v>-0.181173</v>
       </c>
       <c r="U15" t="n">
-        <v>0.581164</v>
+        <v>-0.181194</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181173</v>
+        <v>1.469562</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.181194</v>
+        <v>0.837552</v>
       </c>
       <c r="X15" t="n">
-        <v>1.469562</v>
+        <v>1.907759</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.837552</v>
+        <v>-1.945422</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.907759</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2116,93 +2024,87 @@
         <v>-0.32</v>
       </c>
       <c r="H16" t="n">
-        <v>101.17973</v>
+        <v>101.38087</v>
       </c>
       <c r="I16" t="n">
-        <v>101.38087</v>
+        <v>5.4066</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="K16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="L16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="M16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="N16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="R16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="S16" t="n">
-        <v>327580</v>
+        <v>-3.043062</v>
       </c>
       <c r="T16" t="n">
-        <v>0.10532</v>
+        <v>4.394671</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.043062</v>
+        <v>4.39518</v>
       </c>
       <c r="V16" t="n">
-        <v>4.394671</v>
+        <v>1.814888</v>
       </c>
       <c r="W16" t="n">
-        <v>4.39518</v>
+        <v>2.210221</v>
       </c>
       <c r="X16" t="n">
-        <v>1.814888</v>
+        <v>1.543645</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.210221</v>
+        <v>-3.557633</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.543645</v>
+        <v>7.168596</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2229,93 +2131,87 @@
         <v>0.47</v>
       </c>
       <c r="H17" t="n">
-        <v>101.46342</v>
+        <v>100.20398</v>
       </c>
       <c r="I17" t="n">
-        <v>100.20398</v>
+        <v>5.257</v>
       </c>
       <c r="J17" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="L17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="M17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="N17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="R17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="S17" t="n">
-        <v>325546</v>
+        <v>-1.16086</v>
       </c>
       <c r="T17" t="n">
-        <v>0.280382</v>
+        <v>-2.766988</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.16086</v>
+        <v>-2.767296</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.766988</v>
+        <v>0.991621</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.767296</v>
+        <v>-0.187221</v>
       </c>
       <c r="X17" t="n">
-        <v>0.991621</v>
+        <v>1.805747</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.187221</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.805747</v>
+        <v>6.470016</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2342,93 +2238,87 @@
         <v>0.38</v>
       </c>
       <c r="H18" t="n">
-        <v>100.66227</v>
+        <v>99.36927</v>
       </c>
       <c r="I18" t="n">
-        <v>99.36927</v>
+        <v>5.2941</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="L18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="M18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="N18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="R18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="S18" t="n">
-        <v>331505</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.789595</v>
+        <v>0.705726</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>0.705806</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705726</v>
+        <v>1.335643</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705806</v>
+        <v>1.161333</v>
       </c>
       <c r="X18" t="n">
-        <v>1.335643</v>
+        <v>1.453667</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.161333</v>
+        <v>1.830463</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.453667</v>
+        <v>5.900488</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2455,93 +2345,87 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>100.58196</v>
+        <v>99.97806</v>
       </c>
       <c r="I19" t="n">
-        <v>99.97806</v>
+        <v>5.2177</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="L19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="M19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="N19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="R19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="S19" t="n">
-        <v>324703</v>
+        <v>0.612654</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>-1.443116</v>
       </c>
       <c r="U19" t="n">
-        <v>0.612654</v>
+        <v>-1.443279</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443116</v>
+        <v>1.521325</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.443279</v>
+        <v>2.249624</v>
       </c>
       <c r="X19" t="n">
-        <v>1.521325</v>
+        <v>1.029618</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.249624</v>
+        <v>-2.051854</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.029618</v>
+        <v>5.784842</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2568,93 +2452,87 @@
         <v>0.46</v>
       </c>
       <c r="H20" t="n">
-        <v>100.05178</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0993</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="L20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="M20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="N20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="O20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="R20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="S20" t="n">
-        <v>331122</v>
+        <v>-6.187047</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.527112</v>
+        <v>-2.269199</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.187047</v>
+        <v>-2.26946</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.269199</v>
+        <v>0.133468</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.26946</v>
+        <v>-1.232052</v>
       </c>
       <c r="X20" t="n">
-        <v>0.133468</v>
+        <v>1.066493</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.232052</v>
+        <v>1.976883</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.066493</v>
+        <v>5.77432</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2681,93 +2559,87 @@
         <v>0.77</v>
       </c>
       <c r="H21" t="n">
-        <v>103.00964</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2078</v>
       </c>
       <c r="J21" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="L21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="M21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="N21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="R21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="S21" t="n">
-        <v>328098</v>
+        <v>5.286443</v>
       </c>
       <c r="T21" t="n">
-        <v>2.956329</v>
+        <v>2.127743</v>
       </c>
       <c r="U21" t="n">
-        <v>5.286443</v>
+        <v>2.127993</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127743</v>
+        <v>-0.042451</v>
       </c>
       <c r="W21" t="n">
-        <v>2.127993</v>
+        <v>-0.710886</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.042451</v>
+        <v>0.403932</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.710886</v>
+        <v>-0.913259</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.403932</v>
+        <v>5.596302</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2794,93 +2666,87 @@
         <v>0.64</v>
       </c>
       <c r="H22" t="n">
-        <v>103.09341</v>
+        <v>110.62354</v>
       </c>
       <c r="I22" t="n">
-        <v>110.62354</v>
+        <v>5.0804</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="L22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="M22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="N22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="R22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="S22" t="n">
-        <v>341158</v>
+        <v>12.023101</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08132200000000001</v>
+        <v>-2.446331</v>
       </c>
       <c r="U22" t="n">
-        <v>12.023101</v>
+        <v>-2.446612</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446331</v>
+        <v>1.002821</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.446612</v>
+        <v>0.879872</v>
       </c>
       <c r="X22" t="n">
-        <v>1.002821</v>
+        <v>1.083978</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.879872</v>
+        <v>3.980518</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.083978</v>
+        <v>4.650694</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2907,93 +2773,87 @@
         <v>0.53</v>
       </c>
       <c r="H23" t="n">
-        <v>104.1626</v>
+        <v>104.34152</v>
       </c>
       <c r="I23" t="n">
-        <v>104.34152</v>
+        <v>5.0007</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="K23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="L23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="M23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="N23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="R23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="S23" t="n">
-        <v>345725</v>
+        <v>-5.678737</v>
       </c>
       <c r="T23" t="n">
-        <v>1.037108</v>
+        <v>-1.568774</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.678737</v>
+        <v>-1.568959</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568774</v>
+        <v>0.027577</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.568959</v>
+        <v>-0.459418</v>
       </c>
       <c r="X23" t="n">
-        <v>0.027577</v>
+        <v>0.348572</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.459418</v>
+        <v>1.338676</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.348572</v>
+        <v>4.184706</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -3020,93 +2880,87 @@
         <v>0.36</v>
       </c>
       <c r="H24" t="n">
-        <v>102.3642</v>
+        <v>102.66392</v>
       </c>
       <c r="I24" t="n">
-        <v>102.66392</v>
+        <v>5.0959</v>
       </c>
       <c r="J24" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="K24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="L24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="M24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="N24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="R24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="S24" t="n">
-        <v>343489</v>
+        <v>-1.607797</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.726531</v>
+        <v>1.903733</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.607797</v>
+        <v>1.903962</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903733</v>
+        <v>0.504966</v>
       </c>
       <c r="W24" t="n">
-        <v>1.903962</v>
+        <v>0.024709</v>
       </c>
       <c r="X24" t="n">
-        <v>0.504966</v>
+        <v>0.818881</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.024709</v>
+        <v>-0.646757</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.818881</v>
+        <v>3.935832</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3133,93 +2987,87 @@
         <v>-0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>102.50431</v>
+        <v>102.53174</v>
       </c>
       <c r="I25" t="n">
-        <v>102.53174</v>
+        <v>4.8192</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="L25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="M25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="N25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="R25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="S25" t="n">
-        <v>343620</v>
+        <v>-0.12875</v>
       </c>
       <c r="T25" t="n">
-        <v>0.136874</v>
+        <v>-5.429855</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.12875</v>
+        <v>-5.430495</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.429855</v>
+        <v>0.472174</v>
       </c>
       <c r="W25" t="n">
-        <v>-5.430495</v>
+        <v>1.122473</v>
       </c>
       <c r="X25" t="n">
-        <v>0.472174</v>
+        <v>0.050421</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.122473</v>
+        <v>0.038138</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.050421</v>
+        <v>3.161501</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.038138</v>
+        <v>-6.84947</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3246,93 +3094,87 @@
         <v>-0.09</v>
       </c>
       <c r="H26" t="n">
-        <v>102.83357</v>
+        <v>105.47522</v>
       </c>
       <c r="I26" t="n">
-        <v>105.47522</v>
+        <v>4.7415</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="L26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="M26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="N26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="R26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="S26" t="n">
-        <v>345476</v>
+        <v>2.870799</v>
       </c>
       <c r="T26" t="n">
-        <v>0.321216</v>
+        <v>-1.612301</v>
       </c>
       <c r="U26" t="n">
-        <v>2.870799</v>
+        <v>-1.612502</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612301</v>
+        <v>0.098769</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.612502</v>
+        <v>-0.740777</v>
       </c>
       <c r="X26" t="n">
-        <v>0.098769</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.740777</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6490939999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="AC26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3359,93 +3201,87 @@
         <v>0.2</v>
       </c>
       <c r="H27" t="n">
-        <v>102.45222</v>
+        <v>106.13139</v>
       </c>
       <c r="I27" t="n">
-        <v>106.13139</v>
+        <v>4.9219</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="L27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="M27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="N27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="R27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="S27" t="n">
-        <v>344177</v>
+        <v>0.622108</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.370842</v>
+        <v>3.804703</v>
       </c>
       <c r="U27" t="n">
-        <v>0.622108</v>
+        <v>3.805185</v>
       </c>
       <c r="V27" t="n">
-        <v>3.804703</v>
+        <v>1.352666</v>
       </c>
       <c r="W27" t="n">
-        <v>3.805185</v>
+        <v>0.887701</v>
       </c>
       <c r="X27" t="n">
-        <v>1.352666</v>
+        <v>1.653244</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.887701</v>
+        <v>-0.376003</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.653244</v>
+        <v>4.608216</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3472,93 +3308,87 @@
         <v>0.11</v>
       </c>
       <c r="H28" t="n">
-        <v>102.57885</v>
+        <v>102.00419</v>
       </c>
       <c r="I28" t="n">
-        <v>102.00419</v>
+        <v>5.0076</v>
       </c>
       <c r="J28" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="K28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="L28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="M28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="N28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="O28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="R28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="S28" t="n">
-        <v>340324</v>
+        <v>-3.888765</v>
       </c>
       <c r="T28" t="n">
-        <v>0.123599</v>
+        <v>1.741198</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.888765</v>
+        <v>1.74141</v>
       </c>
       <c r="V28" t="n">
-        <v>1.741198</v>
+        <v>1.203116</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74141</v>
+        <v>1.956912</v>
       </c>
       <c r="X28" t="n">
-        <v>1.203116</v>
+        <v>0.719465</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.956912</v>
+        <v>-1.119482</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.719465</v>
+        <v>5.185235</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3585,93 +3415,87 @@
         <v>0.12</v>
       </c>
       <c r="H29" t="n">
-        <v>102.87707</v>
+        <v>102.0744</v>
       </c>
       <c r="I29" t="n">
-        <v>102.0744</v>
+        <v>5.0575</v>
       </c>
       <c r="J29" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="K29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="L29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="M29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="N29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="P29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="R29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="S29" t="n">
-        <v>340247</v>
+        <v>0.068831</v>
       </c>
       <c r="T29" t="n">
-        <v>0.290723</v>
+        <v>0.996485</v>
       </c>
       <c r="U29" t="n">
-        <v>0.068831</v>
+        <v>0.996605</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996485</v>
+        <v>0.495259</v>
       </c>
       <c r="W29" t="n">
-        <v>0.996605</v>
+        <v>-0.467999</v>
       </c>
       <c r="X29" t="n">
-        <v>0.495259</v>
+        <v>1.120891</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.467999</v>
+        <v>-0.022625</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.120891</v>
+        <v>4.819246</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3698,93 +3522,87 @@
         <v>0.1</v>
       </c>
       <c r="H30" t="n">
-        <v>103.528</v>
+        <v>101.86494</v>
       </c>
       <c r="I30" t="n">
-        <v>101.86494</v>
+        <v>4.9355</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="L30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="M30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="N30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="O30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="R30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="S30" t="n">
-        <v>348406</v>
+        <v>-0.205203</v>
       </c>
       <c r="T30" t="n">
-        <v>0.632726</v>
+        <v>-2.412259</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.205203</v>
+        <v>-2.412545</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412259</v>
+        <v>1.013388</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.412545</v>
+        <v>0.723782</v>
       </c>
       <c r="X30" t="n">
-        <v>1.013388</v>
+        <v>1.198521</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.723782</v>
+        <v>2.397964</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.198521</v>
+        <v>4.683537</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3811,93 +3629,87 @@
         <v>0.55</v>
       </c>
       <c r="H31" t="n">
-        <v>104.8991</v>
+        <v>101.74606</v>
       </c>
       <c r="I31" t="n">
-        <v>101.74606</v>
+        <v>4.8413</v>
       </c>
       <c r="J31" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="L31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="M31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="N31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="P31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="R31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="S31" t="n">
-        <v>355034</v>
+        <v>-0.116704</v>
       </c>
       <c r="T31" t="n">
-        <v>1.324376</v>
+        <v>-1.908621</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.116704</v>
+        <v>-1.908853</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908621</v>
+        <v>1.646862</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.908853</v>
+        <v>2.824206</v>
       </c>
       <c r="X31" t="n">
-        <v>1.646862</v>
+        <v>0.897764</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.824206</v>
+        <v>1.902378</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.897764</v>
+        <v>4.621114</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3924,93 +3736,87 @@
         <v>0.57</v>
       </c>
       <c r="H32" t="n">
-        <v>104.53245</v>
+        <v>98.01879</v>
       </c>
       <c r="I32" t="n">
-        <v>98.01879</v>
+        <v>4.9535</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="L32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="M32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="N32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="S32" t="n">
-        <v>355066</v>
+        <v>-3.663306</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.349526</v>
+        <v>2.317559</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.663306</v>
+        <v>2.317847</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317559</v>
+        <v>-0.180012</v>
       </c>
       <c r="W32" t="n">
-        <v>2.317847</v>
+        <v>-2.151229</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.180012</v>
+        <v>1.098143</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.151229</v>
+        <v>0.009013</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.098143</v>
+        <v>4.506637</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="AC32" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -4037,93 +3843,87 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>104.75961</v>
+        <v>102.37988</v>
       </c>
       <c r="I33" t="n">
-        <v>102.37988</v>
+        <v>4.9833</v>
       </c>
       <c r="J33" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="L33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="M33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="N33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="O33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="R33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="S33" t="n">
-        <v>352705</v>
+        <v>4.449239</v>
       </c>
       <c r="T33" t="n">
-        <v>0.217311</v>
+        <v>0.601595</v>
       </c>
       <c r="U33" t="n">
-        <v>4.449239</v>
+        <v>0.601668</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601595</v>
+        <v>0.366662</v>
       </c>
       <c r="W33" t="n">
-        <v>0.601668</v>
+        <v>0.04207</v>
       </c>
       <c r="X33" t="n">
-        <v>0.366662</v>
+        <v>0.570366</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04207</v>
+        <v>-0.664947</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.570366</v>
+        <v>4.496274</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4150,93 +3950,87 @@
         <v>0.19</v>
       </c>
       <c r="H34" t="n">
-        <v>104.7097</v>
+        <v>109.58504</v>
       </c>
       <c r="I34" t="n">
-        <v>109.58504</v>
+        <v>4.9962</v>
       </c>
       <c r="J34" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="L34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="M34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="N34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="R34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="S34" t="n">
-        <v>355008</v>
+        <v>7.037672</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.047642</v>
+        <v>0.258865</v>
       </c>
       <c r="U34" t="n">
-        <v>7.037672</v>
+        <v>0.258896</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258865</v>
+        <v>1.440658</v>
       </c>
       <c r="W34" t="n">
-        <v>0.258896</v>
+        <v>2.257995</v>
       </c>
       <c r="X34" t="n">
-        <v>1.440658</v>
+        <v>0.930417</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.257995</v>
+        <v>0.652954</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.930417</v>
+        <v>3.925596</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4263,93 +4057,87 @@
         <v>0.37</v>
       </c>
       <c r="H35" t="n">
-        <v>104.75682</v>
+        <v>109.36335</v>
       </c>
       <c r="I35" t="n">
-        <v>109.36335</v>
+        <v>5.1718</v>
       </c>
       <c r="J35" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="L35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="M35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="N35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="R35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="S35" t="n">
-        <v>351599</v>
+        <v>-0.2023</v>
       </c>
       <c r="T35" t="n">
-        <v>0.045001</v>
+        <v>3.514671</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.2023</v>
+        <v>3.515093</v>
       </c>
       <c r="V35" t="n">
-        <v>3.514671</v>
+        <v>0.267741</v>
       </c>
       <c r="W35" t="n">
-        <v>3.515093</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="X35" t="n">
-        <v>0.267741</v>
+        <v>0.904602</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>-0.96026</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.904602</v>
+        <v>3.688016</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4376,93 +4164,87 @@
         <v>0.46</v>
       </c>
       <c r="H36" t="n">
-        <v>105.70704</v>
+        <v>104.84682</v>
       </c>
       <c r="I36" t="n">
-        <v>104.84682</v>
+        <v>5.2416</v>
       </c>
       <c r="J36" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="K36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="L36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="M36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="N36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="O36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="R36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="S36" t="n">
-        <v>355560</v>
+        <v>-4.129839</v>
       </c>
       <c r="T36" t="n">
-        <v>0.907072</v>
+        <v>1.349627</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.129839</v>
+        <v>1.349783</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349627</v>
+        <v>0.64951</v>
       </c>
       <c r="W36" t="n">
-        <v>1.349783</v>
+        <v>0.415624</v>
       </c>
       <c r="X36" t="n">
-        <v>0.64951</v>
+        <v>0.795057</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.415624</v>
+        <v>1.126567</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.795057</v>
+        <v>3.925952</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4489,93 +4271,87 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>106.57623</v>
+        <v>106.03093</v>
       </c>
       <c r="I37" t="n">
-        <v>106.03093</v>
+        <v>5.5589</v>
       </c>
       <c r="J37" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="L37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="M37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="N37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="R37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="S37" t="n">
-        <v>357827</v>
+        <v>1.129371</v>
       </c>
       <c r="T37" t="n">
-        <v>0.822263</v>
+        <v>6.053495</v>
       </c>
       <c r="U37" t="n">
-        <v>1.129371</v>
+        <v>6.054188</v>
       </c>
       <c r="V37" t="n">
-        <v>6.053495</v>
+        <v>1.476967</v>
       </c>
       <c r="W37" t="n">
-        <v>6.054188</v>
+        <v>2.569845</v>
       </c>
       <c r="X37" t="n">
-        <v>1.476967</v>
+        <v>0.799559</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.569845</v>
+        <v>0.637586</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.799559</v>
+        <v>4.227578</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4602,93 +4378,87 @@
         <v>0.26</v>
       </c>
       <c r="H38" t="n">
-        <v>106.88756</v>
+        <v>111.55002</v>
       </c>
       <c r="I38" t="n">
-        <v>111.55002</v>
+        <v>5.6621</v>
       </c>
       <c r="J38" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="L38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="M38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="N38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="R38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="S38" t="n">
-        <v>363282</v>
+        <v>5.20517</v>
       </c>
       <c r="T38" t="n">
-        <v>0.29212</v>
+        <v>1.856482</v>
       </c>
       <c r="U38" t="n">
-        <v>5.20517</v>
+        <v>1.856683</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856482</v>
+        <v>0.451961</v>
       </c>
       <c r="W38" t="n">
-        <v>1.856683</v>
+        <v>-0.577528</v>
       </c>
       <c r="X38" t="n">
-        <v>0.451961</v>
+        <v>1.101283</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.577528</v>
+        <v>1.52448</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.101283</v>
+        <v>4.498245</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4715,93 +4485,87 @@
         <v>-0.14</v>
       </c>
       <c r="H39" t="n">
-        <v>107.14396</v>
+        <v>110.19363</v>
       </c>
       <c r="I39" t="n">
-        <v>110.19363</v>
+        <v>5.6562</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="L39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="M39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="N39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="R39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="S39" t="n">
-        <v>369214</v>
+        <v>-1.215948</v>
       </c>
       <c r="T39" t="n">
-        <v>0.239878</v>
+        <v>-0.104202</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.215948</v>
+        <v>-0.104213</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104202</v>
+        <v>1.088989</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.104213</v>
+        <v>0.905369</v>
       </c>
       <c r="X39" t="n">
-        <v>1.088989</v>
+        <v>1.202826</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.905369</v>
+        <v>1.632891</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.202826</v>
+        <v>4.237599</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4828,93 +4592,87 @@
         <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99916</v>
+        <v>107.28836</v>
       </c>
       <c r="I40" t="n">
-        <v>107.28836</v>
+        <v>5.4481</v>
       </c>
       <c r="J40" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="L40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="M40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="N40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="R40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="S40" t="n">
-        <v>372016</v>
+        <v>-2.636514</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7981780000000001</v>
+        <v>-3.679149</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.636514</v>
+        <v>-3.679539</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679149</v>
+        <v>1.323978</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.679539</v>
+        <v>1.72458</v>
       </c>
       <c r="X40" t="n">
-        <v>1.323978</v>
+        <v>1.076262</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72458</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.076262</v>
+        <v>4.42474</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4941,93 +4699,87 @@
         <v>0.61</v>
       </c>
       <c r="H41" t="n">
-        <v>108.15356</v>
+        <v>109.21678</v>
       </c>
       <c r="I41" t="n">
-        <v>109.21678</v>
+        <v>5.7779</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="K41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="L41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="M41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="N41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="R41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="S41" t="n">
-        <v>366096</v>
+        <v>1.797418</v>
       </c>
       <c r="T41" t="n">
-        <v>0.142964</v>
+        <v>6.053487</v>
       </c>
       <c r="U41" t="n">
-        <v>1.797418</v>
+        <v>6.054153</v>
       </c>
       <c r="V41" t="n">
-        <v>6.053487</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="W41" t="n">
-        <v>6.054153</v>
+        <v>0.532743</v>
       </c>
       <c r="X41" t="n">
-        <v>0.9424709999999999</v>
+        <v>1.197484</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.532743</v>
+        <v>-1.591329</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.197484</v>
+        <v>4.758099</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5054,93 +4806,87 @@
         <v>0.33</v>
       </c>
       <c r="H42" t="n">
-        <v>107.98489</v>
+        <v>105.74688</v>
       </c>
       <c r="I42" t="n">
-        <v>105.74688</v>
+        <v>6.0535</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="K42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="L42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="M42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="N42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="O42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="R42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="S42" t="n">
-        <v>363003</v>
+        <v>-3.177076</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.155954</v>
+        <v>4.769899</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.177076</v>
+        <v>4.770394</v>
       </c>
       <c r="V42" t="n">
-        <v>4.769899</v>
+        <v>1.443368</v>
       </c>
       <c r="W42" t="n">
-        <v>4.770394</v>
+        <v>1.605359</v>
       </c>
       <c r="X42" t="n">
-        <v>1.443368</v>
+        <v>1.343208</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.605359</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.343208</v>
+        <v>4.873011</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -5167,93 +4913,87 @@
         <v>0.48</v>
       </c>
       <c r="H43" t="n">
-        <v>107.44467</v>
+        <v>104.2734</v>
       </c>
       <c r="I43" t="n">
-        <v>104.2734</v>
+        <v>6.1923</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="K43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="L43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="M43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="N43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="S43" t="n">
-        <v>329730</v>
+        <v>-1.393403</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.500274</v>
+        <v>2.292888</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.393403</v>
+        <v>2.293116</v>
       </c>
       <c r="V43" t="n">
-        <v>2.292888</v>
+        <v>1.55383</v>
       </c>
       <c r="W43" t="n">
-        <v>2.293116</v>
+        <v>2.592546</v>
       </c>
       <c r="X43" t="n">
-        <v>1.55383</v>
+        <v>0.909924</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.592546</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.909924</v>
+        <v>4.831296</v>
       </c>
       <c r="AA43" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5280,93 +5020,87 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>108.06979</v>
+        <v>101.23438</v>
       </c>
       <c r="I44" t="n">
-        <v>101.23438</v>
+        <v>5.8301</v>
       </c>
       <c r="J44" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="K44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="L44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="M44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="N44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="O44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="P44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="R44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="S44" t="n">
-        <v>328303</v>
+        <v>-2.914473</v>
       </c>
       <c r="T44" t="n">
-        <v>0.581806</v>
+        <v>-5.8492</v>
       </c>
       <c r="U44" t="n">
-        <v>-2.914473</v>
+        <v>-5.849767</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.8492</v>
+        <v>0.006404</v>
       </c>
       <c r="W44" t="n">
-        <v>-5.849767</v>
+        <v>-1.889422</v>
       </c>
       <c r="X44" t="n">
-        <v>0.006404</v>
+        <v>1.201233</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.889422</v>
+        <v>-0.432778</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.201233</v>
+        <v>4.559874</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5393,93 +5127,87 @@
         <v>1.48</v>
       </c>
       <c r="H45" t="n">
-        <v>108.77346</v>
+        <v>107.07838</v>
       </c>
       <c r="I45" t="n">
-        <v>107.07838</v>
+        <v>5.8488</v>
       </c>
       <c r="J45" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="L45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="M45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="N45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="O45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="R45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="S45" t="n">
-        <v>332508</v>
+        <v>5.772742</v>
       </c>
       <c r="T45" t="n">
-        <v>0.651126</v>
+        <v>0.320749</v>
       </c>
       <c r="U45" t="n">
-        <v>5.772742</v>
+        <v>0.320782</v>
       </c>
       <c r="V45" t="n">
-        <v>0.320749</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>0.320782</v>
+        <v>1.027506</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7181419999999999</v>
+        <v>0.529123</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.027506</v>
+        <v>1.280829</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.529123</v>
+        <v>5.05763</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5506,93 +5234,87 @@
         <v>0.51</v>
       </c>
       <c r="H46" t="n">
-        <v>110.09056</v>
+        <v>114.05013</v>
       </c>
       <c r="I46" t="n">
-        <v>114.05013</v>
+        <v>5.7422</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="L46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="M46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="N46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="P46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="R46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="S46" t="n">
-        <v>336157</v>
+        <v>6.510885</v>
       </c>
       <c r="T46" t="n">
-        <v>1.210865</v>
+        <v>-1.822596</v>
       </c>
       <c r="U46" t="n">
-        <v>6.510885</v>
+        <v>-1.822783</v>
       </c>
       <c r="V46" t="n">
-        <v>-1.822596</v>
+        <v>0.99855</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.822783</v>
+        <v>0.852229</v>
       </c>
       <c r="X46" t="n">
-        <v>0.99855</v>
+        <v>1.088394</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.852229</v>
+        <v>1.097417</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.088394</v>
+        <v>5.47719</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5619,93 +5341,87 @@
         <v>0.48</v>
       </c>
       <c r="H47" t="n">
-        <v>109.72323</v>
+        <v>112.73813</v>
       </c>
       <c r="I47" t="n">
-        <v>112.73813</v>
+        <v>5.6608</v>
       </c>
       <c r="J47" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="K47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="L47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="M47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="N47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="R47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="S47" t="n">
-        <v>340789</v>
+        <v>-1.150371</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.333662</v>
+        <v>-1.417575</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.150371</v>
+        <v>-1.417723</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.417575</v>
+        <v>0.722029</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.417723</v>
+        <v>0.566954</v>
       </c>
       <c r="X47" t="n">
-        <v>0.722029</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.566954</v>
+        <v>1.377928</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8170269999999999</v>
+        <v>5.529729</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5732,93 +5448,87 @@
         <v>0.35</v>
       </c>
       <c r="H48" t="n">
-        <v>109.00057</v>
+        <v>108.66481</v>
       </c>
       <c r="I48" t="n">
-        <v>108.66481</v>
+        <v>5.7087</v>
       </c>
       <c r="J48" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="K48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="L48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="M48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="N48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="R48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="S48" t="n">
-        <v>341459</v>
+        <v>-3.613081</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.658621</v>
+        <v>0.84617</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.613081</v>
+        <v>0.84626</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84617</v>
+        <v>0.639181</v>
       </c>
       <c r="W48" t="n">
-        <v>0.84626</v>
+        <v>0.807268</v>
       </c>
       <c r="X48" t="n">
-        <v>0.639181</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.807268</v>
+        <v>0.196603</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5364679999999999</v>
+        <v>5.319636</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5845,93 +5555,87 @@
         <v>0.23</v>
       </c>
       <c r="H49" t="n">
-        <v>108.76683</v>
+        <v>107.55639</v>
       </c>
       <c r="I49" t="n">
-        <v>107.55639</v>
+        <v>5.4571</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="L49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="M49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="N49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="O49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="R49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="S49" t="n">
-        <v>344440</v>
+        <v>-1.020036</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.214439</v>
+        <v>-4.407308</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.020036</v>
+        <v>-4.407771</v>
       </c>
       <c r="V49" t="n">
-        <v>-4.407308</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>-4.407771</v>
+        <v>0.591659</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.541686</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.591659</v>
+        <v>0.873018</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.541686</v>
+        <v>5.351165</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5958,93 +5662,87 @@
         <v>0.21</v>
       </c>
       <c r="H50" t="n">
-        <v>108.27053</v>
+        <v>113.14433</v>
       </c>
       <c r="I50" t="n">
-        <v>113.14433</v>
+        <v>5.6021</v>
       </c>
       <c r="J50" t="n">
-        <v>5.6021</v>
+        <v>5.6015</v>
       </c>
       <c r="K50" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="L50" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="M50" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="N50" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="O50" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="P50" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="R50" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="S50" t="n">
-        <v>345111</v>
+        <v>5.195358</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.456297</v>
+        <v>2.657089</v>
       </c>
       <c r="U50" t="n">
-        <v>5.195358</v>
+        <v>2.657381</v>
       </c>
       <c r="V50" t="n">
-        <v>2.657089</v>
+        <v>0.440744</v>
       </c>
       <c r="W50" t="n">
-        <v>2.657381</v>
+        <v>-0.129254</v>
       </c>
       <c r="X50" t="n">
-        <v>0.440744</v>
+        <v>0.79014</v>
       </c>
       <c r="Y50" t="n">
-        <v>-0.129254</v>
+        <v>0.194809</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.79014</v>
+        <v>5.225222</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.194809</v>
+        <v>2.961368</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.225222</v>
+        <v>5.127976</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.961368</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -6071,93 +5769,87 @@
         <v>-0.21</v>
       </c>
       <c r="H51" t="n">
-        <v>108.80021</v>
+        <v>110.57963</v>
       </c>
       <c r="I51" t="n">
-        <v>110.57963</v>
+        <v>5.4264</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="L51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="M51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="N51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="O51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="P51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="R51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="S51" t="n">
-        <v>350767</v>
+        <v>-2.266751</v>
       </c>
       <c r="T51" t="n">
-        <v>0.489219</v>
+        <v>-3.136324</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.266751</v>
+        <v>-3.13666</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.136324</v>
+        <v>0.612293</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.13666</v>
+        <v>0.073298</v>
       </c>
       <c r="X51" t="n">
-        <v>0.612293</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.073298</v>
+        <v>1.638893</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.9397180000000001</v>
+        <v>5.130501</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6184,93 +5876,87 @@
         <v>0.52</v>
       </c>
       <c r="H52" t="n">
-        <v>108.63642</v>
+        <v>109.59513</v>
       </c>
       <c r="I52" t="n">
-        <v>109.59513</v>
+        <v>5.3186</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="K52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="L52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="M52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="N52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="O52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="P52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="R52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="S52" t="n">
-        <v>356582</v>
+        <v>-0.890309</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.150542</v>
+        <v>-1.986584</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.890309</v>
+        <v>-1.986804</v>
       </c>
       <c r="V52" t="n">
-        <v>-1.986584</v>
+        <v>1.155358</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.986804</v>
+        <v>1.710427</v>
       </c>
       <c r="X52" t="n">
-        <v>1.155358</v>
+        <v>0.821088</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.710427</v>
+        <v>1.657796</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.821088</v>
+        <v>5.172369</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6297,93 +5983,87 @@
         <v>0.03</v>
       </c>
       <c r="H53" t="n">
-        <v>108.7159</v>
+        <v>110.16346</v>
       </c>
       <c r="I53" t="n">
-        <v>110.16346</v>
+        <v>5.3843</v>
       </c>
       <c r="J53" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="K53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="L53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="M53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="N53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="O53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="P53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="R53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="S53" t="n">
-        <v>357103</v>
+        <v>0.518572</v>
       </c>
       <c r="T53" t="n">
-        <v>0.073161</v>
+        <v>1.235287</v>
       </c>
       <c r="U53" t="n">
-        <v>0.518572</v>
+        <v>1.235427</v>
       </c>
       <c r="V53" t="n">
-        <v>1.235287</v>
+        <v>1.038729</v>
       </c>
       <c r="W53" t="n">
-        <v>1.235427</v>
+        <v>0.301682</v>
       </c>
       <c r="X53" t="n">
-        <v>1.038729</v>
+        <v>1.486504</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.301682</v>
+        <v>0.146109</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.486504</v>
+        <v>4.680811</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.146109</v>
+        <v>0.924206</v>
       </c>
       <c r="AB53" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6410,93 +6090,87 @@
         <v>0.03</v>
       </c>
       <c r="H54" t="n">
-        <v>109.27405</v>
+        <v>106.90236</v>
       </c>
       <c r="I54" t="n">
-        <v>106.90236</v>
+        <v>5.3338</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="L54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="M54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="N54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="O54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="P54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="R54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="S54" t="n">
-        <v>360578</v>
+        <v>-2.960237</v>
       </c>
       <c r="T54" t="n">
-        <v>0.513402</v>
+        <v>-0.937912</v>
       </c>
       <c r="U54" t="n">
-        <v>-2.960237</v>
+        <v>-0.938017</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.937912</v>
+        <v>1.146567</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.938017</v>
+        <v>0.715383</v>
       </c>
       <c r="X54" t="n">
-        <v>1.146567</v>
+        <v>1.405488</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.715383</v>
+        <v>0.973109</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.405488</v>
+        <v>4.461836</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6523,93 +6197,87 @@
         <v>0.21</v>
       </c>
       <c r="H55" t="n">
-        <v>109.41762</v>
+        <v>107.17649</v>
       </c>
       <c r="I55" t="n">
-        <v>107.17649</v>
+        <v>5.5024</v>
       </c>
       <c r="J55" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="K55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="L55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="M55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="N55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="P55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="R55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="S55" t="n">
-        <v>358234</v>
+        <v>0.25643</v>
       </c>
       <c r="T55" t="n">
-        <v>0.131385</v>
+        <v>3.160973</v>
       </c>
       <c r="U55" t="n">
-        <v>0.25643</v>
+        <v>3.161329</v>
       </c>
       <c r="V55" t="n">
-        <v>3.160973</v>
+        <v>1.90144</v>
       </c>
       <c r="W55" t="n">
-        <v>3.161329</v>
+        <v>3.24641</v>
       </c>
       <c r="X55" t="n">
-        <v>1.90144</v>
+        <v>1.099346</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.24641</v>
+        <v>-0.650067</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.099346</v>
+        <v>4.264385</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6636,93 +6304,87 @@
         <v>0.39</v>
       </c>
       <c r="H56" t="n">
-        <v>110.05486</v>
+        <v>102.36456</v>
       </c>
       <c r="I56" t="n">
-        <v>102.36456</v>
+        <v>5.2301</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="L56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="M56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="N56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="O56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="P56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="S56" t="n">
-        <v>364367</v>
+        <v>-4.489725</v>
       </c>
       <c r="T56" t="n">
-        <v>0.582392</v>
+        <v>-4.94875</v>
       </c>
       <c r="U56" t="n">
-        <v>-4.489725</v>
+        <v>-4.949289</v>
       </c>
       <c r="V56" t="n">
-        <v>-4.94875</v>
+        <v>-0.083179</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.949289</v>
+        <v>-1.743482</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.083179</v>
+        <v>0.927966</v>
       </c>
       <c r="Y56" t="n">
-        <v>-1.743482</v>
+        <v>1.712009</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.927966</v>
+        <v>4.441351</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6749,93 +6411,87 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>110.65892</v>
+        <v>106.82125</v>
       </c>
       <c r="I57" t="n">
-        <v>106.82125</v>
+        <v>5.1495</v>
       </c>
       <c r="J57" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="K57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="L57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="M57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="N57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="P57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="R57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="S57" t="n">
-        <v>371074</v>
+        <v>4.353743</v>
       </c>
       <c r="T57" t="n">
-        <v>0.548872</v>
+        <v>-1.54108</v>
       </c>
       <c r="U57" t="n">
-        <v>4.353743</v>
+        <v>-1.541256</v>
       </c>
       <c r="V57" t="n">
-        <v>-1.54108</v>
+        <v>0.371461</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.541256</v>
+        <v>0.070797</v>
       </c>
       <c r="X57" t="n">
-        <v>0.371461</v>
+        <v>0.549722</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.070797</v>
+        <v>1.840727</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.549722</v>
+        <v>3.812497</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="AB57" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="AC57" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6862,93 +6518,87 @@
         <v>0.91</v>
       </c>
       <c r="H58" t="n">
-        <v>110.51078</v>
+        <v>117.8089</v>
       </c>
       <c r="I58" t="n">
-        <v>117.8089</v>
+        <v>5.2194</v>
       </c>
       <c r="J58" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="L58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="M58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="N58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="O58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="P58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="R58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="S58" t="n">
-        <v>362002</v>
+        <v>10.286015</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.133871</v>
+        <v>1.357413</v>
       </c>
       <c r="U58" t="n">
-        <v>10.286015</v>
+        <v>1.357572</v>
       </c>
       <c r="V58" t="n">
-        <v>1.357413</v>
+        <v>1.12824</v>
       </c>
       <c r="W58" t="n">
-        <v>1.357572</v>
+        <v>1.133877</v>
       </c>
       <c r="X58" t="n">
-        <v>1.12824</v>
+        <v>1.124914</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.133877</v>
+        <v>-2.444795</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.124914</v>
+        <v>4.142847</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="AC58" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="AE58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6975,93 +6625,87 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>110.95732</v>
+        <v>113.99365</v>
       </c>
       <c r="I59" t="n">
-        <v>113.99365</v>
+        <v>4.9886</v>
       </c>
       <c r="J59" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="K59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="L59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="M59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="N59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="O59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="R59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="S59" t="n">
-        <v>366913</v>
+        <v>-3.238507</v>
       </c>
       <c r="T59" t="n">
-        <v>0.404069</v>
+        <v>-4.421964</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.238507</v>
+        <v>-4.422473</v>
       </c>
       <c r="V59" t="n">
-        <v>-4.421964</v>
+        <v>0.288267</v>
       </c>
       <c r="W59" t="n">
-        <v>-4.422473</v>
+        <v>-0.052977</v>
       </c>
       <c r="X59" t="n">
-        <v>0.288267</v>
+        <v>0.489642</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.052977</v>
+        <v>1.356622</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.489642</v>
+        <v>4.39172</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -7088,93 +6732,87 @@
         <v>0.65</v>
       </c>
       <c r="H60" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="I60" t="n">
-        <v>109.52993</v>
+        <v>5.0569</v>
       </c>
       <c r="J60" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="L60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="M60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="N60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="O60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="P60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="R60" t="n">
-        <v>33.42</v>
+        <v>371137</v>
       </c>
       <c r="S60" t="n">
-        <v>371137</v>
+        <v>-3.915762</v>
       </c>
       <c r="T60" t="n">
-        <v>0.07079299999999999</v>
+        <v>1.369122</v>
       </c>
       <c r="U60" t="n">
-        <v>-3.915762</v>
+        <v>1.369286</v>
       </c>
       <c r="V60" t="n">
-        <v>1.369122</v>
+        <v>0.565068</v>
       </c>
       <c r="W60" t="n">
-        <v>1.369286</v>
+        <v>0.742264</v>
       </c>
       <c r="X60" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.742264</v>
+        <v>1.151227</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.461065</v>
+        <v>4.724907</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -7201,59 +6839,57 @@
         <v>0.14</v>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>5.1766</v>
+      </c>
       <c r="J61" t="n">
-        <v>5.1766</v>
-      </c>
-      <c r="K61" t="n">
         <v>5.176</v>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>367558</v>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="W61" t="n">
+      <c r="U61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Y61" t="n">
+        <v>-0.964334</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4.641328</v>
+      </c>
       <c r="AA61" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="AC61" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="AD61" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7272,13 +6908,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>5.0666</v>
+      </c>
       <c r="J62" t="n">
-        <v>5.0666</v>
-      </c>
-      <c r="K62" t="n">
         <v>5.066</v>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7287,34 +6923,32 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
+      <c r="T62" t="n">
         <v>-2.124947</v>
       </c>
-      <c r="W62" t="n">
+      <c r="U62" t="n">
         <v>-2.125193</v>
       </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AG62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,140 +458,150 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>var_pct_ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -620,39 +630,41 @@
         <v>1.02</v>
       </c>
       <c r="H2" t="n">
+        <v>96.31464</v>
+      </c>
+      <c r="I2" t="n">
         <v>99.83978</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.121</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4271865</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1833179</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2438686</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2.36</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.58</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2.94</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>20.26</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>355671</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -669,6 +681,8 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -693,81 +707,87 @@
         <v>0.88</v>
       </c>
       <c r="H3" t="n">
+        <v>97.07568000000001</v>
+      </c>
+      <c r="I3" t="n">
         <v>99.32829</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4346060</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1851006</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2495054</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2.37</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1.56</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2.96</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>20.92</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>370395</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="U3" t="n">
         <v>-0.512311</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -794,81 +814,87 @@
         <v>1.2</v>
       </c>
       <c r="H4" t="n">
+        <v>96.95968999999999</v>
+      </c>
+      <c r="I4" t="n">
         <v>97.24746</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4441056</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1894119</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2546936</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2.34</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1.43</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>21.42</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>368886</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>-0.119484</v>
+      </c>
+      <c r="U4" t="n">
         <v>-2.094902</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -895,81 +921,87 @@
         <v>1.16</v>
       </c>
       <c r="H5" t="n">
+        <v>97.48142</v>
+      </c>
+      <c r="I5" t="n">
         <v>96.62081999999999</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5.643</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4511956</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1910940</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2601017</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2.33</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.43</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>22.89</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>367927</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
+        <v>0.53809</v>
+      </c>
+      <c r="U5" t="n">
         <v>-0.644377</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -996,81 +1028,87 @@
         <v>0.84</v>
       </c>
       <c r="H6" t="n">
+        <v>98.97262000000001</v>
+      </c>
+      <c r="I6" t="n">
         <v>98.05768</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4597507</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1933111</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2664395</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>2.36</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.46</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3.01</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>23.91</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>367772</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
+        <v>1.529727</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.487112</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1097,81 +1135,87 @@
         <v>0.73</v>
       </c>
       <c r="H7" t="n">
+        <v>99.35339</v>
+      </c>
+      <c r="I7" t="n">
         <v>99.33126</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4682852</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1974391</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2708461</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2.35</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1.4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.05</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>24.21</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>362204</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>0.384723</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.298807</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1198,81 +1242,87 @@
         <v>0.67</v>
       </c>
       <c r="H8" t="n">
+        <v>97.34401</v>
+      </c>
+      <c r="I8" t="n">
         <v>90.45032</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4682131</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1947035</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2735096</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2.51</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1.46</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>25.23</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>358398</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>-2.022457</v>
+      </c>
+      <c r="U8" t="n">
         <v>-8.94073</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1299,81 +1349,87 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
+        <v>98.43725000000001</v>
+      </c>
+      <c r="I9" t="n">
         <v>95.72214</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>4727818</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1971524</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2756295</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2.57</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1.44</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>25.63</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>357740</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>1.123069</v>
+      </c>
+      <c r="U9" t="n">
         <v>5.828415</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1400,81 +1456,87 @@
         <v>1.71</v>
       </c>
       <c r="H10" t="n">
+        <v>99.55981</v>
+      </c>
+      <c r="I10" t="n">
         <v>104.61484</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4794583</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1994119</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>2800464</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.66</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>1.55</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>26.54</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>353169</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>1.140381</v>
+      </c>
+      <c r="U10" t="n">
         <v>9.290118</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.11</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1501,81 +1563,87 @@
         <v>1.04</v>
       </c>
       <c r="H11" t="n">
+        <v>99.51646</v>
+      </c>
+      <c r="I11" t="n">
         <v>100.42352</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>4833732</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2003312</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>2830420</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2.72</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1.57</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>27.46</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>345097</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
+        <v>-0.043542</v>
+      </c>
+      <c r="U11" t="n">
         <v>-4.00643</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1602,81 +1670,87 @@
         <v>0.45</v>
       </c>
       <c r="H12" t="n">
+        <v>99.67415</v>
+      </c>
+      <c r="I12" t="n">
         <v>99.79777</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>4889397</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2013726</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2875671</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2.79</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1.57</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>27.42</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>346415</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
+        <v>0.158456</v>
+      </c>
+      <c r="U12" t="n">
         <v>-0.623111</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1703,87 +1777,93 @@
         <v>0.62</v>
       </c>
       <c r="H13" t="n">
+        <v>99.6343</v>
+      </c>
+      <c r="I13" t="n">
         <v>99.53784</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.238</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>4965603</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2052569</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2913035</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>2.73</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1.52</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>3.57</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>27.88</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>341958</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
+        <v>-0.03998</v>
+      </c>
+      <c r="U13" t="n">
         <v>-0.260457</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1810,87 +1890,93 @@
         <v>-0.6</v>
       </c>
       <c r="H14" t="n">
+        <v>101.27684</v>
+      </c>
+      <c r="I14" t="n">
         <v>103.95861</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4999244</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2047038</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2952207</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>2.84</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1.6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>29.24</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>346403</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
+        <v>1.648569</v>
+      </c>
+      <c r="U14" t="n">
         <v>4.441296</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AJ14" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1917,87 +2003,93 @@
         <v>-0.31</v>
       </c>
       <c r="H15" t="n">
+        <v>101.07328</v>
+      </c>
+      <c r="I15" t="n">
         <v>104.56278</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>5.179</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5072711</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2064183</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3008528</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2.9</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>28.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>339664</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
+        <v>-0.200994</v>
+      </c>
+      <c r="U15" t="n">
         <v>0.581164</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2024,87 +2116,93 @@
         <v>-0.32</v>
       </c>
       <c r="H16" t="n">
+        <v>101.17973</v>
+      </c>
+      <c r="I16" t="n">
         <v>101.38087</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>5.406</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5164775</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2109806</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>3054969</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2.92</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.65</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>28.57</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>327580</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="U16" t="n">
         <v>-3.043062</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.03</v>
       </c>
       <c r="AH16" t="n">
         <v>0.02</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2131,87 +2229,93 @@
         <v>0.47</v>
       </c>
       <c r="H17" t="n">
+        <v>101.46342</v>
+      </c>
+      <c r="I17" t="n">
         <v>100.20398</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>5.257</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>5215990</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2105856</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>3110134</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.04</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.77</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>29.68</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>325546</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
+        <v>0.280382</v>
+      </c>
+      <c r="U17" t="n">
         <v>-1.16086</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2238,87 +2342,93 @@
         <v>0.38</v>
       </c>
       <c r="H18" t="n">
+        <v>100.66227</v>
+      </c>
+      <c r="I18" t="n">
         <v>99.36927</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5285657</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2130312</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3155345</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3.07</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1.81</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>3.92</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>30.52</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>331505</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
+        <v>-0.789595</v>
+      </c>
+      <c r="U18" t="n">
         <v>-0.8330109999999999</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0.03</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2345,87 +2455,93 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H19" t="n">
+        <v>100.58196</v>
+      </c>
+      <c r="I19" t="n">
         <v>99.97806</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5366069</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2178236</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>3187833</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>3.07</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1.8</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3.94</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>29.64</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>324703</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
+        <v>-0.07978200000000001</v>
+      </c>
+      <c r="U19" t="n">
         <v>0.612654</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>-0</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>-0</v>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2452,87 +2568,93 @@
         <v>0.46</v>
       </c>
       <c r="H20" t="n">
+        <v>100.05178</v>
+      </c>
+      <c r="I20" t="n">
         <v>93.79237000000001</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>5373231</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2151399</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>3221831</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.24</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1.94</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>30.54</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>331122</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
+        <v>-0.527112</v>
+      </c>
+      <c r="U20" t="n">
         <v>-6.187047</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0.17</v>
       </c>
       <c r="AI20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2559,87 +2681,93 @@
         <v>0.77</v>
       </c>
       <c r="H21" t="n">
+        <v>103.00964</v>
+      </c>
+      <c r="I21" t="n">
         <v>98.75064999999999</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>5370950</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2136105</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>3234845</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.36</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.17</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>30.48</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>328098</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
+        <v>2.956329</v>
+      </c>
+      <c r="U21" t="n">
         <v>5.286443</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2666,87 +2794,93 @@
         <v>0.64</v>
       </c>
       <c r="H22" t="n">
+        <v>103.09341</v>
+      </c>
+      <c r="I22" t="n">
         <v>110.62354</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5424811</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>2154900</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>3269910</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.35</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>4.11</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>30.99</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>341158</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
+        <v>0.08132200000000001</v>
+      </c>
+      <c r="U22" t="n">
         <v>12.023101</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2773,87 +2907,93 @@
         <v>0.53</v>
       </c>
       <c r="H23" t="n">
+        <v>104.1626</v>
+      </c>
+      <c r="I23" t="n">
         <v>104.34152</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5426307</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2145000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3281308</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3.54</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2.45</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>31.62</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>345725</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
+        <v>1.037108</v>
+      </c>
+      <c r="U23" t="n">
         <v>-5.678737</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>0.15</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2880,87 +3020,93 @@
         <v>0.36</v>
       </c>
       <c r="H24" t="n">
+        <v>102.3642</v>
+      </c>
+      <c r="I24" t="n">
         <v>102.66392</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5453708</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2145530</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>3308178</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.65</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>2.58</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>4.35</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>31.63</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>343489</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
+        <v>-1.726531</v>
+      </c>
+      <c r="U24" t="n">
         <v>-1.607797</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
         <v>-0</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>-0</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.13</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AJ24" t="n">
         <v>0.09</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2987,87 +3133,93 @@
         <v>-0.1</v>
       </c>
       <c r="H25" t="n">
+        <v>102.50431</v>
+      </c>
+      <c r="I25" t="n">
         <v>102.53174</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5479459</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2169613</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>3309846</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>2.63</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>30.85</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>343620</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
+        <v>0.136874</v>
+      </c>
+      <c r="U25" t="n">
         <v>-0.12875</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AB25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3094,87 +3246,93 @@
         <v>-0.09</v>
       </c>
       <c r="H26" t="n">
+        <v>102.83357</v>
+      </c>
+      <c r="I26" t="n">
         <v>105.47522</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5484871</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2153541</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3331330</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3.63</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2.73</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>4.22</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>30.43</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>345476</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
+        <v>0.321216</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.870799</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3201,87 +3359,93 @@
         <v>0.2</v>
       </c>
       <c r="H27" t="n">
+        <v>102.45222</v>
+      </c>
+      <c r="I27" t="n">
         <v>106.13139</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5559063</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2172658</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>3386405</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3.61</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>2.82</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>4.12</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>29.92</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>344177</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
+        <v>-0.370842</v>
+      </c>
+      <c r="U27" t="n">
         <v>0.622108</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3308,87 +3472,93 @@
         <v>0.11</v>
       </c>
       <c r="H28" t="n">
+        <v>102.57885</v>
+      </c>
+      <c r="I28" t="n">
         <v>102.00419</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>5.007</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5625945</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2215175</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>3410769</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>3.54</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>2.82</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>29.66</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>340324</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
+        <v>0.123599</v>
+      </c>
+      <c r="U28" t="n">
         <v>-3.888765</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3415,87 +3585,93 @@
         <v>0.12</v>
       </c>
       <c r="H29" t="n">
+        <v>102.87707</v>
+      </c>
+      <c r="I29" t="n">
         <v>102.0744</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>5653808</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2204808</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>3449000</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>3.56</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>2.92</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>3.97</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>29.24</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>340247</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
+        <v>0.290723</v>
+      </c>
+      <c r="U29" t="n">
         <v>0.068831</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.02</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.1</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3522,87 +3698,93 @@
         <v>0.1</v>
       </c>
       <c r="H30" t="n">
+        <v>103.528</v>
+      </c>
+      <c r="I30" t="n">
         <v>101.86494</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>5711103</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2220766</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3490337</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>3.53</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2.99</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>29.01</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>348406</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
+        <v>0.632726</v>
+      </c>
+      <c r="U30" t="n">
         <v>-0.205203</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AJ30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3629,87 +3811,93 @@
         <v>0.55</v>
       </c>
       <c r="H31" t="n">
+        <v>104.8991</v>
+      </c>
+      <c r="I31" t="n">
         <v>101.74606</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>5805157</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2283485</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3521672</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>3.29</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2.59</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>28.14</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>355034</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
+        <v>1.324376</v>
+      </c>
+      <c r="U31" t="n">
         <v>-0.116704</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AJ31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3736,87 +3924,93 @@
         <v>0.57</v>
       </c>
       <c r="H32" t="n">
+        <v>104.53245</v>
+      </c>
+      <c r="I32" t="n">
         <v>98.01879</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>5794707</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2234362</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3560345</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>3.38</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>2.77</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>28</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>355066</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
+        <v>-0.349526</v>
+      </c>
+      <c r="U32" t="n">
         <v>-3.663306</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.18</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AJ32" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3843,87 +4037,93 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="n">
+        <v>104.75961</v>
+      </c>
+      <c r="I33" t="n">
         <v>102.37988</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5815954</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>2235302</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3580652</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>3.38</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>2.76</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>3.76</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>27.85</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>352705</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
+        <v>0.217311</v>
+      </c>
+      <c r="U33" t="n">
         <v>4.449239</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3950,87 +4150,93 @@
         <v>0.19</v>
       </c>
       <c r="H34" t="n">
+        <v>104.7097</v>
+      </c>
+      <c r="I34" t="n">
         <v>109.58504</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>5899742</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>2285775</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>3613967</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>3.33</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>2.71</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>28.14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>355008</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
+        <v>-0.047642</v>
+      </c>
+      <c r="U34" t="n">
         <v>7.037672</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>-0.05</v>
       </c>
       <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
       <c r="AI34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4057,87 +4263,93 @@
         <v>0.37</v>
       </c>
       <c r="H35" t="n">
+        <v>104.75682</v>
+      </c>
+      <c r="I35" t="n">
         <v>109.36335</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>5915538</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2268879</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3646659</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3.37</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2.76</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>27.86</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>351599</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
+        <v>0.045001</v>
+      </c>
+      <c r="U35" t="n">
         <v>-0.2023</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.05</v>
       </c>
       <c r="AH35" t="n">
         <v>0.04</v>
       </c>
       <c r="AI35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4164,87 +4376,93 @@
         <v>0.46</v>
       </c>
       <c r="H36" t="n">
+        <v>105.70704</v>
+      </c>
+      <c r="I36" t="n">
         <v>104.84682</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>5.241</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>5953960</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2278309</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>3675652</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>3.43</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.8</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>27.75</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>355560</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
+        <v>0.907072</v>
+      </c>
+      <c r="U36" t="n">
         <v>-4.129839</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.06</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4271,87 +4489,93 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
+        <v>106.57623</v>
+      </c>
+      <c r="I37" t="n">
         <v>106.03093</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6041898</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2336858</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>3705041</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>3.29</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>2.64</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>27.81</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>357827</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
+        <v>0.822263</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.129371</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4378,87 +4602,93 @@
         <v>0.26</v>
       </c>
       <c r="H38" t="n">
+        <v>106.88756</v>
+      </c>
+      <c r="I38" t="n">
         <v>111.55002</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6069205</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2323362</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>3745844</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>3.3</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>2.52</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>3.78</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>27.74</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>363282</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="U38" t="n">
         <v>5.20517</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4485,87 +4715,93 @@
         <v>-0.14</v>
       </c>
       <c r="H39" t="n">
+        <v>107.14396</v>
+      </c>
+      <c r="I39" t="n">
         <v>110.19363</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>6135298</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2344397</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3790900</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>3.33</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>2.55</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.82</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>27.59</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>369214</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
+        <v>0.239878</v>
+      </c>
+      <c r="U39" t="n">
         <v>-1.215948</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.04</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4592,87 +4828,93 @@
         <v>0.48</v>
       </c>
       <c r="H40" t="n">
+        <v>107.99916</v>
+      </c>
+      <c r="I40" t="n">
         <v>107.28836</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>6216528</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2384828</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>3831700</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.34</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>2.56</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>27.49</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>372016</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
+        <v>0.7981780000000001</v>
+      </c>
+      <c r="U40" t="n">
         <v>-2.636514</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.01</v>
       </c>
       <c r="AH40" t="n">
         <v>0.01</v>
       </c>
       <c r="AI40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4699,87 +4941,93 @@
         <v>0.61</v>
       </c>
       <c r="H41" t="n">
+        <v>108.15356</v>
+      </c>
+      <c r="I41" t="n">
         <v>109.21678</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>6275117</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2397533</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>3877584</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>3.3</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2.52</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>27.94</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>366096</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
+        <v>0.142964</v>
+      </c>
+      <c r="U41" t="n">
         <v>1.797418</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>-0.04</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
       <c r="AI41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4806,87 +5054,93 @@
         <v>0.33</v>
       </c>
       <c r="H42" t="n">
+        <v>107.98489</v>
+      </c>
+      <c r="I42" t="n">
         <v>105.74688</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>6365690</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2436022</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>3929668</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>3.27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>2.5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>28.45</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>363003</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
+        <v>-0.155954</v>
+      </c>
+      <c r="U42" t="n">
         <v>-3.177076</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AB42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AJ42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4913,87 +5167,93 @@
         <v>0.48</v>
       </c>
       <c r="H43" t="n">
+        <v>107.44467</v>
+      </c>
+      <c r="I43" t="n">
         <v>104.2734</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>6464602</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2499177</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>3965425</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>3.08</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2.21</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>3.63</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>28.5</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>329730</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
+        <v>-0.500274</v>
+      </c>
+      <c r="U43" t="n">
         <v>-1.393403</v>
       </c>
-      <c r="T43" t="n">
+      <c r="V43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="U43" t="n">
+      <c r="W43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="V43" t="n">
+      <c r="X43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Z43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AB43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>1</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AF43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AJ43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5020,87 +5280,93 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
+        <v>108.06979</v>
+      </c>
+      <c r="I44" t="n">
         <v>101.23438</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>6465016</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2451957</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>4013059</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>3.34</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>2.43</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>3.89</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>29.88</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>328303</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
+        <v>0.581806</v>
+      </c>
+      <c r="U44" t="n">
         <v>-2.914473</v>
       </c>
-      <c r="T44" t="n">
+      <c r="V44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AG44" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.22</v>
       </c>
       <c r="AH44" t="n">
         <v>0.26</v>
       </c>
       <c r="AI44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5127,87 +5393,93 @@
         <v>1.48</v>
       </c>
       <c r="H45" t="n">
+        <v>108.77346</v>
+      </c>
+      <c r="I45" t="n">
         <v>107.07838</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>6511444</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2477151</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>4034293</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>3.41</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>2.52</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>3.96</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>30.53</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>332508</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
+        <v>0.651126</v>
+      </c>
+      <c r="U45" t="n">
         <v>5.772742</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AI45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5234,87 +5506,93 @@
         <v>0.51</v>
       </c>
       <c r="H46" t="n">
+        <v>110.09056</v>
+      </c>
+      <c r="I46" t="n">
         <v>114.05013</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>6576464</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2498262</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>4078202</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>3.44</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>2.49</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>31.34</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>336157</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
+        <v>1.210865</v>
+      </c>
+      <c r="U46" t="n">
         <v>6.510885</v>
       </c>
-      <c r="T46" t="n">
+      <c r="V46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Z46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AB46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>1</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AJ46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5341,87 +5619,93 @@
         <v>0.48</v>
       </c>
       <c r="H47" t="n">
+        <v>109.72323</v>
+      </c>
+      <c r="I47" t="n">
         <v>112.73813</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>6623948</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2512426</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>4111522</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>3.67</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>2.72</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>4.25</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>31.63</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>340789</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
+        <v>-0.333662</v>
+      </c>
+      <c r="U47" t="n">
         <v>-1.150371</v>
       </c>
-      <c r="T47" t="n">
+      <c r="V47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="U47" t="n">
+      <c r="W47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="V47" t="n">
+      <c r="X47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Z47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AA47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AJ47" t="n">
         <v>0.22</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5448,87 +5732,93 @@
         <v>0.35</v>
       </c>
       <c r="H48" t="n">
+        <v>109.00057</v>
+      </c>
+      <c r="I48" t="n">
         <v>108.66481</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>6666287</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2532708</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>4133579</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>3.72</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>2.67</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>4.36</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>31.7</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>341459</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
+        <v>-0.658621</v>
+      </c>
+      <c r="U48" t="n">
         <v>-3.613081</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="V48" t="n">
+      <c r="X48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Z48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AA48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AB48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AF48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AJ48" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5555,87 +5845,93 @@
         <v>0.23</v>
       </c>
       <c r="H49" t="n">
+        <v>108.76683</v>
+      </c>
+      <c r="I49" t="n">
         <v>107.55639</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>6703663</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2547693</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>4155970</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>3.75</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>2.67</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>31.85</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>344440</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
+        <v>-0.214439</v>
+      </c>
+      <c r="U49" t="n">
         <v>-1.020036</v>
       </c>
-      <c r="T49" t="n">
+      <c r="V49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="U49" t="n">
+      <c r="W49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="V49" t="n">
+      <c r="X49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="W49" t="n">
+      <c r="Y49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Z49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AA49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AB49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AF49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AG49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>0.03</v>
       </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.05</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5662,87 +5958,93 @@
         <v>0.21</v>
       </c>
       <c r="H50" t="n">
+        <v>108.27053</v>
+      </c>
+      <c r="I50" t="n">
         <v>113.14433</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>6733209</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2544400</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>4188808</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>3.96</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>2.79</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>4.66</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>31.75</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>345111</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
+        <v>-0.456297</v>
+      </c>
+      <c r="U50" t="n">
         <v>5.195358</v>
       </c>
-      <c r="T50" t="n">
+      <c r="V50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="U50" t="n">
+      <c r="W50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Z50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AG50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>0.12</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AJ50" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5769,87 +6071,93 @@
         <v>-0.21</v>
       </c>
       <c r="H51" t="n">
+        <v>108.80021</v>
+      </c>
+      <c r="I51" t="n">
         <v>110.57963</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>6774436</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2546265</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>4228171</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>4.14</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>2.85</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>4.92</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>31.87</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>350767</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
+        <v>0.489219</v>
+      </c>
+      <c r="U51" t="n">
         <v>-2.266751</v>
       </c>
-      <c r="T51" t="n">
+      <c r="V51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="V51" t="n">
+      <c r="X51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="W51" t="n">
+      <c r="Y51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AA51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AB51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.06</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5876,87 +6184,93 @@
         <v>0.52</v>
       </c>
       <c r="H52" t="n">
+        <v>108.63642</v>
+      </c>
+      <c r="I52" t="n">
         <v>109.59513</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>5.318</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>6852705</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2589817</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>4262888</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>4.09</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>2.77</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>4.89</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>31.47</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>356582</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
+        <v>-0.150542</v>
+      </c>
+      <c r="U52" t="n">
         <v>-0.890309</v>
       </c>
-      <c r="T52" t="n">
+      <c r="V52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="V52" t="n">
+      <c r="X52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="W52" t="n">
+      <c r="Y52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Z52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AA52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AB52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AC52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AI52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5983,87 +6297,93 @@
         <v>0.03</v>
       </c>
       <c r="H53" t="n">
+        <v>108.7159</v>
+      </c>
+      <c r="I53" t="n">
         <v>110.16346</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>6923886</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2597630</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>4326256</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4.18</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>2.82</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>32.04</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>357103</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
+        <v>0.073161</v>
+      </c>
+      <c r="U53" t="n">
         <v>0.518572</v>
       </c>
-      <c r="T53" t="n">
+      <c r="V53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Z53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AA53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AB53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AJ53" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6090,87 +6410,93 @@
         <v>0.03</v>
       </c>
       <c r="H54" t="n">
+        <v>109.27405</v>
+      </c>
+      <c r="I54" t="n">
         <v>106.90236</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>7003273</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2616213</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>4387061</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>4.23</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>2.74</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>32.32</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>360578</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
+        <v>0.513402</v>
+      </c>
+      <c r="U54" t="n">
         <v>-2.960237</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Z54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AA54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AB54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AC54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AD54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
         <v>-0</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>-0</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AH54" t="n">
         <v>0.05</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AJ54" t="n">
         <v>0.13</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6197,87 +6523,93 @@
         <v>0.21</v>
       </c>
       <c r="H55" t="n">
+        <v>109.41762</v>
+      </c>
+      <c r="I55" t="n">
         <v>107.17649</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>7136436</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2701146</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>4435290</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>4.2</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>2.68</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>5.12</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>31.99</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>358234</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
+        <v>0.131385</v>
+      </c>
+      <c r="U55" t="n">
         <v>0.25643</v>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Z55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AB55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AC55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
         <v>3.897866</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
       <c r="AE55" t="n">
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6304,87 +6636,93 @@
         <v>0.39</v>
       </c>
       <c r="H56" t="n">
+        <v>110.05486</v>
+      </c>
+      <c r="I56" t="n">
         <v>102.36456</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>7130500</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2654052</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>4476448</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>4.45</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>2.87</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>5.38</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>32.6</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>364367</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
+        <v>0.582392</v>
+      </c>
+      <c r="U56" t="n">
         <v>-4.489725</v>
       </c>
-      <c r="T56" t="n">
+      <c r="V56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="U56" t="n">
+      <c r="W56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="V56" t="n">
+      <c r="X56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Z56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AA56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AB56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AC56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
       <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AI56" t="n">
         <v>0.19</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AJ56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6411,87 +6749,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H57" t="n">
+        <v>110.65892</v>
+      </c>
+      <c r="I57" t="n">
         <v>106.82125</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>7156987</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2655931</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>4501056</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>3.07</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>5.56</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>32.78</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>371074</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
+        <v>0.548872</v>
+      </c>
+      <c r="U57" t="n">
         <v>4.353743</v>
       </c>
-      <c r="T57" t="n">
+      <c r="V57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="U57" t="n">
+      <c r="W57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Z57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AA57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AB57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AC57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
       <c r="AE57" t="n">
         <v>0</v>
       </c>
       <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.19</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AJ57" t="n">
         <v>0.18</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6518,87 +6862,93 @@
         <v>0.91</v>
       </c>
       <c r="H58" t="n">
+        <v>110.51078</v>
+      </c>
+      <c r="I58" t="n">
         <v>117.8089</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>7237735</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2686046</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>4551689</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>4.52</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>3.04</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>32.99</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>362002</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
+        <v>-0.133871</v>
+      </c>
+      <c r="U58" t="n">
         <v>10.286015</v>
       </c>
-      <c r="T58" t="n">
+      <c r="V58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="U58" t="n">
+      <c r="W58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Y58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Z58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AA58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AB58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AC58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AD58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AE58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AF58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AH58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AI58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AJ58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6625,87 +6975,93 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H59" t="n">
+        <v>110.95732</v>
+      </c>
+      <c r="I59" t="n">
         <v>113.99365</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>4.988</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>7258599</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2684623</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>4573976</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>4.63</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>3.15</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>5.51</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>33.51</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>366913</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
+        <v>0.404069</v>
+      </c>
+      <c r="U59" t="n">
         <v>-3.238507</v>
       </c>
-      <c r="T59" t="n">
+      <c r="V59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="U59" t="n">
+      <c r="W59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="V59" t="n">
+      <c r="X59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="W59" t="n">
+      <c r="Y59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Z59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AA59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AB59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AC59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AD59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AE59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AG59" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0.11</v>
       </c>
       <c r="AH59" t="n">
         <v>0.11</v>
       </c>
       <c r="AI59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6732,87 +7088,93 @@
         <v>0.65</v>
       </c>
       <c r="H60" t="n">
+        <v>111.03587</v>
+      </c>
+      <c r="I60" t="n">
         <v>109.52993</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>7299615</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2704550</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>4595065</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>4.74</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>3.24</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>5.62</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>33.42</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>371137</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
+        <v>0.07079299999999999</v>
+      </c>
+      <c r="U60" t="n">
         <v>-3.915762</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="V60" t="n">
+      <c r="X60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="W60" t="n">
+      <c r="Y60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Z60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AA60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AB60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AC60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AD60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AG60" t="n">
         <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0.09</v>
       </c>
       <c r="AH60" t="n">
         <v>0.11</v>
       </c>
       <c r="AI60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -6839,57 +7201,59 @@
         <v>0.14</v>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>5.176</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>367558</v>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="U61" t="n">
+      <c r="W61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="n">
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AB61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AC61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AD61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AE61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AG61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6908,13 +7272,13 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>5.0666</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>5.066</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>5.1005</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.0998</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -6923,32 +7287,34 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="n">
-        <v>-2.124947</v>
-      </c>
-      <c r="U62" t="n">
-        <v>-2.125193</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
+        <v>-1.470077</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-1.472179</v>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AG62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AE62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,170 +438,140 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>cdi</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>ipca</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>saldo_credito_pf</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inadimplencia_pj</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>var_pct_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>var_pct_saldo_credito_pf</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>dif_cdi</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -618,53 +588,47 @@
         <v>0.016137</v>
       </c>
       <c r="D2" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="E2" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.02</v>
+        <v>99.83978</v>
       </c>
       <c r="H2" t="n">
-        <v>96.31464</v>
+        <v>5.1216</v>
       </c>
       <c r="I2" t="n">
-        <v>99.83978</v>
+        <v>5.121</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="K2" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="L2" t="n">
-        <v>4271865</v>
+        <v>2.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1833179</v>
+        <v>1.58</v>
       </c>
       <c r="N2" t="n">
-        <v>2438686</v>
+        <v>2.94</v>
       </c>
       <c r="O2" t="n">
-        <v>2.36</v>
+        <v>20.26</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="S2" t="n">
         <v>355671</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -677,12 +641,6 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -695,99 +653,81 @@
         <v>0.019413</v>
       </c>
       <c r="D3" t="n">
-        <v>0.019413</v>
+        <v>0.87</v>
       </c>
       <c r="E3" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="F3" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>0.88</v>
+        <v>99.32829</v>
       </c>
       <c r="H3" t="n">
-        <v>97.07568000000001</v>
+        <v>5.1433</v>
       </c>
       <c r="I3" t="n">
-        <v>99.32829</v>
+        <v>5.1427</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1433</v>
+        <v>4346060</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1427</v>
+        <v>1851006</v>
       </c>
       <c r="L3" t="n">
-        <v>4346060</v>
+        <v>2.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1851006</v>
+        <v>1.56</v>
       </c>
       <c r="N3" t="n">
-        <v>2495054</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>20.92</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>370395</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>-0.512311</v>
       </c>
       <c r="R3" t="n">
-        <v>20.92</v>
+        <v>0.423696</v>
       </c>
       <c r="S3" t="n">
-        <v>370395</v>
+        <v>0.423745</v>
       </c>
       <c r="T3" t="n">
-        <v>0.79016</v>
+        <v>1.736829</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.512311</v>
+        <v>0.972464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423696</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.423745</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.736829</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.972464</v>
-      </c>
+        <v>4.139781</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>2.311409</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.139781</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+        <v>0.003276</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -802,99 +742,81 @@
         <v>0.021003</v>
       </c>
       <c r="D4" t="n">
-        <v>0.021003</v>
+        <v>1.16</v>
       </c>
       <c r="E4" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>97.24746</v>
       </c>
       <c r="H4" t="n">
-        <v>96.95968999999999</v>
+        <v>5.4394</v>
       </c>
       <c r="I4" t="n">
-        <v>97.24746</v>
+        <v>5.4388</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4394</v>
+        <v>4441056</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4388</v>
+        <v>1894119</v>
       </c>
       <c r="L4" t="n">
-        <v>4441056</v>
+        <v>2.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1894119</v>
+        <v>1.43</v>
       </c>
       <c r="N4" t="n">
-        <v>2546936</v>
+        <v>3.01</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>21.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>368886</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>-2.094902</v>
       </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>5.757004</v>
       </c>
       <c r="S4" t="n">
-        <v>368886</v>
+        <v>5.757676</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.119484</v>
+        <v>2.185796</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.094902</v>
+        <v>2.329166</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757004</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5.757676</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.185796</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.329166</v>
-      </c>
+        <v>-0.407403</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>2.079394</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.407403</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+        <v>0.001591</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.001591</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.001591</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -909,99 +831,81 @@
         <v>0.024244</v>
       </c>
       <c r="D5" t="n">
-        <v>0.024244</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.16</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>97.48142</v>
+        <v>5.643</v>
       </c>
       <c r="I5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.6424</v>
       </c>
       <c r="J5" t="n">
-        <v>5.643</v>
+        <v>4511956</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6424</v>
+        <v>1910940</v>
       </c>
       <c r="L5" t="n">
-        <v>4511956</v>
+        <v>2.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1910940</v>
+        <v>1.43</v>
       </c>
       <c r="N5" t="n">
-        <v>2601017</v>
+        <v>2.99</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>22.89</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>367927</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.99</v>
+        <v>-0.644377</v>
       </c>
       <c r="R5" t="n">
-        <v>22.89</v>
+        <v>3.74306</v>
       </c>
       <c r="S5" t="n">
-        <v>367927</v>
+        <v>3.743473</v>
       </c>
       <c r="T5" t="n">
-        <v>0.53809</v>
+        <v>1.596467</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.644377</v>
+        <v>0.888065</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74306</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.743473</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.596467</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.888065</v>
-      </c>
+        <v>-0.259972</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>2.123375</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.259972</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>0.00324</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.00324</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.00324</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1016,99 +920,81 @@
         <v>0.029256</v>
       </c>
       <c r="D6" t="n">
-        <v>0.029256</v>
+        <v>0.95</v>
       </c>
       <c r="E6" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G6" t="n">
+        <v>98.05768</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.6199</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4597507</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1933111</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O6" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="P6" t="n">
+        <v>367772</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.487112</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.409357</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.896096</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.160214</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.042128</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AD6" t="n">
         <v>0.02</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H6" t="n">
-        <v>98.97262000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>98.05768</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.6199</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.6193</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4597507</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1933111</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2664395</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="S6" t="n">
-        <v>367772</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.529727</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.487112</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.409357</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.042128</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1123,99 +1009,81 @@
         <v>0.033316</v>
       </c>
       <c r="D7" t="n">
-        <v>0.033316</v>
+        <v>0.73</v>
       </c>
       <c r="E7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.73</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.87</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.73</v>
+        <v>99.33126</v>
       </c>
       <c r="H7" t="n">
-        <v>99.35339</v>
+        <v>5.5805</v>
       </c>
       <c r="I7" t="n">
-        <v>99.33126</v>
+        <v>5.5799</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5805</v>
+        <v>4682852</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5799</v>
+        <v>1974391</v>
       </c>
       <c r="L7" t="n">
-        <v>4682852</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1974391</v>
+        <v>1.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2708461</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>24.21</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>362204</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>1.298807</v>
       </c>
       <c r="R7" t="n">
-        <v>24.21</v>
+        <v>-0.70108</v>
       </c>
       <c r="S7" t="n">
-        <v>362204</v>
+        <v>-0.701155</v>
       </c>
       <c r="T7" t="n">
-        <v>0.384723</v>
+        <v>1.856332</v>
       </c>
       <c r="U7" t="n">
-        <v>1.298807</v>
+        <v>2.135418</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.70108</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.701155</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.856332</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.135418</v>
-      </c>
+        <v>-1.513981</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>1.653884</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.513981</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+        <v>0.00406</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.04</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1230,99 +1098,81 @@
         <v>0.034749</v>
       </c>
       <c r="D8" t="n">
-        <v>0.034749</v>
+        <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>0.67</v>
+        <v>90.45032</v>
       </c>
       <c r="H8" t="n">
-        <v>97.34401</v>
+        <v>5.3574</v>
       </c>
       <c r="I8" t="n">
-        <v>90.45032</v>
+        <v>5.3568</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3574</v>
+        <v>4682131</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3568</v>
+        <v>1947035</v>
       </c>
       <c r="L8" t="n">
-        <v>4682131</v>
+        <v>2.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1947035</v>
+        <v>1.46</v>
       </c>
       <c r="N8" t="n">
-        <v>2735096</v>
+        <v>3.26</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>25.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>358398</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>-8.94073</v>
       </c>
       <c r="R8" t="n">
-        <v>25.23</v>
+        <v>-3.99785</v>
       </c>
       <c r="S8" t="n">
-        <v>358398</v>
+        <v>-3.99828</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.022457</v>
+        <v>-0.015397</v>
       </c>
       <c r="U8" t="n">
-        <v>-8.94073</v>
+        <v>-1.385541</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99785</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-3.99828</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.015397</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.385541</v>
-      </c>
+        <v>-1.050789</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9834000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.050789</v>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+        <v>0.001433</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.21</v>
+      </c>
       <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1337,99 +1187,81 @@
         <v>0.039598</v>
       </c>
       <c r="D9" t="n">
-        <v>0.039598</v>
+        <v>1.01</v>
       </c>
       <c r="E9" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>95.72214</v>
       </c>
       <c r="H9" t="n">
-        <v>98.43725000000001</v>
+        <v>5.1394</v>
       </c>
       <c r="I9" t="n">
-        <v>95.72214</v>
+        <v>5.1388</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1394</v>
+        <v>4727818</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1388</v>
+        <v>1971524</v>
       </c>
       <c r="L9" t="n">
-        <v>4727818</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="n">
-        <v>1971524</v>
+        <v>1.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2756295</v>
+        <v>3.38</v>
       </c>
       <c r="O9" t="n">
-        <v>2.57</v>
+        <v>25.63</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>357740</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>5.828415</v>
       </c>
       <c r="R9" t="n">
-        <v>25.63</v>
+        <v>-4.069138</v>
       </c>
       <c r="S9" t="n">
-        <v>357740</v>
+        <v>-4.069594</v>
       </c>
       <c r="T9" t="n">
-        <v>1.123069</v>
+        <v>0.975774</v>
       </c>
       <c r="U9" t="n">
-        <v>5.828415</v>
+        <v>1.257759</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069138</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-4.069594</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.975774</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.257759</v>
-      </c>
+        <v>-0.183595</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.775073</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.183595</v>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+        <v>0.004849</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.12</v>
+      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1444,99 +1276,81 @@
         <v>0.041954</v>
       </c>
       <c r="D10" t="n">
-        <v>0.041954</v>
+        <v>1.62</v>
       </c>
       <c r="E10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>104.61484</v>
       </c>
       <c r="H10" t="n">
-        <v>99.55981</v>
+        <v>4.7378</v>
       </c>
       <c r="I10" t="n">
-        <v>104.61484</v>
+        <v>4.7372</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7378</v>
+        <v>4794583</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7372</v>
+        <v>1994119</v>
       </c>
       <c r="L10" t="n">
-        <v>4794583</v>
+        <v>2.66</v>
       </c>
       <c r="M10" t="n">
-        <v>1994119</v>
+        <v>1.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2800464</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>26.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>353169</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>9.290118</v>
       </c>
       <c r="R10" t="n">
-        <v>26.54</v>
+        <v>-7.814142</v>
       </c>
       <c r="S10" t="n">
-        <v>353169</v>
+        <v>-7.815054</v>
       </c>
       <c r="T10" t="n">
-        <v>1.140381</v>
+        <v>1.412174</v>
       </c>
       <c r="U10" t="n">
-        <v>9.290118</v>
+        <v>1.146068</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.814142</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-7.815054</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.412174</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.146068</v>
-      </c>
+        <v>-1.277744</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>1.602477</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.277744</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+        <v>0.002356</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1551,99 +1365,81 @@
         <v>0.043739</v>
       </c>
       <c r="D11" t="n">
-        <v>0.043739</v>
+        <v>1.06</v>
       </c>
       <c r="E11" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.04</v>
+        <v>100.42352</v>
       </c>
       <c r="H11" t="n">
-        <v>99.51646</v>
+        <v>4.9191</v>
       </c>
       <c r="I11" t="n">
-        <v>100.42352</v>
+        <v>4.9185</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9191</v>
+        <v>4833732</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9185</v>
+        <v>2003312</v>
       </c>
       <c r="L11" t="n">
-        <v>4833732</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>2003312</v>
+        <v>1.57</v>
       </c>
       <c r="N11" t="n">
-        <v>2830420</v>
+        <v>3.54</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>27.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>345097</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>-4.00643</v>
       </c>
       <c r="R11" t="n">
-        <v>27.46</v>
+        <v>3.826671</v>
       </c>
       <c r="S11" t="n">
-        <v>345097</v>
+        <v>3.827155</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.043542</v>
+        <v>0.816526</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.00643</v>
+        <v>0.461006</v>
       </c>
       <c r="V11" t="n">
-        <v>3.826671</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.827155</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.816526</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.461006</v>
-      </c>
+        <v>-2.285591</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>1.06968</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.285591</v>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+        <v>0.001785</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1658,99 +1454,81 @@
         <v>0.046796</v>
       </c>
       <c r="D12" t="n">
-        <v>0.046796</v>
+        <v>0.47</v>
       </c>
       <c r="E12" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="F12" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.45</v>
+        <v>99.79777</v>
       </c>
       <c r="H12" t="n">
-        <v>99.67415</v>
+        <v>4.7289</v>
       </c>
       <c r="I12" t="n">
-        <v>99.79777</v>
+        <v>4.7283</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7289</v>
+        <v>4889397</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7283</v>
+        <v>2013726</v>
       </c>
       <c r="L12" t="n">
-        <v>4889397</v>
+        <v>2.79</v>
       </c>
       <c r="M12" t="n">
-        <v>2013726</v>
+        <v>1.57</v>
       </c>
       <c r="N12" t="n">
-        <v>2875671</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>27.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>346415</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.65</v>
+        <v>-0.623111</v>
       </c>
       <c r="R12" t="n">
-        <v>27.42</v>
+        <v>-3.866561</v>
       </c>
       <c r="S12" t="n">
-        <v>346415</v>
+        <v>-3.867033</v>
       </c>
       <c r="T12" t="n">
-        <v>0.158456</v>
+        <v>1.151595</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.623111</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.866561</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-3.867033</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.151595</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
+        <v>0.381922</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>1.598738</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.381922</v>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+        <v>0.003057</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.11</v>
+      </c>
       <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1765,105 +1543,87 @@
         <v>0.048116</v>
       </c>
       <c r="D13" t="n">
-        <v>0.048116</v>
+        <v>0.67</v>
       </c>
       <c r="E13" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="F13" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.62</v>
+        <v>99.53784</v>
       </c>
       <c r="H13" t="n">
-        <v>99.6343</v>
+        <v>5.238</v>
       </c>
       <c r="I13" t="n">
-        <v>99.53784</v>
+        <v>5.2374</v>
       </c>
       <c r="J13" t="n">
-        <v>5.238</v>
+        <v>4965603</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2374</v>
+        <v>2052569</v>
       </c>
       <c r="L13" t="n">
-        <v>4965603</v>
+        <v>2.73</v>
       </c>
       <c r="M13" t="n">
-        <v>2052569</v>
+        <v>1.52</v>
       </c>
       <c r="N13" t="n">
-        <v>2913035</v>
+        <v>3.57</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>27.88</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>341958</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>-0.260457</v>
       </c>
       <c r="R13" t="n">
-        <v>27.88</v>
+        <v>10.765717</v>
       </c>
       <c r="S13" t="n">
-        <v>341958</v>
+        <v>10.767083</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.03998</v>
+        <v>1.558597</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.260457</v>
+        <v>1.928912</v>
       </c>
       <c r="V13" t="n">
-        <v>10.765717</v>
+        <v>-1.286607</v>
       </c>
       <c r="W13" t="n">
-        <v>10.767083</v>
+        <v>11.88673</v>
       </c>
       <c r="X13" t="n">
-        <v>1.558597</v>
+        <v>10.700862</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.928912</v>
+        <v>11.919595</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.299314</v>
+        <v>0.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.286607</v>
+        <v>0.00132</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.88673</v>
+        <v>-0.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.700862</v>
+        <v>-0.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.919595</v>
+        <v>-0.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1878,105 +1638,87 @@
         <v>0.049037</v>
       </c>
       <c r="D14" t="n">
-        <v>0.049037</v>
+        <v>-0.68</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="F14" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6</v>
+        <v>103.95861</v>
       </c>
       <c r="H14" t="n">
-        <v>101.27684</v>
+        <v>5.1884</v>
       </c>
       <c r="I14" t="n">
-        <v>103.95861</v>
+        <v>5.1878</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1884</v>
+        <v>4999244</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1878</v>
+        <v>2047038</v>
       </c>
       <c r="L14" t="n">
-        <v>4999244</v>
+        <v>2.84</v>
       </c>
       <c r="M14" t="n">
-        <v>2047038</v>
+        <v>1.6</v>
       </c>
       <c r="N14" t="n">
-        <v>2952207</v>
+        <v>3.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>29.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>346403</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.71</v>
+        <v>4.441296</v>
       </c>
       <c r="R14" t="n">
-        <v>29.24</v>
+        <v>-0.946926</v>
       </c>
       <c r="S14" t="n">
-        <v>346403</v>
+        <v>-0.947035</v>
       </c>
       <c r="T14" t="n">
-        <v>1.648569</v>
+        <v>0.677481</v>
       </c>
       <c r="U14" t="n">
-        <v>4.441296</v>
+        <v>-0.269467</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.946926</v>
+        <v>1.299867</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.947035</v>
+        <v>10.069235</v>
       </c>
       <c r="X14" t="n">
-        <v>0.677481</v>
+        <v>10.074751</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.269467</v>
+        <v>10.124804</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.344714</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.299867</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.069235</v>
+        <v>0.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.074751</v>
+        <v>0.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.124804</v>
+        <v>0.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1991,105 +1733,87 @@
         <v>0.05056</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05056</v>
+        <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.31</v>
+        <v>104.56278</v>
       </c>
       <c r="H15" t="n">
-        <v>101.07328</v>
+        <v>5.179</v>
       </c>
       <c r="I15" t="n">
-        <v>104.56278</v>
+        <v>5.1784</v>
       </c>
       <c r="J15" t="n">
-        <v>5.179</v>
+        <v>5072711</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1784</v>
+        <v>2064183</v>
       </c>
       <c r="L15" t="n">
-        <v>5072711</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2064183</v>
+        <v>1.62</v>
       </c>
       <c r="N15" t="n">
-        <v>3008528</v>
+        <v>3.78</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>339664</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>0.581164</v>
       </c>
       <c r="R15" t="n">
-        <v>28.6</v>
+        <v>-0.181173</v>
       </c>
       <c r="S15" t="n">
-        <v>339664</v>
+        <v>-0.181194</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.200994</v>
+        <v>1.469562</v>
       </c>
       <c r="U15" t="n">
-        <v>0.581164</v>
+        <v>0.837552</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181173</v>
+        <v>-1.945422</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.181194</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>1.469562</v>
+        <v>8.58755</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.837552</v>
+        <v>8.825751</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.907759</v>
+        <v>0.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.945422</v>
+        <v>0.001523</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.727061000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.58755</v>
+        <v>0.02</v>
       </c>
       <c r="AD15" t="n">
-        <v>8.825751</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2104,105 +1828,87 @@
         <v>0.050788</v>
       </c>
       <c r="D16" t="n">
-        <v>0.050788</v>
+        <v>-0.29</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.32</v>
+        <v>101.38087</v>
       </c>
       <c r="H16" t="n">
-        <v>101.17973</v>
+        <v>5.4066</v>
       </c>
       <c r="I16" t="n">
-        <v>101.38087</v>
+        <v>5.406</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4066</v>
+        <v>5164775</v>
       </c>
       <c r="K16" t="n">
-        <v>5.406</v>
+        <v>2109806</v>
       </c>
       <c r="L16" t="n">
-        <v>5164775</v>
+        <v>2.92</v>
       </c>
       <c r="M16" t="n">
-        <v>2109806</v>
+        <v>1.65</v>
       </c>
       <c r="N16" t="n">
-        <v>3054969</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>28.57</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>327580</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>-3.043062</v>
       </c>
       <c r="R16" t="n">
-        <v>28.57</v>
+        <v>4.394671</v>
       </c>
       <c r="S16" t="n">
-        <v>327580</v>
+        <v>4.39518</v>
       </c>
       <c r="T16" t="n">
-        <v>0.10532</v>
+        <v>1.814888</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.043062</v>
+        <v>2.210221</v>
       </c>
       <c r="V16" t="n">
-        <v>4.394671</v>
+        <v>-3.557633</v>
       </c>
       <c r="W16" t="n">
-        <v>4.39518</v>
+        <v>7.168596</v>
       </c>
       <c r="X16" t="n">
-        <v>1.814888</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.210221</v>
+        <v>7.191214</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.543645</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3.557633</v>
+        <v>0.000228</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.168596</v>
+        <v>0.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.248760000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.191214</v>
+        <v>0.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2217,105 +1923,87 @@
         <v>0.050788</v>
       </c>
       <c r="D17" t="n">
-        <v>0.050788</v>
+        <v>0.59</v>
       </c>
       <c r="E17" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.47</v>
+        <v>100.20398</v>
       </c>
       <c r="H17" t="n">
-        <v>101.46342</v>
+        <v>5.257</v>
       </c>
       <c r="I17" t="n">
-        <v>100.20398</v>
+        <v>5.2564</v>
       </c>
       <c r="J17" t="n">
-        <v>5.257</v>
+        <v>5215990</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2564</v>
+        <v>2105856</v>
       </c>
       <c r="L17" t="n">
-        <v>5215990</v>
+        <v>3.04</v>
       </c>
       <c r="M17" t="n">
-        <v>2105856</v>
+        <v>1.77</v>
       </c>
       <c r="N17" t="n">
-        <v>3110134</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>29.68</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>325546</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>-1.16086</v>
       </c>
       <c r="R17" t="n">
-        <v>29.68</v>
+        <v>-2.766988</v>
       </c>
       <c r="S17" t="n">
-        <v>325546</v>
+        <v>-2.767296</v>
       </c>
       <c r="T17" t="n">
-        <v>0.280382</v>
+        <v>0.991621</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.16086</v>
+        <v>-0.187221</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.766988</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.767296</v>
+        <v>6.470016</v>
       </c>
       <c r="X17" t="n">
-        <v>0.991621</v>
+        <v>6.517038</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.187221</v>
+        <v>6.460076</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.805747</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.470016</v>
+        <v>0.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.517038</v>
+        <v>0.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.460076</v>
+        <v>0.09</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2330,105 +2018,87 @@
         <v>0.050788</v>
       </c>
       <c r="D18" t="n">
-        <v>0.050788</v>
+        <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.38</v>
+        <v>99.36927</v>
       </c>
       <c r="H18" t="n">
-        <v>100.66227</v>
+        <v>5.2941</v>
       </c>
       <c r="I18" t="n">
-        <v>99.36927</v>
+        <v>5.2935</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2941</v>
+        <v>5285657</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2935</v>
+        <v>2130312</v>
       </c>
       <c r="L18" t="n">
-        <v>5285657</v>
+        <v>3.07</v>
       </c>
       <c r="M18" t="n">
-        <v>2130312</v>
+        <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>3155345</v>
+        <v>3.92</v>
       </c>
       <c r="O18" t="n">
-        <v>3.07</v>
+        <v>30.52</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>331505</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.92</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>30.52</v>
+        <v>0.705726</v>
       </c>
       <c r="S18" t="n">
-        <v>331505</v>
+        <v>0.705806</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.789595</v>
+        <v>1.335643</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>1.161333</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705726</v>
+        <v>1.830463</v>
       </c>
       <c r="W18" t="n">
-        <v>0.705806</v>
+        <v>5.900488</v>
       </c>
       <c r="X18" t="n">
-        <v>1.335643</v>
+        <v>5.899363</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.161333</v>
+        <v>5.974439</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.453667</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.830463</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.900488</v>
+        <v>0.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.899363</v>
+        <v>0.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.974439</v>
+        <v>0.03</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2443,105 +2113,87 @@
         <v>0.050788</v>
       </c>
       <c r="D19" t="n">
-        <v>0.050788</v>
+        <v>0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6899999999999999</v>
+        <v>99.97806</v>
       </c>
       <c r="H19" t="n">
-        <v>100.58196</v>
+        <v>5.2177</v>
       </c>
       <c r="I19" t="n">
-        <v>99.97806</v>
+        <v>5.2171</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2177</v>
+        <v>5366069</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2171</v>
+        <v>2178236</v>
       </c>
       <c r="L19" t="n">
-        <v>5366069</v>
+        <v>3.07</v>
       </c>
       <c r="M19" t="n">
-        <v>2178236</v>
+        <v>1.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3187833</v>
+        <v>3.94</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>29.64</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>324703</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>0.612654</v>
       </c>
       <c r="R19" t="n">
-        <v>29.64</v>
+        <v>-1.443116</v>
       </c>
       <c r="S19" t="n">
-        <v>324703</v>
+        <v>-1.443279</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>1.521325</v>
       </c>
       <c r="U19" t="n">
-        <v>0.612654</v>
+        <v>2.249624</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443116</v>
+        <v>-2.051854</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.443279</v>
+        <v>5.784842</v>
       </c>
       <c r="X19" t="n">
-        <v>1.521325</v>
+        <v>5.458422</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.249624</v>
+        <v>5.932356</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.029618</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-2.051854</v>
+        <v>-0</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.784842</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.458422</v>
+        <v>-0.01</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.932356</v>
+        <v>0.02</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2556,105 +2208,87 @@
         <v>0.050788</v>
       </c>
       <c r="D20" t="n">
-        <v>0.050788</v>
+        <v>0.53</v>
       </c>
       <c r="E20" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="F20" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.46</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>100.05178</v>
+        <v>5.0993</v>
       </c>
       <c r="I20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0987</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0993</v>
+        <v>5373231</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0987</v>
+        <v>2151399</v>
       </c>
       <c r="L20" t="n">
-        <v>5373231</v>
+        <v>3.24</v>
       </c>
       <c r="M20" t="n">
-        <v>2151399</v>
+        <v>1.94</v>
       </c>
       <c r="N20" t="n">
-        <v>3221831</v>
+        <v>4.11</v>
       </c>
       <c r="O20" t="n">
-        <v>3.24</v>
+        <v>30.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>331122</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.11</v>
+        <v>-6.187047</v>
       </c>
       <c r="R20" t="n">
-        <v>30.54</v>
+        <v>-2.269199</v>
       </c>
       <c r="S20" t="n">
-        <v>331122</v>
+        <v>-2.26946</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.527112</v>
+        <v>0.133468</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.187047</v>
+        <v>-1.232052</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.269199</v>
+        <v>1.976883</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.26946</v>
+        <v>5.77432</v>
       </c>
       <c r="X20" t="n">
-        <v>0.133468</v>
+        <v>3.79089</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.232052</v>
+        <v>5.711379</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.066493</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.976883</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.77432</v>
+        <v>0.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.79089</v>
+        <v>0.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.711379</v>
+        <v>0.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2669,105 +2303,87 @@
         <v>0.050788</v>
       </c>
       <c r="D21" t="n">
-        <v>0.050788</v>
+        <v>0.84</v>
       </c>
       <c r="E21" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="G21" t="n">
-        <v>0.77</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>103.00964</v>
+        <v>5.2078</v>
       </c>
       <c r="I21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2072</v>
       </c>
       <c r="J21" t="n">
-        <v>5.2078</v>
+        <v>5370950</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2072</v>
+        <v>2136105</v>
       </c>
       <c r="L21" t="n">
-        <v>5370950</v>
+        <v>3.36</v>
       </c>
       <c r="M21" t="n">
-        <v>2136105</v>
+        <v>2.17</v>
       </c>
       <c r="N21" t="n">
-        <v>3234845</v>
+        <v>4.16</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>30.48</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>328098</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.16</v>
+        <v>5.286443</v>
       </c>
       <c r="R21" t="n">
-        <v>30.48</v>
+        <v>2.127743</v>
       </c>
       <c r="S21" t="n">
-        <v>328098</v>
+        <v>2.127993</v>
       </c>
       <c r="T21" t="n">
-        <v>2.956329</v>
+        <v>-0.042451</v>
       </c>
       <c r="U21" t="n">
-        <v>5.286443</v>
+        <v>-0.710886</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127743</v>
+        <v>-0.913259</v>
       </c>
       <c r="W21" t="n">
-        <v>2.127993</v>
+        <v>5.596302</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.042451</v>
+        <v>1.864495</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.710886</v>
+        <v>5.47065</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.403932</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.913259</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.596302</v>
+        <v>0.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.864495</v>
+        <v>0.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.47065</v>
+        <v>0.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2782,105 +2398,87 @@
         <v>0.050788</v>
       </c>
       <c r="D22" t="n">
-        <v>0.050788</v>
+        <v>0.71</v>
       </c>
       <c r="E22" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="G22" t="n">
-        <v>0.64</v>
+        <v>110.62354</v>
       </c>
       <c r="H22" t="n">
-        <v>103.09341</v>
+        <v>5.0804</v>
       </c>
       <c r="I22" t="n">
-        <v>110.62354</v>
+        <v>5.0798</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0804</v>
+        <v>5424811</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0798</v>
+        <v>2154900</v>
       </c>
       <c r="L22" t="n">
-        <v>5424811</v>
+        <v>3.35</v>
       </c>
       <c r="M22" t="n">
-        <v>2154900</v>
+        <v>2.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3269910</v>
+        <v>4.11</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>30.99</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>341158</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.11</v>
+        <v>12.023101</v>
       </c>
       <c r="R22" t="n">
-        <v>30.99</v>
+        <v>-2.446331</v>
       </c>
       <c r="S22" t="n">
-        <v>341158</v>
+        <v>-2.446612</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08132200000000001</v>
+        <v>1.002821</v>
       </c>
       <c r="U22" t="n">
-        <v>12.023101</v>
+        <v>0.879872</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446331</v>
+        <v>3.980518</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.446612</v>
+        <v>4.650694</v>
       </c>
       <c r="X22" t="n">
-        <v>1.002821</v>
+        <v>0.172427</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.879872</v>
+        <v>4.361088</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.083978</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.980518</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.650694</v>
+        <v>-0.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.172427</v>
+        <v>0.03</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.361088</v>
+        <v>-0.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2895,105 +2493,87 @@
         <v>0.050788</v>
       </c>
       <c r="D23" t="n">
-        <v>0.050788</v>
+        <v>0.61</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.53</v>
+        <v>104.34152</v>
       </c>
       <c r="H23" t="n">
-        <v>104.1626</v>
+        <v>5.0007</v>
       </c>
       <c r="I23" t="n">
-        <v>104.34152</v>
+        <v>5.0001</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0007</v>
+        <v>5426307</v>
       </c>
       <c r="K23" t="n">
-        <v>5.0001</v>
+        <v>2145000</v>
       </c>
       <c r="L23" t="n">
-        <v>5426307</v>
+        <v>3.54</v>
       </c>
       <c r="M23" t="n">
-        <v>2145000</v>
+        <v>2.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3281308</v>
+        <v>4.26</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>31.62</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>345725</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>-5.678737</v>
       </c>
       <c r="R23" t="n">
-        <v>31.62</v>
+        <v>-1.568774</v>
       </c>
       <c r="S23" t="n">
-        <v>345725</v>
+        <v>-1.568959</v>
       </c>
       <c r="T23" t="n">
-        <v>1.037108</v>
+        <v>0.027577</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.678737</v>
+        <v>-0.459418</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568774</v>
+        <v>1.338676</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.568959</v>
+        <v>4.184706</v>
       </c>
       <c r="X23" t="n">
-        <v>0.027577</v>
+        <v>-2.158772</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.459418</v>
+        <v>3.834324</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.348572</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.338676</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.184706</v>
+        <v>0.19</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.158772</v>
+        <v>0.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.834324</v>
+        <v>0.15</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -3008,105 +2588,87 @@
         <v>0.050788</v>
       </c>
       <c r="D24" t="n">
-        <v>0.050788</v>
+        <v>0.23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.36</v>
+        <v>102.66392</v>
       </c>
       <c r="H24" t="n">
-        <v>102.3642</v>
+        <v>5.0959</v>
       </c>
       <c r="I24" t="n">
-        <v>102.66392</v>
+        <v>5.0953</v>
       </c>
       <c r="J24" t="n">
-        <v>5.0959</v>
+        <v>5453708</v>
       </c>
       <c r="K24" t="n">
-        <v>5.0953</v>
+        <v>2145530</v>
       </c>
       <c r="L24" t="n">
-        <v>5453708</v>
+        <v>3.65</v>
       </c>
       <c r="M24" t="n">
-        <v>2145530</v>
+        <v>2.58</v>
       </c>
       <c r="N24" t="n">
-        <v>3308178</v>
+        <v>4.35</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>31.63</v>
       </c>
       <c r="P24" t="n">
-        <v>2.58</v>
+        <v>343489</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.35</v>
+        <v>-1.607797</v>
       </c>
       <c r="R24" t="n">
-        <v>31.63</v>
+        <v>1.903733</v>
       </c>
       <c r="S24" t="n">
-        <v>343489</v>
+        <v>1.903962</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.726531</v>
+        <v>0.504966</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.607797</v>
+        <v>0.024709</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903733</v>
+        <v>-0.646757</v>
       </c>
       <c r="W24" t="n">
-        <v>1.903962</v>
+        <v>3.935832</v>
       </c>
       <c r="X24" t="n">
-        <v>0.504966</v>
+        <v>-4.45588</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.024709</v>
+        <v>3.741292</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.818881</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.646757</v>
+        <v>-0</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.935832</v>
+        <v>0.11</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.45588</v>
+        <v>0.13</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.741292</v>
+        <v>0.09</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3121,105 +2683,87 @@
         <v>0.050788</v>
       </c>
       <c r="D25" t="n">
-        <v>0.050788</v>
+        <v>-0.08</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" t="n">
+        <v>102.53174</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.8192</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5479459</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2169613</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="P25" t="n">
+        <v>343620</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.12875</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-5.429855</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.472174</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.122473</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.038138</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.161501</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-6.84947</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.998957</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AD25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H25" t="n">
-        <v>102.50431</v>
-      </c>
-      <c r="I25" t="n">
-        <v>102.53174</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.8192</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.8186</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5479459</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2169613</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3309846</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="S25" t="n">
-        <v>343620</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.136874</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.12875</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-5.429855</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-5.430495</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.472174</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.122473</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.050421</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.038138</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.161501</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>-6.84947</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.998957</v>
-      </c>
       <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3234,105 +2778,87 @@
         <v>0.050788</v>
       </c>
       <c r="D26" t="n">
-        <v>0.050788</v>
+        <v>0.12</v>
       </c>
       <c r="E26" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.09</v>
+        <v>105.47522</v>
       </c>
       <c r="H26" t="n">
-        <v>102.83357</v>
+        <v>4.7415</v>
       </c>
       <c r="I26" t="n">
-        <v>105.47522</v>
+        <v>4.7409</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7415</v>
+        <v>5484871</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7409</v>
+        <v>2153541</v>
       </c>
       <c r="L26" t="n">
-        <v>5484871</v>
+        <v>3.63</v>
       </c>
       <c r="M26" t="n">
-        <v>2153541</v>
+        <v>2.73</v>
       </c>
       <c r="N26" t="n">
-        <v>3331330</v>
+        <v>4.22</v>
       </c>
       <c r="O26" t="n">
-        <v>3.63</v>
+        <v>30.43</v>
       </c>
       <c r="P26" t="n">
-        <v>2.73</v>
+        <v>345476</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.22</v>
+        <v>2.870799</v>
       </c>
       <c r="R26" t="n">
-        <v>30.43</v>
+        <v>-1.612301</v>
       </c>
       <c r="S26" t="n">
-        <v>345476</v>
+        <v>-1.612502</v>
       </c>
       <c r="T26" t="n">
-        <v>0.321216</v>
+        <v>0.098769</v>
       </c>
       <c r="U26" t="n">
-        <v>2.870799</v>
+        <v>-0.740777</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612301</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.612502</v>
+        <v>3.992444</v>
       </c>
       <c r="X26" t="n">
-        <v>0.098769</v>
+        <v>-7.713954</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.740777</v>
+        <v>3.527423</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5401319999999999</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.992444</v>
+        <v>0.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>-7.713954</v>
+        <v>0.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.527423</v>
+        <v>-0.03</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3347,105 +2873,87 @@
         <v>0.049189</v>
       </c>
       <c r="D27" t="n">
-        <v>0.049189</v>
+        <v>0.23</v>
       </c>
       <c r="E27" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>106.13139</v>
       </c>
       <c r="H27" t="n">
-        <v>102.45222</v>
+        <v>4.9219</v>
       </c>
       <c r="I27" t="n">
-        <v>106.13139</v>
+        <v>4.9213</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9219</v>
+        <v>5559063</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9213</v>
+        <v>2172658</v>
       </c>
       <c r="L27" t="n">
-        <v>5559063</v>
+        <v>3.61</v>
       </c>
       <c r="M27" t="n">
-        <v>2172658</v>
+        <v>2.82</v>
       </c>
       <c r="N27" t="n">
-        <v>3386405</v>
+        <v>4.12</v>
       </c>
       <c r="O27" t="n">
-        <v>3.61</v>
+        <v>29.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.82</v>
+        <v>344177</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>0.622108</v>
       </c>
       <c r="R27" t="n">
-        <v>29.92</v>
+        <v>3.804703</v>
       </c>
       <c r="S27" t="n">
-        <v>344177</v>
+        <v>3.805185</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.370842</v>
+        <v>1.352666</v>
       </c>
       <c r="U27" t="n">
-        <v>0.622108</v>
+        <v>0.887701</v>
       </c>
       <c r="V27" t="n">
-        <v>3.804703</v>
+        <v>-0.376003</v>
       </c>
       <c r="W27" t="n">
-        <v>3.805185</v>
+        <v>4.608216</v>
       </c>
       <c r="X27" t="n">
-        <v>1.352666</v>
+        <v>-7.193509</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.887701</v>
+        <v>4.057054</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.653244</v>
+        <v>-0.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.376003</v>
+        <v>-0.001599</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.608216</v>
+        <v>-0.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.193509</v>
+        <v>0.09</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.057054</v>
+        <v>-0.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3460,105 +2968,87 @@
         <v>0.048422</v>
       </c>
       <c r="D28" t="n">
-        <v>0.048422</v>
+        <v>0.26</v>
       </c>
       <c r="E28" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="F28" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11</v>
+        <v>102.00419</v>
       </c>
       <c r="H28" t="n">
-        <v>102.57885</v>
+        <v>5.0076</v>
       </c>
       <c r="I28" t="n">
-        <v>102.00419</v>
+        <v>5.007</v>
       </c>
       <c r="J28" t="n">
-        <v>5.0076</v>
+        <v>5625945</v>
       </c>
       <c r="K28" t="n">
-        <v>5.007</v>
+        <v>2215175</v>
       </c>
       <c r="L28" t="n">
-        <v>5625945</v>
+        <v>3.54</v>
       </c>
       <c r="M28" t="n">
-        <v>2215175</v>
+        <v>2.82</v>
       </c>
       <c r="N28" t="n">
-        <v>3410769</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>3.54</v>
+        <v>29.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>340324</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>-3.888765</v>
       </c>
       <c r="R28" t="n">
-        <v>29.66</v>
+        <v>1.741198</v>
       </c>
       <c r="S28" t="n">
-        <v>340324</v>
+        <v>1.74141</v>
       </c>
       <c r="T28" t="n">
-        <v>0.123599</v>
+        <v>1.203116</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.888765</v>
+        <v>1.956912</v>
       </c>
       <c r="V28" t="n">
-        <v>1.741198</v>
+        <v>-1.119482</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74141</v>
+        <v>5.185235</v>
       </c>
       <c r="X28" t="n">
-        <v>1.203116</v>
+        <v>-5.956714</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.956912</v>
+        <v>4.505936</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.719465</v>
+        <v>-0.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>-1.119482</v>
+        <v>-0.000768</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.185235</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>-5.956714</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.505936</v>
+        <v>-0.12</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3573,105 +3063,87 @@
         <v>0.047279</v>
       </c>
       <c r="D29" t="n">
-        <v>0.047279</v>
+        <v>0.24</v>
       </c>
       <c r="E29" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.12</v>
+        <v>102.0744</v>
       </c>
       <c r="H29" t="n">
-        <v>102.87707</v>
+        <v>5.0575</v>
       </c>
       <c r="I29" t="n">
-        <v>102.0744</v>
+        <v>5.0569</v>
       </c>
       <c r="J29" t="n">
-        <v>5.0575</v>
+        <v>5653808</v>
       </c>
       <c r="K29" t="n">
-        <v>5.0569</v>
+        <v>2204808</v>
       </c>
       <c r="L29" t="n">
-        <v>5653808</v>
+        <v>3.56</v>
       </c>
       <c r="M29" t="n">
-        <v>2204808</v>
+        <v>2.92</v>
       </c>
       <c r="N29" t="n">
-        <v>3449000</v>
+        <v>3.97</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>29.24</v>
       </c>
       <c r="P29" t="n">
-        <v>2.92</v>
+        <v>340247</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.97</v>
+        <v>0.068831</v>
       </c>
       <c r="R29" t="n">
-        <v>29.24</v>
+        <v>0.996485</v>
       </c>
       <c r="S29" t="n">
-        <v>340247</v>
+        <v>0.996605</v>
       </c>
       <c r="T29" t="n">
-        <v>0.290723</v>
+        <v>0.495259</v>
       </c>
       <c r="U29" t="n">
-        <v>0.068831</v>
+        <v>-0.467999</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996485</v>
+        <v>-0.022625</v>
       </c>
       <c r="W29" t="n">
-        <v>0.996605</v>
+        <v>4.819246</v>
       </c>
       <c r="X29" t="n">
-        <v>0.495259</v>
+        <v>-4.560737</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.467999</v>
+        <v>4.141877</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.120891</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.022625</v>
+        <v>-0.001143</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.819246</v>
+        <v>0.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.560737</v>
+        <v>0.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.141877</v>
+        <v>-0.03</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3686,105 +3158,87 @@
         <v>0.045601</v>
       </c>
       <c r="D30" t="n">
-        <v>0.045601</v>
+        <v>0.28</v>
       </c>
       <c r="E30" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="F30" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1</v>
+        <v>101.86494</v>
       </c>
       <c r="H30" t="n">
-        <v>103.528</v>
+        <v>4.9355</v>
       </c>
       <c r="I30" t="n">
-        <v>101.86494</v>
+        <v>4.9349</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9355</v>
+        <v>5711103</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9349</v>
+        <v>2220766</v>
       </c>
       <c r="L30" t="n">
-        <v>5711103</v>
+        <v>3.53</v>
       </c>
       <c r="M30" t="n">
-        <v>2220766</v>
+        <v>2.99</v>
       </c>
       <c r="N30" t="n">
-        <v>3490337</v>
+        <v>3.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.53</v>
+        <v>29.01</v>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>348406</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.88</v>
+        <v>-0.205203</v>
       </c>
       <c r="R30" t="n">
-        <v>29.01</v>
+        <v>-2.412259</v>
       </c>
       <c r="S30" t="n">
-        <v>348406</v>
+        <v>-2.412545</v>
       </c>
       <c r="T30" t="n">
-        <v>0.632726</v>
+        <v>1.013388</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.205203</v>
+        <v>0.723782</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412259</v>
+        <v>2.397964</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.412545</v>
+        <v>4.683537</v>
       </c>
       <c r="X30" t="n">
-        <v>1.013388</v>
+        <v>-3.457004</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.723782</v>
+        <v>3.851383</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.198521</v>
+        <v>-0.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.397964</v>
+        <v>-0.001678</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.683537</v>
+        <v>-0.03</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.457004</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.851383</v>
+        <v>-0.09</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3799,105 +3253,87 @@
         <v>0.044537</v>
       </c>
       <c r="D31" t="n">
-        <v>0.044537</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="F31" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.55</v>
+        <v>101.74606</v>
       </c>
       <c r="H31" t="n">
-        <v>104.8991</v>
+        <v>4.8413</v>
       </c>
       <c r="I31" t="n">
-        <v>101.74606</v>
+        <v>4.8407</v>
       </c>
       <c r="J31" t="n">
-        <v>4.8413</v>
+        <v>5805157</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8407</v>
+        <v>2283485</v>
       </c>
       <c r="L31" t="n">
-        <v>5805157</v>
+        <v>3.29</v>
       </c>
       <c r="M31" t="n">
-        <v>2283485</v>
+        <v>2.59</v>
       </c>
       <c r="N31" t="n">
-        <v>3521672</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3.29</v>
+        <v>28.14</v>
       </c>
       <c r="P31" t="n">
-        <v>2.59</v>
+        <v>355034</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>-0.116704</v>
       </c>
       <c r="R31" t="n">
-        <v>28.14</v>
+        <v>-1.908621</v>
       </c>
       <c r="S31" t="n">
-        <v>355034</v>
+        <v>-1.908853</v>
       </c>
       <c r="T31" t="n">
-        <v>1.324376</v>
+        <v>1.646862</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.116704</v>
+        <v>2.824206</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908621</v>
+        <v>1.902378</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.908853</v>
+        <v>4.621114</v>
       </c>
       <c r="X31" t="n">
-        <v>1.646862</v>
+        <v>-3.178284</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.824206</v>
+        <v>3.706988</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.897764</v>
+        <v>-0.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.902378</v>
+        <v>-0.001064</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.621114</v>
+        <v>-0.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.178284</v>
+        <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.706988</v>
+        <v>-0.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3912,105 +3348,87 @@
         <v>0.043739</v>
       </c>
       <c r="D32" t="n">
-        <v>0.043739</v>
+        <v>0.42</v>
       </c>
       <c r="E32" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="G32" t="n">
-        <v>0.57</v>
+        <v>98.01879</v>
       </c>
       <c r="H32" t="n">
-        <v>104.53245</v>
+        <v>4.9535</v>
       </c>
       <c r="I32" t="n">
-        <v>98.01879</v>
+        <v>4.9529</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9535</v>
+        <v>5794707</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9529</v>
+        <v>2234362</v>
       </c>
       <c r="L32" t="n">
-        <v>5794707</v>
+        <v>3.38</v>
       </c>
       <c r="M32" t="n">
-        <v>2234362</v>
+        <v>2.77</v>
       </c>
       <c r="N32" t="n">
-        <v>3560345</v>
+        <v>3.76</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>355066</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>-3.663306</v>
       </c>
       <c r="R32" t="n">
-        <v>28</v>
+        <v>2.317559</v>
       </c>
       <c r="S32" t="n">
-        <v>355066</v>
+        <v>2.317847</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.349526</v>
+        <v>-0.180012</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.663306</v>
+        <v>-2.151229</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317559</v>
+        <v>0.009013</v>
       </c>
       <c r="W32" t="n">
-        <v>2.317847</v>
+        <v>4.506637</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.180012</v>
+        <v>-3.31355</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.151229</v>
+        <v>3.820543</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.098143</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009013</v>
+        <v>-0.000798</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.506637</v>
+        <v>0.09</v>
       </c>
       <c r="AC32" t="n">
-        <v>-3.31355</v>
+        <v>0.18</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.820543</v>
+        <v>0.01</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -4025,105 +3443,87 @@
         <v>0.041957</v>
       </c>
       <c r="D33" t="n">
-        <v>0.041957</v>
+        <v>0.83</v>
       </c>
       <c r="E33" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>102.37988</v>
       </c>
       <c r="H33" t="n">
-        <v>104.75961</v>
+        <v>4.9833</v>
       </c>
       <c r="I33" t="n">
-        <v>102.37988</v>
+        <v>4.9827</v>
       </c>
       <c r="J33" t="n">
-        <v>4.9833</v>
+        <v>5815954</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9827</v>
+        <v>2235302</v>
       </c>
       <c r="L33" t="n">
-        <v>5815954</v>
+        <v>3.38</v>
       </c>
       <c r="M33" t="n">
-        <v>2235302</v>
+        <v>2.76</v>
       </c>
       <c r="N33" t="n">
-        <v>3580652</v>
+        <v>3.76</v>
       </c>
       <c r="O33" t="n">
-        <v>3.38</v>
+        <v>27.85</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>352705</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.76</v>
+        <v>4.449239</v>
       </c>
       <c r="R33" t="n">
-        <v>27.85</v>
+        <v>0.601595</v>
       </c>
       <c r="S33" t="n">
-        <v>352705</v>
+        <v>0.601668</v>
       </c>
       <c r="T33" t="n">
-        <v>0.217311</v>
+        <v>0.366662</v>
       </c>
       <c r="U33" t="n">
-        <v>4.449239</v>
+        <v>0.04207</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601595</v>
+        <v>-0.664947</v>
       </c>
       <c r="W33" t="n">
-        <v>0.601668</v>
+        <v>4.496274</v>
       </c>
       <c r="X33" t="n">
-        <v>0.366662</v>
+        <v>-3.758575</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.04207</v>
+        <v>3.861754</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.570366</v>
+        <v>-0.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.664947</v>
+        <v>-0.001782</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.496274</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>-3.758575</v>
+        <v>-0.01</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.861754</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4138,105 +3538,87 @@
         <v>0.04142</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04142</v>
+        <v>0.16</v>
       </c>
       <c r="E34" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="G34" t="n">
-        <v>0.19</v>
+        <v>109.58504</v>
       </c>
       <c r="H34" t="n">
-        <v>104.7097</v>
+        <v>4.9962</v>
       </c>
       <c r="I34" t="n">
-        <v>109.58504</v>
+        <v>4.9956</v>
       </c>
       <c r="J34" t="n">
-        <v>4.9962</v>
+        <v>5899742</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9956</v>
+        <v>2285775</v>
       </c>
       <c r="L34" t="n">
-        <v>5899742</v>
+        <v>3.33</v>
       </c>
       <c r="M34" t="n">
-        <v>2285775</v>
+        <v>2.71</v>
       </c>
       <c r="N34" t="n">
-        <v>3613967</v>
+        <v>3.71</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>28.14</v>
       </c>
       <c r="P34" t="n">
-        <v>2.71</v>
+        <v>355008</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.71</v>
+        <v>7.037672</v>
       </c>
       <c r="R34" t="n">
-        <v>28.14</v>
+        <v>0.258865</v>
       </c>
       <c r="S34" t="n">
-        <v>355008</v>
+        <v>0.258896</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.047642</v>
+        <v>1.440658</v>
       </c>
       <c r="U34" t="n">
-        <v>7.037672</v>
+        <v>2.257995</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258865</v>
+        <v>0.652954</v>
       </c>
       <c r="W34" t="n">
-        <v>0.258896</v>
+        <v>3.925596</v>
       </c>
       <c r="X34" t="n">
-        <v>1.440658</v>
+        <v>-4.25878</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.257995</v>
+        <v>3.397348</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.930417</v>
+        <v>-0.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.652954</v>
+        <v>-0.000537</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.925596</v>
+        <v>-0.05</v>
       </c>
       <c r="AC34" t="n">
-        <v>-4.25878</v>
+        <v>-0.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.397348</v>
+        <v>-0.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4251,105 +3633,87 @@
         <v>0.040168</v>
       </c>
       <c r="D35" t="n">
-        <v>0.040168</v>
+        <v>0.38</v>
       </c>
       <c r="E35" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="F35" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="G35" t="n">
-        <v>0.37</v>
+        <v>109.36335</v>
       </c>
       <c r="H35" t="n">
-        <v>104.75682</v>
+        <v>5.1718</v>
       </c>
       <c r="I35" t="n">
-        <v>109.36335</v>
+        <v>5.1712</v>
       </c>
       <c r="J35" t="n">
-        <v>5.1718</v>
+        <v>5915538</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1712</v>
+        <v>2268879</v>
       </c>
       <c r="L35" t="n">
-        <v>5915538</v>
+        <v>3.37</v>
       </c>
       <c r="M35" t="n">
-        <v>2268879</v>
+        <v>2.76</v>
       </c>
       <c r="N35" t="n">
-        <v>3646659</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
-        <v>3.37</v>
+        <v>27.86</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>351599</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>-0.2023</v>
       </c>
       <c r="R35" t="n">
-        <v>27.86</v>
+        <v>3.514671</v>
       </c>
       <c r="S35" t="n">
-        <v>351599</v>
+        <v>3.515093</v>
       </c>
       <c r="T35" t="n">
-        <v>0.045001</v>
+        <v>0.267741</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.2023</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="V35" t="n">
-        <v>3.514671</v>
+        <v>-0.96026</v>
       </c>
       <c r="W35" t="n">
-        <v>3.515093</v>
+        <v>3.688016</v>
       </c>
       <c r="X35" t="n">
-        <v>0.267741</v>
+        <v>-3.040871</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>3.232784</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.904602</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.96026</v>
+        <v>-0.001252</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.688016</v>
+        <v>0.04</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.040871</v>
+        <v>0.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.232784</v>
+        <v>0.04</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4364,105 +3728,87 @@
         <v>0.039484</v>
       </c>
       <c r="D36" t="n">
-        <v>0.039484</v>
+        <v>0.46</v>
       </c>
       <c r="E36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.46</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.89</v>
-      </c>
       <c r="G36" t="n">
-        <v>0.46</v>
+        <v>104.84682</v>
       </c>
       <c r="H36" t="n">
-        <v>105.70704</v>
+        <v>5.2416</v>
       </c>
       <c r="I36" t="n">
-        <v>104.84682</v>
+        <v>5.241</v>
       </c>
       <c r="J36" t="n">
-        <v>5.2416</v>
+        <v>5953960</v>
       </c>
       <c r="K36" t="n">
-        <v>5.241</v>
+        <v>2278309</v>
       </c>
       <c r="L36" t="n">
-        <v>5953960</v>
+        <v>3.43</v>
       </c>
       <c r="M36" t="n">
-        <v>2278309</v>
+        <v>2.8</v>
       </c>
       <c r="N36" t="n">
-        <v>3675652</v>
+        <v>3.82</v>
       </c>
       <c r="O36" t="n">
-        <v>3.43</v>
+        <v>27.75</v>
       </c>
       <c r="P36" t="n">
-        <v>2.8</v>
+        <v>355560</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.82</v>
+        <v>-4.129839</v>
       </c>
       <c r="R36" t="n">
-        <v>27.75</v>
+        <v>1.349627</v>
       </c>
       <c r="S36" t="n">
-        <v>355560</v>
+        <v>1.349783</v>
       </c>
       <c r="T36" t="n">
-        <v>0.907072</v>
+        <v>0.64951</v>
       </c>
       <c r="U36" t="n">
-        <v>-4.129839</v>
+        <v>0.415624</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349627</v>
+        <v>1.126567</v>
       </c>
       <c r="W36" t="n">
-        <v>1.349783</v>
+        <v>3.925952</v>
       </c>
       <c r="X36" t="n">
-        <v>0.64951</v>
+        <v>-0.344269</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.415624</v>
+        <v>3.335647</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.795057</v>
+        <v>-0.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.126567</v>
+        <v>-0.000684</v>
       </c>
       <c r="AB36" t="n">
-        <v>3.925952</v>
+        <v>0.06</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.344269</v>
+        <v>0.04</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.335647</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4477,105 +3823,87 @@
         <v>0.03927</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03927</v>
+        <v>0.21</v>
       </c>
       <c r="E37" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="G37" t="n">
-        <v>0.25</v>
+        <v>106.03093</v>
       </c>
       <c r="H37" t="n">
-        <v>106.57623</v>
+        <v>5.5589</v>
       </c>
       <c r="I37" t="n">
-        <v>106.03093</v>
+        <v>5.5583</v>
       </c>
       <c r="J37" t="n">
-        <v>5.5589</v>
+        <v>6041898</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5583</v>
+        <v>2336858</v>
       </c>
       <c r="L37" t="n">
-        <v>6041898</v>
+        <v>3.29</v>
       </c>
       <c r="M37" t="n">
-        <v>2336858</v>
+        <v>2.64</v>
       </c>
       <c r="N37" t="n">
-        <v>3705041</v>
+        <v>3.71</v>
       </c>
       <c r="O37" t="n">
-        <v>3.29</v>
+        <v>27.81</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>357827</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.71</v>
+        <v>1.129371</v>
       </c>
       <c r="R37" t="n">
-        <v>27.81</v>
+        <v>6.053495</v>
       </c>
       <c r="S37" t="n">
-        <v>357827</v>
+        <v>6.054188</v>
       </c>
       <c r="T37" t="n">
-        <v>0.822263</v>
+        <v>1.476967</v>
       </c>
       <c r="U37" t="n">
-        <v>1.129371</v>
+        <v>2.569845</v>
       </c>
       <c r="V37" t="n">
-        <v>6.053495</v>
+        <v>0.637586</v>
       </c>
       <c r="W37" t="n">
-        <v>6.054188</v>
+        <v>4.227578</v>
       </c>
       <c r="X37" t="n">
-        <v>1.476967</v>
+        <v>2.440035</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.569845</v>
+        <v>3.697684</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.799559</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.637586</v>
+        <v>-0.000214</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.227578</v>
+        <v>-0.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.440035</v>
+        <v>-0.16</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.697684</v>
+        <v>-0.11</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4590,105 +3918,87 @@
         <v>0.03927</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03927</v>
+        <v>0.38</v>
       </c>
       <c r="E38" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="F38" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="G38" t="n">
-        <v>0.26</v>
+        <v>111.55002</v>
       </c>
       <c r="H38" t="n">
-        <v>106.88756</v>
+        <v>5.6621</v>
       </c>
       <c r="I38" t="n">
-        <v>111.55002</v>
+        <v>5.6615</v>
       </c>
       <c r="J38" t="n">
-        <v>5.6621</v>
+        <v>6069205</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6615</v>
+        <v>2323362</v>
       </c>
       <c r="L38" t="n">
-        <v>6069205</v>
+        <v>3.3</v>
       </c>
       <c r="M38" t="n">
-        <v>2323362</v>
+        <v>2.52</v>
       </c>
       <c r="N38" t="n">
-        <v>3745844</v>
+        <v>3.78</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>27.74</v>
       </c>
       <c r="P38" t="n">
-        <v>2.52</v>
+        <v>363282</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.78</v>
+        <v>5.20517</v>
       </c>
       <c r="R38" t="n">
-        <v>27.74</v>
+        <v>1.856482</v>
       </c>
       <c r="S38" t="n">
-        <v>363282</v>
+        <v>1.856683</v>
       </c>
       <c r="T38" t="n">
-        <v>0.29212</v>
+        <v>0.451961</v>
       </c>
       <c r="U38" t="n">
-        <v>5.20517</v>
+        <v>-0.577528</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856482</v>
+        <v>1.52448</v>
       </c>
       <c r="W38" t="n">
-        <v>1.856683</v>
+        <v>4.498245</v>
       </c>
       <c r="X38" t="n">
-        <v>0.451961</v>
+        <v>3.812368</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.577528</v>
+        <v>4.060953</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.101283</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.52448</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.498245</v>
+        <v>0.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.812368</v>
+        <v>-0.12</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.060953</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4703,105 +4013,87 @@
         <v>0.03927</v>
       </c>
       <c r="D39" t="n">
-        <v>0.03927</v>
+        <v>-0.02</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="F39" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.14</v>
+        <v>110.19363</v>
       </c>
       <c r="H39" t="n">
-        <v>107.14396</v>
+        <v>5.6562</v>
       </c>
       <c r="I39" t="n">
-        <v>110.19363</v>
+        <v>5.6556</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6562</v>
+        <v>6135298</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6556</v>
+        <v>2344397</v>
       </c>
       <c r="L39" t="n">
-        <v>6135298</v>
+        <v>3.33</v>
       </c>
       <c r="M39" t="n">
-        <v>2344397</v>
+        <v>2.55</v>
       </c>
       <c r="N39" t="n">
-        <v>3790900</v>
+        <v>3.82</v>
       </c>
       <c r="O39" t="n">
-        <v>3.33</v>
+        <v>27.59</v>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>369214</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.82</v>
+        <v>-1.215948</v>
       </c>
       <c r="R39" t="n">
-        <v>27.59</v>
+        <v>-0.104202</v>
       </c>
       <c r="S39" t="n">
-        <v>369214</v>
+        <v>-0.104213</v>
       </c>
       <c r="T39" t="n">
-        <v>0.239878</v>
+        <v>1.088989</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.215948</v>
+        <v>0.905369</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104202</v>
+        <v>1.632891</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.104213</v>
+        <v>4.237599</v>
       </c>
       <c r="X39" t="n">
-        <v>1.088989</v>
+        <v>4.259387</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.905369</v>
+        <v>3.707852</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.202826</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.632891</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.237599</v>
+        <v>0.03</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.259387</v>
+        <v>0.03</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.707852</v>
+        <v>0.04</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4816,105 +4108,87 @@
         <v>0.039612</v>
       </c>
       <c r="D40" t="n">
-        <v>0.039612</v>
+        <v>0.44</v>
       </c>
       <c r="E40" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="F40" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="G40" t="n">
-        <v>0.48</v>
+        <v>107.28836</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99916</v>
+        <v>5.4481</v>
       </c>
       <c r="I40" t="n">
-        <v>107.28836</v>
+        <v>5.4475</v>
       </c>
       <c r="J40" t="n">
-        <v>5.4481</v>
+        <v>6216528</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4475</v>
+        <v>2384828</v>
       </c>
       <c r="L40" t="n">
-        <v>6216528</v>
+        <v>3.34</v>
       </c>
       <c r="M40" t="n">
-        <v>2384828</v>
+        <v>2.56</v>
       </c>
       <c r="N40" t="n">
-        <v>3831700</v>
+        <v>3.83</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>27.49</v>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>372016</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.83</v>
+        <v>-2.636514</v>
       </c>
       <c r="R40" t="n">
-        <v>27.49</v>
+        <v>-3.679149</v>
       </c>
       <c r="S40" t="n">
-        <v>372016</v>
+        <v>-3.679539</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7981780000000001</v>
+        <v>1.323978</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.636514</v>
+        <v>1.72458</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679149</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.679539</v>
+        <v>4.42474</v>
       </c>
       <c r="X40" t="n">
-        <v>1.323978</v>
+        <v>4.519075</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.72458</v>
+        <v>4.091149</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.076262</v>
+        <v>0.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7589089999999999</v>
+        <v>0.000342</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.42474</v>
+        <v>0.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.519075</v>
+        <v>0.01</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.091149</v>
+        <v>0.01</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4929,105 +4203,87 @@
         <v>0.040168</v>
       </c>
       <c r="D41" t="n">
-        <v>0.040168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="F41" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="G41" t="n">
-        <v>0.61</v>
+        <v>109.21678</v>
       </c>
       <c r="H41" t="n">
-        <v>108.15356</v>
+        <v>5.7779</v>
       </c>
       <c r="I41" t="n">
-        <v>109.21678</v>
+        <v>5.7773</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7779</v>
+        <v>6275117</v>
       </c>
       <c r="K41" t="n">
-        <v>5.7773</v>
+        <v>2397533</v>
       </c>
       <c r="L41" t="n">
-        <v>6275117</v>
+        <v>3.3</v>
       </c>
       <c r="M41" t="n">
-        <v>2397533</v>
+        <v>2.52</v>
       </c>
       <c r="N41" t="n">
-        <v>3877584</v>
+        <v>3.79</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>27.94</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>366096</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.79</v>
+        <v>1.797418</v>
       </c>
       <c r="R41" t="n">
-        <v>27.94</v>
+        <v>6.053487</v>
       </c>
       <c r="S41" t="n">
-        <v>366096</v>
+        <v>6.054153</v>
       </c>
       <c r="T41" t="n">
-        <v>0.142964</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="U41" t="n">
-        <v>1.797418</v>
+        <v>0.532743</v>
       </c>
       <c r="V41" t="n">
-        <v>6.053487</v>
+        <v>-1.591329</v>
       </c>
       <c r="W41" t="n">
-        <v>6.054153</v>
+        <v>4.758099</v>
       </c>
       <c r="X41" t="n">
-        <v>0.9424709999999999</v>
+        <v>5.579866</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.532743</v>
+        <v>4.600584</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.197484</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>-1.591329</v>
+        <v>0.000556</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.758099</v>
+        <v>-0.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.579866</v>
+        <v>-0.04</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.600584</v>
+        <v>-0.04</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -5042,105 +4298,87 @@
         <v>0.04158</v>
       </c>
       <c r="D42" t="n">
-        <v>0.04158</v>
+        <v>0.39</v>
       </c>
       <c r="E42" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="G42" t="n">
-        <v>0.33</v>
+        <v>105.74688</v>
       </c>
       <c r="H42" t="n">
-        <v>107.98489</v>
+        <v>6.0535</v>
       </c>
       <c r="I42" t="n">
-        <v>105.74688</v>
+        <v>6.0529</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0535</v>
+        <v>6365690</v>
       </c>
       <c r="K42" t="n">
-        <v>6.0529</v>
+        <v>2436022</v>
       </c>
       <c r="L42" t="n">
-        <v>6365690</v>
+        <v>3.27</v>
       </c>
       <c r="M42" t="n">
-        <v>2436022</v>
+        <v>2.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3929668</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
-        <v>3.27</v>
+        <v>28.45</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>363003</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>-3.177076</v>
       </c>
       <c r="R42" t="n">
-        <v>28.45</v>
+        <v>4.769899</v>
       </c>
       <c r="S42" t="n">
-        <v>363003</v>
+        <v>4.770394</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.155954</v>
+        <v>1.443368</v>
       </c>
       <c r="U42" t="n">
-        <v>-3.177076</v>
+        <v>1.605359</v>
       </c>
       <c r="V42" t="n">
-        <v>4.769899</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="W42" t="n">
-        <v>4.770394</v>
+        <v>4.873011</v>
       </c>
       <c r="X42" t="n">
-        <v>1.443368</v>
+        <v>6.325086</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.605359</v>
+        <v>4.840925</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.343208</v>
+        <v>0.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>0.001412</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.873011</v>
+        <v>-0.03</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.325086</v>
+        <v>-0.02</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.840925</v>
+        <v>-0.04</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -5155,105 +4393,87 @@
         <v>0.044158</v>
       </c>
       <c r="D43" t="n">
-        <v>0.044158</v>
+        <v>0.52</v>
       </c>
       <c r="E43" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G43" t="n">
-        <v>0.48</v>
+        <v>104.2734</v>
       </c>
       <c r="H43" t="n">
-        <v>107.44467</v>
+        <v>6.1923</v>
       </c>
       <c r="I43" t="n">
-        <v>104.2734</v>
+        <v>6.1917</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1923</v>
+        <v>6464602</v>
       </c>
       <c r="K43" t="n">
-        <v>6.1917</v>
+        <v>2499177</v>
       </c>
       <c r="L43" t="n">
-        <v>6464602</v>
+        <v>3.08</v>
       </c>
       <c r="M43" t="n">
-        <v>2499177</v>
+        <v>2.21</v>
       </c>
       <c r="N43" t="n">
-        <v>3965425</v>
+        <v>3.63</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>28.5</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>329730</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.63</v>
+        <v>-1.393403</v>
       </c>
       <c r="R43" t="n">
-        <v>28.5</v>
+        <v>2.292888</v>
       </c>
       <c r="S43" t="n">
-        <v>329730</v>
+        <v>2.293116</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.500274</v>
+        <v>1.55383</v>
       </c>
       <c r="U43" t="n">
-        <v>-1.393403</v>
+        <v>2.592546</v>
       </c>
       <c r="V43" t="n">
-        <v>2.292888</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="W43" t="n">
-        <v>2.293116</v>
+        <v>4.831296</v>
       </c>
       <c r="X43" t="n">
-        <v>1.55383</v>
+        <v>6.536174</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.592546</v>
+        <v>4.767938</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.909924</v>
+        <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>-9.166040000000001</v>
+        <v>0.002578</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.831296</v>
+        <v>-0.19</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.536174</v>
+        <v>-0.29</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.767938</v>
+        <v>-0.12</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -5268,105 +4488,87 @@
         <v>0.045833</v>
       </c>
       <c r="D44" t="n">
-        <v>0.045833</v>
+        <v>0.16</v>
       </c>
       <c r="E44" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="F44" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>101.23438</v>
       </c>
       <c r="H44" t="n">
-        <v>108.06979</v>
+        <v>5.8301</v>
       </c>
       <c r="I44" t="n">
-        <v>101.23438</v>
+        <v>5.8295</v>
       </c>
       <c r="J44" t="n">
-        <v>5.8301</v>
+        <v>6465016</v>
       </c>
       <c r="K44" t="n">
-        <v>5.8295</v>
+        <v>2451957</v>
       </c>
       <c r="L44" t="n">
-        <v>6465016</v>
+        <v>3.34</v>
       </c>
       <c r="M44" t="n">
-        <v>2451957</v>
+        <v>2.43</v>
       </c>
       <c r="N44" t="n">
-        <v>4013059</v>
+        <v>3.89</v>
       </c>
       <c r="O44" t="n">
-        <v>3.34</v>
+        <v>29.88</v>
       </c>
       <c r="P44" t="n">
-        <v>2.43</v>
+        <v>328303</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>-2.914473</v>
       </c>
       <c r="R44" t="n">
-        <v>29.88</v>
+        <v>-5.8492</v>
       </c>
       <c r="S44" t="n">
-        <v>328303</v>
+        <v>-5.849767</v>
       </c>
       <c r="T44" t="n">
-        <v>0.581806</v>
+        <v>0.006404</v>
       </c>
       <c r="U44" t="n">
-        <v>-2.914473</v>
+        <v>-1.889422</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.8492</v>
+        <v>-0.432778</v>
       </c>
       <c r="W44" t="n">
-        <v>-5.849767</v>
+        <v>4.559874</v>
       </c>
       <c r="X44" t="n">
-        <v>0.006404</v>
+        <v>6.749097</v>
       </c>
       <c r="Y44" t="n">
-        <v>-1.889422</v>
+        <v>4.174145</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.201233</v>
+        <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.432778</v>
+        <v>0.001675</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.559874</v>
+        <v>0.26</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.749097</v>
+        <v>0.22</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.174145</v>
+        <v>0.26</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -5381,105 +4583,87 @@
         <v>0.049037</v>
       </c>
       <c r="D45" t="n">
-        <v>0.049037</v>
+        <v>1.31</v>
       </c>
       <c r="E45" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="F45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="G45" t="n">
-        <v>1.48</v>
+        <v>107.07838</v>
       </c>
       <c r="H45" t="n">
-        <v>108.77346</v>
+        <v>5.8488</v>
       </c>
       <c r="I45" t="n">
-        <v>107.07838</v>
+        <v>5.8482</v>
       </c>
       <c r="J45" t="n">
-        <v>5.8488</v>
+        <v>6511444</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8482</v>
+        <v>2477151</v>
       </c>
       <c r="L45" t="n">
-        <v>6511444</v>
+        <v>3.41</v>
       </c>
       <c r="M45" t="n">
-        <v>2477151</v>
+        <v>2.52</v>
       </c>
       <c r="N45" t="n">
-        <v>4034293</v>
+        <v>3.96</v>
       </c>
       <c r="O45" t="n">
-        <v>3.41</v>
+        <v>30.53</v>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>332508</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>5.772742</v>
       </c>
       <c r="R45" t="n">
-        <v>30.53</v>
+        <v>0.320749</v>
       </c>
       <c r="S45" t="n">
-        <v>332508</v>
+        <v>0.320782</v>
       </c>
       <c r="T45" t="n">
-        <v>0.651126</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="U45" t="n">
-        <v>5.772742</v>
+        <v>1.027506</v>
       </c>
       <c r="V45" t="n">
-        <v>0.320749</v>
+        <v>1.280829</v>
       </c>
       <c r="W45" t="n">
-        <v>0.320782</v>
+        <v>5.05763</v>
       </c>
       <c r="X45" t="n">
-        <v>0.7181419999999999</v>
+        <v>8.444549</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.027506</v>
+        <v>4.866504</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.529123</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.280829</v>
+        <v>0.003204</v>
       </c>
       <c r="AB45" t="n">
-        <v>5.05763</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.444549</v>
+        <v>0.09</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.866504</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -5494,105 +4678,87 @@
         <v>0.050508</v>
       </c>
       <c r="D46" t="n">
-        <v>0.050508</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="G46" t="n">
-        <v>0.51</v>
+        <v>114.05013</v>
       </c>
       <c r="H46" t="n">
-        <v>110.09056</v>
+        <v>5.7422</v>
       </c>
       <c r="I46" t="n">
-        <v>114.05013</v>
+        <v>5.7416</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7422</v>
+        <v>6576464</v>
       </c>
       <c r="K46" t="n">
-        <v>5.7416</v>
+        <v>2498262</v>
       </c>
       <c r="L46" t="n">
-        <v>6576464</v>
+        <v>3.44</v>
       </c>
       <c r="M46" t="n">
-        <v>2498262</v>
+        <v>2.49</v>
       </c>
       <c r="N46" t="n">
-        <v>4078202</v>
+        <v>4.03</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>31.34</v>
       </c>
       <c r="P46" t="n">
-        <v>2.49</v>
+        <v>336157</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.03</v>
+        <v>6.510885</v>
       </c>
       <c r="R46" t="n">
-        <v>31.34</v>
+        <v>-1.822596</v>
       </c>
       <c r="S46" t="n">
-        <v>336157</v>
+        <v>-1.822783</v>
       </c>
       <c r="T46" t="n">
-        <v>1.210865</v>
+        <v>0.99855</v>
       </c>
       <c r="U46" t="n">
-        <v>6.510885</v>
+        <v>0.852229</v>
       </c>
       <c r="V46" t="n">
-        <v>-1.822596</v>
+        <v>1.097417</v>
       </c>
       <c r="W46" t="n">
-        <v>-1.822783</v>
+        <v>5.47719</v>
       </c>
       <c r="X46" t="n">
-        <v>0.99855</v>
+        <v>8.586193</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.852229</v>
+        <v>5.201441</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.088394</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.097417</v>
+        <v>0.001471</v>
       </c>
       <c r="AB46" t="n">
-        <v>5.47719</v>
+        <v>0.03</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.586193</v>
+        <v>-0.03</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.201441</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -5607,105 +4773,87 @@
         <v>0.052531</v>
       </c>
       <c r="D47" t="n">
-        <v>0.052531</v>
+        <v>0.43</v>
       </c>
       <c r="E47" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="F47" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="G47" t="n">
-        <v>0.48</v>
+        <v>112.73813</v>
       </c>
       <c r="H47" t="n">
-        <v>109.72323</v>
+        <v>5.6608</v>
       </c>
       <c r="I47" t="n">
-        <v>112.73813</v>
+        <v>5.6602</v>
       </c>
       <c r="J47" t="n">
-        <v>5.6608</v>
+        <v>6623948</v>
       </c>
       <c r="K47" t="n">
-        <v>5.6602</v>
+        <v>2512426</v>
       </c>
       <c r="L47" t="n">
-        <v>6623948</v>
+        <v>3.67</v>
       </c>
       <c r="M47" t="n">
-        <v>2512426</v>
+        <v>2.72</v>
       </c>
       <c r="N47" t="n">
-        <v>4111522</v>
+        <v>4.25</v>
       </c>
       <c r="O47" t="n">
-        <v>3.67</v>
+        <v>31.63</v>
       </c>
       <c r="P47" t="n">
-        <v>2.72</v>
+        <v>340789</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>-1.150371</v>
       </c>
       <c r="R47" t="n">
-        <v>31.63</v>
+        <v>-1.417575</v>
       </c>
       <c r="S47" t="n">
-        <v>340789</v>
+        <v>-1.417723</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.333662</v>
+        <v>0.722029</v>
       </c>
       <c r="U47" t="n">
-        <v>-1.150371</v>
+        <v>0.566954</v>
       </c>
       <c r="V47" t="n">
-        <v>-1.417575</v>
+        <v>1.377928</v>
       </c>
       <c r="W47" t="n">
-        <v>-1.417723</v>
+        <v>5.529729</v>
       </c>
       <c r="X47" t="n">
-        <v>0.722029</v>
+        <v>8.510418</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.566954</v>
+        <v>5.316736</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8170269999999999</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.377928</v>
+        <v>0.002023</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.529729</v>
+        <v>0.23</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.510418</v>
+        <v>0.23</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.316736</v>
+        <v>0.22</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -5720,105 +4868,87 @@
         <v>0.053936</v>
       </c>
       <c r="D48" t="n">
-        <v>0.053936</v>
+        <v>0.26</v>
       </c>
       <c r="E48" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="G48" t="n">
-        <v>0.35</v>
+        <v>108.66481</v>
       </c>
       <c r="H48" t="n">
-        <v>109.00057</v>
+        <v>5.7087</v>
       </c>
       <c r="I48" t="n">
-        <v>108.66481</v>
+        <v>5.7081</v>
       </c>
       <c r="J48" t="n">
-        <v>5.7087</v>
+        <v>6666287</v>
       </c>
       <c r="K48" t="n">
-        <v>5.7081</v>
+        <v>2532708</v>
       </c>
       <c r="L48" t="n">
-        <v>6666287</v>
+        <v>3.72</v>
       </c>
       <c r="M48" t="n">
-        <v>2532708</v>
+        <v>2.67</v>
       </c>
       <c r="N48" t="n">
-        <v>4133579</v>
+        <v>4.36</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>31.7</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>341459</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.36</v>
+        <v>-3.613081</v>
       </c>
       <c r="R48" t="n">
-        <v>31.7</v>
+        <v>0.84617</v>
       </c>
       <c r="S48" t="n">
-        <v>341459</v>
+        <v>0.84626</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.658621</v>
+        <v>0.639181</v>
       </c>
       <c r="U48" t="n">
-        <v>-3.613081</v>
+        <v>0.807268</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84617</v>
+        <v>0.196603</v>
       </c>
       <c r="W48" t="n">
-        <v>0.84626</v>
+        <v>5.319636</v>
       </c>
       <c r="X48" t="n">
-        <v>0.639181</v>
+        <v>7.026183</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.807268</v>
+        <v>5.201418</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.196603</v>
+        <v>0.001405</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.319636</v>
+        <v>0.05</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.026183</v>
+        <v>-0.05</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.201418</v>
+        <v>0.11</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5833,105 +4963,87 @@
         <v>0.054569</v>
       </c>
       <c r="D49" t="n">
-        <v>0.054569</v>
+        <v>0.24</v>
       </c>
       <c r="E49" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="G49" t="n">
-        <v>0.23</v>
+        <v>107.55639</v>
       </c>
       <c r="H49" t="n">
-        <v>108.76683</v>
+        <v>5.4571</v>
       </c>
       <c r="I49" t="n">
-        <v>107.55639</v>
+        <v>5.4565</v>
       </c>
       <c r="J49" t="n">
-        <v>5.4571</v>
+        <v>6703663</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4565</v>
+        <v>2547693</v>
       </c>
       <c r="L49" t="n">
-        <v>6703663</v>
+        <v>3.75</v>
       </c>
       <c r="M49" t="n">
-        <v>2547693</v>
+        <v>2.67</v>
       </c>
       <c r="N49" t="n">
-        <v>4155970</v>
+        <v>4.41</v>
       </c>
       <c r="O49" t="n">
-        <v>3.75</v>
+        <v>31.85</v>
       </c>
       <c r="P49" t="n">
-        <v>2.67</v>
+        <v>344440</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.41</v>
+        <v>-1.020036</v>
       </c>
       <c r="R49" t="n">
-        <v>31.85</v>
+        <v>-4.407308</v>
       </c>
       <c r="S49" t="n">
-        <v>344440</v>
+        <v>-4.407771</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.214439</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.020036</v>
+        <v>0.591659</v>
       </c>
       <c r="V49" t="n">
-        <v>-4.407308</v>
+        <v>0.873018</v>
       </c>
       <c r="W49" t="n">
-        <v>-4.407771</v>
+        <v>5.351165</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5606719999999999</v>
+        <v>4.393261</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.591659</v>
+        <v>5.18043</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.541686</v>
+        <v>0.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.873018</v>
+        <v>0.000633</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.351165</v>
+        <v>0.03</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.393261</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.18043</v>
+        <v>0.05</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5946,105 +5058,87 @@
         <v>0.055131</v>
       </c>
       <c r="D50" t="n">
-        <v>0.055131</v>
+        <v>0.26</v>
       </c>
       <c r="E50" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="G50" t="n">
+        <v>113.14433</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="J50" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="O50" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="P50" t="n">
+        <v>345111</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5.195358</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="U50" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="W50" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AB50" t="n">
         <v>0.21</v>
       </c>
-      <c r="H50" t="n">
-        <v>108.27053</v>
-      </c>
-      <c r="I50" t="n">
-        <v>113.14433</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="L50" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="O50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R50" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="S50" t="n">
-        <v>345111</v>
-      </c>
-      <c r="T50" t="n">
-        <v>-0.456297</v>
-      </c>
-      <c r="U50" t="n">
-        <v>5.195358</v>
-      </c>
-      <c r="V50" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>5.225222</v>
-      </c>
       <c r="AC50" t="n">
-        <v>2.961368</v>
+        <v>0.12</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.127976</v>
+        <v>0.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -6059,105 +5153,87 @@
         <v>0.055131</v>
       </c>
       <c r="D51" t="n">
-        <v>0.055131</v>
+        <v>-0.11</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="F51" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.21</v>
+        <v>110.57963</v>
       </c>
       <c r="H51" t="n">
-        <v>108.80021</v>
+        <v>5.4264</v>
       </c>
       <c r="I51" t="n">
-        <v>110.57963</v>
+        <v>5.4258</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4264</v>
+        <v>6774436</v>
       </c>
       <c r="K51" t="n">
-        <v>5.4258</v>
+        <v>2546265</v>
       </c>
       <c r="L51" t="n">
-        <v>6774436</v>
+        <v>4.14</v>
       </c>
       <c r="M51" t="n">
-        <v>2546265</v>
+        <v>2.85</v>
       </c>
       <c r="N51" t="n">
-        <v>4228171</v>
+        <v>4.92</v>
       </c>
       <c r="O51" t="n">
-        <v>4.14</v>
+        <v>31.87</v>
       </c>
       <c r="P51" t="n">
-        <v>2.85</v>
+        <v>350767</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.92</v>
+        <v>-2.266751</v>
       </c>
       <c r="R51" t="n">
-        <v>31.87</v>
+        <v>-3.136324</v>
       </c>
       <c r="S51" t="n">
-        <v>350767</v>
+        <v>-3.13666</v>
       </c>
       <c r="T51" t="n">
-        <v>0.489219</v>
+        <v>0.612293</v>
       </c>
       <c r="U51" t="n">
-        <v>-2.266751</v>
+        <v>0.073298</v>
       </c>
       <c r="V51" t="n">
-        <v>-3.136324</v>
+        <v>1.638893</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.13666</v>
+        <v>5.130501</v>
       </c>
       <c r="X51" t="n">
-        <v>0.612293</v>
+        <v>3.033233</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.073298</v>
+        <v>5.054283</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.9397180000000001</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.638893</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.130501</v>
+        <v>0.18</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.033233</v>
+        <v>0.06</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.054283</v>
+        <v>0.26</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -6172,105 +5248,87 @@
         <v>0.055131</v>
       </c>
       <c r="D52" t="n">
-        <v>0.055131</v>
+        <v>0.48</v>
       </c>
       <c r="E52" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="F52" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="G52" t="n">
-        <v>0.52</v>
+        <v>109.59513</v>
       </c>
       <c r="H52" t="n">
-        <v>108.63642</v>
+        <v>5.3186</v>
       </c>
       <c r="I52" t="n">
-        <v>109.59513</v>
+        <v>5.318</v>
       </c>
       <c r="J52" t="n">
-        <v>5.3186</v>
+        <v>6852705</v>
       </c>
       <c r="K52" t="n">
-        <v>5.318</v>
+        <v>2589817</v>
       </c>
       <c r="L52" t="n">
-        <v>6852705</v>
+        <v>4.09</v>
       </c>
       <c r="M52" t="n">
-        <v>2589817</v>
+        <v>2.77</v>
       </c>
       <c r="N52" t="n">
-        <v>4262888</v>
+        <v>4.89</v>
       </c>
       <c r="O52" t="n">
-        <v>4.09</v>
+        <v>31.47</v>
       </c>
       <c r="P52" t="n">
-        <v>2.77</v>
+        <v>356582</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.89</v>
+        <v>-0.890309</v>
       </c>
       <c r="R52" t="n">
-        <v>31.47</v>
+        <v>-1.986584</v>
       </c>
       <c r="S52" t="n">
-        <v>356582</v>
+        <v>-1.986804</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.150542</v>
+        <v>1.155358</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.890309</v>
+        <v>1.710427</v>
       </c>
       <c r="V52" t="n">
-        <v>-1.986584</v>
+        <v>1.657796</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.986804</v>
+        <v>5.172369</v>
       </c>
       <c r="X52" t="n">
-        <v>1.155358</v>
+        <v>2.828436</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.710427</v>
+        <v>5.096104</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.821088</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.657796</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>5.172369</v>
+        <v>-0.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.828436</v>
+        <v>-0.08</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.096104</v>
+        <v>-0.03</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -6285,105 +5343,87 @@
         <v>0.055131</v>
       </c>
       <c r="D53" t="n">
-        <v>0.055131</v>
+        <v>0.09</v>
       </c>
       <c r="E53" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G53" t="n">
+        <v>110.16346</v>
+      </c>
+      <c r="H53" t="n">
+        <v>5.3843</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5.3837</v>
+      </c>
+      <c r="J53" t="n">
+        <v>6923886</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2597630</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="O53" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="P53" t="n">
+        <v>357103</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.518572</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.235287</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.235427</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.038729</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.301682</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.146109</v>
+      </c>
+      <c r="W53" t="n">
+        <v>4.680811</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.924206</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>4.490243</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
         <v>0.09</v>
       </c>
-      <c r="F53" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H53" t="n">
-        <v>108.7159</v>
-      </c>
-      <c r="I53" t="n">
-        <v>110.16346</v>
-      </c>
-      <c r="J53" t="n">
-        <v>5.3843</v>
-      </c>
-      <c r="K53" t="n">
-        <v>5.3837</v>
-      </c>
-      <c r="L53" t="n">
-        <v>6923886</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2597630</v>
-      </c>
-      <c r="N53" t="n">
-        <v>4326256</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="R53" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="S53" t="n">
-        <v>357103</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0.073161</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0.518572</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.235287</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.235427</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.038729</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0.301682</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.486504</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.146109</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>4.680811</v>
-      </c>
       <c r="AC53" t="n">
-        <v>0.924206</v>
+        <v>0.05</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.490243</v>
+        <v>0.1</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -6398,105 +5438,87 @@
         <v>0.055131</v>
       </c>
       <c r="D54" t="n">
-        <v>0.055131</v>
+        <v>0.18</v>
       </c>
       <c r="E54" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="F54" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="G54" t="n">
-        <v>0.03</v>
+        <v>106.90236</v>
       </c>
       <c r="H54" t="n">
-        <v>109.27405</v>
+        <v>5.3338</v>
       </c>
       <c r="I54" t="n">
-        <v>106.90236</v>
+        <v>5.3332</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3338</v>
+        <v>7003273</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3332</v>
+        <v>2616213</v>
       </c>
       <c r="L54" t="n">
-        <v>7003273</v>
+        <v>4.23</v>
       </c>
       <c r="M54" t="n">
-        <v>2616213</v>
+        <v>2.74</v>
       </c>
       <c r="N54" t="n">
-        <v>4387061</v>
+        <v>5.12</v>
       </c>
       <c r="O54" t="n">
-        <v>4.23</v>
+        <v>32.32</v>
       </c>
       <c r="P54" t="n">
-        <v>2.74</v>
+        <v>360578</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.12</v>
+        <v>-2.960237</v>
       </c>
       <c r="R54" t="n">
-        <v>32.32</v>
+        <v>-0.937912</v>
       </c>
       <c r="S54" t="n">
-        <v>360578</v>
+        <v>-0.938017</v>
       </c>
       <c r="T54" t="n">
-        <v>0.513402</v>
+        <v>1.146567</v>
       </c>
       <c r="U54" t="n">
-        <v>-2.960237</v>
+        <v>0.715383</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.937912</v>
+        <v>0.973109</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.938017</v>
+        <v>4.461836</v>
       </c>
       <c r="X54" t="n">
-        <v>1.146567</v>
+        <v>-0.101973</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.715383</v>
+        <v>4.177803</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.405488</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.973109</v>
+        <v>-0</v>
       </c>
       <c r="AB54" t="n">
-        <v>4.461836</v>
+        <v>0.05</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.101973</v>
+        <v>-0.08</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.177803</v>
+        <v>0.13</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -6511,105 +5533,87 @@
         <v>0.055131</v>
       </c>
       <c r="D55" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="E55" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="G55" t="n">
-        <v>0.21</v>
+        <v>107.17649</v>
       </c>
       <c r="H55" t="n">
-        <v>109.41762</v>
+        <v>5.5024</v>
       </c>
       <c r="I55" t="n">
-        <v>107.17649</v>
+        <v>5.5018</v>
       </c>
       <c r="J55" t="n">
-        <v>5.5024</v>
+        <v>7136436</v>
       </c>
       <c r="K55" t="n">
-        <v>5.5018</v>
+        <v>2701146</v>
       </c>
       <c r="L55" t="n">
-        <v>7136436</v>
+        <v>4.2</v>
       </c>
       <c r="M55" t="n">
-        <v>2701146</v>
+        <v>2.68</v>
       </c>
       <c r="N55" t="n">
-        <v>4435290</v>
+        <v>5.12</v>
       </c>
       <c r="O55" t="n">
-        <v>4.2</v>
+        <v>31.99</v>
       </c>
       <c r="P55" t="n">
-        <v>2.68</v>
+        <v>358234</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.12</v>
+        <v>0.25643</v>
       </c>
       <c r="R55" t="n">
-        <v>31.99</v>
+        <v>3.160973</v>
       </c>
       <c r="S55" t="n">
-        <v>358234</v>
+        <v>3.161329</v>
       </c>
       <c r="T55" t="n">
-        <v>0.131385</v>
+        <v>1.90144</v>
       </c>
       <c r="U55" t="n">
-        <v>0.25643</v>
+        <v>3.24641</v>
       </c>
       <c r="V55" t="n">
-        <v>3.160973</v>
+        <v>-0.650067</v>
       </c>
       <c r="W55" t="n">
-        <v>3.161329</v>
+        <v>4.264385</v>
       </c>
       <c r="X55" t="n">
-        <v>1.90144</v>
+        <v>-1.042167</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.24641</v>
+        <v>3.897866</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.099346</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.650067</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.264385</v>
+        <v>-0.03</v>
       </c>
       <c r="AC55" t="n">
-        <v>-1.042167</v>
+        <v>-0.06</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -6624,105 +5628,87 @@
         <v>0.055131</v>
       </c>
       <c r="D56" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="E56" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="F56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G56" t="n">
-        <v>0.39</v>
+        <v>102.36456</v>
       </c>
       <c r="H56" t="n">
-        <v>110.05486</v>
+        <v>5.2301</v>
       </c>
       <c r="I56" t="n">
-        <v>102.36456</v>
+        <v>5.2295</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2301</v>
+        <v>7130500</v>
       </c>
       <c r="K56" t="n">
-        <v>5.2295</v>
+        <v>2654052</v>
       </c>
       <c r="L56" t="n">
-        <v>7130500</v>
+        <v>4.45</v>
       </c>
       <c r="M56" t="n">
-        <v>2654052</v>
+        <v>2.87</v>
       </c>
       <c r="N56" t="n">
-        <v>4476448</v>
+        <v>5.38</v>
       </c>
       <c r="O56" t="n">
-        <v>4.45</v>
+        <v>32.6</v>
       </c>
       <c r="P56" t="n">
-        <v>2.87</v>
+        <v>364367</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.38</v>
+        <v>-4.489725</v>
       </c>
       <c r="R56" t="n">
-        <v>32.6</v>
+        <v>-4.94875</v>
       </c>
       <c r="S56" t="n">
-        <v>364367</v>
+        <v>-4.949289</v>
       </c>
       <c r="T56" t="n">
-        <v>0.582392</v>
+        <v>-0.083179</v>
       </c>
       <c r="U56" t="n">
-        <v>-4.489725</v>
+        <v>-1.743482</v>
       </c>
       <c r="V56" t="n">
-        <v>-4.94875</v>
+        <v>1.712009</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.949289</v>
+        <v>4.441351</v>
       </c>
       <c r="X56" t="n">
-        <v>-0.083179</v>
+        <v>-0.903999</v>
       </c>
       <c r="Y56" t="n">
-        <v>-1.743482</v>
+        <v>4.303068</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.927966</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.712009</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>4.441351</v>
+        <v>0.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.903999</v>
+        <v>0.19</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.303068</v>
+        <v>0.26</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -6737,105 +5723,87 @@
         <v>0.055131</v>
       </c>
       <c r="D57" t="n">
-        <v>0.055131</v>
+        <v>0.7</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5600000000000001</v>
+        <v>106.82125</v>
       </c>
       <c r="H57" t="n">
-        <v>110.65892</v>
+        <v>5.1495</v>
       </c>
       <c r="I57" t="n">
-        <v>106.82125</v>
+        <v>5.1489</v>
       </c>
       <c r="J57" t="n">
-        <v>5.1495</v>
+        <v>7156987</v>
       </c>
       <c r="K57" t="n">
-        <v>5.1489</v>
+        <v>2655931</v>
       </c>
       <c r="L57" t="n">
-        <v>7156987</v>
+        <v>4.64</v>
       </c>
       <c r="M57" t="n">
-        <v>2655931</v>
+        <v>3.07</v>
       </c>
       <c r="N57" t="n">
-        <v>4501056</v>
+        <v>5.56</v>
       </c>
       <c r="O57" t="n">
-        <v>4.64</v>
+        <v>32.78</v>
       </c>
       <c r="P57" t="n">
-        <v>3.07</v>
+        <v>371074</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.56</v>
+        <v>4.353743</v>
       </c>
       <c r="R57" t="n">
-        <v>32.78</v>
+        <v>-1.54108</v>
       </c>
       <c r="S57" t="n">
-        <v>371074</v>
+        <v>-1.541256</v>
       </c>
       <c r="T57" t="n">
-        <v>0.548872</v>
+        <v>0.371461</v>
       </c>
       <c r="U57" t="n">
-        <v>4.353743</v>
+        <v>0.070797</v>
       </c>
       <c r="V57" t="n">
-        <v>-1.54108</v>
+        <v>1.840727</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.541256</v>
+        <v>3.812497</v>
       </c>
       <c r="X57" t="n">
-        <v>0.371461</v>
+        <v>-2.659212</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.070797</v>
+        <v>3.357475</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.549722</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.840727</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>3.812497</v>
+        <v>0.19</v>
       </c>
       <c r="AC57" t="n">
-        <v>-2.659212</v>
+        <v>0.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.357475</v>
+        <v>0.18</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -6850,105 +5818,87 @@
         <v>0.054777</v>
       </c>
       <c r="D58" t="n">
-        <v>0.054777</v>
+        <v>0.88</v>
       </c>
       <c r="E58" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="F58" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="G58" t="n">
-        <v>0.91</v>
+        <v>117.8089</v>
       </c>
       <c r="H58" t="n">
-        <v>110.51078</v>
+        <v>5.2194</v>
       </c>
       <c r="I58" t="n">
-        <v>117.8089</v>
+        <v>5.2188</v>
       </c>
       <c r="J58" t="n">
-        <v>5.2194</v>
+        <v>7237735</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2188</v>
+        <v>2686046</v>
       </c>
       <c r="L58" t="n">
-        <v>7237735</v>
+        <v>4.52</v>
       </c>
       <c r="M58" t="n">
-        <v>2686046</v>
+        <v>3.04</v>
       </c>
       <c r="N58" t="n">
-        <v>4551689</v>
+        <v>5.4</v>
       </c>
       <c r="O58" t="n">
-        <v>4.52</v>
+        <v>32.99</v>
       </c>
       <c r="P58" t="n">
-        <v>3.04</v>
+        <v>362002</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.4</v>
+        <v>10.286015</v>
       </c>
       <c r="R58" t="n">
-        <v>32.99</v>
+        <v>1.357413</v>
       </c>
       <c r="S58" t="n">
-        <v>362002</v>
+        <v>1.357572</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.133871</v>
+        <v>1.12824</v>
       </c>
       <c r="U58" t="n">
-        <v>10.286015</v>
+        <v>1.133877</v>
       </c>
       <c r="V58" t="n">
-        <v>1.357413</v>
+        <v>-2.444795</v>
       </c>
       <c r="W58" t="n">
-        <v>1.357572</v>
+        <v>4.142847</v>
       </c>
       <c r="X58" t="n">
-        <v>1.12824</v>
+        <v>-1.819225</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.133877</v>
+        <v>3.768807</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.124914</v>
+        <v>-0.25</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.444795</v>
+        <v>-0.000354</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.142847</v>
+        <v>-0.12</v>
       </c>
       <c r="AC58" t="n">
-        <v>-1.819225</v>
+        <v>-0.03</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.768807</v>
+        <v>-0.16</v>
       </c>
       <c r="AE58" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -6963,105 +5913,87 @@
         <v>0.054223</v>
       </c>
       <c r="D59" t="n">
-        <v>0.054223</v>
+        <v>0.67</v>
       </c>
       <c r="E59" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="F59" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8100000000000001</v>
+        <v>113.99365</v>
       </c>
       <c r="H59" t="n">
-        <v>110.95732</v>
+        <v>4.9886</v>
       </c>
       <c r="I59" t="n">
-        <v>113.99365</v>
+        <v>4.988</v>
       </c>
       <c r="J59" t="n">
-        <v>4.9886</v>
+        <v>7258599</v>
       </c>
       <c r="K59" t="n">
-        <v>4.988</v>
+        <v>2684623</v>
       </c>
       <c r="L59" t="n">
-        <v>7258599</v>
+        <v>4.63</v>
       </c>
       <c r="M59" t="n">
-        <v>2684623</v>
+        <v>3.15</v>
       </c>
       <c r="N59" t="n">
-        <v>4573976</v>
+        <v>5.51</v>
       </c>
       <c r="O59" t="n">
-        <v>4.63</v>
+        <v>33.51</v>
       </c>
       <c r="P59" t="n">
-        <v>3.15</v>
+        <v>366913</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.51</v>
+        <v>-3.238507</v>
       </c>
       <c r="R59" t="n">
-        <v>33.51</v>
+        <v>-4.421964</v>
       </c>
       <c r="S59" t="n">
-        <v>366913</v>
+        <v>-4.422473</v>
       </c>
       <c r="T59" t="n">
-        <v>0.404069</v>
+        <v>0.288267</v>
       </c>
       <c r="U59" t="n">
-        <v>-3.238507</v>
+        <v>-0.052977</v>
       </c>
       <c r="V59" t="n">
-        <v>-4.421964</v>
+        <v>1.356622</v>
       </c>
       <c r="W59" t="n">
-        <v>-4.422473</v>
+        <v>4.39172</v>
       </c>
       <c r="X59" t="n">
-        <v>0.288267</v>
+        <v>0.619623</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.052977</v>
+        <v>4.109608</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.489642</v>
+        <v>-0.25</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.356622</v>
+        <v>-0.000554</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.39172</v>
+        <v>0.11</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.619623</v>
+        <v>0.11</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.109608</v>
+        <v>0.11</v>
       </c>
       <c r="AE59" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -7076,105 +6008,87 @@
         <v>0.0534</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0534</v>
+        <v>0.58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="F60" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="G60" t="n">
-        <v>0.65</v>
+        <v>109.52993</v>
       </c>
       <c r="H60" t="n">
-        <v>111.03587</v>
+        <v>5.0569</v>
       </c>
       <c r="I60" t="n">
-        <v>109.52993</v>
+        <v>5.0563</v>
       </c>
       <c r="J60" t="n">
-        <v>5.0569</v>
+        <v>7299615</v>
       </c>
       <c r="K60" t="n">
-        <v>5.0563</v>
+        <v>2704550</v>
       </c>
       <c r="L60" t="n">
-        <v>7299615</v>
+        <v>4.74</v>
       </c>
       <c r="M60" t="n">
-        <v>2704550</v>
+        <v>3.24</v>
       </c>
       <c r="N60" t="n">
-        <v>4595065</v>
+        <v>5.62</v>
       </c>
       <c r="O60" t="n">
-        <v>4.74</v>
+        <v>33.42</v>
       </c>
       <c r="P60" t="n">
-        <v>3.24</v>
+        <v>371137</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.62</v>
+        <v>-3.915762</v>
       </c>
       <c r="R60" t="n">
-        <v>33.42</v>
+        <v>1.369122</v>
       </c>
       <c r="S60" t="n">
-        <v>371137</v>
+        <v>1.369286</v>
       </c>
       <c r="T60" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.565068</v>
       </c>
       <c r="U60" t="n">
-        <v>-3.915762</v>
+        <v>0.742264</v>
       </c>
       <c r="V60" t="n">
-        <v>1.369122</v>
+        <v>1.151227</v>
       </c>
       <c r="W60" t="n">
-        <v>1.369286</v>
+        <v>4.724907</v>
       </c>
       <c r="X60" t="n">
-        <v>0.565068</v>
+        <v>1.964454</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.742264</v>
+        <v>4.420848</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.461065</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.151227</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.724907</v>
+        <v>0.11</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.964454</v>
+        <v>0.09</v>
       </c>
       <c r="AD60" t="n">
-        <v>4.420848</v>
+        <v>0.11</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -7189,71 +6103,61 @@
         <v>0.053028</v>
       </c>
       <c r="D61" t="n">
-        <v>0.053028</v>
+        <v>0.16</v>
       </c>
       <c r="E61" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="G61" t="n">
         <v>0.14</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="K61" t="n">
+      <c r="I61" t="n">
         <v>5.176</v>
       </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>367558</v>
+      </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="S61" t="n">
-        <v>367558</v>
+        <v>2.367344</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="n">
-        <v>2.367063</v>
+        <v>-0.964334</v>
       </c>
       <c r="W61" t="n">
-        <v>2.367344</v>
-      </c>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+        <v>4.641328</v>
+      </c>
+      <c r="X61" t="n">
+        <v>3.177699</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>4.327084</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="AA61" t="n">
-        <v>-0.964334</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>4.641328</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>3.177699</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>4.327084</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AG61" t="n">
-        <v>-0.000372</v>
-      </c>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -7265,56 +6169,46 @@
       <c r="C62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="D62" t="n">
-        <v>0.052531</v>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>5.1005</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.0998</v>
-      </c>
+      <c r="H62" t="n">
+        <v>5.1177</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.1171</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>-1.137812</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-1.137944</v>
+      </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
-        <v>-1.470077</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-1.472179</v>
-      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE62"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,140 +438,160 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cdi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>ipca</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>igp_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inpc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>ibc_br</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>saldo_credito_pf</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>var_pct_ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>var_pct_saldo_credito_pf</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>dif_cdi</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -588,46 +608,50 @@
         <v>0.016137</v>
       </c>
       <c r="D2" t="n">
+        <v>0.016137</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.96</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.78</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1.02</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>96.31464</v>
+      </c>
+      <c r="I2" t="n">
         <v>99.83978</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>5.121</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>4271865</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1833179</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
+        <v>2438686</v>
+      </c>
+      <c r="O2" t="n">
         <v>2.36</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>2.94</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>20.26</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>355671</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -641,6 +665,10 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -653,81 +681,93 @@
         <v>0.019413</v>
       </c>
       <c r="D3" t="n">
+        <v>0.019413</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.87</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.66</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.88</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>97.07568000000001</v>
+      </c>
+      <c r="I3" t="n">
         <v>99.32829</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>4346060</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1851006</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
+        <v>2495054</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.37</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>2.96</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>20.92</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>370395</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="T3" t="n">
         <v>-0.512311</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
+        <v>2.311409</v>
+      </c>
+      <c r="Z3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
         <v>0.02</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -742,81 +782,93 @@
         <v>0.021003</v>
       </c>
       <c r="D4" t="n">
+        <v>0.021003</v>
+      </c>
+      <c r="E4" t="n">
         <v>1.16</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.2</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>96.95968999999999</v>
+      </c>
+      <c r="I4" t="n">
         <v>97.24746</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>4441056</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1894119</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
+        <v>2546936</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.34</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>3.01</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>21.42</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>368886</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v>-0.119484</v>
+      </c>
+      <c r="T4" t="n">
         <v>-2.094902</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
+        <v>2.079394</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
         <v>1</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="AG4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AC4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AH4" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AI4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -831,81 +883,93 @@
         <v>0.024244</v>
       </c>
       <c r="D5" t="n">
+        <v>0.024244</v>
+      </c>
+      <c r="E5" t="n">
         <v>1.25</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.64</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1.16</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>97.48142</v>
+      </c>
+      <c r="I5" t="n">
         <v>96.62081999999999</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>5.643</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>4511956</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1910940</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
+        <v>2601017</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.33</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>2.99</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>22.89</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>367927</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v>0.53809</v>
+      </c>
+      <c r="T5" t="n">
         <v>-0.644377</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="U5" t="n">
+      <c r="X5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
+        <v>2.123375</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AE5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AF5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="AG5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AH5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AI5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -920,81 +984,93 @@
         <v>0.029256</v>
       </c>
       <c r="D6" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.95</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.02</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.84</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>98.97262000000001</v>
+      </c>
+      <c r="I6" t="n">
         <v>98.05768</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>4597507</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1933111</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>2664395</v>
+      </c>
+      <c r="O6" t="n">
         <v>2.36</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>3.01</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>23.91</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>367772</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>1.529727</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.487112</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
+        <v>2.436662</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AG6" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AH6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AI6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1009,81 +1085,93 @@
         <v>0.033316</v>
       </c>
       <c r="D7" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.73</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.87</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.73</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>99.35339</v>
+      </c>
+      <c r="I7" t="n">
         <v>99.33126</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>4682852</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1974391</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
+        <v>2708461</v>
+      </c>
+      <c r="O7" t="n">
         <v>2.35</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>3.05</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>24.21</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>362204</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v>0.384723</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.298807</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
+        <v>1.653884</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="n">
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AF7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="AG7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AC7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="n">
         <v>0.04</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AI7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1098,81 +1186,93 @@
         <v>0.034749</v>
       </c>
       <c r="D8" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.82</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.67</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>97.34401</v>
+      </c>
+      <c r="I8" t="n">
         <v>90.45032</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>4682131</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1947035</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
+        <v>2735096</v>
+      </c>
+      <c r="O8" t="n">
         <v>2.51</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>3.26</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>25.23</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>358398</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v>-2.022457</v>
+      </c>
+      <c r="T8" t="n">
         <v>-8.94073</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AF8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="AG8" t="n">
         <v>0.16</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AH8" t="n">
         <v>0.21</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AI8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1187,81 +1287,93 @@
         <v>0.039598</v>
       </c>
       <c r="D9" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="E9" t="n">
         <v>1.01</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1.83</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>98.43725000000001</v>
+      </c>
+      <c r="I9" t="n">
         <v>95.72214</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>4727818</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>1971524</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
+        <v>2756295</v>
+      </c>
+      <c r="O9" t="n">
         <v>2.57</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>3.38</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>25.63</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>357740</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>1.123069</v>
+      </c>
+      <c r="T9" t="n">
         <v>5.828415</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
+        <v>0.775073</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="n">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AF9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="AG9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AH9" t="n">
         <v>0.12</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1276,81 +1388,93 @@
         <v>0.041954</v>
       </c>
       <c r="D10" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="E10" t="n">
         <v>1.62</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1.74</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1.71</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>99.55981</v>
+      </c>
+      <c r="I10" t="n">
         <v>104.61484</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>4794583</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>1994119</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
+        <v>2800464</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.66</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>3.45</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>26.54</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>353169</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>1.140381</v>
+      </c>
+      <c r="T10" t="n">
         <v>9.290118</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
+        <v>1.602477</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="n">
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AE10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="AG10" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AH10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1365,81 +1489,93 @@
         <v>0.043739</v>
       </c>
       <c r="D11" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.06</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1.41</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1.04</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
+        <v>99.51646</v>
+      </c>
+      <c r="I11" t="n">
         <v>100.42352</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>4833732</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>2003312</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
+        <v>2830420</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.72</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>3.54</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>27.46</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>345097</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
+        <v>-0.043542</v>
+      </c>
+      <c r="T11" t="n">
         <v>-4.00643</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
+        <v>1.06968</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AF11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="AG11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AH11" t="n">
         <v>0.09</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AI11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1454,81 +1590,93 @@
         <v>0.046796</v>
       </c>
       <c r="D12" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.47</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.52</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.45</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
+        <v>99.67415</v>
+      </c>
+      <c r="I12" t="n">
         <v>99.79777</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>4889397</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>2013726</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
+        <v>2875671</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.79</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>3.65</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>27.42</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>346415</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
+        <v>0.158456</v>
+      </c>
+      <c r="T12" t="n">
         <v>-0.623111</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
+        <v>1.598738</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="n">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AE12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AF12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="AG12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AH12" t="n">
         <v>0.11</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AI12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1543,87 +1691,99 @@
         <v>0.048116</v>
       </c>
       <c r="D13" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.67</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.59</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.62</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
+        <v>99.6343</v>
+      </c>
+      <c r="I13" t="n">
         <v>99.53784</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>5.238</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>4965603</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>2052569</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
+        <v>2913035</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.73</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>3.57</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>27.88</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>341958</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
+        <v>-0.03998</v>
+      </c>
+      <c r="T13" t="n">
         <v>-0.260457</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
+        <v>1.299314</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AA13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AB13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AC13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AD13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AE13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AF13" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="AG13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AC13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AH13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AI13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1638,87 +1798,99 @@
         <v>0.049037</v>
       </c>
       <c r="D14" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="E14" t="n">
         <v>-0.68</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0.21</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
+        <v>101.27684</v>
+      </c>
+      <c r="I14" t="n">
         <v>103.95861</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>4999244</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>2047038</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
+        <v>2952207</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.84</v>
       </c>
-      <c r="M14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>3.71</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>29.24</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>346403</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
+        <v>1.648569</v>
+      </c>
+      <c r="T14" t="n">
         <v>4.441296</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
+        <v>1.344714</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AA14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AB14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AC14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AF14" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="AG14" t="n">
         <v>0.11</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AH14" t="n">
         <v>0.14</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AI14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1733,87 +1905,99 @@
         <v>0.05056</v>
       </c>
       <c r="D15" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="E15" t="n">
         <v>-0.36</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-0.31</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
+        <v>101.07328</v>
+      </c>
+      <c r="I15" t="n">
         <v>104.56278</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>5.179</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>5072711</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>2064183</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
+        <v>3008528</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.9</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>3.78</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>28.6</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>339664</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
+        <v>-0.200994</v>
+      </c>
+      <c r="T15" t="n">
         <v>0.581164</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
+        <v>1.907759</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AA15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AB15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AC15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AD15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AE15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AF15" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="AG15" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AH15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AI15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -1828,87 +2012,99 @@
         <v>0.050788</v>
       </c>
       <c r="D16" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E16" t="n">
         <v>-0.29</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
+        <v>101.17973</v>
+      </c>
+      <c r="I16" t="n">
         <v>101.38087</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>5.406</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>5164775</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>2109806</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
+        <v>3054969</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.92</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>3.8</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>28.57</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>327580</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="T16" t="n">
         <v>-3.043062</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
+        <v>1.543645</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AA16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AB16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AC16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AF16" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AG16" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AH16" t="n">
         <v>0.02</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AI16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -1923,87 +2119,99 @@
         <v>0.050788</v>
       </c>
       <c r="D17" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.59</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-0.97</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.47</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
+        <v>101.46342</v>
+      </c>
+      <c r="I17" t="n">
         <v>100.20398</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>5.257</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>5215990</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>2105856</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
+        <v>3110134</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.04</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>3.89</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>29.68</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>325546</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
+        <v>0.280382</v>
+      </c>
+      <c r="T17" t="n">
         <v>-1.16086</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
+        <v>1.805747</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AA17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AB17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AC17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AH17" t="n">
         <v>0.09</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AI17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2018,87 +2226,99 @@
         <v>0.050788</v>
       </c>
       <c r="D18" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.41</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>0.38</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
+        <v>100.66227</v>
+      </c>
+      <c r="I18" t="n">
         <v>99.36927</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>5285657</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>2130312</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
+        <v>3155345</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.07</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>3.92</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>30.52</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>331505</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
+        <v>-0.789595</v>
+      </c>
+      <c r="T18" t="n">
         <v>-0.8330109999999999</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
+        <v>1.453667</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AC18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AH18" t="n">
         <v>0.03</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AI18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2113,87 +2333,99 @@
         <v>0.050788</v>
       </c>
       <c r="D19" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.62</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.45</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
+        <v>100.58196</v>
+      </c>
+      <c r="I19" t="n">
         <v>99.97806</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>5366069</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>2178236</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
+        <v>3187833</v>
+      </c>
+      <c r="O19" t="n">
         <v>3.07</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>3.94</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>29.64</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>324703</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
+        <v>-0.07978200000000001</v>
+      </c>
+      <c r="T19" t="n">
         <v>0.612654</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
+        <v>1.029618</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AA19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AB19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AC19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
         <v>-0</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.02</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AI19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2208,87 +2440,99 @@
         <v>0.050788</v>
       </c>
       <c r="D20" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.53</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.21</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.46</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
+        <v>100.05178</v>
+      </c>
+      <c r="I20" t="n">
         <v>93.79237000000001</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>5373231</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>2151399</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
+        <v>3221831</v>
+      </c>
+      <c r="O20" t="n">
         <v>3.24</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>4.11</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>30.54</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>331122</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
+        <v>-0.527112</v>
+      </c>
+      <c r="T20" t="n">
         <v>-6.187047</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
+        <v>1.066493</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AA20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AB20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AC20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
         <v>0.17</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
         <v>0.17</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AI20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2303,87 +2547,99 @@
         <v>0.050788</v>
       </c>
       <c r="D21" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.84</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.77</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
+        <v>103.00964</v>
+      </c>
+      <c r="I21" t="n">
         <v>98.75064999999999</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>5370950</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>2136105</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
+        <v>3234845</v>
+      </c>
+      <c r="O21" t="n">
         <v>3.36</v>
       </c>
-      <c r="M21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>4.16</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>30.48</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>328098</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
+        <v>2.956329</v>
+      </c>
+      <c r="T21" t="n">
         <v>5.286443</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
+        <v>0.403932</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AA21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AB21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AC21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AH21" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AI21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2398,87 +2654,99 @@
         <v>0.050788</v>
       </c>
       <c r="D22" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.71</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.05</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.64</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
+        <v>103.09341</v>
+      </c>
+      <c r="I22" t="n">
         <v>110.62354</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>5424811</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>2154900</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
+        <v>3269910</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.35</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>4.11</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>30.99</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>341158</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
+        <v>0.08132200000000001</v>
+      </c>
+      <c r="T22" t="n">
         <v>12.023101</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
+        <v>1.083978</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AA22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AB22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AC22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AI22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2493,87 +2761,99 @@
         <v>0.050788</v>
       </c>
       <c r="D23" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.61</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-0.95</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>0.53</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
+        <v>104.1626</v>
+      </c>
+      <c r="I23" t="n">
         <v>104.34152</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>5426307</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>2145000</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
+        <v>3281308</v>
+      </c>
+      <c r="O23" t="n">
         <v>3.54</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>4.26</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>31.62</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>345725</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
+        <v>1.037108</v>
+      </c>
+      <c r="T23" t="n">
         <v>-5.678737</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
+        <v>0.348572</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AA23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AB23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AC23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
         <v>0.19</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AH23" t="n">
         <v>0.15</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AI23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2588,87 +2868,99 @@
         <v>0.050788</v>
       </c>
       <c r="D24" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.23</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-1.84</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0.36</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
+        <v>102.3642</v>
+      </c>
+      <c r="I24" t="n">
         <v>102.66392</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>5453708</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>2145530</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
+        <v>3308178</v>
+      </c>
+      <c r="O24" t="n">
         <v>3.65</v>
       </c>
-      <c r="M24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>4.35</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>31.63</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>343489</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
+        <v>-1.726531</v>
+      </c>
+      <c r="T24" t="n">
         <v>-1.607797</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
+        <v>0.818881</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AA24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AB24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AC24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
         <v>-0</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AF24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.11</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AH24" t="n">
         <v>0.09</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AI24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2683,87 +2975,99 @@
         <v>0.050788</v>
       </c>
       <c r="D25" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E25" t="n">
         <v>-0.08</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-1.93</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
+        <v>102.50431</v>
+      </c>
+      <c r="I25" t="n">
         <v>102.53174</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>5479459</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>2169613</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
+        <v>3309846</v>
+      </c>
+      <c r="O25" t="n">
         <v>3.61</v>
       </c>
-      <c r="M25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>4.25</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>30.85</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>343620</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
+        <v>0.136874</v>
+      </c>
+      <c r="T25" t="n">
         <v>-0.12875</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
+        <v>0.050421</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AA25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AB25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AC25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="AH25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AI25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -2778,87 +3082,99 @@
         <v>0.050788</v>
       </c>
       <c r="D26" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.12</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-0.72</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>102.83357</v>
+      </c>
+      <c r="I26" t="n">
         <v>105.47522</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>5484871</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>2153541</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
+        <v>3331330</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.63</v>
       </c>
-      <c r="M26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>4.22</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>30.43</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>345476</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
+        <v>0.321216</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.870799</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
+        <v>0.6490939999999999</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AA26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AB26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AC26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AH26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AI26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -2873,87 +3189,99 @@
         <v>0.049189</v>
       </c>
       <c r="D27" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.23</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.2</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>102.45222</v>
+      </c>
+      <c r="I27" t="n">
         <v>106.13139</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>5559063</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>2172658</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
+        <v>3386405</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.61</v>
       </c>
-      <c r="M27" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>4.12</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>29.92</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>344177</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
+        <v>-0.370842</v>
+      </c>
+      <c r="T27" t="n">
         <v>0.622108</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
+        <v>1.653244</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="W27" t="n">
+      <c r="AA27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AB27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AC27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AD27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AE27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AF27" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="AG27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AH27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AI27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -2968,87 +3296,99 @@
         <v>0.048422</v>
       </c>
       <c r="D28" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.26</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.37</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>0.11</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>102.57885</v>
+      </c>
+      <c r="I28" t="n">
         <v>102.00419</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>5.007</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>5625945</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>2215175</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
+        <v>3410769</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.54</v>
       </c>
-      <c r="M28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>4</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>29.66</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>340324</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
+        <v>0.123599</v>
+      </c>
+      <c r="T28" t="n">
         <v>-3.888765</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="T28" t="n">
+      <c r="W28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
+        <v>0.719465</v>
+      </c>
+      <c r="Z28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="W28" t="n">
+      <c r="AA28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AB28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AC28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AD28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AE28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AF28" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="AG28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AH28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AI28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3063,87 +3403,99 @@
         <v>0.047279</v>
       </c>
       <c r="D29" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.24</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.5</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>0.12</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>102.87707</v>
+      </c>
+      <c r="I29" t="n">
         <v>102.0744</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>5653808</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>2204808</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
+        <v>3449000</v>
+      </c>
+      <c r="O29" t="n">
         <v>3.56</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>3.97</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>29.24</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>340247</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
+        <v>0.290723</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.068831</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="T29" t="n">
+      <c r="W29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="U29" t="n">
+      <c r="X29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
+        <v>1.120891</v>
+      </c>
+      <c r="Z29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AA29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AB29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AC29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AF29" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.02</v>
       </c>
-      <c r="AC29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AH29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AI29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3158,87 +3510,99 @@
         <v>0.045601</v>
       </c>
       <c r="D30" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.28</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>0.59</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.1</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
+        <v>103.528</v>
+      </c>
+      <c r="I30" t="n">
         <v>101.86494</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>5711103</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>2220766</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
+        <v>3490337</v>
+      </c>
+      <c r="O30" t="n">
         <v>3.53</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>3.88</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>29.01</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>348406</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
+        <v>0.632726</v>
+      </c>
+      <c r="T30" t="n">
         <v>-0.205203</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="T30" t="n">
+      <c r="W30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
+        <v>1.198521</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AA30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AB30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AC30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AD30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AE30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AF30" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="AG30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AH30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AI30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3253,87 +3617,99 @@
         <v>0.044537</v>
       </c>
       <c r="D31" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="E31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.74</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.55</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
+        <v>104.8991</v>
+      </c>
+      <c r="I31" t="n">
         <v>101.74606</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>5805157</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>2283485</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
+        <v>3521672</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.29</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>3.75</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>28.14</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>355034</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
+        <v>1.324376</v>
+      </c>
+      <c r="T31" t="n">
         <v>-0.116704</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
+        <v>0.897764</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="W31" t="n">
+      <c r="AA31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AB31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AC31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AD31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AE31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AF31" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="AG31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AC31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AH31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AI31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3348,87 +3724,99 @@
         <v>0.043739</v>
       </c>
       <c r="D32" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.42</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>0.57</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
+        <v>104.53245</v>
+      </c>
+      <c r="I32" t="n">
         <v>98.01879</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>5794707</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>2234362</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
+        <v>3560345</v>
+      </c>
+      <c r="O32" t="n">
         <v>3.38</v>
       </c>
-      <c r="M32" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>3.76</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>28</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>355066</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
+        <v>-0.349526</v>
+      </c>
+      <c r="T32" t="n">
         <v>-3.663306</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="T32" t="n">
+      <c r="W32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="U32" t="n">
+      <c r="X32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
+        <v>1.098143</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AA32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AB32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AC32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AF32" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="AG32" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AH32" t="n">
         <v>0.01</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AI32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3443,87 +3831,99 @@
         <v>0.041957</v>
       </c>
       <c r="D33" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="E33" t="n">
         <v>0.83</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
+        <v>104.75961</v>
+      </c>
+      <c r="I33" t="n">
         <v>102.37988</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>5815954</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>2235302</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
+        <v>3580652</v>
+      </c>
+      <c r="O33" t="n">
         <v>3.38</v>
       </c>
-      <c r="M33" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>3.76</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>27.85</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>352705</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
+        <v>0.217311</v>
+      </c>
+      <c r="T33" t="n">
         <v>4.449239</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="T33" t="n">
+      <c r="W33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="U33" t="n">
+      <c r="X33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
+        <v>0.570366</v>
+      </c>
+      <c r="Z33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="W33" t="n">
+      <c r="AA33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AB33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AC33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AD33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AE33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
+      <c r="AF33" t="n">
+        <v>-0.001782</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3538,87 +3938,99 @@
         <v>0.04142</v>
       </c>
       <c r="D34" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>-0.47</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>0.19</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
+        <v>104.7097</v>
+      </c>
+      <c r="I34" t="n">
         <v>109.58504</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>5899742</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>2285775</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
+        <v>3613967</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.33</v>
       </c>
-      <c r="M34" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>3.71</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>28.14</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>355008</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
+        <v>-0.047642</v>
+      </c>
+      <c r="T34" t="n">
         <v>7.037672</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="T34" t="n">
+      <c r="W34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="U34" t="n">
+      <c r="X34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="V34" t="n">
+      <c r="Y34" t="n">
+        <v>0.930417</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="W34" t="n">
+      <c r="AA34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AB34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AC34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AD34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AE34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AF34" t="n">
+        <v>-0.000537</v>
+      </c>
+      <c r="AG34" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AH34" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AD34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AE34" t="n">
+      <c r="AI34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -3633,87 +4045,99 @@
         <v>0.040168</v>
       </c>
       <c r="D35" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.38</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>0.31</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.37</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>104.75682</v>
+      </c>
+      <c r="I35" t="n">
         <v>109.36335</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>5915538</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>2268879</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
+        <v>3646659</v>
+      </c>
+      <c r="O35" t="n">
         <v>3.37</v>
       </c>
-      <c r="M35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>3.75</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>27.86</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>351599</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
+        <v>0.045001</v>
+      </c>
+      <c r="T35" t="n">
         <v>-0.2023</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="T35" t="n">
+      <c r="W35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="U35" t="n">
+      <c r="X35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
+        <v>0.904602</v>
+      </c>
+      <c r="Z35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="W35" t="n">
+      <c r="AA35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AB35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AC35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AF35" t="n">
+        <v>-0.001252</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AD35" t="n">
+      <c r="AH35" t="n">
         <v>0.04</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AI35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -3728,87 +4152,99 @@
         <v>0.039484</v>
       </c>
       <c r="D36" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.46</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.89</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>0.46</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>105.70704</v>
+      </c>
+      <c r="I36" t="n">
         <v>104.84682</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>5.241</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>5953960</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>2278309</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
+        <v>3675652</v>
+      </c>
+      <c r="O36" t="n">
         <v>3.43</v>
       </c>
-      <c r="M36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>3.82</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>27.75</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>355560</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
+        <v>0.907072</v>
+      </c>
+      <c r="T36" t="n">
         <v>-4.129839</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="T36" t="n">
+      <c r="W36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="U36" t="n">
+      <c r="X36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="V36" t="n">
+      <c r="Y36" t="n">
+        <v>0.795057</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AA36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AB36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AC36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AD36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AE36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AF36" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AH36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AI36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -3823,87 +4259,99 @@
         <v>0.03927</v>
       </c>
       <c r="D37" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.21</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>0.25</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>106.57623</v>
+      </c>
+      <c r="I37" t="n">
         <v>106.03093</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>6041898</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>2336858</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
+        <v>3705041</v>
+      </c>
+      <c r="O37" t="n">
         <v>3.29</v>
       </c>
-      <c r="M37" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>3.71</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>27.81</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>357827</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
+        <v>0.822263</v>
+      </c>
+      <c r="T37" t="n">
         <v>1.129371</v>
       </c>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="T37" t="n">
+      <c r="W37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="U37" t="n">
+      <c r="X37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="V37" t="n">
+      <c r="Y37" t="n">
+        <v>0.799559</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="W37" t="n">
+      <c r="AA37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AB37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AC37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AF37" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="AG37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AC37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AH37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AI37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -3918,87 +4366,99 @@
         <v>0.03927</v>
       </c>
       <c r="D38" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.38</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>0.61</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.26</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>106.88756</v>
+      </c>
+      <c r="I38" t="n">
         <v>111.55002</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>6069205</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>2323362</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
+        <v>3745844</v>
+      </c>
+      <c r="O38" t="n">
         <v>3.3</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>3.78</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>27.74</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>363282</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="T38" t="n">
         <v>5.20517</v>
       </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="T38" t="n">
+      <c r="W38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="U38" t="n">
+      <c r="X38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
+        <v>1.101283</v>
+      </c>
+      <c r="Z38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="W38" t="n">
+      <c r="AA38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AB38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AC38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AH38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AI38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4013,87 +4473,99 @@
         <v>0.03927</v>
       </c>
       <c r="D39" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="E39" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.29</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>-0.14</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>107.14396</v>
+      </c>
+      <c r="I39" t="n">
         <v>110.19363</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>6135298</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>2344397</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
+        <v>3790900</v>
+      </c>
+      <c r="O39" t="n">
         <v>3.33</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>3.82</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>27.59</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>369214</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
+        <v>0.239878</v>
+      </c>
+      <c r="T39" t="n">
         <v>-1.215948</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="T39" t="n">
+      <c r="W39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="U39" t="n">
+      <c r="X39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="V39" t="n">
+      <c r="Y39" t="n">
+        <v>1.202826</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="W39" t="n">
+      <c r="AA39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AB39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AC39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AD39" t="n">
+      <c r="AH39" t="n">
         <v>0.04</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AI39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4108,87 +4580,99 @@
         <v>0.039612</v>
       </c>
       <c r="D40" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="E40" t="n">
         <v>0.44</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>0.62</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.48</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>107.99916</v>
+      </c>
+      <c r="I40" t="n">
         <v>107.28836</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>6216528</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>2384828</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
+        <v>3831700</v>
+      </c>
+      <c r="O40" t="n">
         <v>3.34</v>
       </c>
-      <c r="M40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>3.83</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>27.49</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>372016</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
+        <v>0.7981780000000001</v>
+      </c>
+      <c r="T40" t="n">
         <v>-2.636514</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="T40" t="n">
+      <c r="W40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="U40" t="n">
+      <c r="X40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="V40" t="n">
+      <c r="Y40" t="n">
+        <v>1.076262</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="W40" t="n">
+      <c r="AA40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AB40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AC40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AD40" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AE40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AF40" t="n">
+        <v>0.000342</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AH40" t="n">
         <v>0.01</v>
       </c>
-      <c r="AD40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE40" t="n">
+      <c r="AI40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4203,87 +4687,99 @@
         <v>0.040168</v>
       </c>
       <c r="D41" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="E41" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>1.52</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.61</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
+        <v>108.15356</v>
+      </c>
+      <c r="I41" t="n">
         <v>109.21678</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>6275117</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>2397533</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
+        <v>3877584</v>
+      </c>
+      <c r="O41" t="n">
         <v>3.3</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>3.79</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>27.94</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>366096</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
+        <v>0.142964</v>
+      </c>
+      <c r="T41" t="n">
         <v>1.797418</v>
       </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="T41" t="n">
+      <c r="W41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="U41" t="n">
+      <c r="X41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Y41" t="n">
+        <v>1.197484</v>
+      </c>
+      <c r="Z41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AA41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AB41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AC41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AF41" t="n">
+        <v>0.000556</v>
+      </c>
+      <c r="AG41" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AH41" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AD41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AE41" t="n">
+      <c r="AI41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4298,87 +4794,99 @@
         <v>0.04158</v>
       </c>
       <c r="D42" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="E42" t="n">
         <v>0.39</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1.3</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>0.33</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
+        <v>107.98489</v>
+      </c>
+      <c r="I42" t="n">
         <v>105.74688</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>6365690</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>2436022</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
+        <v>3929668</v>
+      </c>
+      <c r="O42" t="n">
         <v>3.27</v>
       </c>
-      <c r="M42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>3.75</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>28.45</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>363003</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
+        <v>-0.155954</v>
+      </c>
+      <c r="T42" t="n">
         <v>-3.177076</v>
       </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="T42" t="n">
+      <c r="W42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="U42" t="n">
+      <c r="X42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="V42" t="n">
+      <c r="Y42" t="n">
+        <v>1.343208</v>
+      </c>
+      <c r="Z42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="W42" t="n">
+      <c r="AA42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AB42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AC42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AD42" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AE42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AF42" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="AG42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AC42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AD42" t="n">
+      <c r="AH42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AI42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4393,87 +4901,99 @@
         <v>0.044158</v>
       </c>
       <c r="D43" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="E43" t="n">
         <v>0.52</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>0.48</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
+        <v>107.44467</v>
+      </c>
+      <c r="I43" t="n">
         <v>104.2734</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>6464602</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>2499177</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
+        <v>3965425</v>
+      </c>
+      <c r="O43" t="n">
         <v>3.08</v>
       </c>
-      <c r="M43" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>3.63</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>28.5</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>329730</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
+        <v>-0.500274</v>
+      </c>
+      <c r="T43" t="n">
         <v>-1.393403</v>
       </c>
-      <c r="R43" t="n">
+      <c r="U43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="T43" t="n">
+      <c r="W43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="U43" t="n">
+      <c r="X43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="V43" t="n">
+      <c r="Y43" t="n">
+        <v>0.909924</v>
+      </c>
+      <c r="Z43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="W43" t="n">
+      <c r="AA43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AB43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AC43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AD43" t="n">
         <v>1</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AE43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AF43" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="AG43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="AC43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AD43" t="n">
+      <c r="AH43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AI43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4488,87 +5008,99 @@
         <v>0.045833</v>
       </c>
       <c r="D44" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="E44" t="n">
         <v>0.16</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>0.27</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>108.06979</v>
+      </c>
+      <c r="I44" t="n">
         <v>101.23438</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>6465016</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>2451957</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
+        <v>4013059</v>
+      </c>
+      <c r="O44" t="n">
         <v>3.34</v>
       </c>
-      <c r="M44" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>3.89</v>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
         <v>29.88</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>328303</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
+        <v>0.581806</v>
+      </c>
+      <c r="T44" t="n">
         <v>-2.914473</v>
       </c>
-      <c r="R44" t="n">
+      <c r="U44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="T44" t="n">
+      <c r="W44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="U44" t="n">
+      <c r="X44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="V44" t="n">
+      <c r="Y44" t="n">
+        <v>1.201233</v>
+      </c>
+      <c r="Z44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="W44" t="n">
+      <c r="AA44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AB44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AC44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AD44" t="n">
         <v>1</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AE44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AF44" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="AG44" t="n">
         <v>0.26</v>
       </c>
-      <c r="AC44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AD44" t="n">
+      <c r="AH44" t="n">
         <v>0.26</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AI44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -4583,87 +5115,99 @@
         <v>0.049037</v>
       </c>
       <c r="D45" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="E45" t="n">
         <v>1.31</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>1.06</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>1.48</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
+        <v>108.77346</v>
+      </c>
+      <c r="I45" t="n">
         <v>107.07838</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>6511444</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>2477151</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
+        <v>4034293</v>
+      </c>
+      <c r="O45" t="n">
         <v>3.41</v>
       </c>
-      <c r="M45" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>3.96</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>30.53</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>332508</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
+        <v>0.651126</v>
+      </c>
+      <c r="T45" t="n">
         <v>5.772742</v>
       </c>
-      <c r="R45" t="n">
+      <c r="U45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="T45" t="n">
+      <c r="W45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="U45" t="n">
+      <c r="X45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="V45" t="n">
+      <c r="Y45" t="n">
+        <v>0.529123</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="W45" t="n">
+      <c r="AA45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AB45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AC45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AF45" t="n">
+        <v>0.003204</v>
+      </c>
+      <c r="AG45" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AH45" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AI45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -4678,87 +5222,99 @@
         <v>0.050508</v>
       </c>
       <c r="D46" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="E46" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>-0.34</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.51</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
+        <v>110.09056</v>
+      </c>
+      <c r="I46" t="n">
         <v>114.05013</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>6576464</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>2498262</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
+        <v>4078202</v>
+      </c>
+      <c r="O46" t="n">
         <v>3.44</v>
       </c>
-      <c r="M46" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>4.03</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>31.34</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>336157</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
+        <v>1.210865</v>
+      </c>
+      <c r="T46" t="n">
         <v>6.510885</v>
       </c>
-      <c r="R46" t="n">
+      <c r="U46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="S46" t="n">
+      <c r="V46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="T46" t="n">
+      <c r="W46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="U46" t="n">
+      <c r="X46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="V46" t="n">
+      <c r="Y46" t="n">
+        <v>1.088394</v>
+      </c>
+      <c r="Z46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="W46" t="n">
+      <c r="AA46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AB46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AC46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AD46" t="n">
         <v>1</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AE46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AF46" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AD46" t="n">
+      <c r="AH46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AI46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -4773,87 +5329,99 @@
         <v>0.052531</v>
       </c>
       <c r="D47" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="E47" t="n">
         <v>0.43</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>0.24</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>0.48</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
+        <v>109.72323</v>
+      </c>
+      <c r="I47" t="n">
         <v>112.73813</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>6623948</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>2512426</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
+        <v>4111522</v>
+      </c>
+      <c r="O47" t="n">
         <v>3.67</v>
       </c>
-      <c r="M47" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>4.25</v>
       </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
         <v>31.63</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>340789</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="S47" t="n">
+        <v>-0.333662</v>
+      </c>
+      <c r="T47" t="n">
         <v>-1.150371</v>
       </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="S47" t="n">
+      <c r="V47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="T47" t="n">
+      <c r="W47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="U47" t="n">
+      <c r="X47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="V47" t="n">
+      <c r="Y47" t="n">
+        <v>0.8170269999999999</v>
+      </c>
+      <c r="Z47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="W47" t="n">
+      <c r="AA47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AB47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AC47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AF47" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="AG47" t="n">
         <v>0.23</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AD47" t="n">
+      <c r="AH47" t="n">
         <v>0.22</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AI47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4868,87 +5436,99 @@
         <v>0.053936</v>
       </c>
       <c r="D48" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="E48" t="n">
         <v>0.26</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>-0.49</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.35</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
+        <v>109.00057</v>
+      </c>
+      <c r="I48" t="n">
         <v>108.66481</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>6666287</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>2532708</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
+        <v>4133579</v>
+      </c>
+      <c r="O48" t="n">
         <v>3.72</v>
       </c>
-      <c r="M48" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>4.36</v>
       </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
         <v>31.7</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>341459</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="S48" t="n">
+        <v>-0.658621</v>
+      </c>
+      <c r="T48" t="n">
         <v>-3.613081</v>
       </c>
-      <c r="R48" t="n">
+      <c r="U48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="S48" t="n">
+      <c r="V48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="T48" t="n">
+      <c r="W48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="U48" t="n">
+      <c r="X48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Y48" t="n">
+        <v>0.5364679999999999</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AA48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AB48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AC48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AD48" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AE48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AF48" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="AG48" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AD48" t="n">
+      <c r="AH48" t="n">
         <v>0.11</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AI48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -4963,87 +5543,99 @@
         <v>0.054569</v>
       </c>
       <c r="D49" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="E49" t="n">
         <v>0.24</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>-1.67</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>0.23</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
+        <v>108.76683</v>
+      </c>
+      <c r="I49" t="n">
         <v>107.55639</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>6703663</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>2547693</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
+        <v>4155970</v>
+      </c>
+      <c r="O49" t="n">
         <v>3.75</v>
       </c>
-      <c r="M49" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>4.41</v>
       </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
         <v>31.85</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>344440</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
+        <v>-0.214439</v>
+      </c>
+      <c r="T49" t="n">
         <v>-1.020036</v>
       </c>
-      <c r="R49" t="n">
+      <c r="U49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="S49" t="n">
+      <c r="V49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="T49" t="n">
+      <c r="W49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="U49" t="n">
+      <c r="X49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Y49" t="n">
+        <v>0.541686</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AA49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AB49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AC49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AD49" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AE49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AF49" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.03</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
+      <c r="AH49" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AI49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5058,87 +5650,99 @@
         <v>0.055131</v>
       </c>
       <c r="D50" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E50" t="n">
         <v>0.26</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>-0.77</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>0.21</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
+        <v>108.27053</v>
+      </c>
+      <c r="I50" t="n">
         <v>113.14433</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>6733209</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>2544400</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="O50" t="n">
         <v>3.96</v>
       </c>
-      <c r="M50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>4.66</v>
       </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
         <v>31.75</v>
       </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>345111</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="S50" t="n">
+        <v>-0.456297</v>
+      </c>
+      <c r="T50" t="n">
         <v>5.195358</v>
       </c>
-      <c r="R50" t="n">
+      <c r="U50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="S50" t="n">
+      <c r="V50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="T50" t="n">
+      <c r="W50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="U50" t="n">
+      <c r="X50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="V50" t="n">
+      <c r="Y50" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="W50" t="n">
+      <c r="AA50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AB50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AC50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AF50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="AG50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AD50" t="n">
+      <c r="AH50" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AI50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -5153,87 +5757,99 @@
         <v>0.055131</v>
       </c>
       <c r="D51" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E51" t="n">
         <v>-0.11</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>0.36</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
+        <v>108.80021</v>
+      </c>
+      <c r="I51" t="n">
         <v>110.57963</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>6774436</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>2546265</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
+        <v>4228171</v>
+      </c>
+      <c r="O51" t="n">
         <v>4.14</v>
       </c>
-      <c r="M51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>4.92</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>31.87</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>350767</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
+        <v>0.489219</v>
+      </c>
+      <c r="T51" t="n">
         <v>-2.266751</v>
       </c>
-      <c r="R51" t="n">
+      <c r="U51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="S51" t="n">
+      <c r="V51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="T51" t="n">
+      <c r="W51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="U51" t="n">
+      <c r="X51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="V51" t="n">
+      <c r="Y51" t="n">
+        <v>0.9397180000000001</v>
+      </c>
+      <c r="Z51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="W51" t="n">
+      <c r="AA51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AB51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AC51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
         <v>0.18</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AD51" t="n">
+      <c r="AH51" t="n">
         <v>0.26</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AI51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5248,87 +5864,99 @@
         <v>0.055131</v>
       </c>
       <c r="D52" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E52" t="n">
         <v>0.48</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>0.42</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.52</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
+        <v>108.63642</v>
+      </c>
+      <c r="I52" t="n">
         <v>109.59513</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>5.318</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>6852705</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>2589817</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
+        <v>4262888</v>
+      </c>
+      <c r="O52" t="n">
         <v>4.09</v>
       </c>
-      <c r="M52" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>4.89</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
         <v>31.47</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>356582</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
+        <v>-0.150542</v>
+      </c>
+      <c r="T52" t="n">
         <v>-0.890309</v>
       </c>
-      <c r="R52" t="n">
+      <c r="U52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="T52" t="n">
+      <c r="W52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="U52" t="n">
+      <c r="X52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="V52" t="n">
+      <c r="Y52" t="n">
+        <v>0.821088</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="W52" t="n">
+      <c r="AA52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AB52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AC52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AC52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AD52" t="n">
+      <c r="AH52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AI52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5343,87 +5971,99 @@
         <v>0.055131</v>
       </c>
       <c r="D53" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E53" t="n">
         <v>0.09</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>-0.36</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>0.03</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
+        <v>108.7159</v>
+      </c>
+      <c r="I53" t="n">
         <v>110.16346</v>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>6923886</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>2597630</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
+        <v>4326256</v>
+      </c>
+      <c r="O53" t="n">
         <v>4.18</v>
       </c>
-      <c r="M53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>4.99</v>
       </c>
-      <c r="O53" t="n">
+      <c r="Q53" t="n">
         <v>32.04</v>
       </c>
-      <c r="P53" t="n">
+      <c r="R53" t="n">
         <v>357103</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="S53" t="n">
+        <v>0.073161</v>
+      </c>
+      <c r="T53" t="n">
         <v>0.518572</v>
       </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="S53" t="n">
+      <c r="V53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="T53" t="n">
+      <c r="W53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="U53" t="n">
+      <c r="X53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="V53" t="n">
+      <c r="Y53" t="n">
+        <v>1.486504</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="W53" t="n">
+      <c r="AA53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AB53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AC53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AD53" t="n">
+      <c r="AH53" t="n">
         <v>0.1</v>
       </c>
-      <c r="AE53" t="n">
+      <c r="AI53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -5438,87 +6078,99 @@
         <v>0.055131</v>
       </c>
       <c r="D54" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E54" t="n">
         <v>0.18</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>0.27</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.03</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
+        <v>109.27405</v>
+      </c>
+      <c r="I54" t="n">
         <v>106.90236</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>7003273</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>2616213</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
+        <v>4387061</v>
+      </c>
+      <c r="O54" t="n">
         <v>4.23</v>
       </c>
-      <c r="M54" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>5.12</v>
       </c>
-      <c r="O54" t="n">
+      <c r="Q54" t="n">
         <v>32.32</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
         <v>360578</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
+        <v>0.513402</v>
+      </c>
+      <c r="T54" t="n">
         <v>-2.960237</v>
       </c>
-      <c r="R54" t="n">
+      <c r="U54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="S54" t="n">
+      <c r="V54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="T54" t="n">
+      <c r="W54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="U54" t="n">
+      <c r="X54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="V54" t="n">
+      <c r="Y54" t="n">
+        <v>1.405488</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="W54" t="n">
+      <c r="AA54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AB54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AC54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>-0</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AF54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG54" t="n">
         <v>0.05</v>
       </c>
-      <c r="AC54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AD54" t="n">
+      <c r="AH54" t="n">
         <v>0.13</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AI54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -5533,87 +6185,99 @@
         <v>0.055131</v>
       </c>
       <c r="D55" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E55" t="n">
         <v>0.33</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>0.21</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
+        <v>109.41762</v>
+      </c>
+      <c r="I55" t="n">
         <v>107.17649</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>7136436</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>2701146</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
+        <v>4435290</v>
+      </c>
+      <c r="O55" t="n">
         <v>4.2</v>
       </c>
-      <c r="M55" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>5.12</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
         <v>31.99</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>358234</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
+        <v>0.131385</v>
+      </c>
+      <c r="T55" t="n">
         <v>0.25643</v>
       </c>
-      <c r="R55" t="n">
+      <c r="U55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="S55" t="n">
+      <c r="V55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="T55" t="n">
+      <c r="W55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="U55" t="n">
+      <c r="X55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="V55" t="n">
+      <c r="Y55" t="n">
+        <v>1.099346</v>
+      </c>
+      <c r="Z55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="W55" t="n">
+      <c r="AA55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AB55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AC55" t="n">
         <v>3.897866</v>
       </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AC55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -5628,87 +6292,99 @@
         <v>0.055131</v>
       </c>
       <c r="D56" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E56" t="n">
         <v>0.33</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>0.41</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>0.39</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
+        <v>110.05486</v>
+      </c>
+      <c r="I56" t="n">
         <v>102.36456</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>7130500</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>2654052</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
+        <v>4476448</v>
+      </c>
+      <c r="O56" t="n">
         <v>4.45</v>
       </c>
-      <c r="M56" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>5.38</v>
       </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
         <v>32.6</v>
       </c>
-      <c r="P56" t="n">
+      <c r="R56" t="n">
         <v>364367</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
+        <v>0.582392</v>
+      </c>
+      <c r="T56" t="n">
         <v>-4.489725</v>
       </c>
-      <c r="R56" t="n">
+      <c r="U56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="S56" t="n">
+      <c r="V56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="T56" t="n">
+      <c r="W56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="U56" t="n">
+      <c r="X56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="V56" t="n">
+      <c r="Y56" t="n">
+        <v>0.927966</v>
+      </c>
+      <c r="Z56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="W56" t="n">
+      <c r="AA56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AB56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AC56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AD56" t="n">
+      <c r="AH56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AI56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -5723,87 +6399,99 @@
         <v>0.055131</v>
       </c>
       <c r="D57" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="E57" t="n">
         <v>0.7</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>-0.73</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
+        <v>110.65892</v>
+      </c>
+      <c r="I57" t="n">
         <v>106.82125</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>7156987</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>2655931</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
+        <v>4501056</v>
+      </c>
+      <c r="O57" t="n">
         <v>4.64</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>5.56</v>
       </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
         <v>32.78</v>
       </c>
-      <c r="P57" t="n">
+      <c r="R57" t="n">
         <v>371074</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="S57" t="n">
+        <v>0.548872</v>
+      </c>
+      <c r="T57" t="n">
         <v>4.353743</v>
       </c>
-      <c r="R57" t="n">
+      <c r="U57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="S57" t="n">
+      <c r="V57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="T57" t="n">
+      <c r="W57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="U57" t="n">
+      <c r="X57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="V57" t="n">
+      <c r="Y57" t="n">
+        <v>0.549722</v>
+      </c>
+      <c r="Z57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="W57" t="n">
+      <c r="AA57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AB57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AC57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
         <v>0.19</v>
       </c>
-      <c r="AC57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD57" t="n">
+      <c r="AH57" t="n">
         <v>0.18</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AI57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -5818,87 +6506,99 @@
         <v>0.054777</v>
       </c>
       <c r="D58" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="E58" t="n">
         <v>0.88</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>0.52</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.91</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
+        <v>110.51078</v>
+      </c>
+      <c r="I58" t="n">
         <v>117.8089</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="J58" t="n">
-        <v>7237735</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2686046</v>
-      </c>
       <c r="L58" t="n">
-        <v>4.52</v>
+        <v>7240551</v>
       </c>
       <c r="M58" t="n">
-        <v>3.04</v>
+        <v>2687537</v>
       </c>
       <c r="N58" t="n">
+        <v>4553014</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="P58" t="n">
         <v>5.4</v>
       </c>
-      <c r="O58" t="n">
+      <c r="Q58" t="n">
         <v>32.99</v>
       </c>
-      <c r="P58" t="n">
+      <c r="R58" t="n">
         <v>362002</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="S58" t="n">
+        <v>-0.133871</v>
+      </c>
+      <c r="T58" t="n">
         <v>10.286015</v>
       </c>
-      <c r="R58" t="n">
+      <c r="U58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="S58" t="n">
+      <c r="V58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="T58" t="n">
-        <v>1.12824</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.133877</v>
-      </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
+        <v>1.167586</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.190016</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.154351</v>
+      </c>
+      <c r="Z58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="W58" t="n">
+      <c r="AA58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AB58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AC58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AD58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AE58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="AB58" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AD58" t="n">
+      <c r="AF58" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AH58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AI58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -5913,87 +6613,99 @@
         <v>0.054223</v>
       </c>
       <c r="D59" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="E59" t="n">
         <v>0.67</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>2.73</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
+        <v>110.95732</v>
+      </c>
+      <c r="I59" t="n">
         <v>113.99365</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>4.988</v>
       </c>
-      <c r="J59" t="n">
-        <v>7258599</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2684623</v>
-      </c>
       <c r="L59" t="n">
-        <v>4.63</v>
+        <v>7259769</v>
       </c>
       <c r="M59" t="n">
-        <v>3.15</v>
+        <v>2685400</v>
       </c>
       <c r="N59" t="n">
+        <v>4574369</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="P59" t="n">
         <v>5.51</v>
       </c>
-      <c r="O59" t="n">
+      <c r="Q59" t="n">
         <v>33.51</v>
       </c>
-      <c r="P59" t="n">
+      <c r="R59" t="n">
         <v>366913</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="S59" t="n">
+        <v>0.404069</v>
+      </c>
+      <c r="T59" t="n">
         <v>-3.238507</v>
       </c>
-      <c r="R59" t="n">
+      <c r="U59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="S59" t="n">
+      <c r="V59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="T59" t="n">
-        <v>0.288267</v>
-      </c>
-      <c r="U59" t="n">
-        <v>-0.052977</v>
-      </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
+        <v>0.265422</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-0.079515</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.46903</v>
+      </c>
+      <c r="Z59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="W59" t="n">
+      <c r="AA59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AB59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AC59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AD59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AE59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AF59" t="n">
+        <v>-0.000554</v>
+      </c>
+      <c r="AG59" t="n">
         <v>0.11</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AH59" t="n">
         <v>0.11</v>
       </c>
-      <c r="AD59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AE59" t="n">
+      <c r="AI59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -6008,88 +6720,100 @@
         <v>0.0534</v>
       </c>
       <c r="D60" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="E60" t="n">
         <v>0.58</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>0.84</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>0.65</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
+        <v>111.03587</v>
+      </c>
+      <c r="I60" t="n">
         <v>109.52993</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="J60" t="n">
-        <v>7299615</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2704550</v>
-      </c>
       <c r="L60" t="n">
+        <v>7303618</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2707962</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4595657</v>
+      </c>
+      <c r="O60" t="n">
         <v>4.74</v>
       </c>
-      <c r="M60" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N60" t="n">
+      <c r="P60" t="n">
         <v>5.62</v>
       </c>
-      <c r="O60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="R60" t="n">
         <v>371137</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="S60" t="n">
+        <v>0.07079299999999999</v>
+      </c>
+      <c r="T60" t="n">
         <v>-3.915762</v>
       </c>
-      <c r="R60" t="n">
+      <c r="U60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="S60" t="n">
+      <c r="V60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="T60" t="n">
-        <v>0.565068</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.742264</v>
-      </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.8401729999999999</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.465376</v>
+      </c>
+      <c r="Z60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="W60" t="n">
+      <c r="AA60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AB60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AC60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AF60" t="n">
+        <v>-0.0008229999999999999</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH60" t="n">
         <v>0.11</v>
       </c>
-      <c r="AC60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>-0.09</v>
+      <c r="AI60" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="61">
@@ -6103,61 +6827,93 @@
         <v>0.053028</v>
       </c>
       <c r="D61" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="E61" t="n">
         <v>0.16</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>0.14</v>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>5.176</v>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>7355800</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2749001</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4606799</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.68</v>
+      </c>
       <c r="P61" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="R61" t="n">
         <v>367558</v>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="S61" t="n">
+      <c r="V61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
+        <v>0.714468</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.515494</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.242446</v>
+      </c>
+      <c r="Z61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="W61" t="n">
+      <c r="AA61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="X61" t="n">
+      <c r="AB61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AC61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AD61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AE61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="n">
+        <v>-0.000372</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6169,46 +6925,54 @@
       <c r="C62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>0.052531</v>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>5.1177</v>
-      </c>
-      <c r="I62" t="n">
-        <v>5.1171</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>5.1217</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5.1211</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>-1.137812</v>
-      </c>
-      <c r="S62" t="n">
-        <v>-1.137944</v>
-      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-1.060542</v>
+      </c>
+      <c r="V62" t="n">
+        <v>-1.060665</v>
+      </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr"/>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
+++ b/data/final/bcb_sgs/base_bcb_sgs_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,140 +458,130 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ibc_br</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>cambio_venda_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cambio_compra_usd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>saldo_credito_total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>saldo_credito_pj</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>saldo_credito_pf</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inadimplencia_total</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>inadimplencia_pf</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>juros_credito_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>reservas_internacionais</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>var_pct_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>var_pct_ibc_br</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>inpc_acum_12m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>dif_selic_meta</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dif_selic_over</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_cdi</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>dif_juros_credito_total</t>
         </is>
@@ -604,12 +594,8 @@
       <c r="B2" t="n">
         <v>4.25</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.016137</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.016137</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>0.96</v>
       </c>
@@ -619,39 +605,33 @@
       <c r="G2" t="n">
         <v>1.02</v>
       </c>
-      <c r="H2" t="n">
-        <v>96.31464</v>
-      </c>
-      <c r="I2" t="n">
-        <v>99.83978</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="K2" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="L2" t="n">
-        <v>4271865</v>
+        <v>2438686</v>
       </c>
       <c r="M2" t="n">
-        <v>1833179</v>
+        <v>2.36</v>
       </c>
       <c r="N2" t="n">
-        <v>2438686</v>
+        <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="P2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="R2" t="n">
         <v>355671</v>
       </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -667,8 +647,6 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -693,81 +671,67 @@
         <v>0.88</v>
       </c>
       <c r="H3" t="n">
-        <v>97.07568000000001</v>
+        <v>5.1433</v>
       </c>
       <c r="I3" t="n">
-        <v>99.32829</v>
+        <v>5.1427</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1433</v>
+        <v>4346060</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1427</v>
+        <v>1851006</v>
       </c>
       <c r="L3" t="n">
-        <v>4346060</v>
+        <v>2495054</v>
       </c>
       <c r="M3" t="n">
-        <v>1851006</v>
+        <v>2.37</v>
       </c>
       <c r="N3" t="n">
-        <v>2495054</v>
+        <v>1.56</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>2.96</v>
       </c>
       <c r="P3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="R3" t="n">
         <v>370395</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.79016</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>-0.512311</v>
+        <v>1.736829</v>
       </c>
       <c r="U3" t="n">
-        <v>0.423696</v>
+        <v>0.972464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.423745</v>
+        <v>2.311409</v>
       </c>
       <c r="W3" t="n">
-        <v>1.736829</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.972464</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="Z3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.003276</v>
+        <v>0.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -794,81 +758,75 @@
         <v>1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>96.95968999999999</v>
+        <v>5.4394</v>
       </c>
       <c r="I4" t="n">
-        <v>97.24746</v>
+        <v>5.4388</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4394</v>
+        <v>4441056</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4388</v>
+        <v>1894119</v>
       </c>
       <c r="L4" t="n">
-        <v>4441056</v>
+        <v>2546936</v>
       </c>
       <c r="M4" t="n">
-        <v>1894119</v>
+        <v>2.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2546936</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="R4" t="n">
-        <v>368886</v>
+        <v>5.757004</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.119484</v>
+        <v>5.757676</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.094902</v>
+        <v>2.185796</v>
       </c>
       <c r="U4" t="n">
-        <v>5.757004</v>
+        <v>2.329166</v>
       </c>
       <c r="V4" t="n">
-        <v>5.757676</v>
+        <v>2.079394</v>
       </c>
       <c r="W4" t="n">
-        <v>2.185796</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.329166</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="Z4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>-0.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001591</v>
+        <v>0.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -895,81 +853,75 @@
         <v>1.16</v>
       </c>
       <c r="H5" t="n">
-        <v>97.48142</v>
+        <v>5.643</v>
       </c>
       <c r="I5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.6424</v>
       </c>
       <c r="J5" t="n">
-        <v>5.643</v>
+        <v>4511956</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6424</v>
+        <v>1910940</v>
       </c>
       <c r="L5" t="n">
-        <v>4511956</v>
+        <v>2601017</v>
       </c>
       <c r="M5" t="n">
-        <v>1910940</v>
+        <v>2.33</v>
       </c>
       <c r="N5" t="n">
-        <v>2601017</v>
+        <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="P5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="R5" t="n">
-        <v>367927</v>
+        <v>3.74306</v>
       </c>
       <c r="S5" t="n">
-        <v>0.53809</v>
+        <v>3.743473</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.644377</v>
+        <v>1.596467</v>
       </c>
       <c r="U5" t="n">
-        <v>3.74306</v>
+        <v>0.888065</v>
       </c>
       <c r="V5" t="n">
-        <v>3.743473</v>
+        <v>2.123375</v>
       </c>
       <c r="W5" t="n">
-        <v>1.596467</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="Z5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00324</v>
+        <v>-0.02</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AI5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -996,81 +948,75 @@
         <v>0.84</v>
       </c>
       <c r="H6" t="n">
-        <v>98.97262000000001</v>
+        <v>5.6199</v>
       </c>
       <c r="I6" t="n">
-        <v>98.05768</v>
+        <v>5.6193</v>
       </c>
       <c r="J6" t="n">
-        <v>5.6199</v>
+        <v>4597507</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6193</v>
+        <v>1933111</v>
       </c>
       <c r="L6" t="n">
-        <v>4597507</v>
+        <v>2664395</v>
       </c>
       <c r="M6" t="n">
-        <v>1933111</v>
+        <v>2.36</v>
       </c>
       <c r="N6" t="n">
-        <v>2664395</v>
+        <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="P6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="R6" t="n">
-        <v>367772</v>
+        <v>-0.409357</v>
       </c>
       <c r="S6" t="n">
-        <v>1.529727</v>
+        <v>-0.4094</v>
       </c>
       <c r="T6" t="n">
-        <v>1.487112</v>
+        <v>1.896096</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.409357</v>
+        <v>1.160214</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4094</v>
+        <v>2.436662</v>
       </c>
       <c r="W6" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="Z6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.005012</v>
+        <v>0.02</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1097,81 +1043,75 @@
         <v>0.73</v>
       </c>
       <c r="H7" t="n">
-        <v>99.35339</v>
+        <v>5.5805</v>
       </c>
       <c r="I7" t="n">
-        <v>99.33126</v>
+        <v>5.5799</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5805</v>
+        <v>4682852</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5799</v>
+        <v>1974391</v>
       </c>
       <c r="L7" t="n">
-        <v>4682852</v>
+        <v>2708461</v>
       </c>
       <c r="M7" t="n">
-        <v>1974391</v>
+        <v>2.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2708461</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="R7" t="n">
-        <v>362204</v>
+        <v>-0.70108</v>
       </c>
       <c r="S7" t="n">
-        <v>0.384723</v>
+        <v>-0.701155</v>
       </c>
       <c r="T7" t="n">
-        <v>1.298807</v>
+        <v>1.856332</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.70108</v>
+        <v>2.135418</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.701155</v>
+        <v>1.653884</v>
       </c>
       <c r="W7" t="n">
-        <v>1.856332</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="Z7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00406</v>
+        <v>0.04</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1198,81 +1138,75 @@
         <v>0.67</v>
       </c>
       <c r="H8" t="n">
-        <v>97.34401</v>
+        <v>5.3574</v>
       </c>
       <c r="I8" t="n">
-        <v>90.45032</v>
+        <v>5.3568</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3574</v>
+        <v>4682131</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3568</v>
+        <v>1947035</v>
       </c>
       <c r="L8" t="n">
-        <v>4682131</v>
+        <v>2735096</v>
       </c>
       <c r="M8" t="n">
-        <v>1947035</v>
+        <v>2.51</v>
       </c>
       <c r="N8" t="n">
-        <v>2735096</v>
+        <v>1.46</v>
       </c>
       <c r="O8" t="n">
-        <v>2.51</v>
+        <v>3.26</v>
       </c>
       <c r="P8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="R8" t="n">
-        <v>358398</v>
+        <v>-3.99785</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.022457</v>
+        <v>-3.99828</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.94073</v>
+        <v>-0.015397</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.99785</v>
+        <v>-1.385541</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.99828</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.015397</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="Z8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001433</v>
+        <v>0.21</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AI8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1299,81 +1233,75 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>98.43725000000001</v>
+        <v>5.1394</v>
       </c>
       <c r="I9" t="n">
-        <v>95.72214</v>
+        <v>5.1388</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1394</v>
+        <v>4727818</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1388</v>
+        <v>1971524</v>
       </c>
       <c r="L9" t="n">
-        <v>4727818</v>
+        <v>2756295</v>
       </c>
       <c r="M9" t="n">
-        <v>1971524</v>
+        <v>2.57</v>
       </c>
       <c r="N9" t="n">
-        <v>2756295</v>
+        <v>1.44</v>
       </c>
       <c r="O9" t="n">
-        <v>2.57</v>
+        <v>3.38</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="R9" t="n">
-        <v>357740</v>
+        <v>-4.069138</v>
       </c>
       <c r="S9" t="n">
-        <v>1.123069</v>
+        <v>-4.069594</v>
       </c>
       <c r="T9" t="n">
-        <v>5.828415</v>
+        <v>0.975774</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.069138</v>
+        <v>1.257759</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.069594</v>
+        <v>0.775073</v>
       </c>
       <c r="W9" t="n">
-        <v>0.975774</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="Z9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>0.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004849</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AI9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1400,81 +1328,75 @@
         <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>99.55981</v>
+        <v>4.7378</v>
       </c>
       <c r="I10" t="n">
-        <v>104.61484</v>
+        <v>4.7372</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7378</v>
+        <v>4794583</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7372</v>
+        <v>1994119</v>
       </c>
       <c r="L10" t="n">
-        <v>4794583</v>
+        <v>2800464</v>
       </c>
       <c r="M10" t="n">
-        <v>1994119</v>
+        <v>2.66</v>
       </c>
       <c r="N10" t="n">
-        <v>2800464</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="R10" t="n">
-        <v>353169</v>
+        <v>-7.814142</v>
       </c>
       <c r="S10" t="n">
-        <v>1.140381</v>
+        <v>-7.815054</v>
       </c>
       <c r="T10" t="n">
-        <v>9.290118</v>
+        <v>1.412174</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.814142</v>
+        <v>1.146068</v>
       </c>
       <c r="V10" t="n">
-        <v>-7.815054</v>
+        <v>1.602477</v>
       </c>
       <c r="W10" t="n">
-        <v>1.412174</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="Z10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002356</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1501,81 +1423,75 @@
         <v>1.04</v>
       </c>
       <c r="H11" t="n">
-        <v>99.51646</v>
+        <v>4.9191</v>
       </c>
       <c r="I11" t="n">
-        <v>100.42352</v>
+        <v>4.9185</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9191</v>
+        <v>4833732</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9185</v>
+        <v>2003312</v>
       </c>
       <c r="L11" t="n">
-        <v>4833732</v>
+        <v>2830420</v>
       </c>
       <c r="M11" t="n">
-        <v>2003312</v>
+        <v>2.72</v>
       </c>
       <c r="N11" t="n">
-        <v>2830420</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>3.54</v>
       </c>
       <c r="P11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="R11" t="n">
-        <v>345097</v>
+        <v>3.826671</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.043542</v>
+        <v>3.827155</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.00643</v>
+        <v>0.816526</v>
       </c>
       <c r="U11" t="n">
-        <v>3.826671</v>
+        <v>0.461006</v>
       </c>
       <c r="V11" t="n">
-        <v>3.827155</v>
+        <v>1.06968</v>
       </c>
       <c r="W11" t="n">
-        <v>0.816526</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="Z11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001785</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -1602,81 +1518,75 @@
         <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>99.67415</v>
+        <v>4.7289</v>
       </c>
       <c r="I12" t="n">
-        <v>99.79777</v>
+        <v>4.7283</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7289</v>
+        <v>4889397</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7283</v>
+        <v>2013726</v>
       </c>
       <c r="L12" t="n">
-        <v>4889397</v>
+        <v>2875671</v>
       </c>
       <c r="M12" t="n">
-        <v>2013726</v>
+        <v>2.79</v>
       </c>
       <c r="N12" t="n">
-        <v>2875671</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>2.79</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="R12" t="n">
-        <v>346415</v>
+        <v>-3.866561</v>
       </c>
       <c r="S12" t="n">
-        <v>0.158456</v>
+        <v>-3.867033</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.623111</v>
+        <v>1.151595</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.866561</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.867033</v>
+        <v>1.598738</v>
       </c>
       <c r="W12" t="n">
-        <v>1.151595</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="Z12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.003057</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -1703,87 +1613,81 @@
         <v>0.62</v>
       </c>
       <c r="H13" t="n">
-        <v>99.6343</v>
+        <v>5.238</v>
       </c>
       <c r="I13" t="n">
-        <v>99.53784</v>
+        <v>5.2374</v>
       </c>
       <c r="J13" t="n">
-        <v>5.238</v>
+        <v>4965603</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2374</v>
+        <v>2052569</v>
       </c>
       <c r="L13" t="n">
-        <v>4965603</v>
+        <v>2913035</v>
       </c>
       <c r="M13" t="n">
-        <v>2052569</v>
+        <v>2.73</v>
       </c>
       <c r="N13" t="n">
-        <v>2913035</v>
+        <v>1.52</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>3.57</v>
       </c>
       <c r="P13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="R13" t="n">
-        <v>341958</v>
+        <v>10.765717</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.03998</v>
+        <v>10.767083</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.260457</v>
+        <v>1.558597</v>
       </c>
       <c r="U13" t="n">
-        <v>10.765717</v>
+        <v>1.928912</v>
       </c>
       <c r="V13" t="n">
-        <v>10.767083</v>
+        <v>1.299314</v>
       </c>
       <c r="W13" t="n">
-        <v>1.558597</v>
+        <v>-1.286607</v>
       </c>
       <c r="X13" t="n">
-        <v>1.928912</v>
+        <v>11.88673</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.299314</v>
+        <v>10.700862</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.286607</v>
+        <v>11.919595</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.88673</v>
+        <v>0.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.700862</v>
+        <v>0.00132</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5</v>
+        <v>-0.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00132</v>
+        <v>-0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AI13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -1810,87 +1714,81 @@
         <v>-0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>101.27684</v>
+        <v>5.1884</v>
       </c>
       <c r="I14" t="n">
-        <v>103.95861</v>
+        <v>5.1878</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1884</v>
+        <v>4999244</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1878</v>
+        <v>2047038</v>
       </c>
       <c r="L14" t="n">
-        <v>4999244</v>
+        <v>2952207</v>
       </c>
       <c r="M14" t="n">
-        <v>2047038</v>
+        <v>2.84</v>
       </c>
       <c r="N14" t="n">
-        <v>2952207</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>3.71</v>
       </c>
       <c r="P14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="R14" t="n">
-        <v>346403</v>
+        <v>-0.946926</v>
       </c>
       <c r="S14" t="n">
-        <v>1.648569</v>
+        <v>-0.947035</v>
       </c>
       <c r="T14" t="n">
-        <v>4.441296</v>
+        <v>0.677481</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.946926</v>
+        <v>-0.269467</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.947035</v>
+        <v>1.344714</v>
       </c>
       <c r="W14" t="n">
-        <v>0.677481</v>
+        <v>1.299867</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.269467</v>
+        <v>10.069235</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.344714</v>
+        <v>10.074751</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.299867</v>
+        <v>10.124804</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.069235</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.074751</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AI14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -1917,87 +1815,81 @@
         <v>-0.31</v>
       </c>
       <c r="H15" t="n">
-        <v>101.07328</v>
+        <v>5.179</v>
       </c>
       <c r="I15" t="n">
-        <v>104.56278</v>
+        <v>5.1784</v>
       </c>
       <c r="J15" t="n">
-        <v>5.179</v>
+        <v>5072711</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1784</v>
+        <v>2064183</v>
       </c>
       <c r="L15" t="n">
-        <v>5072711</v>
+        <v>3008528</v>
       </c>
       <c r="M15" t="n">
-        <v>2064183</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>3008528</v>
+        <v>1.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>3.78</v>
       </c>
       <c r="P15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="R15" t="n">
-        <v>339664</v>
+        <v>-0.181173</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.200994</v>
+        <v>-0.181194</v>
       </c>
       <c r="T15" t="n">
-        <v>0.581164</v>
+        <v>1.469562</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.181173</v>
+        <v>0.837552</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.181194</v>
+        <v>1.907759</v>
       </c>
       <c r="W15" t="n">
-        <v>1.469562</v>
+        <v>-1.945422</v>
       </c>
       <c r="X15" t="n">
-        <v>0.837552</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.907759</v>
+        <v>8.58755</v>
       </c>
       <c r="Z15" t="n">
-        <v>-1.945422</v>
+        <v>8.825751</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.727061000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.58755</v>
+        <v>0.001523</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001523</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -2024,87 +1916,81 @@
         <v>-0.32</v>
       </c>
       <c r="H16" t="n">
-        <v>101.17973</v>
+        <v>5.4066</v>
       </c>
       <c r="I16" t="n">
-        <v>101.38087</v>
+        <v>5.406</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4066</v>
+        <v>5164775</v>
       </c>
       <c r="K16" t="n">
-        <v>5.406</v>
+        <v>2109806</v>
       </c>
       <c r="L16" t="n">
-        <v>5164775</v>
+        <v>3054969</v>
       </c>
       <c r="M16" t="n">
-        <v>2109806</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>3054969</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="P16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="R16" t="n">
-        <v>327580</v>
+        <v>4.394671</v>
       </c>
       <c r="S16" t="n">
-        <v>0.10532</v>
+        <v>4.39518</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.043062</v>
+        <v>1.814888</v>
       </c>
       <c r="U16" t="n">
-        <v>4.394671</v>
+        <v>2.210221</v>
       </c>
       <c r="V16" t="n">
-        <v>4.39518</v>
+        <v>1.543645</v>
       </c>
       <c r="W16" t="n">
-        <v>1.814888</v>
+        <v>-3.557633</v>
       </c>
       <c r="X16" t="n">
-        <v>2.210221</v>
+        <v>7.168596</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.543645</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="Z16" t="n">
-        <v>-3.557633</v>
+        <v>7.191214</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.168596</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.248760000000001</v>
+        <v>0.000228</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -2131,87 +2017,81 @@
         <v>0.47</v>
       </c>
       <c r="H17" t="n">
-        <v>101.46342</v>
+        <v>5.257</v>
       </c>
       <c r="I17" t="n">
-        <v>100.20398</v>
+        <v>5.2564</v>
       </c>
       <c r="J17" t="n">
-        <v>5.257</v>
+        <v>5215990</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2564</v>
+        <v>2105856</v>
       </c>
       <c r="L17" t="n">
-        <v>5215990</v>
+        <v>3110134</v>
       </c>
       <c r="M17" t="n">
-        <v>2105856</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3110134</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>3.04</v>
+        <v>3.89</v>
       </c>
       <c r="P17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="R17" t="n">
-        <v>325546</v>
+        <v>-2.766988</v>
       </c>
       <c r="S17" t="n">
-        <v>0.280382</v>
+        <v>-2.767296</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.16086</v>
+        <v>0.991621</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.766988</v>
+        <v>-0.187221</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.767296</v>
+        <v>1.805747</v>
       </c>
       <c r="W17" t="n">
-        <v>0.991621</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.187221</v>
+        <v>6.470016</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.805747</v>
+        <v>6.517038</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.460076</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.470016</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -2238,87 +2118,81 @@
         <v>0.38</v>
       </c>
       <c r="H18" t="n">
-        <v>100.66227</v>
+        <v>5.2941</v>
       </c>
       <c r="I18" t="n">
-        <v>99.36927</v>
+        <v>5.2935</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2941</v>
+        <v>5285657</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2935</v>
+        <v>2130312</v>
       </c>
       <c r="L18" t="n">
-        <v>5285657</v>
+        <v>3155345</v>
       </c>
       <c r="M18" t="n">
-        <v>2130312</v>
+        <v>3.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3155345</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
-        <v>3.07</v>
+        <v>3.92</v>
       </c>
       <c r="P18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="R18" t="n">
-        <v>331505</v>
+        <v>0.705726</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.789595</v>
+        <v>0.705806</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>1.335643</v>
       </c>
       <c r="U18" t="n">
-        <v>0.705726</v>
+        <v>1.161333</v>
       </c>
       <c r="V18" t="n">
-        <v>0.705806</v>
+        <v>1.453667</v>
       </c>
       <c r="W18" t="n">
-        <v>1.335643</v>
+        <v>1.830463</v>
       </c>
       <c r="X18" t="n">
-        <v>1.161333</v>
+        <v>5.900488</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.453667</v>
+        <v>5.899363</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.830463</v>
+        <v>5.974439</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.900488</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -2345,87 +2219,81 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>100.58196</v>
+        <v>5.2177</v>
       </c>
       <c r="I19" t="n">
-        <v>99.97806</v>
+        <v>5.2171</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2177</v>
+        <v>5366069</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2171</v>
+        <v>2178236</v>
       </c>
       <c r="L19" t="n">
-        <v>5366069</v>
+        <v>3187833</v>
       </c>
       <c r="M19" t="n">
-        <v>2178236</v>
+        <v>3.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3187833</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
       <c r="P19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="R19" t="n">
-        <v>324703</v>
+        <v>-1.443116</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>-1.443279</v>
       </c>
       <c r="T19" t="n">
-        <v>0.612654</v>
+        <v>1.521325</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.443116</v>
+        <v>2.249624</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.443279</v>
+        <v>1.029618</v>
       </c>
       <c r="W19" t="n">
-        <v>1.521325</v>
+        <v>-2.051854</v>
       </c>
       <c r="X19" t="n">
-        <v>2.249624</v>
+        <v>5.784842</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.029618</v>
+        <v>5.458422</v>
       </c>
       <c r="Z19" t="n">
-        <v>-2.051854</v>
+        <v>5.932356</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.784842</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.458422</v>
+        <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AI19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -2452,87 +2320,81 @@
         <v>0.46</v>
       </c>
       <c r="H20" t="n">
-        <v>100.05178</v>
+        <v>5.0993</v>
       </c>
       <c r="I20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0987</v>
       </c>
       <c r="J20" t="n">
-        <v>5.0993</v>
+        <v>5373231</v>
       </c>
       <c r="K20" t="n">
-        <v>5.0987</v>
+        <v>2151399</v>
       </c>
       <c r="L20" t="n">
-        <v>5373231</v>
+        <v>3221831</v>
       </c>
       <c r="M20" t="n">
-        <v>2151399</v>
+        <v>3.24</v>
       </c>
       <c r="N20" t="n">
-        <v>3221831</v>
+        <v>1.94</v>
       </c>
       <c r="O20" t="n">
-        <v>3.24</v>
+        <v>4.11</v>
       </c>
       <c r="P20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="R20" t="n">
-        <v>331122</v>
+        <v>-2.269199</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.527112</v>
+        <v>-2.26946</v>
       </c>
       <c r="T20" t="n">
-        <v>-6.187047</v>
+        <v>0.133468</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.269199</v>
+        <v>-1.232052</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.26946</v>
+        <v>1.066493</v>
       </c>
       <c r="W20" t="n">
-        <v>0.133468</v>
+        <v>1.976883</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.232052</v>
+        <v>5.77432</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.066493</v>
+        <v>3.79089</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.976883</v>
+        <v>5.711379</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.77432</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AI20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2559,87 +2421,81 @@
         <v>0.77</v>
       </c>
       <c r="H21" t="n">
-        <v>103.00964</v>
+        <v>5.2078</v>
       </c>
       <c r="I21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2072</v>
       </c>
       <c r="J21" t="n">
-        <v>5.2078</v>
+        <v>5370950</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2072</v>
+        <v>2136105</v>
       </c>
       <c r="L21" t="n">
-        <v>5370950</v>
+        <v>3234845</v>
       </c>
       <c r="M21" t="n">
-        <v>2136105</v>
+        <v>3.36</v>
       </c>
       <c r="N21" t="n">
-        <v>3234845</v>
+        <v>2.17</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>4.16</v>
       </c>
       <c r="P21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="R21" t="n">
-        <v>328098</v>
+        <v>2.127743</v>
       </c>
       <c r="S21" t="n">
-        <v>2.956329</v>
+        <v>2.127993</v>
       </c>
       <c r="T21" t="n">
-        <v>5.286443</v>
+        <v>-0.042451</v>
       </c>
       <c r="U21" t="n">
-        <v>2.127743</v>
+        <v>-0.710886</v>
       </c>
       <c r="V21" t="n">
-        <v>2.127993</v>
+        <v>0.403932</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.042451</v>
+        <v>-0.913259</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.710886</v>
+        <v>5.596302</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.403932</v>
+        <v>1.864495</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.913259</v>
+        <v>5.47065</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.596302</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AI21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2666,87 +2522,81 @@
         <v>0.64</v>
       </c>
       <c r="H22" t="n">
-        <v>103.09341</v>
+        <v>5.0804</v>
       </c>
       <c r="I22" t="n">
-        <v>110.62354</v>
+        <v>5.0798</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0804</v>
+        <v>5424811</v>
       </c>
       <c r="K22" t="n">
-        <v>5.0798</v>
+        <v>2154900</v>
       </c>
       <c r="L22" t="n">
-        <v>5424811</v>
+        <v>3269910</v>
       </c>
       <c r="M22" t="n">
-        <v>2154900</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>3269910</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>4.11</v>
       </c>
       <c r="P22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="R22" t="n">
-        <v>341158</v>
+        <v>-2.446331</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08132200000000001</v>
+        <v>-2.446612</v>
       </c>
       <c r="T22" t="n">
-        <v>12.023101</v>
+        <v>1.002821</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.446331</v>
+        <v>0.879872</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.446612</v>
+        <v>1.083978</v>
       </c>
       <c r="W22" t="n">
-        <v>1.002821</v>
+        <v>3.980518</v>
       </c>
       <c r="X22" t="n">
-        <v>0.879872</v>
+        <v>4.650694</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.083978</v>
+        <v>0.172427</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.980518</v>
+        <v>4.361088</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.650694</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -2773,87 +2623,81 @@
         <v>0.53</v>
       </c>
       <c r="H23" t="n">
-        <v>104.1626</v>
+        <v>5.0007</v>
       </c>
       <c r="I23" t="n">
-        <v>104.34152</v>
+        <v>5.0001</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0007</v>
+        <v>5426307</v>
       </c>
       <c r="K23" t="n">
-        <v>5.0001</v>
+        <v>2145000</v>
       </c>
       <c r="L23" t="n">
-        <v>5426307</v>
+        <v>3281308</v>
       </c>
       <c r="M23" t="n">
-        <v>2145000</v>
+        <v>3.54</v>
       </c>
       <c r="N23" t="n">
-        <v>3281308</v>
+        <v>2.45</v>
       </c>
       <c r="O23" t="n">
-        <v>3.54</v>
+        <v>4.26</v>
       </c>
       <c r="P23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="R23" t="n">
-        <v>345725</v>
+        <v>-1.568774</v>
       </c>
       <c r="S23" t="n">
-        <v>1.037108</v>
+        <v>-1.568959</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.678737</v>
+        <v>0.027577</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.568774</v>
+        <v>-0.459418</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.568959</v>
+        <v>0.348572</v>
       </c>
       <c r="W23" t="n">
-        <v>0.027577</v>
+        <v>1.338676</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.459418</v>
+        <v>4.184706</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.348572</v>
+        <v>-2.158772</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.338676</v>
+        <v>3.834324</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.184706</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -2880,87 +2724,81 @@
         <v>0.36</v>
       </c>
       <c r="H24" t="n">
-        <v>102.3642</v>
+        <v>5.0959</v>
       </c>
       <c r="I24" t="n">
-        <v>102.66392</v>
+        <v>5.0953</v>
       </c>
       <c r="J24" t="n">
-        <v>5.0959</v>
+        <v>5453708</v>
       </c>
       <c r="K24" t="n">
-        <v>5.0953</v>
+        <v>2145530</v>
       </c>
       <c r="L24" t="n">
-        <v>5453708</v>
+        <v>3308178</v>
       </c>
       <c r="M24" t="n">
-        <v>2145530</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3308178</v>
+        <v>2.58</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="P24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="R24" t="n">
-        <v>343489</v>
+        <v>1.903733</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.726531</v>
+        <v>1.903962</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.607797</v>
+        <v>0.504966</v>
       </c>
       <c r="U24" t="n">
-        <v>1.903733</v>
+        <v>0.024709</v>
       </c>
       <c r="V24" t="n">
-        <v>1.903962</v>
+        <v>0.818881</v>
       </c>
       <c r="W24" t="n">
-        <v>0.504966</v>
+        <v>-0.646757</v>
       </c>
       <c r="X24" t="n">
-        <v>0.024709</v>
+        <v>3.935832</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.818881</v>
+        <v>-4.45588</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.646757</v>
+        <v>3.741292</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.935832</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-4.45588</v>
+        <v>-0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0</v>
+        <v>0.09</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AI24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2987,87 +2825,81 @@
         <v>-0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>102.50431</v>
+        <v>4.8192</v>
       </c>
       <c r="I25" t="n">
-        <v>102.53174</v>
+        <v>4.8186</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8192</v>
+        <v>5479459</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8186</v>
+        <v>2169613</v>
       </c>
       <c r="L25" t="n">
-        <v>5479459</v>
+        <v>3309846</v>
       </c>
       <c r="M25" t="n">
-        <v>2169613</v>
+        <v>3.61</v>
       </c>
       <c r="N25" t="n">
-        <v>3309846</v>
+        <v>2.63</v>
       </c>
       <c r="O25" t="n">
-        <v>3.61</v>
+        <v>4.25</v>
       </c>
       <c r="P25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="R25" t="n">
-        <v>343620</v>
+        <v>-5.429855</v>
       </c>
       <c r="S25" t="n">
-        <v>0.136874</v>
+        <v>-5.430495</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.12875</v>
+        <v>0.472174</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.429855</v>
+        <v>1.122473</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.430495</v>
+        <v>0.050421</v>
       </c>
       <c r="W25" t="n">
-        <v>0.472174</v>
+        <v>0.038138</v>
       </c>
       <c r="X25" t="n">
-        <v>1.122473</v>
+        <v>3.161501</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.050421</v>
+        <v>-6.84947</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.038138</v>
+        <v>2.998957</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.161501</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AI25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -3094,87 +2926,81 @@
         <v>-0.09</v>
       </c>
       <c r="H26" t="n">
-        <v>102.83357</v>
+        <v>4.7415</v>
       </c>
       <c r="I26" t="n">
-        <v>105.47522</v>
+        <v>4.7409</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7415</v>
+        <v>5484871</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7409</v>
+        <v>2153541</v>
       </c>
       <c r="L26" t="n">
-        <v>5484871</v>
+        <v>3331330</v>
       </c>
       <c r="M26" t="n">
-        <v>2153541</v>
+        <v>3.63</v>
       </c>
       <c r="N26" t="n">
-        <v>3331330</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="P26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="R26" t="n">
-        <v>345476</v>
+        <v>-1.612301</v>
       </c>
       <c r="S26" t="n">
-        <v>0.321216</v>
+        <v>-1.612502</v>
       </c>
       <c r="T26" t="n">
-        <v>2.870799</v>
+        <v>0.098769</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.612301</v>
+        <v>-0.740777</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.612502</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>0.098769</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.740777</v>
+        <v>3.992444</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6490939999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.527423</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.992444</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3201,87 +3027,81 @@
         <v>0.2</v>
       </c>
       <c r="H27" t="n">
-        <v>102.45222</v>
+        <v>4.9219</v>
       </c>
       <c r="I27" t="n">
-        <v>106.13139</v>
+        <v>4.9213</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9219</v>
+        <v>5559063</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9213</v>
+        <v>2172658</v>
       </c>
       <c r="L27" t="n">
-        <v>5559063</v>
+        <v>3386405</v>
       </c>
       <c r="M27" t="n">
-        <v>2172658</v>
+        <v>3.61</v>
       </c>
       <c r="N27" t="n">
-        <v>3386405</v>
+        <v>2.82</v>
       </c>
       <c r="O27" t="n">
-        <v>3.61</v>
+        <v>4.12</v>
       </c>
       <c r="P27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="R27" t="n">
-        <v>344177</v>
+        <v>3.804703</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.370842</v>
+        <v>3.805185</v>
       </c>
       <c r="T27" t="n">
-        <v>0.622108</v>
+        <v>1.352666</v>
       </c>
       <c r="U27" t="n">
-        <v>3.804703</v>
+        <v>0.887701</v>
       </c>
       <c r="V27" t="n">
-        <v>3.805185</v>
+        <v>1.653244</v>
       </c>
       <c r="W27" t="n">
-        <v>1.352666</v>
+        <v>-0.376003</v>
       </c>
       <c r="X27" t="n">
-        <v>0.887701</v>
+        <v>4.608216</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.653244</v>
+        <v>-7.193509</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.376003</v>
+        <v>4.057054</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.608216</v>
+        <v>-0.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>-7.193509</v>
+        <v>-0.001599</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.5</v>
+        <v>-0.02</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.001599</v>
+        <v>-0.1</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AI27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -3308,87 +3128,81 @@
         <v>0.11</v>
       </c>
       <c r="H28" t="n">
-        <v>102.57885</v>
+        <v>5.0076</v>
       </c>
       <c r="I28" t="n">
-        <v>102.00419</v>
+        <v>5.007</v>
       </c>
       <c r="J28" t="n">
-        <v>5.0076</v>
+        <v>5625945</v>
       </c>
       <c r="K28" t="n">
-        <v>5.007</v>
+        <v>2215175</v>
       </c>
       <c r="L28" t="n">
-        <v>5625945</v>
+        <v>3410769</v>
       </c>
       <c r="M28" t="n">
-        <v>2215175</v>
+        <v>3.54</v>
       </c>
       <c r="N28" t="n">
-        <v>3410769</v>
+        <v>2.82</v>
       </c>
       <c r="O28" t="n">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="R28" t="n">
-        <v>340324</v>
+        <v>1.741198</v>
       </c>
       <c r="S28" t="n">
-        <v>0.123599</v>
+        <v>1.74141</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.888765</v>
+        <v>1.203116</v>
       </c>
       <c r="U28" t="n">
-        <v>1.741198</v>
+        <v>1.956912</v>
       </c>
       <c r="V28" t="n">
-        <v>1.74141</v>
+        <v>0.719465</v>
       </c>
       <c r="W28" t="n">
-        <v>1.203116</v>
+        <v>-1.119482</v>
       </c>
       <c r="X28" t="n">
-        <v>1.956912</v>
+        <v>5.185235</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.719465</v>
+        <v>-5.956714</v>
       </c>
       <c r="Z28" t="n">
-        <v>-1.119482</v>
+        <v>4.505936</v>
       </c>
       <c r="AA28" t="n">
-        <v>5.185235</v>
+        <v>-0.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>-5.956714</v>
+        <v>-0.000768</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.5</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.000768</v>
+        <v>-0.12</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AI28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -3415,87 +3229,81 @@
         <v>0.12</v>
       </c>
       <c r="H29" t="n">
-        <v>102.87707</v>
+        <v>5.0575</v>
       </c>
       <c r="I29" t="n">
-        <v>102.0744</v>
+        <v>5.0569</v>
       </c>
       <c r="J29" t="n">
-        <v>5.0575</v>
+        <v>5653808</v>
       </c>
       <c r="K29" t="n">
-        <v>5.0569</v>
+        <v>2204808</v>
       </c>
       <c r="L29" t="n">
-        <v>5653808</v>
+        <v>3449000</v>
       </c>
       <c r="M29" t="n">
-        <v>2204808</v>
+        <v>3.56</v>
       </c>
       <c r="N29" t="n">
-        <v>3449000</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>3.97</v>
       </c>
       <c r="P29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="R29" t="n">
-        <v>340247</v>
+        <v>0.996485</v>
       </c>
       <c r="S29" t="n">
-        <v>0.290723</v>
+        <v>0.996605</v>
       </c>
       <c r="T29" t="n">
-        <v>0.068831</v>
+        <v>0.495259</v>
       </c>
       <c r="U29" t="n">
-        <v>0.996485</v>
+        <v>-0.467999</v>
       </c>
       <c r="V29" t="n">
-        <v>0.996605</v>
+        <v>1.120891</v>
       </c>
       <c r="W29" t="n">
-        <v>0.495259</v>
+        <v>-0.022625</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.467999</v>
+        <v>4.819246</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.120891</v>
+        <v>-4.560737</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.022625</v>
+        <v>4.141877</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.819246</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>-4.560737</v>
+        <v>-0.001143</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.001143</v>
+        <v>-0.03</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -3522,87 +3330,81 @@
         <v>0.1</v>
       </c>
       <c r="H30" t="n">
-        <v>103.528</v>
+        <v>4.9355</v>
       </c>
       <c r="I30" t="n">
-        <v>101.86494</v>
+        <v>4.9349</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9355</v>
+        <v>5711103</v>
       </c>
       <c r="K30" t="n">
-        <v>4.9349</v>
+        <v>2220766</v>
       </c>
       <c r="L30" t="n">
-        <v>5711103</v>
+        <v>3490337</v>
       </c>
       <c r="M30" t="n">
-        <v>2220766</v>
+        <v>3.53</v>
       </c>
       <c r="N30" t="n">
-        <v>3490337</v>
+        <v>2.99</v>
       </c>
       <c r="O30" t="n">
-        <v>3.53</v>
+        <v>3.88</v>
       </c>
       <c r="P30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="Q30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="R30" t="n">
-        <v>348406</v>
+        <v>-2.412259</v>
       </c>
       <c r="S30" t="n">
-        <v>0.632726</v>
+        <v>-2.412545</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.205203</v>
+        <v>1.013388</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.412259</v>
+        <v>0.723782</v>
       </c>
       <c r="V30" t="n">
-        <v>-2.412545</v>
+        <v>1.198521</v>
       </c>
       <c r="W30" t="n">
-        <v>1.013388</v>
+        <v>2.397964</v>
       </c>
       <c r="X30" t="n">
-        <v>0.723782</v>
+        <v>4.683537</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.198521</v>
+        <v>-3.457004</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.397964</v>
+        <v>3.851383</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.683537</v>
+        <v>-0.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.457004</v>
+        <v>-0.001678</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.001678</v>
+        <v>-0.09</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AI30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -3629,87 +3431,81 @@
         <v>0.55</v>
       </c>
       <c r="H31" t="n">
-        <v>104.8991</v>
+        <v>4.8413</v>
       </c>
       <c r="I31" t="n">
-        <v>101.74606</v>
+        <v>4.8407</v>
       </c>
       <c r="J31" t="n">
-        <v>4.8413</v>
+        <v>5805157</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8407</v>
+        <v>2283485</v>
       </c>
       <c r="L31" t="n">
-        <v>5805157</v>
+        <v>3521672</v>
       </c>
       <c r="M31" t="n">
-        <v>2283485</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>3521672</v>
+        <v>2.59</v>
       </c>
       <c r="O31" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="P31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="Q31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="R31" t="n">
-        <v>355034</v>
+        <v>-1.908621</v>
       </c>
       <c r="S31" t="n">
-        <v>1.324376</v>
+        <v>-1.908853</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.116704</v>
+        <v>1.646862</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.908621</v>
+        <v>2.824206</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.908853</v>
+        <v>0.897764</v>
       </c>
       <c r="W31" t="n">
-        <v>1.646862</v>
+        <v>1.902378</v>
       </c>
       <c r="X31" t="n">
-        <v>2.824206</v>
+        <v>4.621114</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.897764</v>
+        <v>-3.178284</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.902378</v>
+        <v>3.706988</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.621114</v>
+        <v>-0.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-3.178284</v>
+        <v>-0.001064</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.001064</v>
+        <v>-0.13</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="AI31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -3736,87 +3532,81 @@
         <v>0.57</v>
       </c>
       <c r="H32" t="n">
-        <v>104.53245</v>
+        <v>4.9535</v>
       </c>
       <c r="I32" t="n">
-        <v>98.01879</v>
+        <v>4.9529</v>
       </c>
       <c r="J32" t="n">
-        <v>4.9535</v>
+        <v>5794707</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9529</v>
+        <v>2234362</v>
       </c>
       <c r="L32" t="n">
-        <v>5794707</v>
+        <v>3560345</v>
       </c>
       <c r="M32" t="n">
-        <v>2234362</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
-        <v>3560345</v>
+        <v>2.77</v>
       </c>
       <c r="O32" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="P32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="Q32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="R32" t="n">
-        <v>355066</v>
+        <v>2.317559</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.349526</v>
+        <v>2.317847</v>
       </c>
       <c r="T32" t="n">
-        <v>-3.663306</v>
+        <v>-0.180012</v>
       </c>
       <c r="U32" t="n">
-        <v>2.317559</v>
+        <v>-2.151229</v>
       </c>
       <c r="V32" t="n">
-        <v>2.317847</v>
+        <v>1.098143</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.180012</v>
+        <v>0.009013</v>
       </c>
       <c r="X32" t="n">
-        <v>-2.151229</v>
+        <v>4.506637</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.098143</v>
+        <v>-3.31355</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.009013</v>
+        <v>3.820543</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.506637</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>-3.31355</v>
+        <v>-0.000798</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.000798</v>
+        <v>0.01</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -3843,87 +3633,81 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>104.75961</v>
+        <v>4.9833</v>
       </c>
       <c r="I33" t="n">
-        <v>102.37988</v>
+        <v>4.9827</v>
       </c>
       <c r="J33" t="n">
-        <v>4.9833</v>
+        <v>5815954</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9827</v>
+        <v>2235302</v>
       </c>
       <c r="L33" t="n">
-        <v>5815954</v>
+        <v>3580652</v>
       </c>
       <c r="M33" t="n">
-        <v>2235302</v>
+        <v>3.38</v>
       </c>
       <c r="N33" t="n">
-        <v>3580652</v>
+        <v>2.76</v>
       </c>
       <c r="O33" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="P33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="R33" t="n">
-        <v>352705</v>
+        <v>0.601595</v>
       </c>
       <c r="S33" t="n">
-        <v>0.217311</v>
+        <v>0.601668</v>
       </c>
       <c r="T33" t="n">
-        <v>4.449239</v>
+        <v>0.366662</v>
       </c>
       <c r="U33" t="n">
-        <v>0.601595</v>
+        <v>0.04207</v>
       </c>
       <c r="V33" t="n">
-        <v>0.601668</v>
+        <v>0.570366</v>
       </c>
       <c r="W33" t="n">
-        <v>0.366662</v>
+        <v>-0.664947</v>
       </c>
       <c r="X33" t="n">
-        <v>0.04207</v>
+        <v>4.496274</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.570366</v>
+        <v>-3.758575</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.664947</v>
+        <v>3.861754</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.496274</v>
+        <v>-0.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>-3.758575</v>
+        <v>-0.001782</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3950,87 +3734,81 @@
         <v>0.19</v>
       </c>
       <c r="H34" t="n">
-        <v>104.7097</v>
+        <v>4.9962</v>
       </c>
       <c r="I34" t="n">
-        <v>109.58504</v>
+        <v>4.9956</v>
       </c>
       <c r="J34" t="n">
-        <v>4.9962</v>
+        <v>5899742</v>
       </c>
       <c r="K34" t="n">
-        <v>4.9956</v>
+        <v>2285775</v>
       </c>
       <c r="L34" t="n">
-        <v>5899742</v>
+        <v>3613967</v>
       </c>
       <c r="M34" t="n">
-        <v>2285775</v>
+        <v>3.33</v>
       </c>
       <c r="N34" t="n">
-        <v>3613967</v>
+        <v>2.71</v>
       </c>
       <c r="O34" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="P34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="Q34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="R34" t="n">
-        <v>355008</v>
+        <v>0.258865</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.047642</v>
+        <v>0.258896</v>
       </c>
       <c r="T34" t="n">
-        <v>7.037672</v>
+        <v>1.440658</v>
       </c>
       <c r="U34" t="n">
-        <v>0.258865</v>
+        <v>2.257995</v>
       </c>
       <c r="V34" t="n">
-        <v>0.258896</v>
+        <v>0.930417</v>
       </c>
       <c r="W34" t="n">
-        <v>1.440658</v>
+        <v>0.652954</v>
       </c>
       <c r="X34" t="n">
-        <v>2.257995</v>
+        <v>3.925596</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.930417</v>
+        <v>-4.25878</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.652954</v>
+        <v>3.397348</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.925596</v>
+        <v>-0.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>-4.25878</v>
+        <v>-0.000537</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AI34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -4057,87 +3835,81 @@
         <v>0.37</v>
       </c>
       <c r="H35" t="n">
-        <v>104.75682</v>
+        <v>5.1718</v>
       </c>
       <c r="I35" t="n">
-        <v>109.36335</v>
+        <v>5.1712</v>
       </c>
       <c r="J35" t="n">
-        <v>5.1718</v>
+        <v>5915538</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1712</v>
+        <v>2268879</v>
       </c>
       <c r="L35" t="n">
-        <v>5915538</v>
+        <v>3646659</v>
       </c>
       <c r="M35" t="n">
-        <v>2268879</v>
+        <v>3.37</v>
       </c>
       <c r="N35" t="n">
-        <v>3646659</v>
+        <v>2.76</v>
       </c>
       <c r="O35" t="n">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="P35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="Q35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="R35" t="n">
-        <v>351599</v>
+        <v>3.514671</v>
       </c>
       <c r="S35" t="n">
-        <v>0.045001</v>
+        <v>3.515093</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.2023</v>
+        <v>0.267741</v>
       </c>
       <c r="U35" t="n">
-        <v>3.514671</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="V35" t="n">
-        <v>3.515093</v>
+        <v>0.904602</v>
       </c>
       <c r="W35" t="n">
-        <v>0.267741</v>
+        <v>-0.96026</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>3.688016</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.904602</v>
+        <v>-3.040871</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.96026</v>
+        <v>3.232784</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.688016</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-3.040871</v>
+        <v>-0.001252</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -4164,87 +3936,81 @@
         <v>0.46</v>
       </c>
       <c r="H36" t="n">
-        <v>105.70704</v>
+        <v>5.2416</v>
       </c>
       <c r="I36" t="n">
-        <v>104.84682</v>
+        <v>5.241</v>
       </c>
       <c r="J36" t="n">
-        <v>5.2416</v>
+        <v>5953960</v>
       </c>
       <c r="K36" t="n">
-        <v>5.241</v>
+        <v>2278309</v>
       </c>
       <c r="L36" t="n">
-        <v>5953960</v>
+        <v>3675652</v>
       </c>
       <c r="M36" t="n">
-        <v>2278309</v>
+        <v>3.43</v>
       </c>
       <c r="N36" t="n">
-        <v>3675652</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>3.43</v>
+        <v>3.82</v>
       </c>
       <c r="P36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="R36" t="n">
-        <v>355560</v>
+        <v>1.349627</v>
       </c>
       <c r="S36" t="n">
-        <v>0.907072</v>
+        <v>1.349783</v>
       </c>
       <c r="T36" t="n">
-        <v>-4.129839</v>
+        <v>0.64951</v>
       </c>
       <c r="U36" t="n">
-        <v>1.349627</v>
+        <v>0.415624</v>
       </c>
       <c r="V36" t="n">
-        <v>1.349783</v>
+        <v>0.795057</v>
       </c>
       <c r="W36" t="n">
-        <v>0.64951</v>
+        <v>1.126567</v>
       </c>
       <c r="X36" t="n">
-        <v>0.415624</v>
+        <v>3.925952</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.795057</v>
+        <v>-0.344269</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.126567</v>
+        <v>3.335647</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.925952</v>
+        <v>-0.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.344269</v>
+        <v>-0.000684</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.25</v>
+        <v>0.06</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.000684</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -4271,87 +4037,81 @@
         <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>106.57623</v>
+        <v>5.5589</v>
       </c>
       <c r="I37" t="n">
-        <v>106.03093</v>
+        <v>5.5583</v>
       </c>
       <c r="J37" t="n">
-        <v>5.5589</v>
+        <v>6041898</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5583</v>
+        <v>2336858</v>
       </c>
       <c r="L37" t="n">
-        <v>6041898</v>
+        <v>3705041</v>
       </c>
       <c r="M37" t="n">
-        <v>2336858</v>
+        <v>3.29</v>
       </c>
       <c r="N37" t="n">
-        <v>3705041</v>
+        <v>2.64</v>
       </c>
       <c r="O37" t="n">
-        <v>3.29</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="Q37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="R37" t="n">
-        <v>357827</v>
+        <v>6.053495</v>
       </c>
       <c r="S37" t="n">
-        <v>0.822263</v>
+        <v>6.054188</v>
       </c>
       <c r="T37" t="n">
-        <v>1.129371</v>
+        <v>1.476967</v>
       </c>
       <c r="U37" t="n">
-        <v>6.053495</v>
+        <v>2.569845</v>
       </c>
       <c r="V37" t="n">
-        <v>6.054188</v>
+        <v>0.799559</v>
       </c>
       <c r="W37" t="n">
-        <v>1.476967</v>
+        <v>0.637586</v>
       </c>
       <c r="X37" t="n">
-        <v>2.569845</v>
+        <v>4.227578</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.799559</v>
+        <v>2.440035</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.637586</v>
+        <v>3.697684</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.227578</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.440035</v>
+        <v>-0.000214</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AE37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.000214</v>
+        <v>-0.11</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AI37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4378,87 +4138,81 @@
         <v>0.26</v>
       </c>
       <c r="H38" t="n">
-        <v>106.88756</v>
+        <v>5.6621</v>
       </c>
       <c r="I38" t="n">
-        <v>111.55002</v>
+        <v>5.6615</v>
       </c>
       <c r="J38" t="n">
-        <v>5.6621</v>
+        <v>6069205</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6615</v>
+        <v>2323362</v>
       </c>
       <c r="L38" t="n">
-        <v>6069205</v>
+        <v>3745844</v>
       </c>
       <c r="M38" t="n">
-        <v>2323362</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>3745844</v>
+        <v>2.52</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="P38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="Q38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="R38" t="n">
-        <v>363282</v>
+        <v>1.856482</v>
       </c>
       <c r="S38" t="n">
-        <v>0.29212</v>
+        <v>1.856683</v>
       </c>
       <c r="T38" t="n">
-        <v>5.20517</v>
+        <v>0.451961</v>
       </c>
       <c r="U38" t="n">
-        <v>1.856482</v>
+        <v>-0.577528</v>
       </c>
       <c r="V38" t="n">
-        <v>1.856683</v>
+        <v>1.101283</v>
       </c>
       <c r="W38" t="n">
-        <v>0.451961</v>
+        <v>1.52448</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.577528</v>
+        <v>4.498245</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.101283</v>
+        <v>3.812368</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.52448</v>
+        <v>4.060953</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.498245</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AI38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -4485,87 +4239,81 @@
         <v>-0.14</v>
       </c>
       <c r="H39" t="n">
-        <v>107.14396</v>
+        <v>5.6562</v>
       </c>
       <c r="I39" t="n">
-        <v>110.19363</v>
+        <v>5.6556</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6562</v>
+        <v>6135298</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6556</v>
+        <v>2344397</v>
       </c>
       <c r="L39" t="n">
-        <v>6135298</v>
+        <v>3790900</v>
       </c>
       <c r="M39" t="n">
-        <v>2344397</v>
+        <v>3.33</v>
       </c>
       <c r="N39" t="n">
-        <v>3790900</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
-        <v>3.33</v>
+        <v>3.82</v>
       </c>
       <c r="P39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="Q39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="R39" t="n">
-        <v>369214</v>
+        <v>-0.104202</v>
       </c>
       <c r="S39" t="n">
-        <v>0.239878</v>
+        <v>-0.104213</v>
       </c>
       <c r="T39" t="n">
-        <v>-1.215948</v>
+        <v>1.088989</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.104202</v>
+        <v>0.905369</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.104213</v>
+        <v>1.202826</v>
       </c>
       <c r="W39" t="n">
-        <v>1.088989</v>
+        <v>1.632891</v>
       </c>
       <c r="X39" t="n">
-        <v>0.905369</v>
+        <v>4.237599</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.202826</v>
+        <v>4.259387</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.632891</v>
+        <v>3.707852</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.237599</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AI39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4592,87 +4340,81 @@
         <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>107.99916</v>
+        <v>5.4481</v>
       </c>
       <c r="I40" t="n">
-        <v>107.28836</v>
+        <v>5.4475</v>
       </c>
       <c r="J40" t="n">
-        <v>5.4481</v>
+        <v>6216528</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4475</v>
+        <v>2384828</v>
       </c>
       <c r="L40" t="n">
-        <v>6216528</v>
+        <v>3831700</v>
       </c>
       <c r="M40" t="n">
-        <v>2384828</v>
+        <v>3.34</v>
       </c>
       <c r="N40" t="n">
-        <v>3831700</v>
+        <v>2.56</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>3.83</v>
       </c>
       <c r="P40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="R40" t="n">
-        <v>372016</v>
+        <v>-3.679149</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7981780000000001</v>
+        <v>-3.679539</v>
       </c>
       <c r="T40" t="n">
-        <v>-2.636514</v>
+        <v>1.323978</v>
       </c>
       <c r="U40" t="n">
-        <v>-3.679149</v>
+        <v>1.72458</v>
       </c>
       <c r="V40" t="n">
-        <v>-3.679539</v>
+        <v>1.076262</v>
       </c>
       <c r="W40" t="n">
-        <v>1.323978</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="X40" t="n">
-        <v>1.72458</v>
+        <v>4.42474</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.076262</v>
+        <v>4.519075</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.091149</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.42474</v>
+        <v>0.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.519075</v>
+        <v>0.000342</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -4699,87 +4441,81 @@
         <v>0.61</v>
       </c>
       <c r="H41" t="n">
-        <v>108.15356</v>
+        <v>5.7779</v>
       </c>
       <c r="I41" t="n">
-        <v>109.21678</v>
+        <v>5.7773</v>
       </c>
       <c r="J41" t="n">
-        <v>5.7779</v>
+        <v>6275117</v>
       </c>
       <c r="K41" t="n">
-        <v>5.7773</v>
+        <v>2397533</v>
       </c>
       <c r="L41" t="n">
-        <v>6275117</v>
+        <v>3877584</v>
       </c>
       <c r="M41" t="n">
-        <v>2397533</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3877584</v>
+        <v>2.52</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>3.79</v>
       </c>
       <c r="P41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="R41" t="n">
-        <v>366096</v>
+        <v>6.053487</v>
       </c>
       <c r="S41" t="n">
-        <v>0.142964</v>
+        <v>6.054153</v>
       </c>
       <c r="T41" t="n">
-        <v>1.797418</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="U41" t="n">
-        <v>6.053487</v>
+        <v>0.532743</v>
       </c>
       <c r="V41" t="n">
-        <v>6.054153</v>
+        <v>1.197484</v>
       </c>
       <c r="W41" t="n">
-        <v>0.9424709999999999</v>
+        <v>-1.591329</v>
       </c>
       <c r="X41" t="n">
-        <v>0.532743</v>
+        <v>4.758099</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.197484</v>
+        <v>5.579866</v>
       </c>
       <c r="Z41" t="n">
-        <v>-1.591329</v>
+        <v>4.600584</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.758099</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>5.579866</v>
+        <v>0.000556</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -4806,87 +4542,81 @@
         <v>0.33</v>
       </c>
       <c r="H42" t="n">
-        <v>107.98489</v>
+        <v>6.0535</v>
       </c>
       <c r="I42" t="n">
-        <v>105.74688</v>
+        <v>6.0529</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0535</v>
+        <v>6365690</v>
       </c>
       <c r="K42" t="n">
-        <v>6.0529</v>
+        <v>2436022</v>
       </c>
       <c r="L42" t="n">
-        <v>6365690</v>
+        <v>3929668</v>
       </c>
       <c r="M42" t="n">
-        <v>2436022</v>
+        <v>3.27</v>
       </c>
       <c r="N42" t="n">
-        <v>3929668</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="P42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="R42" t="n">
-        <v>363003</v>
+        <v>4.769899</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.155954</v>
+        <v>4.770394</v>
       </c>
       <c r="T42" t="n">
-        <v>-3.177076</v>
+        <v>1.443368</v>
       </c>
       <c r="U42" t="n">
-        <v>4.769899</v>
+        <v>1.605359</v>
       </c>
       <c r="V42" t="n">
-        <v>4.770394</v>
+        <v>1.343208</v>
       </c>
       <c r="W42" t="n">
-        <v>1.443368</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="X42" t="n">
-        <v>1.605359</v>
+        <v>4.873011</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.343208</v>
+        <v>6.325086</v>
       </c>
       <c r="Z42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.840925</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.873011</v>
+        <v>0.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.325086</v>
+        <v>0.001412</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.001412</v>
+        <v>-0.04</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AI42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4913,87 +4643,81 @@
         <v>0.48</v>
       </c>
       <c r="H43" t="n">
-        <v>107.44467</v>
+        <v>6.1923</v>
       </c>
       <c r="I43" t="n">
-        <v>104.2734</v>
+        <v>6.1917</v>
       </c>
       <c r="J43" t="n">
-        <v>6.1923</v>
+        <v>6464602</v>
       </c>
       <c r="K43" t="n">
-        <v>6.1917</v>
+        <v>2499177</v>
       </c>
       <c r="L43" t="n">
-        <v>6464602</v>
+        <v>3965425</v>
       </c>
       <c r="M43" t="n">
-        <v>2499177</v>
+        <v>3.08</v>
       </c>
       <c r="N43" t="n">
-    